--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>3374669</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>45.4700012207031</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>44.9900016784668</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>45.0499992370605</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>45.2099990844727</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>2338284</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>45.6300010681152</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>44.689998626709</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>45.0499992370605</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>45.6300010681152</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>1777797</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>45.9700012207031</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>45.5499992370605</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>45.7599983215332</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>45.8800010681152</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>1985507</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>46.2400016784668</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>45.5499992370605</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>45.5900001525879</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>46.189998626709</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>3340584</v>
+        <v>2404277</v>
       </c>
       <c r="C2715" t="n">
-        <v>44.9799995422363</v>
+        <v>44.9599990844727</v>
       </c>
       <c r="D2715" t="n">
-        <v>44.1599998474121</v>
+        <v>44.5800018310547</v>
       </c>
       <c r="E2715" t="n">
-        <v>44.7000007629395</v>
+        <v>44.689998626709</v>
       </c>
       <c r="F2715" t="n">
-        <v>44.4700012207031</v>
+        <v>44.7799987792969</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>2836537</v>
+        <v>3340584</v>
       </c>
       <c r="C2716" t="n">
-        <v>44.8800010681152</v>
+        <v>44.9799995422363</v>
       </c>
       <c r="D2716" t="n">
-        <v>43.2099990844727</v>
+        <v>44.1599998474121</v>
       </c>
       <c r="E2716" t="n">
-        <v>44.2799987792969</v>
+        <v>44.7000007629395</v>
       </c>
       <c r="F2716" t="n">
-        <v>44.5</v>
+        <v>44.4700012207031</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>3005070</v>
+        <v>2836537</v>
       </c>
       <c r="C2717" t="n">
-        <v>44.9900016784668</v>
+        <v>44.8800010681152</v>
       </c>
       <c r="D2717" t="n">
-        <v>44.4099998474121</v>
+        <v>43.2099990844727</v>
       </c>
       <c r="E2717" t="n">
-        <v>44.5499992370605</v>
+        <v>44.2799987792969</v>
       </c>
       <c r="F2717" t="n">
-        <v>44.7200012207031</v>
+        <v>44.5</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>1800337</v>
+        <v>3005070</v>
       </c>
       <c r="C2718" t="n">
-        <v>45.3800010681152</v>
+        <v>44.9900016784668</v>
       </c>
       <c r="D2718" t="n">
-        <v>44.8600006103516</v>
+        <v>44.4099998474121</v>
       </c>
       <c r="E2718" t="n">
-        <v>44.8600006103516</v>
+        <v>44.5499992370605</v>
       </c>
       <c r="F2718" t="n">
-        <v>45.0800018310547</v>
+        <v>44.7200012207031</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>3374669</v>
+        <v>1800337</v>
       </c>
       <c r="C2719" t="n">
-        <v>45.4700012207031</v>
+        <v>45.3800010681152</v>
       </c>
       <c r="D2719" t="n">
-        <v>44.9900016784668</v>
+        <v>44.8600006103516</v>
       </c>
       <c r="E2719" t="n">
-        <v>45.0499992370605</v>
+        <v>44.8600006103516</v>
       </c>
       <c r="F2719" t="n">
-        <v>45.2099990844727</v>
+        <v>45.0800018310547</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>2338284</v>
+        <v>3374669</v>
       </c>
       <c r="C2720" t="n">
-        <v>45.6300010681152</v>
+        <v>45.4700012207031</v>
       </c>
       <c r="D2720" t="n">
-        <v>44.689998626709</v>
+        <v>44.9900016784668</v>
       </c>
       <c r="E2720" t="n">
         <v>45.0499992370605</v>
       </c>
       <c r="F2720" t="n">
-        <v>45.6300010681152</v>
+        <v>45.2099990844727</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>1777797</v>
+        <v>2338284</v>
       </c>
       <c r="C2721" t="n">
-        <v>45.9700012207031</v>
+        <v>45.6300010681152</v>
       </c>
       <c r="D2721" t="n">
-        <v>45.5499992370605</v>
+        <v>44.689998626709</v>
       </c>
       <c r="E2721" t="n">
-        <v>45.7599983215332</v>
+        <v>45.0499992370605</v>
       </c>
       <c r="F2721" t="n">
-        <v>45.8800010681152</v>
+        <v>45.6300010681152</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>1985507</v>
+        <v>1777797</v>
       </c>
       <c r="C2722" t="n">
-        <v>46.2400016784668</v>
+        <v>45.9700012207031</v>
       </c>
       <c r="D2722" t="n">
         <v>45.5499992370605</v>
       </c>
       <c r="E2722" t="n">
-        <v>45.5900001525879</v>
+        <v>45.7599983215332</v>
       </c>
       <c r="F2722" t="n">
-        <v>46.189998626709</v>
+        <v>45.8800010681152</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>8008600</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>46.0699996948242</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>44.7299995422363</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>46.0099983215332</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>45.2799987792969</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>41.5400009155273</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>41.939998626709</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>2397457</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>42.4900016784668</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>42</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>42.0400009155273</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>42.0400009155273</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>42.2000007629395</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>3264142</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>42.1800003051758</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>41.6199989318848</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>41.9900016784668</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>41.9900016784668</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>41.6199989318848</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>2483975</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>41.3499984741211</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>40.5800018310547</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>41.2999992370605</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>41.2999992370605</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>41.0200004577637</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>1617698</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>41.7099990844727</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>41.2299995422363</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>41.3499984741211</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>991721</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>42.0900001525879</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>41.8300018310547</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>41.8300018310547</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>42.060001373291</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -421,7 +421,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>8.82273483276367</v>
+        <v>8.82273197174072</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>8.74648761749268</v>
+        <v>8.74648666381836</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>8.73015022277832</v>
+        <v>8.730149269104</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G6" t="n">
-        <v>8.63756561279297</v>
+        <v>8.63756370544434</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>8.39248943328857</v>
+        <v>8.39248752593994</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G11" t="n">
-        <v>8.38704204559326</v>
+        <v>8.38704109191895</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G13" t="n">
-        <v>8.26722717285156</v>
+        <v>8.26722526550293</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G14" t="n">
-        <v>7.94045925140381</v>
+        <v>7.94045829772949</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>8.1256275177002</v>
+        <v>8.12562656402588</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G17" t="n">
-        <v>7.95679807662964</v>
+        <v>7.95679759979248</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>7.70627641677856</v>
+        <v>7.70627450942993</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>7.60279893875122</v>
+        <v>7.6027979850769</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G21" t="n">
-        <v>7.51021432876587</v>
+        <v>7.51021385192871</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>7.37950849533081</v>
+        <v>7.37950801849365</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>7.10175609588623</v>
+        <v>7.10175514221191</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G24" t="n">
-        <v>6.9274787902832</v>
+        <v>6.92747974395752</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G25" t="n">
-        <v>6.85123348236084</v>
+        <v>6.85123300552368</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>6.45911169052124</v>
+        <v>6.45911121368408</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G29" t="n">
-        <v>6.52446413040161</v>
+        <v>6.52446556091309</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G30" t="n">
-        <v>5.96895933151245</v>
+        <v>5.96895885467529</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G31" t="n">
-        <v>6.07243585586548</v>
+        <v>6.07243537902832</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>6.31751251220703</v>
+        <v>6.31751108169556</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G33" t="n">
-        <v>6.3392972946167</v>
+        <v>6.33929634094238</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G34" t="n">
-        <v>6.48634195327759</v>
+        <v>6.48634099960327</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G35" t="n">
-        <v>6.44277191162109</v>
+        <v>6.44277286529541</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G36" t="n">
-        <v>6.37741994857788</v>
+        <v>6.37741947174072</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G38" t="n">
-        <v>6.60071039199829</v>
+        <v>6.60071134567261</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>6.52446413040161</v>
+        <v>6.52446556091309</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>6.6606183052063</v>
+        <v>6.66061735153198</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G41" t="n">
-        <v>6.95471000671387</v>
+        <v>6.95470857620239</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G42" t="n">
-        <v>6.97649383544922</v>
+        <v>6.97649431228638</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>7.13443326950073</v>
+        <v>7.13443183898926</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>7.06363296508789</v>
+        <v>7.06363201141357</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G47" t="n">
-        <v>6.9383716583252</v>
+        <v>6.93837070465088</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G48" t="n">
-        <v>7.00917196273804</v>
+        <v>7.0091700553894</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G50" t="n">
-        <v>7.05818653106689</v>
+        <v>7.05818605422974</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>7.57012271881104</v>
+        <v>7.57012128829956</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>7.46119928359985</v>
+        <v>7.46119976043701</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>7.54289150238037</v>
+        <v>7.54289197921753</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G55" t="n">
-        <v>7.55922985076904</v>
+        <v>7.5592303276062</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>7.43396806716919</v>
+        <v>7.43396854400635</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>7.21067810058594</v>
+        <v>7.21067762374878</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G61" t="n">
-        <v>7.11264801025391</v>
+        <v>7.11264753341675</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>7.1671085357666</v>
+        <v>7.16710901260376</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G64" t="n">
-        <v>6.99283409118652</v>
+        <v>6.99283266067505</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G66" t="n">
-        <v>6.6878490447998</v>
+        <v>6.68784856796265</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>12.3199996948242</v>
       </c>
       <c r="G67" t="n">
-        <v>6.70963382720947</v>
+        <v>6.70963335037231</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>6.56258916854858</v>
+        <v>6.56258869171143</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>6.75320339202881</v>
+        <v>6.75320148468018</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>6.83489513397217</v>
+        <v>6.83489465713501</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G71" t="n">
-        <v>6.85667896270752</v>
+        <v>6.85667943954468</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G72" t="n">
-        <v>7.1180944442749</v>
+        <v>7.11809301376343</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>7.17800092697144</v>
+        <v>7.17800235748291</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>7.16166257858276</v>
+        <v>7.16166305541992</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G76" t="n">
-        <v>7.22701692581177</v>
+        <v>7.22701597213745</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>7.27603197097778</v>
+        <v>7.27603054046631</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G78" t="n">
-        <v>7.42307758331299</v>
+        <v>7.42307615280151</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G80" t="n">
-        <v>7.45575332641602</v>
+        <v>7.45575380325317</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G82" t="n">
-        <v>7.47209310531616</v>
+        <v>7.47209215164185</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>7.24880170822144</v>
+        <v>7.24880027770996</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G86" t="n">
-        <v>7.10175609588623</v>
+        <v>7.10175514221191</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>7.04184913635254</v>
+        <v>7.04184722900391</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G90" t="n">
-        <v>7.04184913635254</v>
+        <v>7.04184722900391</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>13.25</v>
       </c>
       <c r="G91" t="n">
-        <v>7.21612405776978</v>
+        <v>7.21612310409546</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G93" t="n">
-        <v>6.85667896270752</v>
+        <v>6.85667943954468</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>6.78043413162231</v>
+        <v>6.78043460845947</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G95" t="n">
-        <v>6.86212539672852</v>
+        <v>6.86212635040283</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75864839553833</v>
+        <v>6.75864934921265</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>6.81310939788818</v>
+        <v>6.8131103515625</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>12.75</v>
       </c>
       <c r="G99" t="n">
-        <v>6.94381666183472</v>
+        <v>6.94381713867188</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>7.00731039047241</v>
+        <v>7.00731086730957</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>7.41135692596436</v>
+        <v>7.41135597229004</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G102" t="n">
-        <v>7.51525449752808</v>
+        <v>7.51525354385376</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>7.51525449752808</v>
+        <v>7.51525354385376</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G104" t="n">
-        <v>7.57297372817993</v>
+        <v>7.57297468185425</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>7.60760736465454</v>
+        <v>7.6076078414917</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G106" t="n">
-        <v>7.52102613449097</v>
+        <v>7.52102565765381</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>7.48062229156494</v>
+        <v>7.48062086105347</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22664976119995</v>
+        <v>7.22664928436279</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>12.5</v>
       </c>
       <c r="G110" t="n">
-        <v>7.21510553359985</v>
+        <v>7.2151050567627</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>12.710000038147</v>
       </c>
       <c r="G111" t="n">
-        <v>7.3363184928894</v>
+        <v>7.33631801605225</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.10543632507324</v>
+        <v>7.10543537139893</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G117" t="n">
-        <v>6.70138931274414</v>
+        <v>6.7013897895813</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>6.62635135650635</v>
+        <v>6.62635231018066</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G119" t="n">
-        <v>6.88609647750854</v>
+        <v>6.8860969543457</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G120" t="n">
-        <v>7.09389114379883</v>
+        <v>7.09389066696167</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G121" t="n">
-        <v>7.22087621688843</v>
+        <v>7.22087717056274</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>7.26128244400024</v>
+        <v>7.26128053665161</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G123" t="n">
-        <v>7.57297372817993</v>
+        <v>7.57297468185425</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>5.85866498947144</v>
+        <v>5.85866546630859</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G127" t="n">
-        <v>5.99719524383545</v>
+        <v>5.99719572067261</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.08954906463623</v>
+        <v>6.08954858779907</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G129" t="n">
-        <v>6.15881395339966</v>
+        <v>6.15881252288818</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G130" t="n">
-        <v>5.98565149307251</v>
+        <v>5.98565101623535</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G131" t="n">
-        <v>5.87021017074585</v>
+        <v>5.87020921707153</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>5.66530084609985</v>
+        <v>5.66529941558838</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>6.11840867996216</v>
+        <v>6.11841011047363</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G135" t="n">
-        <v>6.16458702087402</v>
+        <v>6.16458606719971</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G137" t="n">
-        <v>6.41278505325317</v>
+        <v>6.41278600692749</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>6.58017635345459</v>
+        <v>6.58017587661743</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>6.55131578445435</v>
+        <v>6.55131483078003</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>6.55708694458008</v>
+        <v>6.55708789825439</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G144" t="n">
-        <v>6.48782300949097</v>
+        <v>6.48782348632812</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>6.44741773605347</v>
+        <v>6.44741821289062</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G146" t="n">
-        <v>6.40124177932739</v>
+        <v>6.40124130249023</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G149" t="n">
-        <v>6.79951524734497</v>
+        <v>6.79951477050781</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G152" t="n">
-        <v>6.48782300949097</v>
+        <v>6.48782348632812</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G155" t="n">
-        <v>6.90341281890869</v>
+        <v>6.90341377258301</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>6.98422193527222</v>
+        <v>6.98422145843506</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G157" t="n">
-        <v>6.98999500274658</v>
+        <v>6.98999261856079</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G158" t="n">
-        <v>7.03039741516113</v>
+        <v>7.03039884567261</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>6.98422193527222</v>
+        <v>6.98422145843506</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>11.75</v>
       </c>
       <c r="G160" t="n">
-        <v>6.78219938278198</v>
+        <v>6.78219890594482</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>6.59749364852905</v>
+        <v>6.59749221801758</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G162" t="n">
-        <v>6.61480808258057</v>
+        <v>6.61480903625488</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G163" t="n">
-        <v>6.40124177932739</v>
+        <v>6.40124130249023</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>6.45319032669067</v>
+        <v>6.45319128036499</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G165" t="n">
-        <v>6.74179363250732</v>
+        <v>6.74179458618164</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G166" t="n">
-        <v>6.7187066078186</v>
+        <v>6.71870565414429</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G167" t="n">
-        <v>6.52822732925415</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>6.45896148681641</v>
+        <v>6.45896291732788</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G169" t="n">
-        <v>6.33197593688965</v>
+        <v>6.33197546005249</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>11.25</v>
       </c>
       <c r="G170" t="n">
-        <v>6.49359369277954</v>
+        <v>6.49359464645386</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>6.58017635345459</v>
+        <v>6.58017587661743</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G172" t="n">
-        <v>6.64944171905518</v>
+        <v>6.64944076538086</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>6.69561815261841</v>
+        <v>6.69561719894409</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>6.64366960525513</v>
+        <v>6.64366865158081</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G175" t="n">
-        <v>6.59171915054321</v>
+        <v>6.59172010421753</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G176" t="n">
-        <v>6.68407392501831</v>
+        <v>6.68407297134399</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>6.85146284103394</v>
+        <v>6.85146331787109</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G178" t="n">
-        <v>6.94958925247192</v>
+        <v>6.94958972930908</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G180" t="n">
-        <v>6.52822732925415</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G181" t="n">
-        <v>6.41855716705322</v>
+        <v>6.41855812072754</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>11</v>
       </c>
       <c r="G183" t="n">
-        <v>6.34929275512695</v>
+        <v>6.34929227828979</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G184" t="n">
-        <v>6.45896148681641</v>
+        <v>6.45896291732788</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>6.44164562225342</v>
+        <v>6.44164514541626</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G186" t="n">
-        <v>6.51091051101685</v>
+        <v>6.51091146469116</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G187" t="n">
-        <v>6.52822732925415</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>6.31466007232666</v>
+        <v>6.3146595954895</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G190" t="n">
-        <v>6.28580045700073</v>
+        <v>6.28579902648926</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>6.32620429992676</v>
+        <v>6.3262038230896</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G193" t="n">
-        <v>6.26848363876343</v>
+        <v>6.26848316192627</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G194" t="n">
-        <v>6.23962354660034</v>
+        <v>6.23962306976318</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G196" t="n">
-        <v>6.48205041885376</v>
+        <v>6.48205089569092</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G197" t="n">
-        <v>6.56863164901733</v>
+        <v>6.56863117218018</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G198" t="n">
-        <v>6.52822732925415</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G199" t="n">
-        <v>6.5628604888916</v>
+        <v>6.56286096572876</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G200" t="n">
-        <v>6.55708694458008</v>
+        <v>6.55708789825439</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G201" t="n">
-        <v>6.64944171905518</v>
+        <v>6.64944076538086</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G202" t="n">
-        <v>6.45896148681641</v>
+        <v>6.45896291732788</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>6.5628604888916</v>
+        <v>6.56286096572876</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G204" t="n">
-        <v>6.7187066078186</v>
+        <v>6.71870565414429</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>6.85146284103394</v>
+        <v>6.85146331787109</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>6.86300802230835</v>
+        <v>6.86300849914551</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G208" t="n">
-        <v>6.89186906814575</v>
+        <v>6.89186811447144</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G209" t="n">
-        <v>6.97844934463501</v>
+        <v>6.97845029830933</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>6.96113252639771</v>
+        <v>6.96113300323486</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G211" t="n">
-        <v>7.01885461807251</v>
+        <v>7.01885318756104</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>7.00153779983521</v>
+        <v>7.00153827667236</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>6.83992004394531</v>
+        <v>6.83991956710815</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>6.68984508514404</v>
+        <v>6.68984651565552</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>11.25</v>
       </c>
       <c r="G217" t="n">
-        <v>6.49359369277954</v>
+        <v>6.49359464645386</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G218" t="n">
-        <v>6.38969612121582</v>
+        <v>6.38969707489014</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G219" t="n">
-        <v>6.5455436706543</v>
+        <v>6.54554319381714</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G220" t="n">
-        <v>6.64366960525513</v>
+        <v>6.64366865158081</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G221" t="n">
-        <v>6.78797054290771</v>
+        <v>6.78797101974487</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>6.78797054290771</v>
+        <v>6.78797101974487</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.83992004394531</v>
+        <v>6.83991956710815</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G225" t="n">
-        <v>6.77642726898193</v>
+        <v>6.77642679214478</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>6.69561815261841</v>
+        <v>6.69561719894409</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>11.25</v>
       </c>
       <c r="G228" t="n">
-        <v>6.49359369277954</v>
+        <v>6.49359464645386</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G229" t="n">
-        <v>6.48205041885376</v>
+        <v>6.48205089569092</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>6.72447681427002</v>
+        <v>6.72447776794434</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>11.25</v>
       </c>
       <c r="G232" t="n">
-        <v>6.49359369277954</v>
+        <v>6.49359464645386</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69561815261841</v>
+        <v>6.69561719894409</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>6.7187066078186</v>
+        <v>6.71870565414429</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G237" t="n">
-        <v>7.12275266647339</v>
+        <v>7.12275218963623</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G238" t="n">
-        <v>7.10543632507324</v>
+        <v>7.10543537139893</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>7.04194402694702</v>
+        <v>7.04194307327271</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>8.31180000305176</v>
+        <v>8.31180095672607</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G243" t="n">
-        <v>8.09246158599854</v>
+        <v>8.09246253967285</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G244" t="n">
-        <v>8.11555194854736</v>
+        <v>8.11554908752441</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G246" t="n">
-        <v>7.97701978683472</v>
+        <v>7.97702026367188</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>8.31180000305176</v>
+        <v>8.31180095672607</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G249" t="n">
-        <v>8.19635963439941</v>
+        <v>8.1963586807251</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G250" t="n">
-        <v>8.27139759063721</v>
+        <v>8.27139663696289</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G251" t="n">
-        <v>8.21944713592529</v>
+        <v>8.21944808959961</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G252" t="n">
-        <v>8.23099327087402</v>
+        <v>8.23099136352539</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G256" t="n">
-        <v>8.14441013336182</v>
+        <v>8.14441108703613</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>8.15018177032471</v>
+        <v>8.15018367767334</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>8.28294086456299</v>
+        <v>8.2829418182373</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>8.34066200256348</v>
+        <v>8.34066104888916</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.38106632232666</v>
+        <v>8.38106536865234</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G261" t="n">
-        <v>8.32911777496338</v>
+        <v>8.32911682128906</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G263" t="n">
-        <v>8.16172695159912</v>
+        <v>8.1617259979248</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>8.09246158599854</v>
+        <v>8.09246253967285</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G269" t="n">
-        <v>7.88466787338257</v>
+        <v>7.88466644287109</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>7.82117414474487</v>
+        <v>7.8211727142334</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G271" t="n">
-        <v>7.9193000793457</v>
+        <v>7.91930055618286</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G272" t="n">
-        <v>7.91352558135986</v>
+        <v>7.91352844238281</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>14.25</v>
       </c>
       <c r="G273" t="n">
-        <v>8.22522068023682</v>
+        <v>8.2252197265625</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G274" t="n">
-        <v>8.90055465698242</v>
+        <v>8.90055370330811</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>8.98713397979736</v>
+        <v>8.98713493347168</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>8.88900947570801</v>
+        <v>8.88900756835938</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G280" t="n">
-        <v>8.47342014312744</v>
+        <v>8.47341918945312</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>8.64658260345459</v>
+        <v>8.64658164978027</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>8.30602931976318</v>
+        <v>8.30602836608887</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>8.31180000305176</v>
+        <v>8.31180095672607</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>8.66389751434326</v>
+        <v>8.66389942169189</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G291" t="n">
-        <v>8.5311393737793</v>
+        <v>8.53114032745361</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>8.45610332489014</v>
+        <v>8.45610237121582</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43878841400146</v>
+        <v>8.43878746032715</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G296" t="n">
-        <v>8.28871250152588</v>
+        <v>8.28871154785156</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G300" t="n">
-        <v>7.92507123947144</v>
+        <v>7.92507171630859</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G301" t="n">
-        <v>7.9193000793457</v>
+        <v>7.91930055618286</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G303" t="n">
-        <v>7.9193000793457</v>
+        <v>7.91930055618286</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G304" t="n">
-        <v>7.9193000793457</v>
+        <v>7.91930055618286</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G306" t="n">
-        <v>8.15018177032471</v>
+        <v>8.15018367767334</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G307" t="n">
-        <v>8.184814453125</v>
+        <v>8.18481540679932</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G310" t="n">
-        <v>8.20213222503662</v>
+        <v>8.2021312713623</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G311" t="n">
-        <v>8.41569805145264</v>
+        <v>8.41569900512695</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>8.42724323272705</v>
+        <v>8.42724418640137</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G313" t="n">
-        <v>8.41569805145264</v>
+        <v>8.41569900512695</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G315" t="n">
-        <v>8.27139759063721</v>
+        <v>8.27139663696289</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>8.31180000305176</v>
+        <v>8.31180095672607</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G318" t="n">
-        <v>8.40992546081543</v>
+        <v>8.40992736816406</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>8.45610332489014</v>
+        <v>8.45610237121582</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G321" t="n">
-        <v>8.49073600769043</v>
+        <v>8.49073696136475</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>8.6004056930542</v>
+        <v>8.60040473937988</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G324" t="n">
-        <v>8.43301486968994</v>
+        <v>8.43301582336426</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>8.28294086456299</v>
+        <v>8.2829418182373</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G327" t="n">
-        <v>8.26562309265137</v>
+        <v>8.26562404632568</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>14.25</v>
       </c>
       <c r="G329" t="n">
-        <v>8.22522068023682</v>
+        <v>8.2252197265625</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>8.184814453125</v>
+        <v>8.18481540679932</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10977840423584</v>
+        <v>8.10977745056152</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G332" t="n">
-        <v>8.00588226318359</v>
+        <v>8.00588035583496</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14441013336182</v>
+        <v>8.14441108703613</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>8.14441013336182</v>
+        <v>8.14441108703613</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>14.25</v>
       </c>
       <c r="G335" t="n">
-        <v>8.22522068023682</v>
+        <v>8.2252197265625</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G336" t="n">
-        <v>8.5311393737793</v>
+        <v>8.53114032745361</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.42724323272705</v>
+        <v>8.42724418640137</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G339" t="n">
-        <v>8.41569805145264</v>
+        <v>8.41569900512695</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>15</v>
       </c>
       <c r="G343" t="n">
-        <v>8.65812587738037</v>
+        <v>8.65812683105469</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>15.25</v>
       </c>
       <c r="G344" t="n">
-        <v>8.80242729187012</v>
+        <v>8.80242824554443</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>8.84860610961914</v>
+        <v>8.84860420227051</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>8.82551670074463</v>
+        <v>8.82551574707031</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>8.56577205657959</v>
+        <v>8.56577301025391</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>8.56577205657959</v>
+        <v>8.56577301025391</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G351" t="n">
-        <v>8.65235424041748</v>
+        <v>8.65235328674316</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>8.6004056930542</v>
+        <v>8.60040473937988</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>8.68698501586914</v>
+        <v>8.68698787689209</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G356" t="n">
-        <v>8.94036960601807</v>
+        <v>8.9403715133667</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G357" t="n">
-        <v>8.79410743713379</v>
+        <v>8.79410648345947</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>8.74535179138184</v>
+        <v>8.74535274505615</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>8.56861686706543</v>
+        <v>8.56861782073975</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G363" t="n">
-        <v>8.65393733978271</v>
+        <v>8.65393829345703</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G367" t="n">
-        <v>8.36750316619873</v>
+        <v>8.36750411987305</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>8.51376819610596</v>
+        <v>8.51376724243164</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G369" t="n">
-        <v>8.5747127532959</v>
+        <v>8.57471084594727</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G370" t="n">
-        <v>8.6661262512207</v>
+        <v>8.66612720489502</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>14.5</v>
       </c>
       <c r="G371" t="n">
-        <v>8.83676624298096</v>
+        <v>8.83676719665527</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G373" t="n">
-        <v>8.7819185256958</v>
+        <v>8.78191757202148</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>8.80020046234131</v>
+        <v>8.80019950866699</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G378" t="n">
-        <v>8.86114406585693</v>
+        <v>8.86114311218262</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G379" t="n">
-        <v>8.83067321777344</v>
+        <v>8.83067417144775</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G382" t="n">
-        <v>8.85505104064941</v>
+        <v>8.8550500869751</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>8.7819185256958</v>
+        <v>8.78191757202148</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.89771175384521</v>
+        <v>8.8977108001709</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>15</v>
       </c>
       <c r="G389" t="n">
-        <v>9.14148235321045</v>
+        <v>9.14148330688477</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>9.13538932800293</v>
+        <v>9.13538837432861</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>15.1599998474121</v>
       </c>
       <c r="G392" t="n">
-        <v>9.23899269104004</v>
+        <v>9.23899078369141</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G393" t="n">
-        <v>9.3791618347168</v>
+        <v>9.37916278839111</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G394" t="n">
-        <v>9.3791618347168</v>
+        <v>9.37916278839111</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>9.15976619720459</v>
+        <v>9.15976524353027</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G400" t="n">
-        <v>9.12319946289062</v>
+        <v>9.12320137023926</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G401" t="n">
-        <v>9.34259605407715</v>
+        <v>9.34259510040283</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G402" t="n">
-        <v>9.36087894439697</v>
+        <v>9.36087799072266</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G405" t="n">
-        <v>9.34259605407715</v>
+        <v>9.34259510040283</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G407" t="n">
-        <v>9.64731311798096</v>
+        <v>9.64731121063232</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G409" t="n">
-        <v>9.70825481414795</v>
+        <v>9.70825576782227</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G410" t="n">
-        <v>9.7996711730957</v>
+        <v>9.79966926574707</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>15.5</v>
       </c>
       <c r="G415" t="n">
-        <v>9.44619846343994</v>
+        <v>9.44619941711426</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G416" t="n">
-        <v>9.48276615142822</v>
+        <v>9.48276519775391</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G418" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G419" t="n">
-        <v>9.36697292327881</v>
+        <v>9.36697387695312</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G420" t="n">
-        <v>9.29993629455566</v>
+        <v>9.29993534088135</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>9.25118064880371</v>
+        <v>9.25117969512939</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G425" t="n">
-        <v>9.12929344177246</v>
+        <v>9.12929439544678</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G426" t="n">
-        <v>9.11710643768311</v>
+        <v>9.11710548400879</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G428" t="n">
-        <v>9.20851993560791</v>
+        <v>9.20851898193359</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26337051391602</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19023704528809</v>
+        <v>9.1902379989624</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>9.12929344177246</v>
+        <v>9.12929439544678</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G433" t="n">
-        <v>9.11710643768311</v>
+        <v>9.11710548400879</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G435" t="n">
-        <v>9.4705753326416</v>
+        <v>9.47057628631592</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G439" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>9.47667217254639</v>
+        <v>9.47667121887207</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.47667217254639</v>
+        <v>9.47667121887207</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G442" t="n">
-        <v>9.49495315551758</v>
+        <v>9.49495220184326</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G443" t="n">
-        <v>9.48276615142822</v>
+        <v>9.48276519775391</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G444" t="n">
-        <v>9.3791618347168</v>
+        <v>9.37916278839111</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>15.5</v>
       </c>
       <c r="G446" t="n">
-        <v>9.44619846343994</v>
+        <v>9.44619941711426</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G447" t="n">
-        <v>9.45838928222656</v>
+        <v>9.45838832855225</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>9.64121627807617</v>
+        <v>9.64121723175049</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G450" t="n">
-        <v>9.7021598815918</v>
+        <v>9.70216083526611</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G451" t="n">
-        <v>9.48276615142822</v>
+        <v>9.48276519775391</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G456" t="n">
-        <v>9.4705753326416</v>
+        <v>9.47057628631592</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G457" t="n">
-        <v>9.48276615142822</v>
+        <v>9.48276519775391</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G458" t="n">
-        <v>9.43400955200195</v>
+        <v>9.43401050567627</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G460" t="n">
-        <v>9.31212425231934</v>
+        <v>9.3121223449707</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>15.5</v>
       </c>
       <c r="G463" t="n">
-        <v>9.44619846343994</v>
+        <v>9.44619941711426</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G465" t="n">
-        <v>9.57417964935303</v>
+        <v>9.57417869567871</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G469" t="n">
-        <v>9.59246253967285</v>
+        <v>9.59246444702148</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G470" t="n">
-        <v>9.53151988983154</v>
+        <v>9.53152084350586</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G471" t="n">
-        <v>9.69606685638428</v>
+        <v>9.69606590270996</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G472" t="n">
-        <v>9.70825481414795</v>
+        <v>9.70825576782227</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>15.75</v>
       </c>
       <c r="G473" t="n">
-        <v>9.59855842590332</v>
+        <v>9.598557472229</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G475" t="n">
-        <v>9.51933002471924</v>
+        <v>9.51933097839355</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G476" t="n">
-        <v>9.53151988983154</v>
+        <v>9.53152084350586</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G479" t="n">
-        <v>9.47667217254639</v>
+        <v>9.47667121887207</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G480" t="n">
-        <v>9.37306690216064</v>
+        <v>9.37306785583496</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G482" t="n">
-        <v>9.29993629455566</v>
+        <v>9.29993534088135</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G485" t="n">
-        <v>9.29993629455566</v>
+        <v>9.29993534088135</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26337051391602</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G489" t="n">
-        <v>9.19023704528809</v>
+        <v>9.1902379989624</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>9.22680473327637</v>
+        <v>9.22680377960205</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G492" t="n">
-        <v>9.37306690216064</v>
+        <v>9.37306785583496</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25118064880371</v>
+        <v>9.25117969512939</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G498" t="n">
-        <v>9.31212425231934</v>
+        <v>9.3121223449707</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G499" t="n">
-        <v>9.33040714263916</v>
+        <v>9.33040618896484</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G500" t="n">
-        <v>9.31821727752686</v>
+        <v>9.31821823120117</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G501" t="n">
-        <v>9.36087894439697</v>
+        <v>9.36087799072266</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>9.45838928222656</v>
+        <v>9.45838832855225</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G505" t="n">
-        <v>9.39134979248047</v>
+        <v>9.39134883880615</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G506" t="n">
-        <v>9.32431221008301</v>
+        <v>9.32431316375732</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G508" t="n">
-        <v>9.31212425231934</v>
+        <v>9.3121223449707</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>15.25</v>
       </c>
       <c r="G509" t="n">
-        <v>9.2938404083252</v>
+        <v>9.29384231567383</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G510" t="n">
-        <v>9.3791618347168</v>
+        <v>9.37916278839111</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G511" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26337051391602</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G512" t="n">
-        <v>9.15367317199707</v>
+        <v>9.15367221832275</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G513" t="n">
-        <v>9.0744457244873</v>
+        <v>9.07444477081299</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>15</v>
       </c>
       <c r="G514" t="n">
-        <v>9.14148235321045</v>
+        <v>9.14148330688477</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26337051391602</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>9.59246253967285</v>
+        <v>9.59246444702148</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G520" t="n">
-        <v>9.54980373382568</v>
+        <v>9.54980278015137</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G521" t="n">
-        <v>9.5558967590332</v>
+        <v>9.55589580535889</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>9.65340614318848</v>
+        <v>9.65340709686279</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G523" t="n">
-        <v>9.57417964935303</v>
+        <v>9.57417869567871</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G527" t="n">
-        <v>9.76919841766357</v>
+        <v>9.76919746398926</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>9.872802734375</v>
+        <v>9.87280178070068</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G530" t="n">
-        <v>9.88498973846436</v>
+        <v>9.88499069213867</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>9.872802734375</v>
+        <v>9.87280178070068</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G532" t="n">
-        <v>9.74177360534668</v>
+        <v>9.74177265167236</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G533" t="n">
-        <v>9.73263359069824</v>
+        <v>9.73263454437256</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G534" t="n">
-        <v>9.76919841766357</v>
+        <v>9.76919746398926</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>15.9449996948242</v>
       </c>
       <c r="G535" t="n">
-        <v>9.71739673614502</v>
+        <v>9.7173957824707</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G537" t="n">
-        <v>9.31212425231934</v>
+        <v>9.3121223449707</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G542" t="n">
-        <v>9.25118064880371</v>
+        <v>9.25117969512939</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>15.3599996566772</v>
       </c>
       <c r="G543" t="n">
-        <v>9.36087894439697</v>
+        <v>9.36087799072266</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>15.5050001144409</v>
       </c>
       <c r="G545" t="n">
-        <v>9.44924640655518</v>
+        <v>9.44924736022949</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G546" t="n">
-        <v>9.3791618347168</v>
+        <v>9.37916278839111</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>9.40049171447754</v>
+        <v>9.40049076080322</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>15.3649997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>9.36392593383789</v>
+        <v>9.36392688751221</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>9.39134979248047</v>
+        <v>9.39134883880615</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G552" t="n">
-        <v>9.39744567871094</v>
+        <v>9.39744472503662</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>15.4049997329712</v>
       </c>
       <c r="G554" t="n">
-        <v>9.38830280303955</v>
+        <v>9.38830375671387</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>15.5</v>
       </c>
       <c r="G558" t="n">
-        <v>9.44619846343994</v>
+        <v>9.44619941711426</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G559" t="n">
-        <v>9.45229339599609</v>
+        <v>9.45229434967041</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G560" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>15.3149995803833</v>
       </c>
       <c r="G563" t="n">
-        <v>9.33345413208008</v>
+        <v>9.33345508575439</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.56198978424072</v>
+        <v>9.56199169158936</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G567" t="n">
-        <v>9.59246253967285</v>
+        <v>9.59246444702148</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G568" t="n">
-        <v>9.59246253967285</v>
+        <v>9.59246444702148</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>9.50714206695557</v>
+        <v>9.50714302062988</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>9.40049171447754</v>
+        <v>9.40049076080322</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G571" t="n">
-        <v>9.36697292327881</v>
+        <v>9.36697387695312</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G572" t="n">
-        <v>9.43400955200195</v>
+        <v>9.43401050567627</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G573" t="n">
-        <v>9.48276615142822</v>
+        <v>9.48276519775391</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>15.625</v>
       </c>
       <c r="G574" t="n">
-        <v>9.52237892150879</v>
+        <v>9.52237796783447</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G575" t="n">
-        <v>9.54980373382568</v>
+        <v>9.54980278015137</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G576" t="n">
-        <v>9.54675674438477</v>
+        <v>9.54675579071045</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G577" t="n">
-        <v>9.62293434143066</v>
+        <v>9.6229362487793</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G578" t="n">
-        <v>9.65340614318848</v>
+        <v>9.65340709686279</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G579" t="n">
-        <v>9.73263359069824</v>
+        <v>9.73263454437256</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G580" t="n">
-        <v>9.76919841766357</v>
+        <v>9.76919746398926</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>16.2049999237061</v>
       </c>
       <c r="G582" t="n">
-        <v>9.87584781646729</v>
+        <v>9.87584972381592</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>9.85756587982178</v>
+        <v>9.85756492614746</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>16.3950004577637</v>
       </c>
       <c r="G586" t="n">
-        <v>9.99164295196533</v>
+        <v>9.9916410446167</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>10.0830564498901</v>
+        <v>10.0830574035645</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G588" t="n">
-        <v>10.1866579055786</v>
+        <v>10.1866588592529</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G589" t="n">
-        <v>10.3085441589355</v>
+        <v>10.3085460662842</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>17.0550003051758</v>
       </c>
       <c r="G590" t="n">
-        <v>10.3938665390015</v>
+        <v>10.3938674926758</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G591" t="n">
-        <v>10.1805648803711</v>
+        <v>10.1805639266968</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>10.2628393173218</v>
+        <v>10.2628383636475</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>10.1348562240601</v>
+        <v>10.1348581314087</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G594" t="n">
-        <v>10.2018938064575</v>
+        <v>10.2018957138062</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G595" t="n">
-        <v>10.2536964416504</v>
+        <v>10.2536973953247</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G600" t="n">
-        <v>10.0921964645386</v>
+        <v>10.0921983718872</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>16.4050006866455</v>
       </c>
       <c r="G601" t="n">
-        <v>9.99773502349854</v>
+        <v>9.99773597717285</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>10.0921964645386</v>
+        <v>10.0921983718872</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G604" t="n">
-        <v>10.0617246627808</v>
+        <v>10.0617275238037</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G605" t="n">
-        <v>9.8606128692627</v>
+        <v>9.86061191558838</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G606" t="n">
-        <v>9.89413356781006</v>
+        <v>9.89413166046143</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G608" t="n">
-        <v>9.84978103637695</v>
+        <v>9.84978294372559</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81761455535889</v>
+        <v>9.81761360168457</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.70180988311768</v>
+        <v>9.70181083679199</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>14.9049997329712</v>
       </c>
       <c r="G611" t="n">
-        <v>9.5892219543457</v>
+        <v>9.58922290802002</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G613" t="n">
-        <v>9.42194938659668</v>
+        <v>9.421950340271</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>14.1350002288818</v>
       </c>
       <c r="G614" t="n">
-        <v>9.09383964538574</v>
+        <v>9.09383869171143</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G617" t="n">
-        <v>9.46376895904541</v>
+        <v>9.46376800537109</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G619" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G620" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G622" t="n">
-        <v>9.11635494232178</v>
+        <v>9.11635589599609</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G623" t="n">
-        <v>9.38334846496582</v>
+        <v>9.3833475112915</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G624" t="n">
-        <v>9.33831310272217</v>
+        <v>9.33831405639648</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>14.5600004196167</v>
       </c>
       <c r="G625" t="n">
-        <v>9.36726379394531</v>
+        <v>9.36726474761963</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>14.7349996566772</v>
       </c>
       <c r="G626" t="n">
-        <v>9.47985172271729</v>
+        <v>9.47985076904297</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G628" t="n">
-        <v>9.3479642868042</v>
+        <v>9.34796524047852</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G629" t="n">
-        <v>9.38334846496582</v>
+        <v>9.3833475112915</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G630" t="n">
-        <v>9.41229915618896</v>
+        <v>9.41230010986328</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.28684520721436</v>
+        <v>9.28684616088867</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G633" t="n">
-        <v>9.19355964660645</v>
+        <v>9.19355773925781</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G634" t="n">
-        <v>9.20964241027832</v>
+        <v>9.20964050292969</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G635" t="n">
-        <v>9.19355964660645</v>
+        <v>9.19355773925781</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G636" t="n">
-        <v>9.11957359313965</v>
+        <v>9.11957454681396</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G637" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G638" t="n">
-        <v>9.11313819885254</v>
+        <v>9.11313915252686</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G643" t="n">
-        <v>9.35761451721191</v>
+        <v>9.3576135635376</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G646" t="n">
-        <v>9.25146198272705</v>
+        <v>9.25146102905273</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>9.33831310272217</v>
+        <v>9.33831405639648</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G653" t="n">
-        <v>9.35761451721191</v>
+        <v>9.3576135635376</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G654" t="n">
-        <v>9.47020149230957</v>
+        <v>9.4702033996582</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G657" t="n">
-        <v>9.54740428924561</v>
+        <v>9.54740333557129</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>9.53132057189941</v>
+        <v>9.5313196182251</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>9.57635498046875</v>
+        <v>9.57635688781738</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>14.9849996566772</v>
       </c>
       <c r="G664" t="n">
-        <v>9.64069175720215</v>
+        <v>9.64069080352783</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G665" t="n">
-        <v>9.66320896148682</v>
+        <v>9.6632080078125</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>14.4549999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>9.29971218109131</v>
+        <v>9.29971313476562</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>14.4849996566772</v>
       </c>
       <c r="G672" t="n">
-        <v>9.31901264190674</v>
+        <v>9.31901168823242</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G673" t="n">
-        <v>9.43481731414795</v>
+        <v>9.43481636047363</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G674" t="n">
-        <v>9.53132057189941</v>
+        <v>9.5313196182251</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>14.7749996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>9.50558567047119</v>
+        <v>9.50558471679688</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G677" t="n">
-        <v>9.55705451965332</v>
+        <v>9.557053565979</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G678" t="n">
-        <v>9.49915313720703</v>
+        <v>9.49915218353271</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G679" t="n">
-        <v>9.47020149230957</v>
+        <v>9.4702033996582</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G680" t="n">
-        <v>9.33831310272217</v>
+        <v>9.33831405639648</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>14.3450002670288</v>
       </c>
       <c r="G681" t="n">
-        <v>9.22894191741943</v>
+        <v>9.22894287109375</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G682" t="n">
-        <v>9.38334846496582</v>
+        <v>9.3833475112915</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G684" t="n">
-        <v>9.51523685455322</v>
+        <v>9.51523780822754</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>14.8249998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>9.53775405883789</v>
+        <v>9.53775310516357</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>9.52166938781738</v>
+        <v>9.5216703414917</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>15.125</v>
       </c>
       <c r="G687" t="n">
-        <v>9.73076057434082</v>
+        <v>9.7307596206665</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G689" t="n">
-        <v>9.65999031066895</v>
+        <v>9.65999221801758</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>15.125</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73076057434082</v>
+        <v>9.7307596206665</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G694" t="n">
-        <v>9.74041271209717</v>
+        <v>9.74041080474854</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G697" t="n">
-        <v>9.84978103637695</v>
+        <v>9.84978294372559</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>15.5</v>
       </c>
       <c r="G698" t="n">
-        <v>9.97201824188232</v>
+        <v>9.97201919555664</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>9.98810195922852</v>
+        <v>9.98810291290283</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G701" t="n">
-        <v>9.57313823699951</v>
+        <v>9.57314014434814</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G702" t="n">
-        <v>9.53132057189941</v>
+        <v>9.5313196182251</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G703" t="n">
-        <v>9.42194938659668</v>
+        <v>9.421950340271</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>14.835000038147</v>
       </c>
       <c r="G705" t="n">
-        <v>9.54418659210205</v>
+        <v>9.54418754577637</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G706" t="n">
-        <v>9.50880336761475</v>
+        <v>9.50880241394043</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>9.29649639129639</v>
+        <v>9.29649448394775</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>14.4849996566772</v>
       </c>
       <c r="G709" t="n">
-        <v>9.31901264190674</v>
+        <v>9.31901168823242</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G710" t="n">
-        <v>9.18712520599365</v>
+        <v>9.18712425231934</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G711" t="n">
-        <v>9.11635494232178</v>
+        <v>9.11635589599609</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G712" t="n">
-        <v>9.09705543518066</v>
+        <v>9.09705638885498</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G713" t="n">
-        <v>9.20642566680908</v>
+        <v>9.20642471313477</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>14.2349996566772</v>
       </c>
       <c r="G714" t="n">
-        <v>9.15817260742188</v>
+        <v>9.15817356109619</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G715" t="n">
-        <v>9.01341915130615</v>
+        <v>9.01341819763184</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G716" t="n">
-        <v>9.03915309906006</v>
+        <v>9.03915214538574</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>8.8943977355957</v>
+        <v>8.89439678192139</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>13.75</v>
       </c>
       <c r="G719" t="n">
-        <v>8.84614562988281</v>
+        <v>8.84614658355713</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>14.0450000762939</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03593730926514</v>
+        <v>9.0359354019165</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G723" t="n">
-        <v>9.11313819885254</v>
+        <v>9.11313915252686</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G724" t="n">
-        <v>9.18712520599365</v>
+        <v>9.18712425231934</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>9.25467777252197</v>
+        <v>9.25467681884766</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G727" t="n">
-        <v>9.21607398986816</v>
+        <v>9.21607494354248</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G728" t="n">
-        <v>9.18712520599365</v>
+        <v>9.18712425231934</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G730" t="n">
-        <v>9.25467777252197</v>
+        <v>9.25467681884766</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G731" t="n">
-        <v>9.28684520721436</v>
+        <v>9.28684616088867</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>9.19355964660645</v>
+        <v>9.19355773925781</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G733" t="n">
-        <v>9.25789451599121</v>
+        <v>9.25789356231689</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G734" t="n">
-        <v>9.22572708129883</v>
+        <v>9.22572803497314</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>14.25</v>
       </c>
       <c r="G735" t="n">
-        <v>9.16782474517822</v>
+        <v>9.16782379150391</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G737" t="n">
-        <v>9.30292797088623</v>
+        <v>9.30292892456055</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G738" t="n">
-        <v>9.1099214553833</v>
+        <v>9.10992240905762</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>14.2550001144409</v>
       </c>
       <c r="G741" t="n">
-        <v>9.17104148864746</v>
+        <v>9.17104053497314</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G744" t="n">
-        <v>9.47020149230957</v>
+        <v>9.4702033996582</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>14.7550001144409</v>
       </c>
       <c r="G745" t="n">
-        <v>9.49271869659424</v>
+        <v>9.49271965026855</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G746" t="n">
-        <v>9.57957172393799</v>
+        <v>9.5795726776123</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>9.65677547454834</v>
+        <v>9.65677452087402</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G749" t="n">
-        <v>9.47020149230957</v>
+        <v>9.4702033996582</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G751" t="n">
-        <v>9.21607398986816</v>
+        <v>9.21607494354248</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G752" t="n">
-        <v>9.11957359313965</v>
+        <v>9.11957454681396</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>14.2449998855591</v>
       </c>
       <c r="G753" t="n">
-        <v>9.16460704803467</v>
+        <v>9.16460800170898</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G754" t="n">
-        <v>9.23537540435791</v>
+        <v>9.23537635803223</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>14.414999961853</v>
       </c>
       <c r="G755" t="n">
-        <v>9.27397918701172</v>
+        <v>9.27397727966309</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G756" t="n">
-        <v>9.25467777252197</v>
+        <v>9.25467681884766</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G757" t="n">
-        <v>9.20964241027832</v>
+        <v>9.20964050292969</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>14.3450002670288</v>
       </c>
       <c r="G758" t="n">
-        <v>9.22894191741943</v>
+        <v>9.22894287109375</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>9.42194938659668</v>
+        <v>9.421950340271</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G761" t="n">
-        <v>9.3479642868042</v>
+        <v>9.34796524047852</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G762" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G765" t="n">
-        <v>9.35761451721191</v>
+        <v>9.3576135635376</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G769" t="n">
-        <v>9.52810287475586</v>
+        <v>9.52810382843018</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G770" t="n">
-        <v>9.51523685455322</v>
+        <v>9.51523780822754</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G771" t="n">
-        <v>9.59565544128418</v>
+        <v>9.5956563949585</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>9.61817359924316</v>
+        <v>9.61817264556885</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G773" t="n">
-        <v>9.63747406005859</v>
+        <v>9.63747501373291</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>9.81761455535889</v>
+        <v>9.81761360168457</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G777" t="n">
-        <v>9.90446758270264</v>
+        <v>9.90446662902832</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G779" t="n">
-        <v>9.89481639862061</v>
+        <v>9.89481735229492</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>9.87551689147949</v>
+        <v>9.87551593780518</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>15.4449996948242</v>
       </c>
       <c r="G783" t="n">
-        <v>9.93663501739502</v>
+        <v>9.9366340637207</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G786" t="n">
-        <v>9.76614570617676</v>
+        <v>9.76614665985107</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>15.25</v>
       </c>
       <c r="G787" t="n">
-        <v>9.81117916107178</v>
+        <v>9.81118106842041</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G791" t="n">
-        <v>9.59565544128418</v>
+        <v>9.5956563949585</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G792" t="n">
-        <v>9.64390754699707</v>
+        <v>9.64390850067139</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G794" t="n">
-        <v>9.77257919311523</v>
+        <v>9.77257823944092</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G795" t="n">
-        <v>9.65999031066895</v>
+        <v>9.65999221801758</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>15.3050003051758</v>
       </c>
       <c r="G797" t="n">
-        <v>9.84656620025635</v>
+        <v>9.84656524658203</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>15.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>9.7950963973999</v>
+        <v>9.79509544372559</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G800" t="n">
-        <v>9.79187965393066</v>
+        <v>9.79187870025635</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G801" t="n">
-        <v>9.83691501617432</v>
+        <v>9.8369140625</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G802" t="n">
-        <v>9.93985176086426</v>
+        <v>9.93985080718994</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G803" t="n">
-        <v>9.98488616943359</v>
+        <v>9.98488712310791</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G805" t="n">
-        <v>10.0974731445312</v>
+        <v>10.0974740982056</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G806" t="n">
-        <v>10.1585922241211</v>
+        <v>10.1585931777954</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>15.875</v>
       </c>
       <c r="G808" t="n">
-        <v>10.2132778167725</v>
+        <v>10.2132768630981</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G809" t="n">
-        <v>10.2840461730957</v>
+        <v>10.28404712677</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>15.7250003814697</v>
       </c>
       <c r="G811" t="n">
-        <v>10.1167736053467</v>
+        <v>10.1167755126953</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>15.7650003433228</v>
       </c>
       <c r="G813" t="n">
-        <v>10.1425094604492</v>
+        <v>10.1425075531006</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G817" t="n">
-        <v>10.6025066375732</v>
+        <v>10.6025085449219</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G818" t="n">
-        <v>10.5896415710449</v>
+        <v>10.589638710022</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>10.518871307373</v>
+        <v>10.5188722610474</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>16.5</v>
       </c>
       <c r="G826" t="n">
-        <v>10.6153755187988</v>
+        <v>10.6153745651245</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>16.6749992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7279615402222</v>
+        <v>10.7279624938965</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G828" t="n">
-        <v>10.7022275924683</v>
+        <v>10.7022294998169</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7472639083862</v>
+        <v>10.7472629547119</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G833" t="n">
-        <v>10.7022275924683</v>
+        <v>10.7022294998169</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7247447967529</v>
+        <v>10.7247457504272</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G836" t="n">
-        <v>10.8180332183838</v>
+        <v>10.8180322647095</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G837" t="n">
-        <v>10.8759346008301</v>
+        <v>10.8759355545044</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17</v>
       </c>
       <c r="G838" t="n">
-        <v>10.9370536804199</v>
+        <v>10.9370527267456</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>11.0657234191895</v>
+        <v>11.0657243728638</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G840" t="n">
-        <v>10.9660034179688</v>
+        <v>10.9660043716431</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G841" t="n">
-        <v>10.9660034179688</v>
+        <v>10.9660043716431</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>10.9756536483765</v>
+        <v>10.9756546020508</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G845" t="n">
-        <v>11.0625085830688</v>
+        <v>11.0625066757202</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>11.1300592422485</v>
+        <v>11.1300601959229</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>17.1550006866455</v>
       </c>
       <c r="G849" t="n">
-        <v>11.0367727279663</v>
+        <v>11.0367736816406</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G850" t="n">
-        <v>10.9949569702148</v>
+        <v>10.9949560165405</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G851" t="n">
-        <v>10.9820871353149</v>
+        <v>10.9820890426636</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G852" t="n">
-        <v>10.8437652587891</v>
+        <v>10.8437671661377</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G853" t="n">
-        <v>10.8823680877686</v>
+        <v>10.8823671340942</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G854" t="n">
-        <v>10.8180332183838</v>
+        <v>10.8180322647095</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G855" t="n">
-        <v>10.9756536483765</v>
+        <v>10.9756546020508</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G856" t="n">
-        <v>10.9306192398071</v>
+        <v>10.9306201934814</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G857" t="n">
-        <v>11.0206890106201</v>
+        <v>11.0206899642944</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>17.0049991607666</v>
       </c>
       <c r="G858" t="n">
-        <v>10.9402694702148</v>
+        <v>10.9402685165405</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G859" t="n">
-        <v>11.0727338790894</v>
+        <v>11.0727348327637</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G860" t="n">
-        <v>11.0931148529053</v>
+        <v>11.093113899231</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>16.2950000762939</v>
       </c>
       <c r="G861" t="n">
-        <v>11.0693378448486</v>
+        <v>11.0693397521973</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>15.9549999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>10.8383741378784</v>
+        <v>10.8383731842041</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G864" t="n">
-        <v>10.9300804138184</v>
+        <v>10.9300813674927</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>15.9750003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>10.8519582748413</v>
+        <v>10.8519592285156</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>15.8050003051758</v>
       </c>
       <c r="G866" t="n">
-        <v>10.7364778518677</v>
+        <v>10.7364768981934</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>15.7150001525879</v>
       </c>
       <c r="G868" t="n">
-        <v>10.6753396987915</v>
+        <v>10.6753387451172</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G872" t="n">
-        <v>10.7432699203491</v>
+        <v>10.7432708740234</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G873" t="n">
-        <v>10.7704429626465</v>
+        <v>10.7704420089722</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16.1450004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>10.9674425125122</v>
+        <v>10.9674434661865</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G879" t="n">
-        <v>11.0285816192627</v>
+        <v>11.0285806655884</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G880" t="n">
-        <v>11.2459602355957</v>
+        <v>11.2459583282471</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>11.310492515564</v>
+        <v>11.3104934692383</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>11.2459602355957</v>
+        <v>11.2459583282471</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="n">
-        <v>11.3308734893799</v>
+        <v>11.3308725357056</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G885" t="n">
-        <v>11.286717414856</v>
+        <v>11.2867164611816</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G887" t="n">
-        <v>11.215389251709</v>
+        <v>11.2153902053833</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G889" t="n">
-        <v>11.2969055175781</v>
+        <v>11.2969064712524</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G890" t="n">
-        <v>11.3886127471924</v>
+        <v>11.3886117935181</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G891" t="n">
-        <v>11.5924072265625</v>
+        <v>11.5924091339111</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>11.6161823272705</v>
+        <v>11.6161832809448</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>17.0149993896484</v>
       </c>
       <c r="G893" t="n">
-        <v>11.5584402084351</v>
+        <v>11.5584411621094</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G894" t="n">
-        <v>11.6263723373413</v>
+        <v>11.626371383667</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G896" t="n">
-        <v>11.6909065246582</v>
+        <v>11.6909055709839</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G899" t="n">
-        <v>11.6637344360352</v>
+        <v>11.6637334823608</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G901" t="n">
-        <v>11.5924072265625</v>
+        <v>11.5924091339111</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>11.4803199768066</v>
+        <v>11.480320930481</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>11.5142860412598</v>
+        <v>11.5142869949341</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G905" t="n">
-        <v>11.5007009506226</v>
+        <v>11.5006999969482</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G906" t="n">
-        <v>11.5448541641235</v>
+        <v>11.5448532104492</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>11.5142860412598</v>
+        <v>11.5142869949341</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G911" t="n">
-        <v>11.4395627975464</v>
+        <v>11.4395618438721</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G912" t="n">
-        <v>11.4497509002686</v>
+        <v>11.4497518539429</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G913" t="n">
-        <v>11.286717414856</v>
+        <v>11.2867164611816</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>16.4349994659424</v>
       </c>
       <c r="G917" t="n">
-        <v>11.1644420623779</v>
+        <v>11.1644411087036</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G918" t="n">
-        <v>10.8621492385864</v>
+        <v>10.8621482849121</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G919" t="n">
-        <v>10.8961162567139</v>
+        <v>10.8961143493652</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>10.9878206253052</v>
+        <v>10.9878215789795</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G924" t="n">
-        <v>11.0183897018433</v>
+        <v>11.0183887481689</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>16.375</v>
       </c>
       <c r="G925" t="n">
-        <v>11.123682975769</v>
+        <v>11.1236839294434</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G926" t="n">
-        <v>11.0863199234009</v>
+        <v>11.0863208770752</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G927" t="n">
-        <v>10.981029510498</v>
+        <v>10.9810304641724</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G931" t="n">
-        <v>11.1542520523071</v>
+        <v>11.1542530059814</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G932" t="n">
-        <v>11.1882181167603</v>
+        <v>11.1882171630859</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>16.5049991607666</v>
       </c>
       <c r="G933" t="n">
-        <v>11.2119932174683</v>
+        <v>11.2119941711426</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G934" t="n">
-        <v>11.2391662597656</v>
+        <v>11.2391653060913</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G937" t="n">
-        <v>11.6195783615112</v>
+        <v>11.6195793151855</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>11.6841115951538</v>
+        <v>11.6841125488281</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>17.1749992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>11.6671295166016</v>
+        <v>11.6671285629272</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>17.375</v>
       </c>
       <c r="G943" t="n">
-        <v>11.8029928207397</v>
+        <v>11.8029918670654</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>11.7690258026123</v>
+        <v>11.7690267562866</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G950" t="n">
-        <v>12.2003879547119</v>
+        <v>12.2003870010376</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>12.159628868103</v>
+        <v>12.1596298217773</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G953" t="n">
-        <v>12.0781126022339</v>
+        <v>12.0781135559082</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>12.0509395599365</v>
+        <v>12.0509386062622</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>11.8505439758301</v>
+        <v>11.8505430221558</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G956" t="n">
-        <v>11.9150791168213</v>
+        <v>11.9150800704956</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>11.9898014068604</v>
+        <v>11.989800453186</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G958" t="n">
-        <v>12.0713195800781</v>
+        <v>12.0713214874268</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G959" t="n">
-        <v>12.0543384552002</v>
+        <v>12.0543375015259</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G960" t="n">
-        <v>12.1120777130127</v>
+        <v>12.1120767593384</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G965" t="n">
-        <v>12.3022842407227</v>
+        <v>12.3022832870483</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>12.2954902648926</v>
+        <v>12.2954912185669</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G969" t="n">
-        <v>12.4687147140503</v>
+        <v>12.468713760376</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G972" t="n">
-        <v>12.4687147140503</v>
+        <v>12.468713760376</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G973" t="n">
-        <v>12.4958868026733</v>
+        <v>12.4958877563477</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>18.3649997711182</v>
       </c>
       <c r="G974" t="n">
-        <v>12.4755077362061</v>
+        <v>12.4755067825317</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>12.3464393615723</v>
+        <v>12.3464384078979</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G980" t="n">
-        <v>12.6317491531372</v>
+        <v>12.6317472457886</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G982" t="n">
-        <v>13.0291442871094</v>
+        <v>13.0291452407837</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G983" t="n">
-        <v>13.0359392166138</v>
+        <v>13.0359382629395</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>19.5</v>
       </c>
       <c r="G984" t="n">
-        <v>13.246524810791</v>
+        <v>13.2465219497681</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>19.3349990844727</v>
       </c>
       <c r="G985" t="n">
-        <v>13.1344385147095</v>
+        <v>13.1344375610352</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G986" t="n">
-        <v>13.0291442871094</v>
+        <v>13.0291452407837</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G987" t="n">
-        <v>13.0223512649536</v>
+        <v>13.0223503112793</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>19.0499992370605</v>
       </c>
       <c r="G988" t="n">
-        <v>12.9408349990845</v>
+        <v>12.9408330917358</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G989" t="n">
-        <v>12.7030782699585</v>
+        <v>12.7030773162842</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G991" t="n">
-        <v>12.6725082397461</v>
+        <v>12.6725091934204</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>18.6550006866455</v>
       </c>
       <c r="G992" t="n">
-        <v>12.6725082397461</v>
+        <v>12.6725091934204</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G993" t="n">
-        <v>12.594388961792</v>
+        <v>12.5943880081177</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G996" t="n">
-        <v>12.6317491531372</v>
+        <v>12.6317472457886</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>12.5875949859619</v>
+        <v>12.5875940322876</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>12.424560546875</v>
+        <v>12.4245595932007</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>12.3770084381104</v>
+        <v>12.377007484436</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1006" t="n">
-        <v>12.4721126556396</v>
+        <v>12.4721117019653</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1008" t="n">
-        <v>12.5570268630981</v>
+        <v>12.5570249557495</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.5740070343018</v>
+        <v>12.5740079879761</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.6181631088257</v>
+        <v>12.6181640625</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>12.8898868560791</v>
+        <v>12.8898859024048</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1013" t="n">
-        <v>12.6894903182983</v>
+        <v>12.6894912719727</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.4958868026733</v>
+        <v>12.4958877563477</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.5740070343018</v>
+        <v>12.5740079879761</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5094747543335</v>
+        <v>12.5094738006592</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.5094747543335</v>
+        <v>12.5094738006592</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.4958868026733</v>
+        <v>12.4958877563477</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.546835899353</v>
+        <v>12.5468368530273</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1022" t="n">
-        <v>12.594388961792</v>
+        <v>12.5943880081177</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.5196628570557</v>
+        <v>12.51966381073</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.2950000762939</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.4279556274414</v>
+        <v>12.42795753479</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.1834058761597</v>
+        <v>12.183403968811</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1032" t="n">
-        <v>12.3226633071899</v>
+        <v>12.3226623535156</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1033" t="n">
-        <v>12.037353515625</v>
+        <v>12.0373525619507</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.3464393615723</v>
+        <v>12.3464384078979</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>18.2450008392334</v>
       </c>
       <c r="G1035" t="n">
-        <v>12.3939924240112</v>
+        <v>12.3939914703369</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1037" t="n">
-        <v>11.9524402618408</v>
+        <v>11.9524393081665</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>17.6849994659424</v>
       </c>
       <c r="G1038" t="n">
-        <v>12.0135774612427</v>
+        <v>12.0135765075684</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.4687147140503</v>
+        <v>12.468713760376</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.6181631088257</v>
+        <v>12.6181640625</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>12.7540245056152</v>
+        <v>12.7540235519409</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1049" t="n">
-        <v>12.7574214935303</v>
+        <v>12.757420539856</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G1051" t="n">
-        <v>12.6317491531372</v>
+        <v>12.6317472457886</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>12.5196628570557</v>
+        <v>12.51966381073</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>17.3349990844727</v>
       </c>
       <c r="G1054" t="n">
-        <v>11.7758188247681</v>
+        <v>11.7758197784424</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>17.2649993896484</v>
       </c>
       <c r="G1055" t="n">
-        <v>11.7282686233521</v>
+        <v>11.7282676696777</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>11.4803199768066</v>
+        <v>11.480320930481</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1057" t="n">
-        <v>11.0455627441406</v>
+        <v>11.0455617904663</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>15.7349996566772</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.6889247894287</v>
+        <v>10.6889266967773</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.3526678085327</v>
+        <v>10.3526668548584</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.34729194641113</v>
+        <v>9.34729099273682</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.20463466644287</v>
+        <v>9.20463562011719</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.20463466644287</v>
+        <v>9.20463562011719</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.19925785064697</v>
+        <v>8.19925689697266</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>11.2950000762939</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.67279386520386</v>
+        <v>7.67279434204102</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>7.37050247192383</v>
+        <v>7.37050151824951</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.05462265014648</v>
+        <v>7.05462312698364</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>10.7349996566772</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.29238128662109</v>
+        <v>7.29238033294678</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.39767456054688</v>
+        <v>7.3976731300354</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>10.8950004577637</v>
       </c>
       <c r="G1073" t="n">
-        <v>7.40107107162476</v>
+        <v>7.40107154846191</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.21963882446289</v>
+        <v>8.21963787078857</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>12.375</v>
       </c>
       <c r="G1077" t="n">
-        <v>8.40644836425781</v>
+        <v>8.4064474105835</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>12.3649997711182</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.39965438842773</v>
+        <v>8.39965343475342</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.27737903594971</v>
+        <v>8.27737998962402</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496322631836</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496322631836</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.74270534515381</v>
+        <v>8.74270629882812</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.92272281646729</v>
+        <v>8.92272186279297</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.4166374206543</v>
+        <v>8.41663837432861</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>12.164999961853</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.26379299163818</v>
+        <v>8.2637939453125</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>12.3649997711182</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.39965438842773</v>
+        <v>8.39965343475342</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1095" t="n">
-        <v>8.40305042266846</v>
+        <v>8.40305233001709</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>12.7449998855591</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.65779113769531</v>
+        <v>8.65779209136963</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.62722301483154</v>
+        <v>8.62722396850586</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>12.7349996566772</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.65099906921387</v>
+        <v>8.65099811553955</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.708740234375</v>
+        <v>8.70874118804932</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.53211975097656</v>
+        <v>8.53211879730225</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.53211975097656</v>
+        <v>8.53211879730225</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>12.414999961853</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.7832727432251</v>
+        <v>8.78327369689941</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>12.1949996948242</v>
       </c>
       <c r="G1111" t="n">
-        <v>8.62762832641602</v>
+        <v>8.62762928009033</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1112" t="n">
-        <v>8.67361545562744</v>
+        <v>8.67361354827881</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>11.8950004577637</v>
       </c>
       <c r="G1113" t="n">
-        <v>8.41538715362549</v>
+        <v>8.4153881072998</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.58164310455322</v>
+        <v>8.58164405822754</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G1116" t="n">
-        <v>8.81864738464355</v>
+        <v>8.81864643096924</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.99905204772949</v>
+        <v>8.99905109405518</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>12.4849996566772</v>
       </c>
       <c r="G1119" t="n">
-        <v>8.83279514312744</v>
+        <v>8.83279418945312</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>9.11932373046875</v>
+        <v>9.11932277679443</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>13.9449996948242</v>
       </c>
       <c r="G1122" t="n">
-        <v>9.8657054901123</v>
+        <v>9.86570453643799</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>14.2650003433228</v>
       </c>
       <c r="G1126" t="n">
-        <v>10.092098236084</v>
+        <v>10.0920972824097</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.50135612487793</v>
+        <v>9.50135803222656</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>13.4250001907349</v>
       </c>
       <c r="G1129" t="n">
-        <v>9.49781894683838</v>
+        <v>9.49782085418701</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>13.4049997329712</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.48366928100586</v>
+        <v>9.48367023468018</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>13.6049995422363</v>
       </c>
       <c r="G1132" t="n">
-        <v>9.62516498565674</v>
+        <v>9.62516403198242</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>13.4350004196167</v>
       </c>
       <c r="G1133" t="n">
-        <v>9.5048942565918</v>
+        <v>9.50489521026611</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.63224029541016</v>
+        <v>9.63223934173584</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1135" t="n">
-        <v>9.50135612487793</v>
+        <v>9.50135803222656</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.64285182952881</v>
+        <v>9.64285087585449</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>13.2650003433228</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.38462448120117</v>
+        <v>9.38462543487549</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1141" t="n">
-        <v>9.52965545654297</v>
+        <v>9.52965641021729</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.52611923217773</v>
+        <v>9.52612018585205</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1143" t="n">
-        <v>9.78788375854492</v>
+        <v>9.78788471221924</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>13.7449998855591</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.72421073913574</v>
+        <v>9.72421169281006</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G1145" t="n">
-        <v>9.82325839996338</v>
+        <v>9.8232593536377</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>13.7550001144409</v>
       </c>
       <c r="G1146" t="n">
-        <v>9.73128509521484</v>
+        <v>9.73128604888916</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1147" t="n">
-        <v>9.63224029541016</v>
+        <v>9.63223934173584</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>13.3950004577637</v>
       </c>
       <c r="G1148" t="n">
-        <v>9.47659587860107</v>
+        <v>9.47659492492676</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>13.4949998855591</v>
       </c>
       <c r="G1149" t="n">
-        <v>9.54734325408936</v>
+        <v>9.54734420776367</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G1152" t="n">
-        <v>9.77373313903809</v>
+        <v>9.77373218536377</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1159" t="n">
-        <v>9.61455249786377</v>
+        <v>9.61455345153809</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>13.5150003433228</v>
       </c>
       <c r="G1160" t="n">
-        <v>9.56149101257324</v>
+        <v>9.56149387359619</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>9.61455249786377</v>
+        <v>9.61455345153809</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1163" t="n">
-        <v>9.06272506713867</v>
+        <v>9.06272602081299</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1164" t="n">
-        <v>8.95660400390625</v>
+        <v>8.95660305023193</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.15115928649902</v>
+        <v>9.15115833282471</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>12.7049999237061</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.98844051361084</v>
+        <v>8.98843955993652</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>13.2449998855591</v>
       </c>
       <c r="G1171" t="n">
-        <v>9.37047481536865</v>
+        <v>9.37047386169434</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G1174" t="n">
-        <v>9.2749662399292</v>
+        <v>9.27496528625488</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G1175" t="n">
-        <v>9.13347244262695</v>
+        <v>9.13347148895264</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>9.15115928649902</v>
+        <v>9.15115833282471</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1177" t="n">
-        <v>9.29619121551514</v>
+        <v>9.29619026184082</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1178" t="n">
-        <v>9.21836853027344</v>
+        <v>9.21836757659912</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>13.3950004577637</v>
       </c>
       <c r="G1182" t="n">
-        <v>9.47659587860107</v>
+        <v>9.47659492492676</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>9.3669376373291</v>
+        <v>9.36693668365479</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>13.0050001144409</v>
       </c>
       <c r="G1185" t="n">
-        <v>9.20068264007568</v>
+        <v>9.20068168640137</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>9.16884613037109</v>
+        <v>9.16884517669678</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1189" t="n">
-        <v>9.06979942321777</v>
+        <v>9.06979846954346</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G1190" t="n">
-        <v>9.13347244262695</v>
+        <v>9.13347148895264</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.97429180145264</v>
+        <v>8.974289894104</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>9.16177177429199</v>
+        <v>9.16176986694336</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1193" t="n">
-        <v>9.16884613037109</v>
+        <v>9.16884517669678</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>12.8050003051758</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.05918788909912</v>
+        <v>9.0591869354248</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>12.3249998092651</v>
       </c>
       <c r="G1199" t="n">
-        <v>8.71959972381592</v>
+        <v>8.7195987701416</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.33402824401855</v>
+        <v>8.33402729034424</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.29865264892578</v>
+        <v>8.2986536026001</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.23144435882568</v>
+        <v>8.23144340515137</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>12.0050001144409</v>
       </c>
       <c r="G1205" t="n">
-        <v>8.49320983886719</v>
+        <v>8.49320888519287</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>11.9350004196167</v>
       </c>
       <c r="G1206" t="n">
-        <v>8.44368553161621</v>
+        <v>8.44368648529053</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>12.0249996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>8.50735759735107</v>
+        <v>8.50735855102539</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G1208" t="n">
-        <v>8.39416217803955</v>
+        <v>8.39416313171387</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>11.9350004196167</v>
       </c>
       <c r="G1209" t="n">
-        <v>8.44368553161621</v>
+        <v>8.44368648529053</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>12.375</v>
       </c>
       <c r="G1211" t="n">
-        <v>8.75497341156006</v>
+        <v>8.75497436523438</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>12.335000038147</v>
       </c>
       <c r="G1212" t="n">
-        <v>8.72667407989502</v>
+        <v>8.72667598724365</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G1214" t="n">
-        <v>8.85048389434814</v>
+        <v>8.85048198699951</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>8.73728847503662</v>
+        <v>8.7372875213623</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1217" t="n">
-        <v>8.73374938964844</v>
+        <v>8.73374843597412</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1219" t="n">
-        <v>8.58871841430664</v>
+        <v>8.58871746063232</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>8.53211975097656</v>
+        <v>8.53211879730225</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>8.23144435882568</v>
+        <v>8.23144340515137</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1227" t="n">
-        <v>8.03688812255859</v>
+        <v>8.03688907623291</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>11.3950004577637</v>
       </c>
       <c r="G1228" t="n">
-        <v>8.06165027618408</v>
+        <v>8.06165218353271</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>12.0349998474121</v>
       </c>
       <c r="G1231" t="n">
-        <v>8.51443386077881</v>
+        <v>8.51443290710449</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1232" t="n">
-        <v>8.63116645812988</v>
+        <v>8.63116550445557</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>8.73728847503662</v>
+        <v>8.7372875213623</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.52965545654297</v>
+        <v>9.52965641021729</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>13.6350002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>9.64638900756836</v>
+        <v>9.64638996124268</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.0496482849121</v>
+        <v>10.0496492385864</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.0602607727051</v>
+        <v>10.0602617263794</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>14.4949998855591</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.2548160552979</v>
+        <v>10.2548151016235</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.1310081481934</v>
+        <v>10.131007194519</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.1345443725586</v>
+        <v>10.1345453262329</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>14.085000038147</v>
       </c>
       <c r="G1259" t="n">
-        <v>9.96475124359131</v>
+        <v>9.96475219726562</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.1345443725586</v>
+        <v>10.1345453262329</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.1274690628052</v>
+        <v>10.1274700164795</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1277" t="n">
-        <v>10.2442026138306</v>
+        <v>10.2442035675049</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1279" t="n">
-        <v>10.1876058578491</v>
+        <v>10.1876068115234</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>14.5050001144409</v>
       </c>
       <c r="G1282" t="n">
-        <v>10.2618913650513</v>
+        <v>10.261890411377</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G1283" t="n">
-        <v>10.4776697158813</v>
+        <v>10.477668762207</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>14.6549997329712</v>
       </c>
       <c r="G1284" t="n">
-        <v>10.3680114746094</v>
+        <v>10.3680105209351</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>14.4049997329712</v>
       </c>
       <c r="G1286" t="n">
-        <v>10.1911420822144</v>
+        <v>10.1911430358887</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>14.4750003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.240665435791</v>
+        <v>10.2406663894653</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1293" t="n">
-        <v>10.576717376709</v>
+        <v>10.5767154693604</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1294" t="n">
-        <v>10.9092292785645</v>
+        <v>10.9092283248901</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>15.5349998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>10.9905862808228</v>
+        <v>10.9905872344971</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.1922168731689</v>
+        <v>11.1922178268433</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.1073198318481</v>
+        <v>11.1073207855225</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>15.8249998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.1957540512085</v>
+        <v>11.1957550048828</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.9163036346436</v>
+        <v>10.9163026809692</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.0224237442017</v>
+        <v>11.0224227905273</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>15.5649995803833</v>
       </c>
       <c r="G1308" t="n">
-        <v>11.0118112564087</v>
+        <v>11.011812210083</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.1992921829224</v>
+        <v>11.199291229248</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.3407869338989</v>
+        <v>11.3407859802246</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>16.0750007629395</v>
       </c>
       <c r="G1314" t="n">
-        <v>11.3726224899292</v>
+        <v>11.3726234436035</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>16.5</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.6732978820801</v>
+        <v>11.6732988357544</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.6945238113403</v>
+        <v>11.694522857666</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1318" t="n">
-        <v>11.7581968307495</v>
+        <v>11.7581958770752</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>16.8349990844727</v>
       </c>
       <c r="G1321" t="n">
-        <v>11.9103002548218</v>
+        <v>11.9103021621704</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.9492120742798</v>
+        <v>11.9492111206055</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1324" t="n">
-        <v>11.9279899597168</v>
+        <v>11.9279890060425</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.8360166549683</v>
+        <v>11.8360157012939</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1326" t="n">
-        <v>11.8890790939331</v>
+        <v>11.8890771865845</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.9492120742798</v>
+        <v>11.9492111206055</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1329" t="n">
-        <v>11.9032278060913</v>
+        <v>11.9032287597656</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.0694818496704</v>
+        <v>12.0694828033447</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1332" t="n">
-        <v>12.1260814666748</v>
+        <v>12.1260805130005</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1333" t="n">
-        <v>12.0694818496704</v>
+        <v>12.0694828033447</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>17.1350002288818</v>
       </c>
       <c r="G1335" t="n">
-        <v>12.1225442886353</v>
+        <v>12.1225433349609</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.1473064422607</v>
+        <v>12.1473054885864</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G1337" t="n">
-        <v>12.101318359375</v>
+        <v>12.1013193130493</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1339" t="n">
-        <v>12.0765571594238</v>
+        <v>12.0765562057495</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.0871686935425</v>
+        <v>12.0871696472168</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1341" t="n">
-        <v>12.0871686935425</v>
+        <v>12.0871696472168</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1342" t="n">
-        <v>12.0447206497192</v>
+        <v>12.0447216033936</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1346" t="n">
-        <v>11.9173755645752</v>
+        <v>11.9173746109009</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>16.8349990844727</v>
       </c>
       <c r="G1347" t="n">
-        <v>11.9103002548218</v>
+        <v>11.9103021621704</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.9032278060913</v>
+        <v>11.9032287597656</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>16.875</v>
       </c>
       <c r="G1349" t="n">
-        <v>11.9386005401611</v>
+        <v>11.9386014938354</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1350" t="n">
-        <v>11.9032278060913</v>
+        <v>11.9032287597656</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>17</v>
       </c>
       <c r="G1354" t="n">
-        <v>12.0270347595215</v>
+        <v>12.0270357131958</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G1358" t="n">
-        <v>12.288800239563</v>
+        <v>12.2888011932373</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1360" t="n">
-        <v>12.3170986175537</v>
+        <v>12.3170967102051</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1361" t="n">
-        <v>12.3666219711304</v>
+        <v>12.3666229248047</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1362" t="n">
-        <v>12.4090719223022</v>
+        <v>12.4090709686279</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1363" t="n">
-        <v>12.4798173904419</v>
+        <v>12.4798164367676</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G1364" t="n">
-        <v>12.4833555221558</v>
+        <v>12.4833545684814</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G1366" t="n">
-        <v>12.3347864151001</v>
+        <v>12.3347854614258</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G1367" t="n">
-        <v>12.3418607711792</v>
+        <v>12.3418598175049</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1370" t="n">
-        <v>12.5615005493164</v>
+        <v>12.5615015029907</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G1371" t="n">
-        <v>12.4264297485352</v>
+        <v>12.4264307022095</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G1372" t="n">
-        <v>12.5352363586426</v>
+        <v>12.5352373123169</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1373" t="n">
-        <v>12.6402912139893</v>
+        <v>12.6402921676636</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>12.7190828323364</v>
+        <v>12.7190837860107</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1377" t="n">
-        <v>12.8203840255737</v>
+        <v>12.820384979248</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1378" t="n">
-        <v>12.8203840255737</v>
+        <v>12.820384979248</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>17.2250003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>12.9254379272461</v>
+        <v>12.9254388809204</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.125</v>
       </c>
       <c r="G1382" t="n">
-        <v>12.8504018783569</v>
+        <v>12.8504009246826</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>12.8616571426392</v>
+        <v>12.8616561889648</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.8804168701172</v>
+        <v>12.8804159164429</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1387" t="n">
-        <v>12.936695098877</v>
+        <v>12.9366960525513</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>12.6740589141846</v>
+        <v>12.6740579605103</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>16.9349994659424</v>
       </c>
       <c r="G1389" t="n">
-        <v>12.7078266143799</v>
+        <v>12.7078256607056</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>16.6550006866455</v>
       </c>
       <c r="G1391" t="n">
-        <v>12.4977188110352</v>
+        <v>12.4977178573608</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>17.0149993896484</v>
       </c>
       <c r="G1393" t="n">
-        <v>12.7678575515747</v>
+        <v>12.7678565979004</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G1395" t="n">
-        <v>12.6140270233154</v>
+        <v>12.6140279769897</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G1396" t="n">
-        <v>12.6853160858154</v>
+        <v>12.6853170394897</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>17</v>
       </c>
       <c r="G1398" t="n">
-        <v>12.7566022872925</v>
+        <v>12.7566032409668</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>16.9349994659424</v>
       </c>
       <c r="G1401" t="n">
-        <v>12.7078266143799</v>
+        <v>12.7078256607056</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G1402" t="n">
-        <v>12.433934211731</v>
+        <v>12.4339361190796</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.0049991607666</v>
       </c>
       <c r="G1404" t="n">
-        <v>12.7603530883789</v>
+        <v>12.7603540420532</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1405" t="n">
-        <v>12.7641077041626</v>
+        <v>12.7641067504883</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G1408" t="n">
-        <v>12.5577507019043</v>
+        <v>12.5577487945557</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>16.2250003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>12.1750507354736</v>
+        <v>12.1750516891479</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>12.5577507019043</v>
+        <v>12.5577487945557</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1414" t="n">
-        <v>12.6402912139893</v>
+        <v>12.6402921676636</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1415" t="n">
-        <v>12.5727567672729</v>
+        <v>12.5727577209473</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>12.6440448760986</v>
+        <v>12.6440439224243</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1419" t="n">
-        <v>12.6440448760986</v>
+        <v>12.6440439224243</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>16.625</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.4752073287964</v>
+        <v>12.4752063751221</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G1426" t="n">
-        <v>12.902928352356</v>
+        <v>12.9029273986816</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.992974281311</v>
+        <v>12.9929752349854</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.9629592895508</v>
+        <v>12.9629602432251</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.8091287612915</v>
+        <v>12.8091297149658</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>17.1550006866455</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.8729114532471</v>
+        <v>12.8729124069214</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>17.125</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.8504018783569</v>
+        <v>12.8504009246826</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1440" t="n">
-        <v>12.95920753479</v>
+        <v>12.9592065811157</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.9967260360718</v>
+        <v>12.9967269897461</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>17.5349998474121</v>
       </c>
       <c r="G1444" t="n">
-        <v>13.1580600738525</v>
+        <v>13.1580591201782</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>17.5349998474121</v>
       </c>
       <c r="G1445" t="n">
-        <v>13.1580600738525</v>
+        <v>13.1580591201782</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1446" t="n">
-        <v>13.2518587112427</v>
+        <v>13.2518577575684</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1450" t="n">
-        <v>13.2068347930908</v>
+        <v>13.2068357467651</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1452" t="n">
-        <v>13.4094390869141</v>
+        <v>13.4094400405884</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>17.6849994659424</v>
       </c>
       <c r="G1453" t="n">
-        <v>13.2706174850464</v>
+        <v>13.2706184387207</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>13.094277381897</v>
+        <v>13.0942783355713</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>13.491982460022</v>
+        <v>13.4919834136963</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>18.625</v>
       </c>
       <c r="G1459" t="n">
-        <v>13.9759826660156</v>
+        <v>13.9759836196899</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>18.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>13.6945867538452</v>
+        <v>13.6945886611938</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1462" t="n">
-        <v>13.7996416091919</v>
+        <v>13.7996406555176</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G1463" t="n">
-        <v>13.8146486282349</v>
+        <v>13.8146505355835</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>18.375</v>
       </c>
       <c r="G1464" t="n">
-        <v>13.7883853912354</v>
+        <v>13.7883863449097</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>18.7450008392334</v>
       </c>
       <c r="G1465" t="n">
-        <v>14.066029548645</v>
+        <v>14.0660285949707</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>18.5849990844727</v>
       </c>
       <c r="G1466" t="n">
-        <v>13.9459686279297</v>
+        <v>13.9459676742554</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1467" t="n">
-        <v>14.0772857666016</v>
+        <v>14.0772867202759</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1468" t="n">
-        <v>14.1035490036011</v>
+        <v>14.1035499572754</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1470" t="n">
-        <v>14.2498750686646</v>
+        <v>14.2498760223389</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>14.0510215759277</v>
+        <v>14.0510234832764</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1473" t="n">
-        <v>14.0997972488403</v>
+        <v>14.0997982025146</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1476" t="n">
-        <v>14.3382549285889</v>
+        <v>14.3382539749146</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>14.288257598877</v>
+        <v>14.2882585525513</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1480" t="n">
-        <v>14.4767150878906</v>
+        <v>14.4767141342163</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>18.7549991607666</v>
       </c>
       <c r="G1481" t="n">
-        <v>14.4267148971558</v>
+        <v>14.4267158508301</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1483" t="n">
-        <v>14.4997940063477</v>
+        <v>14.4997930526733</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1486" t="n">
-        <v>14.6728658676147</v>
+        <v>14.6728668212891</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G1489" t="n">
-        <v>14.5959453582764</v>
+        <v>14.5959434509277</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1491" t="n">
-        <v>14.6305599212646</v>
+        <v>14.6305589675903</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>14.799786567688</v>
+        <v>14.7997846603394</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1495" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1496" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>18.2849998474121</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.0651826858521</v>
+        <v>14.0651836395264</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.1305675506592</v>
+        <v>14.1305665969849</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1503" t="n">
-        <v>13.5844202041626</v>
+        <v>13.5844192504883</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>13.6921110153198</v>
+        <v>13.6921100616455</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.6382656097412</v>
+        <v>13.6382646560669</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.3151807785034</v>
+        <v>14.3151817321777</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.2267208099365</v>
+        <v>14.2267198562622</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>18.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.2305641174316</v>
+        <v>14.2305660247803</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>18.5</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.2305641174316</v>
+        <v>14.2305660247803</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.3382549285889</v>
+        <v>14.3382539749146</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.2267208099365</v>
+        <v>14.2267198562622</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.1305675506592</v>
+        <v>14.1305665969849</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G1520" t="n">
-        <v>14.0536441802979</v>
+        <v>14.0536451339722</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.1459503173828</v>
+        <v>14.1459493637085</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.2690258026123</v>
+        <v>14.269024848938</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>18.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.422869682312</v>
+        <v>14.4228687286377</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.4767150878906</v>
+        <v>14.4767141342163</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.6190195083618</v>
+        <v>14.6190204620361</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1529" t="n">
-        <v>14.5344066619873</v>
+        <v>14.5344047546387</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>18.4650001525879</v>
       </c>
       <c r="G1530" t="n">
-        <v>14.2036418914795</v>
+        <v>14.2036428451538</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.2844104766846</v>
+        <v>14.2844095230103</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1532" t="n">
-        <v>14.1997966766357</v>
+        <v>14.1997957229614</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.2997951507568</v>
+        <v>14.2997932434082</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G1535" t="n">
-        <v>14.4036388397217</v>
+        <v>14.4036407470703</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.2921018600464</v>
+        <v>14.2921028137207</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>18.8549995422363</v>
       </c>
       <c r="G1538" t="n">
-        <v>14.5036382675171</v>
+        <v>14.5036363601685</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.3997917175293</v>
+        <v>14.3997926712036</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G1541" t="n">
-        <v>14.0536441802979</v>
+        <v>14.0536451339722</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>13.6921110153198</v>
+        <v>13.6921100616455</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1545" t="n">
-        <v>14.0613374710083</v>
+        <v>14.061336517334</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>18.2649993896484</v>
       </c>
       <c r="G1546" t="n">
-        <v>14.0497980117798</v>
+        <v>14.0497989654541</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.2921018600464</v>
+        <v>14.2921028137207</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1549" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G1550" t="n">
-        <v>14.3574886322021</v>
+        <v>14.3574876785278</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>18.3449993133545</v>
       </c>
       <c r="G1553" t="n">
-        <v>14.1113357543945</v>
+        <v>14.1113367080688</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>14.3459463119507</v>
+        <v>14.3459482192993</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1556" t="n">
-        <v>14.3228740692139</v>
+        <v>14.3228731155396</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1557" t="n">
-        <v>14.1190280914307</v>
+        <v>14.119029045105</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>18.9549999237061</v>
       </c>
       <c r="G1559" t="n">
-        <v>14.5805606842041</v>
+        <v>14.5805616378784</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1560" t="n">
-        <v>14.3151807785034</v>
+        <v>14.3151817321777</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1561" t="n">
-        <v>14.2613353729248</v>
+        <v>14.2613363265991</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.1190280914307</v>
+        <v>14.119029045105</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1563" t="n">
-        <v>13.9382629394531</v>
+        <v>13.9382619857788</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G1566" t="n">
-        <v>13.7613401412964</v>
+        <v>13.7613410949707</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.6382656097412</v>
+        <v>13.6382646560669</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>17.3349990844727</v>
       </c>
       <c r="G1568" t="n">
-        <v>13.3344230651855</v>
+        <v>13.3344240188599</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>17.2250003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.2498083114624</v>
+        <v>13.2498092651367</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>13.1921186447144</v>
+        <v>13.19211769104</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>15.8649997711182</v>
       </c>
       <c r="G1572" t="n">
-        <v>12.2036714553833</v>
+        <v>12.203670501709</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>12.4421281814575</v>
+        <v>12.4421291351318</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1576" t="n">
-        <v>13.2075042724609</v>
+        <v>13.2075023651123</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.288257598877</v>
+        <v>14.2882585525513</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.3151807785034</v>
+        <v>14.3151817321777</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.442099571228</v>
+        <v>14.4421014785767</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>18.7350006103516</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.4113340377808</v>
+        <v>14.4113321304321</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1583" t="n">
-        <v>14.4767150878906</v>
+        <v>14.4767141342163</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.976692199707</v>
+        <v>15.9766931533813</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.6151609420776</v>
+        <v>15.6151599884033</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1594" t="n">
-        <v>15.369010925293</v>
+        <v>15.3690099716187</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.9536323547363</v>
+        <v>14.953631401062</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>19.1849994659424</v>
       </c>
       <c r="G1599" t="n">
-        <v>14.7574806213379</v>
+        <v>14.7574796676636</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1600" t="n">
-        <v>14.8190174102783</v>
+        <v>14.8190183639526</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>18.75</v>
       </c>
       <c r="G1601" t="n">
-        <v>14.422869682312</v>
+        <v>14.4228687286377</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42047,7 +42047,7 @@
         <v>18.6700000762939</v>
       </c>
       <c r="G1603" t="n">
-        <v>14.3613309860229</v>
+        <v>14.3613319396973</v>
       </c>
       <c r="H1603" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.9382629394531</v>
+        <v>13.9382619857788</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>18.1049995422363</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.9267225265503</v>
+        <v>13.9267234802246</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>18</v>
       </c>
       <c r="G1608" t="n">
-        <v>13.8459548950195</v>
+        <v>13.8459558486938</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8074932098389</v>
+        <v>13.8074941635132</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>14.0805673599243</v>
+        <v>14.0805683135986</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.9998006820679</v>
+        <v>13.9997987747192</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.8382625579834</v>
+        <v>13.8382616043091</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G1614" t="n">
-        <v>13.6421127319336</v>
+        <v>13.6421117782593</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.4151916503906</v>
+        <v>13.4151926040649</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G1616" t="n">
-        <v>13.6228818893433</v>
+        <v>13.6228809356689</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1617" t="n">
-        <v>13.6613416671753</v>
+        <v>13.6613435745239</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G1619" t="n">
-        <v>13.6421127319336</v>
+        <v>13.6421117782593</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>18</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8459548950195</v>
+        <v>13.8459558486938</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>17.9950008392334</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.8421106338501</v>
+        <v>13.8421096801758</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1625" t="n">
-        <v>14.2551221847534</v>
+        <v>14.2551212310791</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>14.1283559799194</v>
+        <v>14.1283569335938</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>17.3549995422363</v>
       </c>
       <c r="G1627" t="n">
-        <v>14.1937837600708</v>
+        <v>14.1937847137451</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>17.4249992370605</v>
       </c>
       <c r="G1628" t="n">
-        <v>14.251033782959</v>
+        <v>14.2510328292847</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1631" t="n">
-        <v>13.8625555038452</v>
+        <v>13.8625564575195</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G1634" t="n">
-        <v>13.6703596115112</v>
+        <v>13.6703605651855</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>16.9349994659424</v>
       </c>
       <c r="G1635" t="n">
-        <v>13.8502864837646</v>
+        <v>13.8502855300903</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>15.4949998855591</v>
       </c>
       <c r="G1640" t="n">
-        <v>12.6725826263428</v>
+        <v>12.6725835800171</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>15.6750001907349</v>
       </c>
       <c r="G1643" t="n">
-        <v>12.8197975158691</v>
+        <v>12.8197965621948</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>15.6850004196167</v>
       </c>
       <c r="G1646" t="n">
-        <v>12.8279752731323</v>
+        <v>12.827974319458</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G1647" t="n">
-        <v>12.6930303573608</v>
+        <v>12.6930294036865</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>15.5349998474121</v>
       </c>
       <c r="G1650" t="n">
-        <v>12.7052965164185</v>
+        <v>12.7052974700928</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1651" t="n">
-        <v>12.8565998077393</v>
+        <v>12.8565988540649</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1652" t="n">
-        <v>12.7257442474365</v>
+        <v>12.7257452011108</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G1659" t="n">
-        <v>12.570351600647</v>
+        <v>12.5703525543213</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1660" t="n">
-        <v>12.4067821502686</v>
+        <v>12.4067831039429</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>15.2150001525879</v>
       </c>
       <c r="G1661" t="n">
-        <v>12.443585395813</v>
+        <v>12.4435863494873</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G1662" t="n">
-        <v>12.2350339889526</v>
+        <v>12.2350330352783</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1668" t="n">
-        <v>11.6461811065674</v>
+        <v>11.6461820602417</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1671" t="n">
-        <v>11.6625394821167</v>
+        <v>11.6625385284424</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1673" t="n">
-        <v>11.8097505569458</v>
+        <v>11.8097515106201</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1678" t="n">
-        <v>12.1041774749756</v>
+        <v>12.1041784286499</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>15.4849996566772</v>
       </c>
       <c r="G1684" t="n">
-        <v>12.6644048690796</v>
+        <v>12.6644039154053</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>14.8699998855591</v>
       </c>
       <c r="G1691" t="n">
-        <v>12.1614274978638</v>
+        <v>12.1614284515381</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G1694" t="n">
-        <v>11.9774112701416</v>
+        <v>11.9774122238159</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.1205348968506</v>
+        <v>12.1205339431763</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G1702" t="n">
-        <v>12.0060358047485</v>
+        <v>12.0060367584229</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1703" t="n">
-        <v>12.2268562316895</v>
+        <v>12.2268552780151</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1704" t="n">
-        <v>12.6112451553345</v>
+        <v>12.6112442016602</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G1705" t="n">
-        <v>12.4190502166748</v>
+        <v>12.4190492630005</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G1709" t="n">
-        <v>12.4067821502686</v>
+        <v>12.4067831039429</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1712" t="n">
-        <v>12.1041774749756</v>
+        <v>12.1041784286499</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1716" t="n">
-        <v>11.5071477890015</v>
+        <v>11.5071468353271</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>14</v>
       </c>
       <c r="G1724" t="n">
-        <v>11.449896812439</v>
+        <v>11.4498977661133</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>13.8050003051758</v>
       </c>
       <c r="G1726" t="n">
-        <v>11.2904186248779</v>
+        <v>11.2904176712036</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>14.4750003814697</v>
       </c>
       <c r="G1730" t="n">
-        <v>11.8383760452271</v>
+        <v>11.8383769989014</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G1733" t="n">
-        <v>11.8138408660889</v>
+        <v>11.8138418197632</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G1735" t="n">
-        <v>12.1491594314575</v>
+        <v>12.1491584777832</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G1736" t="n">
-        <v>12.169605255127</v>
+        <v>12.1696062088013</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G1740" t="n">
-        <v>12.5417261123657</v>
+        <v>12.54172706604</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>15.6850004196167</v>
       </c>
       <c r="G1743" t="n">
-        <v>12.8279752731323</v>
+        <v>12.827974319458</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1757" t="n">
-        <v>13.8625555038452</v>
+        <v>13.8625564575195</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>17.125</v>
       </c>
       <c r="G1762" t="n">
-        <v>14.0056800842285</v>
+        <v>14.0056791305542</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1766" t="n">
-        <v>14.1651592254639</v>
+        <v>14.1651601791382</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1767" t="n">
-        <v>14.0670166015625</v>
+        <v>14.0670175552368</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1771" t="n">
-        <v>14.2142295837402</v>
+        <v>14.2142305374146</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1778" t="n">
-        <v>13.7398777008057</v>
+        <v>13.7398767471313</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1779" t="n">
-        <v>13.7030735015869</v>
+        <v>13.7030744552612</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1785" t="n">
-        <v>14.1242666244507</v>
+        <v>14.1242656707764</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1786" t="n">
-        <v>14.1283559799194</v>
+        <v>14.1283569335938</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G1789" t="n">
-        <v>14.17333984375</v>
+        <v>14.1733388900757</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>17.3549995422363</v>
       </c>
       <c r="G1792" t="n">
-        <v>14.1937837600708</v>
+        <v>14.1937847137451</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>17.4249992370605</v>
       </c>
       <c r="G1793" t="n">
-        <v>14.251033782959</v>
+        <v>14.2510328292847</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1794" t="n">
-        <v>14.3205499649048</v>
+        <v>14.3205509185791</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G1796" t="n">
-        <v>14.2060527801514</v>
+        <v>14.2060518264771</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47091,7 +47091,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1797" t="n">
-        <v>14.5250129699707</v>
+        <v>14.525013923645</v>
       </c>
       <c r="H1797" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G1799" t="n">
-        <v>14.6517810821533</v>
+        <v>14.651780128479</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47169,7 +47169,7 @@
         <v>17.8649997711182</v>
       </c>
       <c r="G1800" t="n">
-        <v>14.6108875274658</v>
+        <v>14.6108865737915</v>
       </c>
       <c r="H1800" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>14.6395120620728</v>
+        <v>14.6395111083984</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>18.1849994659424</v>
       </c>
       <c r="G1805" t="n">
-        <v>14.8725996017456</v>
+        <v>14.8725986480713</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1806" t="n">
-        <v>14.8439750671387</v>
+        <v>14.8439741134644</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G1808" t="n">
-        <v>14.8112602233887</v>
+        <v>14.811261177063</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>18.1049995422363</v>
       </c>
       <c r="G1809" t="n">
-        <v>14.8071708679199</v>
+        <v>14.8071718215942</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1811" t="n">
-        <v>14.9012241363525</v>
+        <v>14.9012231826782</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>18.2450008392334</v>
       </c>
       <c r="G1812" t="n">
-        <v>14.9216718673706</v>
+        <v>14.9216709136963</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>18.2649993896484</v>
       </c>
       <c r="G1813" t="n">
-        <v>14.938027381897</v>
+        <v>14.9380283355713</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>18.25</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.9257583618164</v>
+        <v>14.9257593154907</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1816" t="n">
-        <v>14.9707412719727</v>
+        <v>14.970742225647</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47611,7 +47611,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1817" t="n">
-        <v>14.9830093383789</v>
+        <v>14.9830102920532</v>
       </c>
       <c r="H1817" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>14.8439750671387</v>
+        <v>14.8439741134644</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47767,7 +47767,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1823" t="n">
-        <v>14.9993658065796</v>
+        <v>14.9993667602539</v>
       </c>
       <c r="H1823" t="s">
         <v>8</v>
@@ -47819,7 +47819,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G1825" t="n">
-        <v>15.1547594070435</v>
+        <v>15.1547584533691</v>
       </c>
       <c r="H1825" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>18.5249996185303</v>
       </c>
       <c r="G1826" t="n">
-        <v>15.1506671905518</v>
+        <v>15.1506681442261</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1827" t="n">
-        <v>15.2120065689087</v>
+        <v>15.212007522583</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1829" t="n">
-        <v>15.3469524383545</v>
+        <v>15.3469505310059</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>18.4449996948242</v>
       </c>
       <c r="G1834" t="n">
-        <v>15.0852394104004</v>
+        <v>15.0852403640747</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>18.1849994659424</v>
       </c>
       <c r="G1839" t="n">
-        <v>14.8725996017456</v>
+        <v>14.8725986480713</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1841" t="n">
-        <v>14.7540130615234</v>
+        <v>14.7540121078491</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G1842" t="n">
-        <v>14.4677639007568</v>
+        <v>14.4677648544312</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1845" t="n">
-        <v>14.7867259979248</v>
+        <v>14.7867250442505</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G1849" t="n">
-        <v>14.958475112915</v>
+        <v>14.9584741592407</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G1850" t="n">
-        <v>15.0566148757935</v>
+        <v>15.0566158294678</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1851" t="n">
-        <v>15.1711149215698</v>
+        <v>15.1711139678955</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>18.9300003051758</v>
       </c>
       <c r="G1855" t="n">
-        <v>15.4819002151489</v>
+        <v>15.4818983078003</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1857" t="n">
-        <v>15.453272819519</v>
+        <v>15.4532709121704</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G1859" t="n">
-        <v>15.612753868103</v>
+        <v>15.6127519607544</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48729,7 +48729,7 @@
         <v>19.0949993133545</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.6168432235718</v>
+        <v>15.6168413162231</v>
       </c>
       <c r="H1860" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1862" t="n">
-        <v>15.5309686660767</v>
+        <v>15.530969619751</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>18.8850002288818</v>
       </c>
       <c r="G1863" t="n">
-        <v>15.4450931549072</v>
+        <v>15.4450950622559</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1866" t="n">
-        <v>15.1956491470337</v>
+        <v>15.1956510543823</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1870" t="n">
-        <v>15.5309686660767</v>
+        <v>15.530969619751</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1874" t="n">
-        <v>15.3101472854614</v>
+        <v>15.3101491928101</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>18.8649997711182</v>
       </c>
       <c r="G1875" t="n">
-        <v>15.4287366867065</v>
+        <v>15.4287385940552</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>18.7700004577637</v>
       </c>
       <c r="G1876" t="n">
-        <v>15.3510427474976</v>
+        <v>15.3510408401489</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>42.439998626709</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>1221416</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>42.9599990844727</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>42.439998626709</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>42.439998626709</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>42.9300003051758</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>42.9300003051758</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>8.82273292541504</v>
+        <v>8.82273197174072</v>
       </c>
       <c r="H2" t="n">
         <v>8813463</v>
@@ -456,7 +456,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G3" t="n">
-        <v>8.91531753540039</v>
+        <v>8.91531658172607</v>
       </c>
       <c r="H3" t="n">
         <v>6212233</v>
@@ -485,7 +485,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G4" t="n">
-        <v>8.74648666381836</v>
+        <v>8.74648571014404</v>
       </c>
       <c r="H4" t="n">
         <v>7523791</v>
@@ -514,7 +514,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>8.730149269104</v>
+        <v>8.73015022277832</v>
       </c>
       <c r="H5" t="n">
         <v>9816902</v>
@@ -543,7 +543,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G6" t="n">
-        <v>8.63756275177002</v>
+        <v>8.63756561279297</v>
       </c>
       <c r="H6" t="n">
         <v>7668785</v>
@@ -572,7 +572,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>8.39248847961426</v>
+        <v>8.39248752593994</v>
       </c>
       <c r="H7" t="n">
         <v>10432648</v>
@@ -601,7 +601,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G8" t="n">
-        <v>8.51230335235596</v>
+        <v>8.51230239868164</v>
       </c>
       <c r="H8" t="n">
         <v>6548268</v>
@@ -630,7 +630,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G9" t="n">
-        <v>8.68113231658936</v>
+        <v>8.68113422393799</v>
       </c>
       <c r="H9" t="n">
         <v>6266552</v>
@@ -659,7 +659,7 @@
         <v>15.75</v>
       </c>
       <c r="G10" t="n">
-        <v>8.57765769958496</v>
+        <v>8.57765579223633</v>
       </c>
       <c r="H10" t="n">
         <v>6568025</v>
@@ -833,7 +833,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>8.12562942504883</v>
+        <v>8.1256275177002</v>
       </c>
       <c r="H16" t="n">
         <v>8398594</v>
@@ -862,7 +862,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G17" t="n">
-        <v>7.95679712295532</v>
+        <v>7.95679759979248</v>
       </c>
       <c r="H17" t="n">
         <v>6645329</v>
@@ -949,7 +949,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G20" t="n">
-        <v>7.29237031936646</v>
+        <v>7.29237079620361</v>
       </c>
       <c r="H20" t="n">
         <v>12172727</v>
@@ -978,7 +978,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G21" t="n">
-        <v>7.51021575927734</v>
+        <v>7.51021432876587</v>
       </c>
       <c r="H21" t="n">
         <v>9216215</v>
@@ -1007,7 +1007,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G22" t="n">
-        <v>7.37950801849365</v>
+        <v>7.37950849533081</v>
       </c>
       <c r="H22" t="n">
         <v>8015606</v>
@@ -1065,7 +1065,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G24" t="n">
-        <v>6.92747926712036</v>
+        <v>6.92747831344604</v>
       </c>
       <c r="H24" t="n">
         <v>12420806</v>
@@ -1094,7 +1094,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G25" t="n">
-        <v>6.85123252868652</v>
+        <v>6.85123205184937</v>
       </c>
       <c r="H25" t="n">
         <v>15546483</v>
@@ -1123,7 +1123,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G26" t="n">
-        <v>6.66606426239014</v>
+        <v>6.66606378555298</v>
       </c>
       <c r="H26" t="n">
         <v>12839676</v>
@@ -1152,7 +1152,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>6.45911121368408</v>
+        <v>6.45911073684692</v>
       </c>
       <c r="H27" t="n">
         <v>12818374</v>
@@ -1181,7 +1181,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>6.19769668579102</v>
+        <v>6.19769763946533</v>
       </c>
       <c r="H28" t="n">
         <v>14776781</v>
@@ -1210,7 +1210,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G29" t="n">
-        <v>6.52446460723877</v>
+        <v>6.52446413040161</v>
       </c>
       <c r="H29" t="n">
         <v>12955601</v>
@@ -1239,7 +1239,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G30" t="n">
-        <v>5.96895933151245</v>
+        <v>5.96895980834961</v>
       </c>
       <c r="H30" t="n">
         <v>15791674</v>
@@ -1297,7 +1297,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G32" t="n">
-        <v>6.31751251220703</v>
+        <v>6.31751203536987</v>
       </c>
       <c r="H32" t="n">
         <v>12494703</v>
@@ -1384,7 +1384,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G35" t="n">
-        <v>6.44277381896973</v>
+        <v>6.44277286529541</v>
       </c>
       <c r="H35" t="n">
         <v>9100095</v>
@@ -1413,7 +1413,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G36" t="n">
-        <v>6.37741947174072</v>
+        <v>6.37741899490356</v>
       </c>
       <c r="H36" t="n">
         <v>9185136</v>
@@ -1442,7 +1442,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G37" t="n">
-        <v>6.6061577796936</v>
+        <v>6.60615730285645</v>
       </c>
       <c r="H37" t="n">
         <v>7480049</v>
@@ -1471,7 +1471,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G38" t="n">
-        <v>6.60071039199829</v>
+        <v>6.60070943832397</v>
       </c>
       <c r="H38" t="n">
         <v>8394663</v>
@@ -1500,7 +1500,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G39" t="n">
-        <v>6.52446460723877</v>
+        <v>6.52446413040161</v>
       </c>
       <c r="H39" t="n">
         <v>8686744</v>
@@ -1529,7 +1529,7 @@
         <v>12.2299995422363</v>
       </c>
       <c r="G40" t="n">
-        <v>6.6606183052063</v>
+        <v>6.66061735153198</v>
       </c>
       <c r="H40" t="n">
         <v>7475822</v>
@@ -1558,7 +1558,7 @@
         <v>12.7700004577637</v>
       </c>
       <c r="G41" t="n">
-        <v>6.95471000671387</v>
+        <v>6.95471048355103</v>
       </c>
       <c r="H41" t="n">
         <v>10059185</v>
@@ -1616,7 +1616,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G43" t="n">
-        <v>7.03095579147339</v>
+        <v>7.03095483779907</v>
       </c>
       <c r="H43" t="n">
         <v>9057402</v>
@@ -1645,7 +1645,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G44" t="n">
-        <v>7.1398777961731</v>
+        <v>7.13987684249878</v>
       </c>
       <c r="H44" t="n">
         <v>9000959</v>
@@ -1674,7 +1674,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>7.1344313621521</v>
+        <v>7.13443231582642</v>
       </c>
       <c r="H45" t="n">
         <v>6775484</v>
@@ -1732,7 +1732,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G47" t="n">
-        <v>6.93837070465088</v>
+        <v>6.93837213516235</v>
       </c>
       <c r="H47" t="n">
         <v>6529467</v>
@@ -1790,7 +1790,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G49" t="n">
-        <v>7.06907796859741</v>
+        <v>7.06907844543457</v>
       </c>
       <c r="H49" t="n">
         <v>5929215</v>
@@ -1819,7 +1819,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G50" t="n">
-        <v>7.05818653106689</v>
+        <v>7.05818557739258</v>
       </c>
       <c r="H50" t="n">
         <v>13767476</v>
@@ -1848,7 +1848,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G51" t="n">
-        <v>7.57012176513672</v>
+        <v>7.57012224197388</v>
       </c>
       <c r="H51" t="n">
         <v>13648282</v>
@@ -1877,7 +1877,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G52" t="n">
-        <v>7.50477027893066</v>
+        <v>7.50476884841919</v>
       </c>
       <c r="H52" t="n">
         <v>9174548</v>
@@ -1906,7 +1906,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>7.4611988067627</v>
+        <v>7.46119976043701</v>
       </c>
       <c r="H53" t="n">
         <v>6342213</v>
@@ -1935,7 +1935,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>7.54289245605469</v>
+        <v>7.54289150238037</v>
       </c>
       <c r="H54" t="n">
         <v>5967449</v>
@@ -1993,7 +1993,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>7.43396759033203</v>
+        <v>7.43396902084351</v>
       </c>
       <c r="H56" t="n">
         <v>15946828</v>
@@ -2022,7 +2022,7 @@
         <v>13.4899997711182</v>
       </c>
       <c r="G57" t="n">
-        <v>7.34683036804199</v>
+        <v>7.34682989120483</v>
       </c>
       <c r="H57" t="n">
         <v>7813827</v>
@@ -2051,7 +2051,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>7.25424766540527</v>
+        <v>7.25424671173096</v>
       </c>
       <c r="H58" t="n">
         <v>10450774</v>
@@ -2080,7 +2080,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>7.21067762374878</v>
+        <v>7.21067714691162</v>
       </c>
       <c r="H59" t="n">
         <v>7927596</v>
@@ -2109,7 +2109,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>7.05273962020874</v>
+        <v>7.05274057388306</v>
       </c>
       <c r="H60" t="n">
         <v>9447130</v>
@@ -2225,7 +2225,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G64" t="n">
-        <v>6.99283218383789</v>
+        <v>6.99283266067505</v>
       </c>
       <c r="H64" t="n">
         <v>7948810</v>
@@ -2283,7 +2283,7 @@
         <v>12.2799997329712</v>
       </c>
       <c r="G66" t="n">
-        <v>6.68784999847412</v>
+        <v>6.68784856796265</v>
       </c>
       <c r="H66" t="n">
         <v>13227644</v>
@@ -2341,7 +2341,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G68" t="n">
-        <v>6.56258869171143</v>
+        <v>6.56258821487427</v>
       </c>
       <c r="H68" t="n">
         <v>7305143</v>
@@ -2370,7 +2370,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G69" t="n">
-        <v>6.75320196151733</v>
+        <v>6.75320386886597</v>
       </c>
       <c r="H69" t="n">
         <v>8497825</v>
@@ -2399,7 +2399,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>6.83489418029785</v>
+        <v>6.83489513397217</v>
       </c>
       <c r="H70" t="n">
         <v>7972522</v>
@@ -2428,7 +2428,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G71" t="n">
-        <v>6.85667991638184</v>
+        <v>6.85667848587036</v>
       </c>
       <c r="H71" t="n">
         <v>9344188</v>
@@ -2457,7 +2457,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G72" t="n">
-        <v>7.11809301376343</v>
+        <v>7.11809349060059</v>
       </c>
       <c r="H72" t="n">
         <v>10923567</v>
@@ -2486,7 +2486,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>7.25424766540527</v>
+        <v>7.25424671173096</v>
       </c>
       <c r="H73" t="n">
         <v>9306936</v>
@@ -2515,7 +2515,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>7.17799949645996</v>
+        <v>7.17800045013428</v>
       </c>
       <c r="H74" t="n">
         <v>6180792</v>
@@ -2544,7 +2544,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>7.16166257858276</v>
+        <v>7.16166305541992</v>
       </c>
       <c r="H75" t="n">
         <v>6869865</v>
@@ -2573,7 +2573,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G76" t="n">
-        <v>7.22701692581177</v>
+        <v>7.22701597213745</v>
       </c>
       <c r="H76" t="n">
         <v>5646337</v>
@@ -2602,7 +2602,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>7.27603149414062</v>
+        <v>7.27603101730347</v>
       </c>
       <c r="H77" t="n">
         <v>6262916</v>
@@ -2631,7 +2631,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G78" t="n">
-        <v>7.42307758331299</v>
+        <v>7.42307662963867</v>
       </c>
       <c r="H78" t="n">
         <v>8319839</v>
@@ -2660,7 +2660,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G79" t="n">
-        <v>7.49932384490967</v>
+        <v>7.49932432174683</v>
       </c>
       <c r="H79" t="n">
         <v>8629525</v>
@@ -2718,7 +2718,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G81" t="n">
-        <v>7.5211067199707</v>
+        <v>7.52110767364502</v>
       </c>
       <c r="H81" t="n">
         <v>6830433</v>
@@ -2776,7 +2776,7 @@
         <v>13.6700000762939</v>
       </c>
       <c r="G83" t="n">
-        <v>7.44486141204834</v>
+        <v>7.44485998153687</v>
       </c>
       <c r="H83" t="n">
         <v>8840725</v>
@@ -2805,7 +2805,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G84" t="n">
-        <v>7.25424766540527</v>
+        <v>7.25424671173096</v>
       </c>
       <c r="H84" t="n">
         <v>9311590</v>
@@ -2921,7 +2921,7 @@
         <v>13</v>
       </c>
       <c r="G88" t="n">
-        <v>7.07997035980225</v>
+        <v>7.0799708366394</v>
       </c>
       <c r="H88" t="n">
         <v>5160867</v>
@@ -2950,7 +2950,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>7.04184818267822</v>
+        <v>7.04184770584106</v>
       </c>
       <c r="H89" t="n">
         <v>7651592</v>
@@ -2979,7 +2979,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G90" t="n">
-        <v>7.04184818267822</v>
+        <v>7.04184770584106</v>
       </c>
       <c r="H90" t="n">
         <v>5919376</v>
@@ -3037,7 +3037,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G92" t="n">
-        <v>7.1398777961731</v>
+        <v>7.13987684249878</v>
       </c>
       <c r="H92" t="n">
         <v>8029065</v>
@@ -3066,7 +3066,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G93" t="n">
-        <v>6.85667991638184</v>
+        <v>6.85667848587036</v>
       </c>
       <c r="H93" t="n">
         <v>19974264</v>
@@ -3095,7 +3095,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>6.78043270111084</v>
+        <v>6.78043222427368</v>
       </c>
       <c r="H94" t="n">
         <v>10320486</v>
@@ -3124,7 +3124,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G95" t="n">
-        <v>6.86212539672852</v>
+        <v>6.86212491989136</v>
       </c>
       <c r="H95" t="n">
         <v>4350981</v>
@@ -3153,7 +3153,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75864744186401</v>
+        <v>6.75864839553833</v>
       </c>
       <c r="H96" t="n">
         <v>9350204</v>
@@ -3211,7 +3211,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>6.81310987472534</v>
+        <v>6.81311082839966</v>
       </c>
       <c r="H98" t="n">
         <v>8273143</v>
@@ -3269,7 +3269,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>7.00730991363525</v>
+        <v>7.00731039047241</v>
       </c>
       <c r="H100" t="n">
         <v>7591339</v>
@@ -3298,7 +3298,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>7.4113564491272</v>
+        <v>7.41135549545288</v>
       </c>
       <c r="H101" t="n">
         <v>9433124</v>
@@ -3327,7 +3327,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G102" t="n">
-        <v>7.51525354385376</v>
+        <v>7.51525402069092</v>
       </c>
       <c r="H102" t="n">
         <v>9385715</v>
@@ -3356,7 +3356,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>7.51525354385376</v>
+        <v>7.51525402069092</v>
       </c>
       <c r="H103" t="n">
         <v>7099537</v>
@@ -3385,7 +3385,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G104" t="n">
-        <v>7.57297468185425</v>
+        <v>7.57297420501709</v>
       </c>
       <c r="H104" t="n">
         <v>4580345</v>
@@ -3414,7 +3414,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>7.60760593414307</v>
+        <v>7.60760688781738</v>
       </c>
       <c r="H105" t="n">
         <v>4459577</v>
@@ -3443,7 +3443,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G106" t="n">
-        <v>7.52102518081665</v>
+        <v>7.52102613449097</v>
       </c>
       <c r="H106" t="n">
         <v>8234351</v>
@@ -3472,7 +3472,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G107" t="n">
-        <v>7.48062133789062</v>
+        <v>7.48062038421631</v>
       </c>
       <c r="H107" t="n">
         <v>5847218</v>
@@ -3530,7 +3530,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22665119171143</v>
+        <v>7.22664928436279</v>
       </c>
       <c r="H109" t="n">
         <v>8338944</v>
@@ -3617,7 +3617,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>7.47484827041626</v>
+        <v>7.47484874725342</v>
       </c>
       <c r="H112" t="n">
         <v>7929338</v>
@@ -3646,7 +3646,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G113" t="n">
-        <v>7.4402174949646</v>
+        <v>7.44021701812744</v>
       </c>
       <c r="H113" t="n">
         <v>5900903</v>
@@ -3675,7 +3675,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.10543632507324</v>
+        <v>7.10543537139893</v>
       </c>
       <c r="H114" t="n">
         <v>10633674</v>
@@ -3704,7 +3704,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>6.87455272674561</v>
+        <v>6.87455224990845</v>
       </c>
       <c r="H115" t="n">
         <v>9110142</v>
@@ -3791,7 +3791,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>6.62635231018066</v>
+        <v>6.62635278701782</v>
       </c>
       <c r="H118" t="n">
         <v>12346070</v>
@@ -3820,7 +3820,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G119" t="n">
-        <v>6.88609743118286</v>
+        <v>6.88609600067139</v>
       </c>
       <c r="H119" t="n">
         <v>11874246</v>
@@ -3849,7 +3849,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G120" t="n">
-        <v>7.09388971328735</v>
+        <v>7.09389162063599</v>
       </c>
       <c r="H120" t="n">
         <v>8839028</v>
@@ -3907,7 +3907,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>7.26128053665161</v>
+        <v>7.26128101348877</v>
       </c>
       <c r="H122" t="n">
         <v>6049193</v>
@@ -3936,7 +3936,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G123" t="n">
-        <v>7.57297468185425</v>
+        <v>7.57297420501709</v>
       </c>
       <c r="H123" t="n">
         <v>9854901</v>
@@ -3965,7 +3965,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G124" t="n">
-        <v>6.30311632156372</v>
+        <v>6.30311584472656</v>
       </c>
       <c r="H124" t="n">
         <v>34410764</v>
@@ -3994,7 +3994,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G125" t="n">
-        <v>5.76919794082642</v>
+        <v>5.76919746398926</v>
       </c>
       <c r="H125" t="n">
         <v>24134297</v>
@@ -4023,7 +4023,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>5.85866594314575</v>
+        <v>5.85866498947144</v>
       </c>
       <c r="H126" t="n">
         <v>18052411</v>
@@ -4052,7 +4052,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G127" t="n">
-        <v>5.99719524383545</v>
+        <v>5.99719572067261</v>
       </c>
       <c r="H127" t="n">
         <v>13590828</v>
@@ -4081,7 +4081,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.08954858779907</v>
+        <v>6.08954906463623</v>
       </c>
       <c r="H128" t="n">
         <v>13839943</v>
@@ -4110,7 +4110,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G129" t="n">
-        <v>6.15881443023682</v>
+        <v>6.15881395339966</v>
       </c>
       <c r="H129" t="n">
         <v>10971382</v>
@@ -4168,7 +4168,7 @@
         <v>10.1700000762939</v>
       </c>
       <c r="G131" t="n">
-        <v>5.87020921707153</v>
+        <v>5.87021017074585</v>
       </c>
       <c r="H131" t="n">
         <v>11362996</v>
@@ -4255,7 +4255,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>6.11840867996216</v>
+        <v>6.11840963363647</v>
       </c>
       <c r="H134" t="n">
         <v>17273291</v>
@@ -4313,7 +4313,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G136" t="n">
-        <v>6.47627878189087</v>
+        <v>6.47627830505371</v>
       </c>
       <c r="H136" t="n">
         <v>12440431</v>
@@ -4342,7 +4342,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G137" t="n">
-        <v>6.41278600692749</v>
+        <v>6.41278409957886</v>
       </c>
       <c r="H137" t="n">
         <v>8413080</v>
@@ -4371,7 +4371,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>6.58017635345459</v>
+        <v>6.58017539978027</v>
       </c>
       <c r="H138" t="n">
         <v>9565721</v>
@@ -4400,7 +4400,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G139" t="n">
-        <v>6.51668405532837</v>
+        <v>6.51668262481689</v>
       </c>
       <c r="H139" t="n">
         <v>9994193</v>
@@ -4429,7 +4429,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>6.55131578445435</v>
+        <v>6.55131483078003</v>
       </c>
       <c r="H140" t="n">
         <v>6444579</v>
@@ -4458,7 +4458,7 @@
         <v>11.210000038147</v>
       </c>
       <c r="G141" t="n">
-        <v>6.47050523757935</v>
+        <v>6.47050619125366</v>
       </c>
       <c r="H141" t="n">
         <v>8188409</v>
@@ -4516,7 +4516,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>6.51668405532837</v>
+        <v>6.51668262481689</v>
       </c>
       <c r="H143" t="n">
         <v>8332885</v>
@@ -4545,7 +4545,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G144" t="n">
-        <v>6.48782300949097</v>
+        <v>6.48782205581665</v>
       </c>
       <c r="H144" t="n">
         <v>6107951</v>
@@ -4574,7 +4574,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G145" t="n">
-        <v>6.44741630554199</v>
+        <v>6.44741725921631</v>
       </c>
       <c r="H145" t="n">
         <v>6733421</v>
@@ -4603,7 +4603,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G146" t="n">
-        <v>6.40124177932739</v>
+        <v>6.40124225616455</v>
       </c>
       <c r="H146" t="n">
         <v>7777276</v>
@@ -4777,7 +4777,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G152" t="n">
-        <v>6.48782300949097</v>
+        <v>6.48782205581665</v>
       </c>
       <c r="H152" t="n">
         <v>8766213</v>
@@ -4835,7 +4835,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G154" t="n">
-        <v>6.76488351821899</v>
+        <v>6.76488208770752</v>
       </c>
       <c r="H154" t="n">
         <v>8742184</v>
@@ -4864,7 +4864,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G155" t="n">
-        <v>6.90341234207153</v>
+        <v>6.90341186523438</v>
       </c>
       <c r="H155" t="n">
         <v>7882791</v>
@@ -4893,7 +4893,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>6.98422145843506</v>
+        <v>6.98422050476074</v>
       </c>
       <c r="H156" t="n">
         <v>7997306</v>
@@ -4922,7 +4922,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G157" t="n">
-        <v>6.98999309539795</v>
+        <v>6.98999357223511</v>
       </c>
       <c r="H157" t="n">
         <v>7790957</v>
@@ -4980,7 +4980,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>6.98422145843506</v>
+        <v>6.98422050476074</v>
       </c>
       <c r="H159" t="n">
         <v>6328424</v>
@@ -5009,7 +5009,7 @@
         <v>11.75</v>
       </c>
       <c r="G160" t="n">
-        <v>6.78219890594482</v>
+        <v>6.78219938278198</v>
       </c>
       <c r="H160" t="n">
         <v>8826122</v>
@@ -5038,7 +5038,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>6.59749221801758</v>
+        <v>6.59749317169189</v>
       </c>
       <c r="H161" t="n">
         <v>11733873</v>
@@ -5067,7 +5067,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G162" t="n">
-        <v>6.61480808258057</v>
+        <v>6.61480855941772</v>
       </c>
       <c r="H162" t="n">
         <v>8706447</v>
@@ -5096,7 +5096,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G163" t="n">
-        <v>6.40124177932739</v>
+        <v>6.40124225616455</v>
       </c>
       <c r="H163" t="n">
         <v>10743233</v>
@@ -5125,7 +5125,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>6.45319080352783</v>
+        <v>6.45319032669067</v>
       </c>
       <c r="H164" t="n">
         <v>6886585</v>
@@ -5154,7 +5154,7 @@
         <v>11.6800003051758</v>
       </c>
       <c r="G165" t="n">
-        <v>6.74179410934448</v>
+        <v>6.7417950630188</v>
       </c>
       <c r="H165" t="n">
         <v>9706198</v>
@@ -5212,7 +5212,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G167" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H167" t="n">
         <v>10954401</v>
@@ -5241,7 +5241,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>6.45896100997925</v>
+        <v>6.45896291732788</v>
       </c>
       <c r="H168" t="n">
         <v>9516470</v>
@@ -5270,7 +5270,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G169" t="n">
-        <v>6.33197641372681</v>
+        <v>6.33197689056396</v>
       </c>
       <c r="H169" t="n">
         <v>8449827</v>
@@ -5299,7 +5299,7 @@
         <v>11.25</v>
       </c>
       <c r="G170" t="n">
-        <v>6.4935941696167</v>
+        <v>6.49359560012817</v>
       </c>
       <c r="H170" t="n">
         <v>9761898</v>
@@ -5328,7 +5328,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>6.58017635345459</v>
+        <v>6.58017539978027</v>
       </c>
       <c r="H171" t="n">
         <v>14284519</v>
@@ -5357,7 +5357,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G172" t="n">
-        <v>6.6494402885437</v>
+        <v>6.64944171905518</v>
       </c>
       <c r="H172" t="n">
         <v>14457087</v>
@@ -5386,7 +5386,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>6.69561767578125</v>
+        <v>6.69561815261841</v>
       </c>
       <c r="H173" t="n">
         <v>10129486</v>
@@ -5415,7 +5415,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>6.64366817474365</v>
+        <v>6.64366960525513</v>
       </c>
       <c r="H174" t="n">
         <v>7255728</v>
@@ -5444,7 +5444,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G175" t="n">
-        <v>6.59172105789185</v>
+        <v>6.59172010421753</v>
       </c>
       <c r="H175" t="n">
         <v>7201471</v>
@@ -5473,7 +5473,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G176" t="n">
-        <v>6.68407344818115</v>
+        <v>6.68407392501831</v>
       </c>
       <c r="H176" t="n">
         <v>9393017</v>
@@ -5560,7 +5560,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G179" t="n">
-        <v>6.76488351821899</v>
+        <v>6.76488208770752</v>
       </c>
       <c r="H179" t="n">
         <v>10292615</v>
@@ -5589,7 +5589,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G180" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H180" t="n">
         <v>12394032</v>
@@ -5618,7 +5618,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G181" t="n">
-        <v>6.41855812072754</v>
+        <v>6.41855669021606</v>
       </c>
       <c r="H181" t="n">
         <v>13961223</v>
@@ -5705,7 +5705,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G184" t="n">
-        <v>6.45896100997925</v>
+        <v>6.45896291732788</v>
       </c>
       <c r="H184" t="n">
         <v>9845181</v>
@@ -5734,7 +5734,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>6.44164657592773</v>
+        <v>6.44164514541626</v>
       </c>
       <c r="H185" t="n">
         <v>7916766</v>
@@ -5763,7 +5763,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G186" t="n">
-        <v>6.51091146469116</v>
+        <v>6.510910987854</v>
       </c>
       <c r="H186" t="n">
         <v>11283638</v>
@@ -5792,7 +5792,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G187" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H187" t="n">
         <v>8857866</v>
@@ -5850,7 +5850,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G189" t="n">
-        <v>6.31466007232666</v>
+        <v>6.31466054916382</v>
       </c>
       <c r="H189" t="n">
         <v>8727790</v>
@@ -5879,7 +5879,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G190" t="n">
-        <v>6.28579950332642</v>
+        <v>6.28579998016357</v>
       </c>
       <c r="H190" t="n">
         <v>8152832</v>
@@ -5908,7 +5908,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G191" t="n">
-        <v>6.2973427772522</v>
+        <v>6.29734420776367</v>
       </c>
       <c r="H191" t="n">
         <v>8512534</v>
@@ -5995,7 +5995,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G194" t="n">
-        <v>6.2396240234375</v>
+        <v>6.23962354660034</v>
       </c>
       <c r="H194" t="n">
         <v>6357213</v>
@@ -6053,7 +6053,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G196" t="n">
-        <v>6.48204946517944</v>
+        <v>6.48205041885376</v>
       </c>
       <c r="H196" t="n">
         <v>14421992</v>
@@ -6082,7 +6082,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G197" t="n">
-        <v>6.56863117218018</v>
+        <v>6.56863307952881</v>
       </c>
       <c r="H197" t="n">
         <v>11639969</v>
@@ -6111,7 +6111,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G198" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822780609131</v>
       </c>
       <c r="H198" t="n">
         <v>9955363</v>
@@ -6140,7 +6140,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G199" t="n">
-        <v>6.56285953521729</v>
+        <v>6.5628604888916</v>
       </c>
       <c r="H199" t="n">
         <v>6209487</v>
@@ -6198,7 +6198,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G201" t="n">
-        <v>6.6494402885437</v>
+        <v>6.64944171905518</v>
       </c>
       <c r="H201" t="n">
         <v>6865636</v>
@@ -6227,7 +6227,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G202" t="n">
-        <v>6.45896100997925</v>
+        <v>6.45896291732788</v>
       </c>
       <c r="H202" t="n">
         <v>8949862</v>
@@ -6256,7 +6256,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>6.56285953521729</v>
+        <v>6.5628604888916</v>
       </c>
       <c r="H203" t="n">
         <v>7401056</v>
@@ -6343,7 +6343,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G206" t="n">
-        <v>6.88032388687134</v>
+        <v>6.8803243637085</v>
       </c>
       <c r="H206" t="n">
         <v>6058132</v>
@@ -6372,7 +6372,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>6.86300802230835</v>
+        <v>6.86300897598267</v>
       </c>
       <c r="H207" t="n">
         <v>7506451</v>
@@ -6401,7 +6401,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G208" t="n">
-        <v>6.89186763763428</v>
+        <v>6.89186811447144</v>
       </c>
       <c r="H208" t="n">
         <v>5934021</v>
@@ -6459,7 +6459,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>6.96113300323486</v>
+        <v>6.96113395690918</v>
       </c>
       <c r="H210" t="n">
         <v>6276601</v>
@@ -6517,7 +6517,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>7.00153875350952</v>
+        <v>7.00153827667236</v>
       </c>
       <c r="H212" t="n">
         <v>7368438</v>
@@ -6546,7 +6546,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>6.839919090271</v>
+        <v>6.83991956710815</v>
       </c>
       <c r="H213" t="n">
         <v>9730239</v>
@@ -6575,7 +6575,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79374265670776</v>
+        <v>6.79374361038208</v>
       </c>
       <c r="H214" t="n">
         <v>7043555</v>
@@ -6604,7 +6604,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G215" t="n">
-        <v>6.68984603881836</v>
+        <v>6.68984460830688</v>
       </c>
       <c r="H215" t="n">
         <v>5180721</v>
@@ -6662,7 +6662,7 @@
         <v>11.25</v>
       </c>
       <c r="G217" t="n">
-        <v>6.4935941696167</v>
+        <v>6.49359560012817</v>
       </c>
       <c r="H217" t="n">
         <v>7507034</v>
@@ -6691,7 +6691,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G218" t="n">
-        <v>6.38969659805298</v>
+        <v>6.38969707489014</v>
       </c>
       <c r="H218" t="n">
         <v>7904227</v>
@@ -6720,7 +6720,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G219" t="n">
-        <v>6.54554319381714</v>
+        <v>6.54554271697998</v>
       </c>
       <c r="H219" t="n">
         <v>6994491</v>
@@ -6749,7 +6749,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G220" t="n">
-        <v>6.64366817474365</v>
+        <v>6.64366960525513</v>
       </c>
       <c r="H220" t="n">
         <v>4846995</v>
@@ -6807,7 +6807,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G222" t="n">
-        <v>6.79374265670776</v>
+        <v>6.79374361038208</v>
       </c>
       <c r="H222" t="n">
         <v>18839988</v>
@@ -6865,7 +6865,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.839919090271</v>
+        <v>6.83991956710815</v>
       </c>
       <c r="H224" t="n">
         <v>10160700</v>
@@ -6894,7 +6894,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G225" t="n">
-        <v>6.77642726898193</v>
+        <v>6.77642774581909</v>
       </c>
       <c r="H225" t="n">
         <v>8656075</v>
@@ -6923,7 +6923,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>6.69561767578125</v>
+        <v>6.69561815261841</v>
       </c>
       <c r="H226" t="n">
         <v>8032846</v>
@@ -6952,7 +6952,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G227" t="n">
-        <v>6.58594799041748</v>
+        <v>6.58594846725464</v>
       </c>
       <c r="H227" t="n">
         <v>11510186</v>
@@ -6981,7 +6981,7 @@
         <v>11.25</v>
       </c>
       <c r="G228" t="n">
-        <v>6.4935941696167</v>
+        <v>6.49359560012817</v>
       </c>
       <c r="H228" t="n">
         <v>11648020</v>
@@ -7010,7 +7010,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G229" t="n">
-        <v>6.48204946517944</v>
+        <v>6.48205041885376</v>
       </c>
       <c r="H229" t="n">
         <v>7631683</v>
@@ -7039,7 +7039,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G230" t="n">
-        <v>6.72447824478149</v>
+        <v>6.72447776794434</v>
       </c>
       <c r="H230" t="n">
         <v>12925930</v>
@@ -7097,7 +7097,7 @@
         <v>11.25</v>
       </c>
       <c r="G232" t="n">
-        <v>6.4935941696167</v>
+        <v>6.49359560012817</v>
       </c>
       <c r="H232" t="n">
         <v>6073154</v>
@@ -7126,7 +7126,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69561767578125</v>
+        <v>6.69561815261841</v>
       </c>
       <c r="H233" t="n">
         <v>13130118</v>
@@ -7213,7 +7213,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G236" t="n">
-        <v>6.88032388687134</v>
+        <v>6.8803243637085</v>
       </c>
       <c r="H236" t="n">
         <v>15814753</v>
@@ -7242,7 +7242,7 @@
         <v>12.3400001525879</v>
       </c>
       <c r="G237" t="n">
-        <v>7.12275266647339</v>
+        <v>7.12275218963623</v>
       </c>
       <c r="H237" t="n">
         <v>21562971</v>
@@ -7271,7 +7271,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G238" t="n">
-        <v>7.10543632507324</v>
+        <v>7.10543537139893</v>
       </c>
       <c r="H238" t="n">
         <v>12074647</v>
@@ -7300,7 +7300,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>7.04194259643555</v>
+        <v>7.04194211959839</v>
       </c>
       <c r="H239" t="n">
         <v>17922065</v>
@@ -7329,7 +7329,7 @@
         <v>12.8299999237061</v>
       </c>
       <c r="G240" t="n">
-        <v>7.40558433532715</v>
+        <v>7.40558481216431</v>
       </c>
       <c r="H240" t="n">
         <v>16863279</v>
@@ -7358,7 +7358,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94816017150879</v>
+        <v>7.94816112518311</v>
       </c>
       <c r="H241" t="n">
         <v>27435629</v>
@@ -7387,7 +7387,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G242" t="n">
-        <v>8.31180095672607</v>
+        <v>8.31180000305176</v>
       </c>
       <c r="H242" t="n">
         <v>27597375</v>
@@ -7416,7 +7416,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G243" t="n">
-        <v>8.09246158599854</v>
+        <v>8.09246253967285</v>
       </c>
       <c r="H243" t="n">
         <v>17725328</v>
@@ -7445,7 +7445,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G244" t="n">
-        <v>8.11555194854736</v>
+        <v>8.11555004119873</v>
       </c>
       <c r="H244" t="n">
         <v>13689455</v>
@@ -7474,7 +7474,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>8.05782890319824</v>
+        <v>8.05783081054688</v>
       </c>
       <c r="H245" t="n">
         <v>13653874</v>
@@ -7561,7 +7561,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G248" t="n">
-        <v>8.31180095672607</v>
+        <v>8.31180000305176</v>
       </c>
       <c r="H248" t="n">
         <v>24539377</v>
@@ -7677,7 +7677,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G252" t="n">
-        <v>8.23099136352539</v>
+        <v>8.23099231719971</v>
       </c>
       <c r="H252" t="n">
         <v>6820617</v>
@@ -7764,7 +7764,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G255" t="n">
-        <v>8.19058704376221</v>
+        <v>8.19058513641357</v>
       </c>
       <c r="H255" t="n">
         <v>4984411</v>
@@ -7793,7 +7793,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G256" t="n">
-        <v>8.14441108703613</v>
+        <v>8.14441013336182</v>
       </c>
       <c r="H256" t="n">
         <v>3921987</v>
@@ -7822,7 +7822,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>8.15018367767334</v>
+        <v>8.15018272399902</v>
       </c>
       <c r="H257" t="n">
         <v>3586162</v>
@@ -7851,7 +7851,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G258" t="n">
-        <v>8.28293991088867</v>
+        <v>8.2829418182373</v>
       </c>
       <c r="H258" t="n">
         <v>3071767</v>
@@ -7880,7 +7880,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G259" t="n">
-        <v>8.34066295623779</v>
+        <v>8.34066104888916</v>
       </c>
       <c r="H259" t="n">
         <v>7598986</v>
@@ -7909,7 +7909,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.38106536865234</v>
+        <v>8.38106727600098</v>
       </c>
       <c r="H260" t="n">
         <v>6953513</v>
@@ -7938,7 +7938,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G261" t="n">
-        <v>8.32911777496338</v>
+        <v>8.32911586761475</v>
       </c>
       <c r="H261" t="n">
         <v>5346832</v>
@@ -7967,7 +7967,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G262" t="n">
-        <v>8.34643268585205</v>
+        <v>8.34643459320068</v>
       </c>
       <c r="H262" t="n">
         <v>4300811</v>
@@ -7996,7 +7996,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G263" t="n">
-        <v>8.16172695159912</v>
+        <v>8.16172790527344</v>
       </c>
       <c r="H263" t="n">
         <v>8779927</v>
@@ -8112,7 +8112,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>8.09246158599854</v>
+        <v>8.09246253967285</v>
       </c>
       <c r="H267" t="n">
         <v>6018850</v>
@@ -8141,7 +8141,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>7.90775442123413</v>
+        <v>7.90775632858276</v>
       </c>
       <c r="H268" t="n">
         <v>9686115</v>
@@ -8170,7 +8170,7 @@
         <v>13.6599998474121</v>
       </c>
       <c r="G269" t="n">
-        <v>7.88466644287109</v>
+        <v>7.88466787338257</v>
       </c>
       <c r="H269" t="n">
         <v>8084671</v>
@@ -8199,7 +8199,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>7.82117366790771</v>
+        <v>7.82117509841919</v>
       </c>
       <c r="H270" t="n">
         <v>11031719</v>
@@ -8228,7 +8228,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G271" t="n">
-        <v>7.91929960250854</v>
+        <v>7.91930103302002</v>
       </c>
       <c r="H271" t="n">
         <v>11744626</v>
@@ -8286,7 +8286,7 @@
         <v>14.25</v>
       </c>
       <c r="G273" t="n">
-        <v>8.22522068023682</v>
+        <v>8.22522163391113</v>
       </c>
       <c r="H273" t="n">
         <v>35023904</v>
@@ -8344,7 +8344,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G275" t="n">
-        <v>8.98713493347168</v>
+        <v>8.987135887146</v>
       </c>
       <c r="H275" t="n">
         <v>38661285</v>
@@ -8373,7 +8373,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G276" t="n">
-        <v>9.02176761627197</v>
+        <v>9.02176666259766</v>
       </c>
       <c r="H276" t="n">
         <v>17073860</v>
@@ -8402,7 +8402,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>8.88900852203369</v>
+        <v>8.88900947570801</v>
       </c>
       <c r="H277" t="n">
         <v>13161667</v>
@@ -8489,7 +8489,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G280" t="n">
-        <v>8.47342014312744</v>
+        <v>8.47341918945312</v>
       </c>
       <c r="H280" t="n">
         <v>10987215</v>
@@ -8547,7 +8547,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G282" t="n">
-        <v>8.64658164978027</v>
+        <v>8.64658069610596</v>
       </c>
       <c r="H282" t="n">
         <v>9449476</v>
@@ -8576,7 +8576,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G283" t="n">
-        <v>8.44455814361572</v>
+        <v>8.44455909729004</v>
       </c>
       <c r="H283" t="n">
         <v>9849068</v>
@@ -8605,7 +8605,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>8.39838314056396</v>
+        <v>8.39838218688965</v>
       </c>
       <c r="H284" t="n">
         <v>10466445</v>
@@ -8634,7 +8634,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G285" t="n">
-        <v>8.3060302734375</v>
+        <v>8.30602836608887</v>
       </c>
       <c r="H285" t="n">
         <v>15049935</v>
@@ -8663,7 +8663,7 @@
         <v>14.5</v>
       </c>
       <c r="G286" t="n">
-        <v>8.36952209472656</v>
+        <v>8.36952114105225</v>
       </c>
       <c r="H286" t="n">
         <v>9647591</v>
@@ -8692,7 +8692,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G287" t="n">
-        <v>8.31180095672607</v>
+        <v>8.31180000305176</v>
       </c>
       <c r="H287" t="n">
         <v>9990083</v>
@@ -8750,7 +8750,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>8.66389751434326</v>
+        <v>8.66390037536621</v>
       </c>
       <c r="H289" t="n">
         <v>10197528</v>
@@ -8779,7 +8779,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G290" t="n">
-        <v>8.50227928161621</v>
+        <v>8.50228023529053</v>
       </c>
       <c r="H290" t="n">
         <v>10605907</v>
@@ -8837,7 +8837,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G292" t="n">
-        <v>8.57731819152832</v>
+        <v>8.57731533050537</v>
       </c>
       <c r="H292" t="n">
         <v>8507711</v>
@@ -8866,7 +8866,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G293" t="n">
-        <v>8.45610332489014</v>
+        <v>8.4561014175415</v>
       </c>
       <c r="H293" t="n">
         <v>6866029</v>
@@ -8895,7 +8895,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43878746032715</v>
+        <v>8.43878650665283</v>
       </c>
       <c r="H294" t="n">
         <v>9612922</v>
@@ -8924,7 +8924,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>8.37529468536377</v>
+        <v>8.37529563903809</v>
       </c>
       <c r="H295" t="n">
         <v>7464036</v>
@@ -8953,7 +8953,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G296" t="n">
-        <v>8.2887134552002</v>
+        <v>8.28871250152588</v>
       </c>
       <c r="H296" t="n">
         <v>8501366</v>
@@ -9011,7 +9011,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>7.90775442123413</v>
+        <v>7.90775632858276</v>
       </c>
       <c r="H298" t="n">
         <v>16724105</v>
@@ -9098,7 +9098,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G301" t="n">
-        <v>7.91929960250854</v>
+        <v>7.91930103302002</v>
       </c>
       <c r="H301" t="n">
         <v>6583459</v>
@@ -9127,7 +9127,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G302" t="n">
-        <v>8.05782890319824</v>
+        <v>8.05783081054688</v>
       </c>
       <c r="H302" t="n">
         <v>7607569</v>
@@ -9156,7 +9156,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G303" t="n">
-        <v>7.91929960250854</v>
+        <v>7.91930103302002</v>
       </c>
       <c r="H303" t="n">
         <v>8771524</v>
@@ -9185,7 +9185,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G304" t="n">
-        <v>7.91929960250854</v>
+        <v>7.91930103302002</v>
       </c>
       <c r="H304" t="n">
         <v>8184922</v>
@@ -9214,7 +9214,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G305" t="n">
-        <v>8.05782890319824</v>
+        <v>8.05783081054688</v>
       </c>
       <c r="H305" t="n">
         <v>8192329</v>
@@ -9243,7 +9243,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G306" t="n">
-        <v>8.15018367767334</v>
+        <v>8.15018272399902</v>
       </c>
       <c r="H306" t="n">
         <v>7721589</v>
@@ -9272,7 +9272,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G307" t="n">
-        <v>8.18481540679932</v>
+        <v>8.18481636047363</v>
       </c>
       <c r="H307" t="n">
         <v>7553571</v>
@@ -9330,7 +9330,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10400676727295</v>
+        <v>8.10400581359863</v>
       </c>
       <c r="H309" t="n">
         <v>9584039</v>
@@ -9417,7 +9417,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G312" t="n">
-        <v>8.42724227905273</v>
+        <v>8.42724132537842</v>
       </c>
       <c r="H312" t="n">
         <v>14415158</v>
@@ -9475,7 +9475,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G314" t="n">
-        <v>8.39838314056396</v>
+        <v>8.39838218688965</v>
       </c>
       <c r="H314" t="n">
         <v>8841352</v>
@@ -9533,7 +9533,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G316" t="n">
-        <v>8.31180095672607</v>
+        <v>8.31180000305176</v>
       </c>
       <c r="H316" t="n">
         <v>7830996</v>
@@ -9562,7 +9562,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>8.42147064208984</v>
+        <v>8.42147159576416</v>
       </c>
       <c r="H317" t="n">
         <v>9353520</v>
@@ -9620,7 +9620,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G319" t="n">
-        <v>8.45610332489014</v>
+        <v>8.4561014175415</v>
       </c>
       <c r="H319" t="n">
         <v>6047384</v>
@@ -9707,7 +9707,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G322" t="n">
-        <v>8.60040473937988</v>
+        <v>8.6004056930542</v>
       </c>
       <c r="H322" t="n">
         <v>6401059</v>
@@ -9765,7 +9765,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G324" t="n">
-        <v>8.43301391601562</v>
+        <v>8.43301582336426</v>
       </c>
       <c r="H324" t="n">
         <v>9250700</v>
@@ -9794,7 +9794,7 @@
         <v>14.5</v>
       </c>
       <c r="G325" t="n">
-        <v>8.36952209472656</v>
+        <v>8.36952114105225</v>
       </c>
       <c r="H325" t="n">
         <v>7413158</v>
@@ -9823,7 +9823,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G326" t="n">
-        <v>8.28293991088867</v>
+        <v>8.2829418182373</v>
       </c>
       <c r="H326" t="n">
         <v>8654336</v>
@@ -9852,7 +9852,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G327" t="n">
-        <v>8.265625</v>
+        <v>8.26562309265137</v>
       </c>
       <c r="H327" t="n">
         <v>5065491</v>
@@ -9910,7 +9910,7 @@
         <v>14.25</v>
       </c>
       <c r="G329" t="n">
-        <v>8.22522068023682</v>
+        <v>8.22522163391113</v>
       </c>
       <c r="H329" t="n">
         <v>8320300</v>
@@ -9939,7 +9939,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>8.18481540679932</v>
+        <v>8.18481636047363</v>
       </c>
       <c r="H330" t="n">
         <v>6275754</v>
@@ -9968,7 +9968,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G331" t="n">
-        <v>8.10977745056152</v>
+        <v>8.10977935791016</v>
       </c>
       <c r="H331" t="n">
         <v>6244666</v>
@@ -10026,7 +10026,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G333" t="n">
-        <v>8.14441108703613</v>
+        <v>8.14441013336182</v>
       </c>
       <c r="H333" t="n">
         <v>6623438</v>
@@ -10055,7 +10055,7 @@
         <v>14.1099996566772</v>
       </c>
       <c r="G334" t="n">
-        <v>8.14441108703613</v>
+        <v>8.14441013336182</v>
       </c>
       <c r="H334" t="n">
         <v>8074475</v>
@@ -10084,7 +10084,7 @@
         <v>14.25</v>
       </c>
       <c r="G335" t="n">
-        <v>8.22522068023682</v>
+        <v>8.22522163391113</v>
       </c>
       <c r="H335" t="n">
         <v>8308780</v>
@@ -10142,7 +10142,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G337" t="n">
-        <v>8.55422878265381</v>
+        <v>8.55422973632812</v>
       </c>
       <c r="H337" t="n">
         <v>5536735</v>
@@ -10171,7 +10171,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>8.42724227905273</v>
+        <v>8.42724132537842</v>
       </c>
       <c r="H338" t="n">
         <v>7682925</v>
@@ -10229,7 +10229,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>8.38683795928955</v>
+        <v>8.38683891296387</v>
       </c>
       <c r="H340" t="n">
         <v>4732198</v>
@@ -10258,7 +10258,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G341" t="n">
-        <v>8.39838314056396</v>
+        <v>8.39838218688965</v>
       </c>
       <c r="H341" t="n">
         <v>7491328</v>
@@ -10287,7 +10287,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G342" t="n">
-        <v>8.49650764465332</v>
+        <v>8.49650859832764</v>
       </c>
       <c r="H342" t="n">
         <v>6479094</v>
@@ -10316,7 +10316,7 @@
         <v>15</v>
       </c>
       <c r="G343" t="n">
-        <v>8.65812683105469</v>
+        <v>8.65812587738037</v>
       </c>
       <c r="H343" t="n">
         <v>9272455</v>
@@ -10345,7 +10345,7 @@
         <v>15.25</v>
       </c>
       <c r="G344" t="n">
-        <v>8.80242824554443</v>
+        <v>8.80242919921875</v>
       </c>
       <c r="H344" t="n">
         <v>8717049</v>
@@ -10403,7 +10403,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>8.84860610961914</v>
+        <v>8.84860515594482</v>
       </c>
       <c r="H346" t="n">
         <v>6043272</v>
@@ -10432,7 +10432,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G347" t="n">
-        <v>8.82551670074463</v>
+        <v>8.82551574707031</v>
       </c>
       <c r="H347" t="n">
         <v>6369062</v>
@@ -10461,7 +10461,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G348" t="n">
-        <v>8.56577491760254</v>
+        <v>8.56577396392822</v>
       </c>
       <c r="H348" t="n">
         <v>18609811</v>
@@ -10490,7 +10490,7 @@
         <v>14.75</v>
       </c>
       <c r="G349" t="n">
-        <v>8.51382350921631</v>
+        <v>8.51382446289062</v>
       </c>
       <c r="H349" t="n">
         <v>7663463</v>
@@ -10519,7 +10519,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G350" t="n">
-        <v>8.56577491760254</v>
+        <v>8.56577396392822</v>
       </c>
       <c r="H350" t="n">
         <v>5918594</v>
@@ -10577,7 +10577,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G352" t="n">
-        <v>8.60040473937988</v>
+        <v>8.6004056930542</v>
       </c>
       <c r="H352" t="n">
         <v>9968753</v>
@@ -10635,7 +10635,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G354" t="n">
-        <v>8.73316287994385</v>
+        <v>8.73316383361816</v>
       </c>
       <c r="H354" t="n">
         <v>10390572</v>
@@ -10664,7 +10664,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G355" t="n">
-        <v>8.90989971160889</v>
+        <v>8.90989875793457</v>
       </c>
       <c r="H355" t="n">
         <v>11545560</v>
@@ -10693,7 +10693,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G356" t="n">
-        <v>8.9403715133667</v>
+        <v>8.94036960601807</v>
       </c>
       <c r="H356" t="n">
         <v>7459778</v>
@@ -10722,7 +10722,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G357" t="n">
-        <v>8.79410743713379</v>
+        <v>8.79410648345947</v>
       </c>
       <c r="H357" t="n">
         <v>6528540</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>8.76972961425781</v>
+        <v>8.7697286605835</v>
       </c>
       <c r="H358" t="n">
         <v>5634717</v>
@@ -10780,7 +10780,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>8.74535179138184</v>
+        <v>8.74535369873047</v>
       </c>
       <c r="H359" t="n">
         <v>5592941</v>
@@ -10809,7 +10809,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>8.56861782073975</v>
+        <v>8.56861686706543</v>
       </c>
       <c r="H360" t="n">
         <v>6590299</v>
@@ -10838,7 +10838,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G361" t="n">
-        <v>8.45891857147217</v>
+        <v>8.45891952514648</v>
       </c>
       <c r="H361" t="n">
         <v>13691722</v>
@@ -10867,7 +10867,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G362" t="n">
-        <v>8.56252193450928</v>
+        <v>8.56252384185791</v>
       </c>
       <c r="H362" t="n">
         <v>15568422</v>
@@ -10925,7 +10925,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G364" t="n">
-        <v>8.56252193450928</v>
+        <v>8.56252384185791</v>
       </c>
       <c r="H364" t="n">
         <v>6162714</v>
@@ -10954,7 +10954,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G365" t="n">
-        <v>8.44063568115234</v>
+        <v>8.44063663482666</v>
       </c>
       <c r="H365" t="n">
         <v>5559424</v>
@@ -11070,7 +11070,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G369" t="n">
-        <v>8.57471084594727</v>
+        <v>8.57470989227295</v>
       </c>
       <c r="H369" t="n">
         <v>5457210</v>
@@ -11099,7 +11099,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G370" t="n">
-        <v>8.6661262512207</v>
+        <v>8.66612720489502</v>
       </c>
       <c r="H370" t="n">
         <v>8294383</v>
@@ -11128,7 +11128,7 @@
         <v>14.5</v>
       </c>
       <c r="G371" t="n">
-        <v>8.83676719665527</v>
+        <v>8.83676624298096</v>
       </c>
       <c r="H371" t="n">
         <v>10116154</v>
@@ -11186,7 +11186,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G373" t="n">
-        <v>8.7819185256958</v>
+        <v>8.78191757202148</v>
       </c>
       <c r="H373" t="n">
         <v>14000240</v>
@@ -11244,7 +11244,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G375" t="n">
-        <v>8.90380382537842</v>
+        <v>8.90380573272705</v>
       </c>
       <c r="H375" t="n">
         <v>6373118</v>
@@ -11360,7 +11360,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G379" t="n">
-        <v>8.83067321777344</v>
+        <v>8.83067226409912</v>
       </c>
       <c r="H379" t="n">
         <v>4281758</v>
@@ -11476,7 +11476,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G383" t="n">
-        <v>8.90989971160889</v>
+        <v>8.90989875793457</v>
       </c>
       <c r="H383" t="n">
         <v>8582882</v>
@@ -11505,7 +11505,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>8.7819185256958</v>
+        <v>8.78191757202148</v>
       </c>
       <c r="H384" t="n">
         <v>5634414</v>
@@ -11534,7 +11534,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.89770984649658</v>
+        <v>8.89770889282227</v>
       </c>
       <c r="H385" t="n">
         <v>4993574</v>
@@ -11592,7 +11592,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G387" t="n">
-        <v>8.98303127288818</v>
+        <v>8.98302936553955</v>
       </c>
       <c r="H387" t="n">
         <v>5038448</v>
@@ -11650,7 +11650,7 @@
         <v>15</v>
       </c>
       <c r="G389" t="n">
-        <v>9.14148426055908</v>
+        <v>9.14148330688477</v>
       </c>
       <c r="H389" t="n">
         <v>4569492</v>
@@ -11708,7 +11708,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>9.13538932800293</v>
+        <v>9.13538837432861</v>
       </c>
       <c r="H391" t="n">
         <v>4976109</v>
@@ -11824,7 +11824,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G395" t="n">
-        <v>9.44010639190674</v>
+        <v>9.44010353088379</v>
       </c>
       <c r="H395" t="n">
         <v>4434441</v>
@@ -11940,7 +11940,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G399" t="n">
-        <v>9.15976619720459</v>
+        <v>9.15976524353027</v>
       </c>
       <c r="H399" t="n">
         <v>4036467</v>
@@ -11969,7 +11969,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G400" t="n">
-        <v>9.12320137023926</v>
+        <v>9.12319946289062</v>
       </c>
       <c r="H400" t="n">
         <v>5860196</v>
@@ -12172,7 +12172,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G407" t="n">
-        <v>9.64731216430664</v>
+        <v>9.64731121063232</v>
       </c>
       <c r="H407" t="n">
         <v>13296739</v>
@@ -12259,7 +12259,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G410" t="n">
-        <v>9.7996711730957</v>
+        <v>9.79966926574707</v>
       </c>
       <c r="H410" t="n">
         <v>5528680</v>
@@ -12317,7 +12317,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G412" t="n">
-        <v>9.63512420654297</v>
+        <v>9.63512325286865</v>
       </c>
       <c r="H412" t="n">
         <v>5482876</v>
@@ -12375,7 +12375,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G414" t="n">
-        <v>9.40963363647461</v>
+        <v>9.40963268280029</v>
       </c>
       <c r="H414" t="n">
         <v>5885179</v>
@@ -12462,7 +12462,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G417" t="n">
-        <v>9.40353870391846</v>
+        <v>9.40353965759277</v>
       </c>
       <c r="H417" t="n">
         <v>5795313</v>
@@ -12491,7 +12491,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G418" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H418" t="n">
         <v>4329120</v>
@@ -12578,7 +12578,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>9.28774547576904</v>
+        <v>9.28774642944336</v>
       </c>
       <c r="H421" t="n">
         <v>4876525</v>
@@ -12636,7 +12636,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G423" t="n">
-        <v>9.28165245056152</v>
+        <v>9.28165149688721</v>
       </c>
       <c r="H423" t="n">
         <v>3002235</v>
@@ -12665,7 +12665,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G424" t="n">
-        <v>9.25118255615234</v>
+        <v>9.25118160247803</v>
       </c>
       <c r="H424" t="n">
         <v>2732024</v>
@@ -12694,7 +12694,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G425" t="n">
-        <v>9.12929439544678</v>
+        <v>9.12929344177246</v>
       </c>
       <c r="H425" t="n">
         <v>6430468</v>
@@ -12723,7 +12723,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G426" t="n">
-        <v>9.11710643768311</v>
+        <v>9.11710548400879</v>
       </c>
       <c r="H426" t="n">
         <v>3676580</v>
@@ -12752,7 +12752,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G427" t="n">
-        <v>9.16586017608643</v>
+        <v>9.16586112976074</v>
       </c>
       <c r="H427" t="n">
         <v>4687689</v>
@@ -12781,7 +12781,7 @@
         <v>15.1099996566772</v>
       </c>
       <c r="G428" t="n">
-        <v>9.20851993560791</v>
+        <v>9.20852088928223</v>
       </c>
       <c r="H428" t="n">
         <v>3114297</v>
@@ -12810,7 +12810,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G429" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26336860656738</v>
       </c>
       <c r="H429" t="n">
         <v>5576704</v>
@@ -12839,7 +12839,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G430" t="n">
-        <v>9.2207088470459</v>
+        <v>9.22070980072021</v>
       </c>
       <c r="H430" t="n">
         <v>4710868</v>
@@ -12868,7 +12868,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G431" t="n">
-        <v>9.19023704528809</v>
+        <v>9.1902379989624</v>
       </c>
       <c r="H431" t="n">
         <v>4472697</v>
@@ -12897,7 +12897,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>9.12929439544678</v>
+        <v>9.12929344177246</v>
       </c>
       <c r="H432" t="n">
         <v>4782153</v>
@@ -12926,7 +12926,7 @@
         <v>14.960000038147</v>
       </c>
       <c r="G433" t="n">
-        <v>9.11710643768311</v>
+        <v>9.11710548400879</v>
       </c>
       <c r="H433" t="n">
         <v>4785053</v>
@@ -12955,7 +12955,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>9.40353870391846</v>
+        <v>9.40353965759277</v>
       </c>
       <c r="H434" t="n">
         <v>9111113</v>
@@ -12984,7 +12984,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G435" t="n">
-        <v>9.47057723999023</v>
+        <v>9.47057628631592</v>
       </c>
       <c r="H435" t="n">
         <v>6196669</v>
@@ -13013,7 +13013,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G436" t="n">
-        <v>9.52542495727539</v>
+        <v>9.52542400360107</v>
       </c>
       <c r="H436" t="n">
         <v>4949676</v>
@@ -13042,7 +13042,7 @@
         <v>15.4899997711182</v>
       </c>
       <c r="G437" t="n">
-        <v>9.44010639190674</v>
+        <v>9.44010353088379</v>
       </c>
       <c r="H437" t="n">
         <v>7238822</v>
@@ -13071,7 +13071,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G438" t="n">
-        <v>9.33650207519531</v>
+        <v>9.336501121521</v>
       </c>
       <c r="H438" t="n">
         <v>6766626</v>
@@ -13100,7 +13100,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G439" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H439" t="n">
         <v>4822335</v>
@@ -13129,7 +13129,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>9.47667121887207</v>
+        <v>9.47667026519775</v>
       </c>
       <c r="H440" t="n">
         <v>3195954</v>
@@ -13158,7 +13158,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.47667121887207</v>
+        <v>9.47667026519775</v>
       </c>
       <c r="H441" t="n">
         <v>5385574</v>
@@ -13332,7 +13332,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G447" t="n">
-        <v>9.45838832855225</v>
+        <v>9.45838737487793</v>
       </c>
       <c r="H447" t="n">
         <v>4551096</v>
@@ -13361,7 +13361,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G448" t="n">
-        <v>9.60465049743652</v>
+        <v>9.60465145111084</v>
       </c>
       <c r="H448" t="n">
         <v>6240489</v>
@@ -13390,7 +13390,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G449" t="n">
-        <v>9.64121723175049</v>
+        <v>9.6412181854248</v>
       </c>
       <c r="H449" t="n">
         <v>4108726</v>
@@ -13477,7 +13477,7 @@
         <v>15.6300001144409</v>
       </c>
       <c r="G452" t="n">
-        <v>9.52542495727539</v>
+        <v>9.52542400360107</v>
       </c>
       <c r="H452" t="n">
         <v>4320426</v>
@@ -13506,7 +13506,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G453" t="n">
-        <v>9.51323699951172</v>
+        <v>9.51323509216309</v>
       </c>
       <c r="H453" t="n">
         <v>4928012</v>
@@ -13535,7 +13535,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G454" t="n">
-        <v>9.51323699951172</v>
+        <v>9.51323509216309</v>
       </c>
       <c r="H454" t="n">
         <v>3315712</v>
@@ -13564,7 +13564,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>9.42791748046875</v>
+        <v>9.42791652679443</v>
       </c>
       <c r="H455" t="n">
         <v>5112544</v>
@@ -13593,7 +13593,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G456" t="n">
-        <v>9.47057723999023</v>
+        <v>9.47057628631592</v>
       </c>
       <c r="H456" t="n">
         <v>5113218</v>
@@ -13738,7 +13738,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>9.33650207519531</v>
+        <v>9.336501121521</v>
       </c>
       <c r="H461" t="n">
         <v>5113182</v>
@@ -13767,7 +13767,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>9.33650207519531</v>
+        <v>9.336501121521</v>
       </c>
       <c r="H462" t="n">
         <v>5103039</v>
@@ -13825,7 +13825,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G464" t="n">
-        <v>9.51323699951172</v>
+        <v>9.51323509216309</v>
       </c>
       <c r="H464" t="n">
         <v>4665406</v>
@@ -13854,7 +13854,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G465" t="n">
-        <v>9.57418060302734</v>
+        <v>9.57417964935303</v>
       </c>
       <c r="H465" t="n">
         <v>6496271</v>
@@ -13970,7 +13970,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G469" t="n">
-        <v>9.59246349334717</v>
+        <v>9.59246253967285</v>
       </c>
       <c r="H469" t="n">
         <v>5452104</v>
@@ -14028,7 +14028,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G471" t="n">
-        <v>9.69606781005859</v>
+        <v>9.69606590270996</v>
       </c>
       <c r="H471" t="n">
         <v>4748769</v>
@@ -14086,7 +14086,7 @@
         <v>15.75</v>
       </c>
       <c r="G473" t="n">
-        <v>9.59855842590332</v>
+        <v>9.598557472229</v>
       </c>
       <c r="H473" t="n">
         <v>4290542</v>
@@ -14202,7 +14202,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G477" t="n">
-        <v>9.46448230743408</v>
+        <v>9.4644832611084</v>
       </c>
       <c r="H477" t="n">
         <v>4793218</v>
@@ -14231,7 +14231,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G478" t="n">
-        <v>9.61074733734131</v>
+        <v>9.61074638366699</v>
       </c>
       <c r="H478" t="n">
         <v>8017354</v>
@@ -14260,7 +14260,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G479" t="n">
-        <v>9.47667121887207</v>
+        <v>9.47667026519775</v>
       </c>
       <c r="H479" t="n">
         <v>5134316</v>
@@ -14289,7 +14289,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G480" t="n">
-        <v>9.37306880950928</v>
+        <v>9.37306785583496</v>
       </c>
       <c r="H480" t="n">
         <v>6454695</v>
@@ -14405,7 +14405,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>9.28774547576904</v>
+        <v>9.28774642944336</v>
       </c>
       <c r="H484" t="n">
         <v>3345978</v>
@@ -14492,7 +14492,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G487" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26336860656738</v>
       </c>
       <c r="H487" t="n">
         <v>2952421</v>
@@ -14521,7 +14521,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G488" t="n">
-        <v>9.28165245056152</v>
+        <v>9.28165149688721</v>
       </c>
       <c r="H488" t="n">
         <v>3235740</v>
@@ -14550,7 +14550,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G489" t="n">
-        <v>9.19023704528809</v>
+        <v>9.1902379989624</v>
       </c>
       <c r="H489" t="n">
         <v>4315576</v>
@@ -14637,7 +14637,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G492" t="n">
-        <v>9.37306880950928</v>
+        <v>9.37306785583496</v>
       </c>
       <c r="H492" t="n">
         <v>5305139</v>
@@ -14666,7 +14666,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G493" t="n">
-        <v>9.17804908752441</v>
+        <v>9.1780481338501</v>
       </c>
       <c r="H493" t="n">
         <v>6388742</v>
@@ -14695,7 +14695,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G494" t="n">
-        <v>9.28165245056152</v>
+        <v>9.28165149688721</v>
       </c>
       <c r="H494" t="n">
         <v>5627908</v>
@@ -14724,7 +14724,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G495" t="n">
-        <v>9.25118255615234</v>
+        <v>9.25118160247803</v>
       </c>
       <c r="H495" t="n">
         <v>4249431</v>
@@ -14753,7 +14753,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G496" t="n">
-        <v>9.20242691040039</v>
+        <v>9.20242595672607</v>
       </c>
       <c r="H496" t="n">
         <v>4499730</v>
@@ -14782,7 +14782,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G497" t="n">
-        <v>9.25727653503418</v>
+        <v>9.25727558135986</v>
       </c>
       <c r="H497" t="n">
         <v>4333453</v>
@@ -14840,7 +14840,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G499" t="n">
-        <v>9.33040809631348</v>
+        <v>9.33040714263916</v>
       </c>
       <c r="H499" t="n">
         <v>3019971</v>
@@ -14869,7 +14869,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G500" t="n">
-        <v>9.31821918487549</v>
+        <v>9.31821727752686</v>
       </c>
       <c r="H500" t="n">
         <v>3137795</v>
@@ -14985,7 +14985,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>9.45838832855225</v>
+        <v>9.45838737487793</v>
       </c>
       <c r="H504" t="n">
         <v>4775495</v>
@@ -15014,7 +15014,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G505" t="n">
-        <v>9.39135074615479</v>
+        <v>9.39134979248047</v>
       </c>
       <c r="H505" t="n">
         <v>4087366</v>
@@ -15072,7 +15072,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>9.28774547576904</v>
+        <v>9.28774642944336</v>
       </c>
       <c r="H507" t="n">
         <v>6928129</v>
@@ -15130,7 +15130,7 @@
         <v>15.25</v>
       </c>
       <c r="G509" t="n">
-        <v>9.29384136199951</v>
+        <v>9.29384231567383</v>
       </c>
       <c r="H509" t="n">
         <v>3234122</v>
@@ -15188,7 +15188,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G511" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26336860656738</v>
       </c>
       <c r="H511" t="n">
         <v>4918573</v>
@@ -15217,7 +15217,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G512" t="n">
-        <v>9.15367317199707</v>
+        <v>9.15367221832275</v>
       </c>
       <c r="H512" t="n">
         <v>5300727</v>
@@ -15246,7 +15246,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G513" t="n">
-        <v>9.07444477081299</v>
+        <v>9.0744457244873</v>
       </c>
       <c r="H513" t="n">
         <v>8118315</v>
@@ -15275,7 +15275,7 @@
         <v>15</v>
       </c>
       <c r="G514" t="n">
-        <v>9.14148426055908</v>
+        <v>9.14148330688477</v>
       </c>
       <c r="H514" t="n">
         <v>7907838</v>
@@ -15304,7 +15304,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G515" t="n">
-        <v>9.2633695602417</v>
+        <v>9.26336860656738</v>
       </c>
       <c r="H515" t="n">
         <v>4851123</v>
@@ -15391,7 +15391,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G518" t="n">
-        <v>9.59246349334717</v>
+        <v>9.59246253967285</v>
       </c>
       <c r="H518" t="n">
         <v>9641025</v>
@@ -15507,7 +15507,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>9.65340614318848</v>
+        <v>9.65340709686279</v>
       </c>
       <c r="H522" t="n">
         <v>5534925</v>
@@ -15536,7 +15536,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G523" t="n">
-        <v>9.57418060302734</v>
+        <v>9.57417964935303</v>
       </c>
       <c r="H523" t="n">
         <v>5450963</v>
@@ -15594,7 +15594,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G525" t="n">
-        <v>9.85451889038086</v>
+        <v>9.85451984405518</v>
       </c>
       <c r="H525" t="n">
         <v>14229701</v>
@@ -15710,7 +15710,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>9.872802734375</v>
+        <v>9.87280082702637</v>
       </c>
       <c r="H529" t="n">
         <v>6365879</v>
@@ -15739,7 +15739,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G530" t="n">
-        <v>9.88499164581299</v>
+        <v>9.88498973846436</v>
       </c>
       <c r="H530" t="n">
         <v>4063571</v>
@@ -15768,7 +15768,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>9.872802734375</v>
+        <v>9.87280082702637</v>
       </c>
       <c r="H531" t="n">
         <v>4458701</v>
@@ -15971,7 +15971,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>9.56808567047119</v>
+        <v>9.56808471679688</v>
       </c>
       <c r="H538" t="n">
         <v>9984938</v>
@@ -16000,7 +16000,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G539" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H539" t="n">
         <v>5955998</v>
@@ -16029,7 +16029,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>9.35478591918945</v>
+        <v>9.35478401184082</v>
       </c>
       <c r="H540" t="n">
         <v>7601697</v>
@@ -16087,7 +16087,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G542" t="n">
-        <v>9.25118255615234</v>
+        <v>9.25118160247803</v>
       </c>
       <c r="H542" t="n">
         <v>8394017</v>
@@ -16145,7 +16145,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G544" t="n">
-        <v>9.35478591918945</v>
+        <v>9.35478401184082</v>
       </c>
       <c r="H544" t="n">
         <v>5356669</v>
@@ -16261,7 +16261,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G548" t="n">
-        <v>9.42791748046875</v>
+        <v>9.42791652679443</v>
       </c>
       <c r="H548" t="n">
         <v>3399052</v>
@@ -16290,7 +16290,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G549" t="n">
-        <v>9.33650207519531</v>
+        <v>9.336501121521</v>
       </c>
       <c r="H549" t="n">
         <v>6237027</v>
@@ -16348,7 +16348,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>9.39135074615479</v>
+        <v>9.39134979248047</v>
       </c>
       <c r="H551" t="n">
         <v>2970106</v>
@@ -16406,7 +16406,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G553" t="n">
-        <v>9.40963363647461</v>
+        <v>9.40963268280029</v>
       </c>
       <c r="H553" t="n">
         <v>4248533</v>
@@ -16435,7 +16435,7 @@
         <v>15.4049997329712</v>
       </c>
       <c r="G554" t="n">
-        <v>9.38830184936523</v>
+        <v>9.38830280303955</v>
       </c>
       <c r="H554" t="n">
         <v>6660424</v>
@@ -16493,7 +16493,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G556" t="n">
-        <v>8.9708423614502</v>
+        <v>8.97084331512451</v>
       </c>
       <c r="H556" t="n">
         <v>12430527</v>
@@ -16522,7 +16522,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G557" t="n">
-        <v>9.24204063415527</v>
+        <v>9.24203872680664</v>
       </c>
       <c r="H557" t="n">
         <v>9426296</v>
@@ -16580,7 +16580,7 @@
         <v>15.5100002288818</v>
       </c>
       <c r="G559" t="n">
-        <v>9.45229434967041</v>
+        <v>9.45229339599609</v>
       </c>
       <c r="H559" t="n">
         <v>4250223</v>
@@ -16667,7 +16667,7 @@
         <v>15.4849996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>9.43705654144287</v>
+        <v>9.43705749511719</v>
       </c>
       <c r="H562" t="n">
         <v>4422978</v>
@@ -16696,7 +16696,7 @@
         <v>15.3149995803833</v>
       </c>
       <c r="G563" t="n">
-        <v>9.33345508575439</v>
+        <v>9.33345413208008</v>
       </c>
       <c r="H563" t="n">
         <v>5387220</v>
@@ -16725,7 +16725,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>9.56808567047119</v>
+        <v>9.56808471679688</v>
       </c>
       <c r="H564" t="n">
         <v>12431022</v>
@@ -16812,7 +16812,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G567" t="n">
-        <v>9.59246349334717</v>
+        <v>9.59246253967285</v>
       </c>
       <c r="H567" t="n">
         <v>5086946</v>
@@ -16841,7 +16841,7 @@
         <v>15.7399997711182</v>
       </c>
       <c r="G568" t="n">
-        <v>9.59246349334717</v>
+        <v>9.59246253967285</v>
       </c>
       <c r="H568" t="n">
         <v>4059986</v>
@@ -16870,7 +16870,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>9.50714206695557</v>
+        <v>9.50714302062988</v>
       </c>
       <c r="H569" t="n">
         <v>6786377</v>
@@ -17073,7 +17073,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G576" t="n">
-        <v>9.54675674438477</v>
+        <v>9.54675579071045</v>
       </c>
       <c r="H576" t="n">
         <v>4474564</v>
@@ -17102,7 +17102,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G577" t="n">
-        <v>9.62293529510498</v>
+        <v>9.62293434143066</v>
       </c>
       <c r="H577" t="n">
         <v>5138435</v>
@@ -17131,7 +17131,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G578" t="n">
-        <v>9.65340614318848</v>
+        <v>9.65340709686279</v>
       </c>
       <c r="H578" t="n">
         <v>4661914</v>
@@ -17218,7 +17218,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G581" t="n">
-        <v>9.72958564758301</v>
+        <v>9.72958660125732</v>
       </c>
       <c r="H581" t="n">
         <v>3572026</v>
@@ -17247,7 +17247,7 @@
         <v>16.2049999237061</v>
       </c>
       <c r="G582" t="n">
-        <v>9.87584972381592</v>
+        <v>9.8758487701416</v>
       </c>
       <c r="H582" t="n">
         <v>4938134</v>
@@ -17276,7 +17276,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>9.85756587982178</v>
+        <v>9.85756397247314</v>
       </c>
       <c r="H583" t="n">
         <v>5193807</v>
@@ -17305,7 +17305,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G584" t="n">
-        <v>9.85451889038086</v>
+        <v>9.85451984405518</v>
       </c>
       <c r="H584" t="n">
         <v>2547585</v>
@@ -17334,7 +17334,7 @@
         <v>16.2549991607666</v>
       </c>
       <c r="G585" t="n">
-        <v>9.90632057189941</v>
+        <v>9.9063196182251</v>
       </c>
       <c r="H585" t="n">
         <v>6197281</v>
@@ -17363,7 +17363,7 @@
         <v>16.3950004577637</v>
       </c>
       <c r="G586" t="n">
-        <v>9.99164199829102</v>
+        <v>9.9916410446167</v>
       </c>
       <c r="H586" t="n">
         <v>5709039</v>
@@ -17392,7 +17392,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G587" t="n">
-        <v>10.0830564498901</v>
+        <v>10.0830554962158</v>
       </c>
       <c r="H587" t="n">
         <v>7181497</v>
@@ -17421,7 +17421,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G588" t="n">
-        <v>10.1866588592529</v>
+        <v>10.1866598129272</v>
       </c>
       <c r="H588" t="n">
         <v>6937160</v>
@@ -17450,7 +17450,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G589" t="n">
-        <v>10.3085460662842</v>
+        <v>10.3085470199585</v>
       </c>
       <c r="H589" t="n">
         <v>5412434</v>
@@ -17479,7 +17479,7 @@
         <v>17.0550003051758</v>
       </c>
       <c r="G590" t="n">
-        <v>10.3938646316528</v>
+        <v>10.3938655853271</v>
       </c>
       <c r="H590" t="n">
         <v>5932050</v>
@@ -17508,7 +17508,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G591" t="n">
-        <v>10.1805648803711</v>
+        <v>10.1805658340454</v>
       </c>
       <c r="H591" t="n">
         <v>8959065</v>
@@ -17537,7 +17537,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>10.2628393173218</v>
+        <v>10.2628383636475</v>
       </c>
       <c r="H592" t="n">
         <v>7553796</v>
@@ -17566,7 +17566,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G593" t="n">
-        <v>10.1348571777344</v>
+        <v>10.1348581314087</v>
       </c>
       <c r="H593" t="n">
         <v>5662257</v>
@@ -17595,7 +17595,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G594" t="n">
-        <v>10.2018966674805</v>
+        <v>10.2018957138062</v>
       </c>
       <c r="H594" t="n">
         <v>5948888</v>
@@ -17653,7 +17653,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G596" t="n">
-        <v>10.2506504058838</v>
+        <v>10.2506494522095</v>
       </c>
       <c r="H596" t="n">
         <v>3996552</v>
@@ -17682,7 +17682,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G597" t="n">
-        <v>10.2262735366821</v>
+        <v>10.2262725830078</v>
       </c>
       <c r="H597" t="n">
         <v>7945721</v>
@@ -17711,7 +17711,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G598" t="n">
-        <v>10.2262735366821</v>
+        <v>10.2262725830078</v>
       </c>
       <c r="H598" t="n">
         <v>5232817</v>
@@ -17769,7 +17769,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G600" t="n">
-        <v>10.0921974182129</v>
+        <v>10.0921983718872</v>
       </c>
       <c r="H600" t="n">
         <v>5548187</v>
@@ -17827,7 +17827,7 @@
         <v>16.5</v>
       </c>
       <c r="G602" t="n">
-        <v>10.0556316375732</v>
+        <v>10.0556325912476</v>
       </c>
       <c r="H602" t="n">
         <v>3301578</v>
@@ -17856,7 +17856,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>10.0921974182129</v>
+        <v>10.0921983718872</v>
       </c>
       <c r="H603" t="n">
         <v>4190167</v>
@@ -17972,7 +17972,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G607" t="n">
-        <v>9.82404804229736</v>
+        <v>9.82404708862305</v>
       </c>
       <c r="H607" t="n">
         <v>8856874</v>
@@ -18001,7 +18001,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G608" t="n">
-        <v>9.84978294372559</v>
+        <v>9.84978199005127</v>
       </c>
       <c r="H608" t="n">
         <v>7216531</v>
@@ -18030,7 +18030,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G609" t="n">
-        <v>9.81761264801025</v>
+        <v>9.81761360168457</v>
       </c>
       <c r="H609" t="n">
         <v>8450956</v>
@@ -18059,7 +18059,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G610" t="n">
-        <v>9.70180892944336</v>
+        <v>9.70180988311768</v>
       </c>
       <c r="H610" t="n">
         <v>8050254</v>
@@ -18146,7 +18146,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G613" t="n">
-        <v>9.421950340271</v>
+        <v>9.42195129394531</v>
       </c>
       <c r="H613" t="n">
         <v>9941412</v>
@@ -18175,7 +18175,7 @@
         <v>14.1350002288818</v>
       </c>
       <c r="G614" t="n">
-        <v>9.09383869171143</v>
+        <v>9.09383773803711</v>
       </c>
       <c r="H614" t="n">
         <v>14805815</v>
@@ -18204,7 +18204,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G615" t="n">
-        <v>9.14852333068848</v>
+        <v>9.14852428436279</v>
       </c>
       <c r="H615" t="n">
         <v>11805952</v>
@@ -18233,7 +18233,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G616" t="n">
-        <v>9.36083221435547</v>
+        <v>9.36083126068115</v>
       </c>
       <c r="H616" t="n">
         <v>20903232</v>
@@ -18320,7 +18320,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G619" t="n">
-        <v>9.24502754211426</v>
+        <v>9.24502658843994</v>
       </c>
       <c r="H619" t="n">
         <v>7182041</v>
@@ -18349,7 +18349,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G620" t="n">
-        <v>9.24502754211426</v>
+        <v>9.24502658843994</v>
       </c>
       <c r="H620" t="n">
         <v>7830245</v>
@@ -18378,7 +18378,7 @@
         <v>14.4049997329712</v>
       </c>
       <c r="G621" t="n">
-        <v>9.26754570007324</v>
+        <v>9.26754379272461</v>
       </c>
       <c r="H621" t="n">
         <v>4722584</v>
@@ -18465,7 +18465,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G624" t="n">
-        <v>9.33831310272217</v>
+        <v>9.33831405639648</v>
       </c>
       <c r="H624" t="n">
         <v>4444636</v>
@@ -18552,7 +18552,7 @@
         <v>14.5950002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>9.3897819519043</v>
+        <v>9.38978099822998</v>
       </c>
       <c r="H627" t="n">
         <v>7853948</v>
@@ -18639,7 +18639,7 @@
         <v>14.6300001144409</v>
       </c>
       <c r="G630" t="n">
-        <v>9.41229915618896</v>
+        <v>9.41230010986328</v>
       </c>
       <c r="H630" t="n">
         <v>5230838</v>
@@ -18668,7 +18668,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.28684425354004</v>
+        <v>9.28684616088867</v>
       </c>
       <c r="H631" t="n">
         <v>4660571</v>
@@ -18697,7 +18697,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G632" t="n">
-        <v>9.35439682006836</v>
+        <v>9.35439777374268</v>
       </c>
       <c r="H632" t="n">
         <v>3243473</v>
@@ -18726,7 +18726,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G633" t="n">
-        <v>9.19355773925781</v>
+        <v>9.19355869293213</v>
       </c>
       <c r="H633" t="n">
         <v>3783491</v>
@@ -18784,7 +18784,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G635" t="n">
-        <v>9.19355773925781</v>
+        <v>9.19355869293213</v>
       </c>
       <c r="H635" t="n">
         <v>5340654</v>
@@ -18842,7 +18842,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G637" t="n">
-        <v>9.24502754211426</v>
+        <v>9.24502658843994</v>
       </c>
       <c r="H637" t="n">
         <v>4871372</v>
@@ -18871,7 +18871,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G638" t="n">
-        <v>9.11313915252686</v>
+        <v>9.11313819885254</v>
       </c>
       <c r="H638" t="n">
         <v>4019736</v>
@@ -18929,7 +18929,7 @@
         <v>14.2749996185303</v>
       </c>
       <c r="G640" t="n">
-        <v>9.18390846252441</v>
+        <v>9.1839075088501</v>
       </c>
       <c r="H640" t="n">
         <v>1890670</v>
@@ -18958,7 +18958,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>9.39299869537354</v>
+        <v>9.39299774169922</v>
       </c>
       <c r="H641" t="n">
         <v>6126069</v>
@@ -18987,7 +18987,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G642" t="n">
-        <v>9.35439682006836</v>
+        <v>9.35439777374268</v>
       </c>
       <c r="H642" t="n">
         <v>3149780</v>
@@ -19016,7 +19016,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G643" t="n">
-        <v>9.3576135635376</v>
+        <v>9.35761451721191</v>
       </c>
       <c r="H643" t="n">
         <v>2266231</v>
@@ -19132,7 +19132,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G647" t="n">
-        <v>9.29327964782715</v>
+        <v>9.29327869415283</v>
       </c>
       <c r="H647" t="n">
         <v>2309071</v>
@@ -19161,7 +19161,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G648" t="n">
-        <v>9.33831310272217</v>
+        <v>9.33831405639648</v>
       </c>
       <c r="H648" t="n">
         <v>2450015</v>
@@ -19219,7 +19219,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G650" t="n">
-        <v>9.4380350112915</v>
+        <v>9.43803310394287</v>
       </c>
       <c r="H650" t="n">
         <v>3330612</v>
@@ -19248,7 +19248,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>9.3994312286377</v>
+        <v>9.39943313598633</v>
       </c>
       <c r="H651" t="n">
         <v>3481748</v>
@@ -19306,7 +19306,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G653" t="n">
-        <v>9.3576135635376</v>
+        <v>9.35761451721191</v>
       </c>
       <c r="H653" t="n">
         <v>2920898</v>
@@ -19335,7 +19335,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G654" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020244598389</v>
       </c>
       <c r="H654" t="n">
         <v>3763142</v>
@@ -19364,7 +19364,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G655" t="n">
-        <v>9.48306846618652</v>
+        <v>9.48306751251221</v>
       </c>
       <c r="H655" t="n">
         <v>3921466</v>
@@ -19422,7 +19422,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G657" t="n">
-        <v>9.54740619659424</v>
+        <v>9.54740524291992</v>
       </c>
       <c r="H657" t="n">
         <v>3604056</v>
@@ -19538,7 +19538,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G661" t="n">
-        <v>9.5313196182251</v>
+        <v>9.53132057189941</v>
       </c>
       <c r="H661" t="n">
         <v>6618837</v>
@@ -19625,7 +19625,7 @@
         <v>14.9849996566772</v>
       </c>
       <c r="G664" t="n">
-        <v>9.64069175720215</v>
+        <v>9.64069080352783</v>
       </c>
       <c r="H664" t="n">
         <v>2840985</v>
@@ -19654,7 +19654,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G665" t="n">
-        <v>9.66320991516113</v>
+        <v>9.66320896148682</v>
       </c>
       <c r="H665" t="n">
         <v>2696909</v>
@@ -19712,7 +19712,7 @@
         <v>14.6850004196167</v>
       </c>
       <c r="G667" t="n">
-        <v>9.4476842880249</v>
+        <v>9.44768333435059</v>
       </c>
       <c r="H667" t="n">
         <v>5999121</v>
@@ -19741,7 +19741,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.3994312286377</v>
+        <v>9.39943313598633</v>
       </c>
       <c r="H668" t="n">
         <v>3214408</v>
@@ -19770,7 +19770,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G669" t="n">
-        <v>9.36083221435547</v>
+        <v>9.36083126068115</v>
       </c>
       <c r="H669" t="n">
         <v>3070203</v>
@@ -19799,7 +19799,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G670" t="n">
-        <v>9.39299869537354</v>
+        <v>9.39299774169922</v>
       </c>
       <c r="H670" t="n">
         <v>4538965</v>
@@ -19857,7 +19857,7 @@
         <v>14.4849996566772</v>
       </c>
       <c r="G672" t="n">
-        <v>9.31901359558105</v>
+        <v>9.31901073455811</v>
       </c>
       <c r="H672" t="n">
         <v>2664551</v>
@@ -19886,7 +19886,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G673" t="n">
-        <v>9.43481636047363</v>
+        <v>9.43481731414795</v>
       </c>
       <c r="H673" t="n">
         <v>3967619</v>
@@ -19915,7 +19915,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G674" t="n">
-        <v>9.5313196182251</v>
+        <v>9.53132057189941</v>
       </c>
       <c r="H674" t="n">
         <v>4973487</v>
@@ -19944,7 +19944,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G675" t="n">
-        <v>9.48306846618652</v>
+        <v>9.48306751251221</v>
       </c>
       <c r="H675" t="n">
         <v>2884965</v>
@@ -19973,7 +19973,7 @@
         <v>14.7749996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>9.50558662414551</v>
+        <v>9.50558471679688</v>
       </c>
       <c r="H676" t="n">
         <v>3002958</v>
@@ -20002,7 +20002,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G677" t="n">
-        <v>9.55705451965332</v>
+        <v>9.557053565979</v>
       </c>
       <c r="H677" t="n">
         <v>3150734</v>
@@ -20031,7 +20031,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G678" t="n">
-        <v>9.49915218353271</v>
+        <v>9.49915313720703</v>
       </c>
       <c r="H678" t="n">
         <v>3851946</v>
@@ -20060,7 +20060,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G679" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020244598389</v>
       </c>
       <c r="H679" t="n">
         <v>3126453</v>
@@ -20089,7 +20089,7 @@
         <v>14.5150003433228</v>
       </c>
       <c r="G680" t="n">
-        <v>9.33831310272217</v>
+        <v>9.33831405639648</v>
       </c>
       <c r="H680" t="n">
         <v>4587711</v>
@@ -20205,7 +20205,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G684" t="n">
-        <v>9.51523685455322</v>
+        <v>9.51523590087891</v>
       </c>
       <c r="H684" t="n">
         <v>7342554</v>
@@ -20234,7 +20234,7 @@
         <v>14.8249998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>9.53775310516357</v>
+        <v>9.53775405883789</v>
       </c>
       <c r="H685" t="n">
         <v>3235761</v>
@@ -20263,7 +20263,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>9.5216703414917</v>
+        <v>9.52166938781738</v>
       </c>
       <c r="H686" t="n">
         <v>3974247</v>
@@ -20292,7 +20292,7 @@
         <v>15.125</v>
       </c>
       <c r="G687" t="n">
-        <v>9.73076057434082</v>
+        <v>9.73076152801514</v>
       </c>
       <c r="H687" t="n">
         <v>8818496</v>
@@ -20437,7 +20437,7 @@
         <v>15.125</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73076057434082</v>
+        <v>9.73076152801514</v>
       </c>
       <c r="H692" t="n">
         <v>4706478</v>
@@ -20466,7 +20466,7 @@
         <v>15.1149997711182</v>
       </c>
       <c r="G693" t="n">
-        <v>9.72432613372803</v>
+        <v>9.72432708740234</v>
       </c>
       <c r="H693" t="n">
         <v>3768620</v>
@@ -20524,7 +20524,7 @@
         <v>15.1549997329712</v>
       </c>
       <c r="G695" t="n">
-        <v>9.75006103515625</v>
+        <v>9.75006198883057</v>
       </c>
       <c r="H695" t="n">
         <v>5294798</v>
@@ -20553,7 +20553,7 @@
         <v>15.3249998092651</v>
       </c>
       <c r="G696" t="n">
-        <v>9.85943126678467</v>
+        <v>9.85943222045898</v>
       </c>
       <c r="H696" t="n">
         <v>6538645</v>
@@ -20582,7 +20582,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G697" t="n">
-        <v>9.84978294372559</v>
+        <v>9.84978199005127</v>
       </c>
       <c r="H697" t="n">
         <v>2977702</v>
@@ -20640,7 +20640,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G699" t="n">
-        <v>9.98810291290283</v>
+        <v>9.98810386657715</v>
       </c>
       <c r="H699" t="n">
         <v>4372908</v>
@@ -20669,7 +20669,7 @@
         <v>15.4350004196167</v>
       </c>
       <c r="G700" t="n">
-        <v>9.93020153045654</v>
+        <v>9.93020057678223</v>
       </c>
       <c r="H700" t="n">
         <v>6167841</v>
@@ -20698,7 +20698,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G701" t="n">
-        <v>9.57313919067383</v>
+        <v>9.57313823699951</v>
       </c>
       <c r="H701" t="n">
         <v>15394005</v>
@@ -20727,7 +20727,7 @@
         <v>14.8149995803833</v>
       </c>
       <c r="G702" t="n">
-        <v>9.5313196182251</v>
+        <v>9.53132057189941</v>
       </c>
       <c r="H702" t="n">
         <v>6148547</v>
@@ -20756,7 +20756,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G703" t="n">
-        <v>9.421950340271</v>
+        <v>9.42195129394531</v>
       </c>
       <c r="H703" t="n">
         <v>6979794</v>
@@ -20785,7 +20785,7 @@
         <v>14.7150001525879</v>
       </c>
       <c r="G704" t="n">
-        <v>9.46698379516602</v>
+        <v>9.46698570251465</v>
       </c>
       <c r="H704" t="n">
         <v>5576395</v>
@@ -20814,7 +20814,7 @@
         <v>14.835000038147</v>
       </c>
       <c r="G705" t="n">
-        <v>9.54418659210205</v>
+        <v>9.54418754577637</v>
       </c>
       <c r="H705" t="n">
         <v>7437108</v>
@@ -20843,7 +20843,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G706" t="n">
-        <v>9.50880336761475</v>
+        <v>9.50880241394043</v>
       </c>
       <c r="H706" t="n">
         <v>6745914</v>
@@ -20872,7 +20872,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>9.29649639129639</v>
+        <v>9.29649448394775</v>
       </c>
       <c r="H707" t="n">
         <v>8920458</v>
@@ -20930,7 +20930,7 @@
         <v>14.4849996566772</v>
       </c>
       <c r="G709" t="n">
-        <v>9.31901359558105</v>
+        <v>9.31901073455811</v>
       </c>
       <c r="H709" t="n">
         <v>6370618</v>
@@ -20959,7 +20959,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G710" t="n">
-        <v>9.18712425231934</v>
+        <v>9.18712520599365</v>
       </c>
       <c r="H710" t="n">
         <v>8447984</v>
@@ -21017,7 +21017,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G712" t="n">
-        <v>9.09705543518066</v>
+        <v>9.09705638885498</v>
       </c>
       <c r="H712" t="n">
         <v>6246372</v>
@@ -21075,7 +21075,7 @@
         <v>14.2349996566772</v>
       </c>
       <c r="G714" t="n">
-        <v>9.15817356109619</v>
+        <v>9.15817451477051</v>
       </c>
       <c r="H714" t="n">
         <v>7725704</v>
@@ -21104,7 +21104,7 @@
         <v>14.0100002288818</v>
       </c>
       <c r="G715" t="n">
-        <v>9.01341819763184</v>
+        <v>9.01341915130615</v>
       </c>
       <c r="H715" t="n">
         <v>5889378</v>
@@ -21133,7 +21133,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G716" t="n">
-        <v>9.03915309906006</v>
+        <v>9.03915405273438</v>
       </c>
       <c r="H716" t="n">
         <v>7883378</v>
@@ -21162,7 +21162,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G717" t="n">
-        <v>9.0102014541626</v>
+        <v>9.01020240783691</v>
       </c>
       <c r="H717" t="n">
         <v>5286237</v>
@@ -21249,7 +21249,7 @@
         <v>14.0450000762939</v>
       </c>
       <c r="G720" t="n">
-        <v>9.0359354019165</v>
+        <v>9.03593635559082</v>
       </c>
       <c r="H720" t="n">
         <v>7100699</v>
@@ -21307,7 +21307,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G722" t="n">
-        <v>9.12922286987305</v>
+        <v>9.12922096252441</v>
       </c>
       <c r="H722" t="n">
         <v>5881506</v>
@@ -21336,7 +21336,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G723" t="n">
-        <v>9.11313915252686</v>
+        <v>9.11313819885254</v>
       </c>
       <c r="H723" t="n">
         <v>5055256</v>
@@ -21365,7 +21365,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G724" t="n">
-        <v>9.18712425231934</v>
+        <v>9.18712520599365</v>
       </c>
       <c r="H724" t="n">
         <v>5408171</v>
@@ -21423,7 +21423,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>9.25467872619629</v>
+        <v>9.25467777252197</v>
       </c>
       <c r="H726" t="n">
         <v>3691753</v>
@@ -21481,7 +21481,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G728" t="n">
-        <v>9.18712425231934</v>
+        <v>9.18712520599365</v>
       </c>
       <c r="H728" t="n">
         <v>2598306</v>
@@ -21510,7 +21510,7 @@
         <v>14.375</v>
       </c>
       <c r="G729" t="n">
-        <v>9.24824237823486</v>
+        <v>9.24824333190918</v>
       </c>
       <c r="H729" t="n">
         <v>4373616</v>
@@ -21539,7 +21539,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G730" t="n">
-        <v>9.25467872619629</v>
+        <v>9.25467777252197</v>
       </c>
       <c r="H730" t="n">
         <v>3623659</v>
@@ -21568,7 +21568,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G731" t="n">
-        <v>9.28684425354004</v>
+        <v>9.28684616088867</v>
       </c>
       <c r="H731" t="n">
         <v>3128092</v>
@@ -21597,7 +21597,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>9.19355773925781</v>
+        <v>9.19355869293213</v>
       </c>
       <c r="H732" t="n">
         <v>2832097</v>
@@ -21626,7 +21626,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G733" t="n">
-        <v>9.25789451599121</v>
+        <v>9.25789356231689</v>
       </c>
       <c r="H733" t="n">
         <v>3847030</v>
@@ -21684,7 +21684,7 @@
         <v>14.25</v>
       </c>
       <c r="G735" t="n">
-        <v>9.16782474517822</v>
+        <v>9.16782569885254</v>
       </c>
       <c r="H735" t="n">
         <v>4196176</v>
@@ -21713,7 +21713,7 @@
         <v>14.4449996948242</v>
       </c>
       <c r="G736" t="n">
-        <v>9.29327964782715</v>
+        <v>9.29327869415283</v>
       </c>
       <c r="H736" t="n">
         <v>5249328</v>
@@ -21742,7 +21742,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G737" t="n">
-        <v>9.30292797088623</v>
+        <v>9.30292892456055</v>
       </c>
       <c r="H737" t="n">
         <v>4897438</v>
@@ -21771,7 +21771,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G738" t="n">
-        <v>9.10992240905762</v>
+        <v>9.1099214553833</v>
       </c>
       <c r="H738" t="n">
         <v>6954782</v>
@@ -21800,7 +21800,7 @@
         <v>14.2849998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>9.19034194946289</v>
+        <v>9.19034004211426</v>
       </c>
       <c r="H739" t="n">
         <v>7573101</v>
@@ -21829,7 +21829,7 @@
         <v>14.2250003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>9.15174007415771</v>
+        <v>9.1517391204834</v>
       </c>
       <c r="H740" t="n">
         <v>4519581</v>
@@ -21887,7 +21887,7 @@
         <v>14.6149997711182</v>
       </c>
       <c r="G742" t="n">
-        <v>9.40265083312988</v>
+        <v>9.40264987945557</v>
       </c>
       <c r="H742" t="n">
         <v>7176150</v>
@@ -21945,7 +21945,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G744" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020244598389</v>
       </c>
       <c r="H744" t="n">
         <v>3824756</v>
@@ -21974,7 +21974,7 @@
         <v>14.7550001144409</v>
       </c>
       <c r="G745" t="n">
-        <v>9.49271965026855</v>
+        <v>9.49271869659424</v>
       </c>
       <c r="H745" t="n">
         <v>4385314</v>
@@ -22003,7 +22003,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G746" t="n">
-        <v>9.57957077026367</v>
+        <v>9.5795726776123</v>
       </c>
       <c r="H746" t="n">
         <v>5194375</v>
@@ -22032,7 +22032,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>9.65677452087402</v>
+        <v>9.65677738189697</v>
       </c>
       <c r="H747" t="n">
         <v>7459546</v>
@@ -22090,7 +22090,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G749" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020244598389</v>
       </c>
       <c r="H749" t="n">
         <v>5686754</v>
@@ -22119,7 +22119,7 @@
         <v>14.2849998474121</v>
       </c>
       <c r="G750" t="n">
-        <v>9.19034194946289</v>
+        <v>9.19034004211426</v>
       </c>
       <c r="H750" t="n">
         <v>10197579</v>
@@ -22235,7 +22235,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G754" t="n">
-        <v>9.23537540435791</v>
+        <v>9.23537635803223</v>
       </c>
       <c r="H754" t="n">
         <v>6843267</v>
@@ -22264,7 +22264,7 @@
         <v>14.414999961853</v>
       </c>
       <c r="G755" t="n">
-        <v>9.27397632598877</v>
+        <v>9.2739782333374</v>
       </c>
       <c r="H755" t="n">
         <v>5735243</v>
@@ -22293,7 +22293,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G756" t="n">
-        <v>9.25467872619629</v>
+        <v>9.25467777252197</v>
       </c>
       <c r="H756" t="n">
         <v>5037982</v>
@@ -22380,7 +22380,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>9.421950340271</v>
+        <v>9.42195129394531</v>
       </c>
       <c r="H759" t="n">
         <v>8335712</v>
@@ -22467,7 +22467,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G762" t="n">
-        <v>9.24502754211426</v>
+        <v>9.24502658843994</v>
       </c>
       <c r="H762" t="n">
         <v>6405329</v>
@@ -22496,7 +22496,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G763" t="n">
-        <v>9.39299869537354</v>
+        <v>9.39299774169922</v>
       </c>
       <c r="H763" t="n">
         <v>5261654</v>
@@ -22525,7 +22525,7 @@
         <v>14.5050001144409</v>
       </c>
       <c r="G764" t="n">
-        <v>9.33188056945801</v>
+        <v>9.33187961578369</v>
       </c>
       <c r="H764" t="n">
         <v>4847874</v>
@@ -22554,7 +22554,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G765" t="n">
-        <v>9.3576135635376</v>
+        <v>9.35761451721191</v>
       </c>
       <c r="H765" t="n">
         <v>5061299</v>
@@ -22583,7 +22583,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G766" t="n">
-        <v>9.47663402557373</v>
+        <v>9.47663497924805</v>
       </c>
       <c r="H766" t="n">
         <v>7307102</v>
@@ -22612,7 +22612,7 @@
         <v>14.6850004196167</v>
       </c>
       <c r="G767" t="n">
-        <v>9.4476842880249</v>
+        <v>9.44768333435059</v>
       </c>
       <c r="H767" t="n">
         <v>4428502</v>
@@ -22670,7 +22670,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G769" t="n">
-        <v>9.52810382843018</v>
+        <v>9.52810478210449</v>
       </c>
       <c r="H769" t="n">
         <v>6671972</v>
@@ -22699,7 +22699,7 @@
         <v>14.789999961853</v>
       </c>
       <c r="G770" t="n">
-        <v>9.51523685455322</v>
+        <v>9.51523590087891</v>
       </c>
       <c r="H770" t="n">
         <v>5633944</v>
@@ -22728,7 +22728,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G771" t="n">
-        <v>9.59565544128418</v>
+        <v>9.59565734863281</v>
       </c>
       <c r="H771" t="n">
         <v>5525152</v>
@@ -22757,7 +22757,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>9.61817264556885</v>
+        <v>9.61817455291748</v>
       </c>
       <c r="H772" t="n">
         <v>3832986</v>
@@ -22786,7 +22786,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G773" t="n">
-        <v>9.63747406005859</v>
+        <v>9.63747310638428</v>
       </c>
       <c r="H773" t="n">
         <v>6218318</v>
@@ -22815,7 +22815,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G774" t="n">
-        <v>9.79831314086914</v>
+        <v>9.79831218719482</v>
       </c>
       <c r="H774" t="n">
         <v>7912891</v>
@@ -22844,7 +22844,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G775" t="n">
-        <v>9.81761264801025</v>
+        <v>9.81761360168457</v>
       </c>
       <c r="H775" t="n">
         <v>5071870</v>
@@ -22902,7 +22902,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G777" t="n">
-        <v>9.90446758270264</v>
+        <v>9.90446662902832</v>
       </c>
       <c r="H777" t="n">
         <v>3603506</v>
@@ -22931,7 +22931,7 @@
         <v>15.3149995803833</v>
       </c>
       <c r="G778" t="n">
-        <v>9.85299873352051</v>
+        <v>9.85299777984619</v>
       </c>
       <c r="H778" t="n">
         <v>5736013</v>
@@ -22960,7 +22960,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G779" t="n">
-        <v>9.89481639862061</v>
+        <v>9.89481735229492</v>
       </c>
       <c r="H779" t="n">
         <v>5979931</v>
@@ -22989,7 +22989,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G780" t="n">
-        <v>9.87551689147949</v>
+        <v>9.87551498413086</v>
       </c>
       <c r="H780" t="n">
         <v>6607168</v>
@@ -23047,7 +23047,7 @@
         <v>15.4350004196167</v>
       </c>
       <c r="G782" t="n">
-        <v>9.93020153045654</v>
+        <v>9.93020057678223</v>
       </c>
       <c r="H782" t="n">
         <v>5355352</v>
@@ -23076,7 +23076,7 @@
         <v>15.4449996948242</v>
       </c>
       <c r="G783" t="n">
-        <v>9.93663311004639</v>
+        <v>9.9366340637207</v>
       </c>
       <c r="H783" t="n">
         <v>4741959</v>
@@ -23163,7 +23163,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G786" t="n">
-        <v>9.76614665985107</v>
+        <v>9.76614570617676</v>
       </c>
       <c r="H786" t="n">
         <v>7341415</v>
@@ -23192,7 +23192,7 @@
         <v>15.25</v>
       </c>
       <c r="G787" t="n">
-        <v>9.81118011474609</v>
+        <v>9.81118106842041</v>
       </c>
       <c r="H787" t="n">
         <v>5078796</v>
@@ -23250,7 +23250,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G789" t="n">
-        <v>9.79831314086914</v>
+        <v>9.79831218719482</v>
       </c>
       <c r="H789" t="n">
         <v>6280350</v>
@@ -23308,7 +23308,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G791" t="n">
-        <v>9.59565544128418</v>
+        <v>9.59565734863281</v>
       </c>
       <c r="H791" t="n">
         <v>7002729</v>
@@ -23366,7 +23366,7 @@
         <v>15.0749998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>9.69859313964844</v>
+        <v>9.69859218597412</v>
       </c>
       <c r="H793" t="n">
         <v>4491564</v>
@@ -23395,7 +23395,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G794" t="n">
-        <v>9.77258014678955</v>
+        <v>9.77257919311523</v>
       </c>
       <c r="H794" t="n">
         <v>5015536</v>
@@ -23453,7 +23453,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G796" t="n">
-        <v>9.79831314086914</v>
+        <v>9.79831218719482</v>
       </c>
       <c r="H796" t="n">
         <v>6917671</v>
@@ -23511,7 +23511,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G798" t="n">
-        <v>9.75649547576904</v>
+        <v>9.75649452209473</v>
       </c>
       <c r="H798" t="n">
         <v>4227766</v>
@@ -23540,7 +23540,7 @@
         <v>15.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>9.7950963973999</v>
+        <v>9.79509735107422</v>
       </c>
       <c r="H799" t="n">
         <v>3880189</v>
@@ -23598,7 +23598,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G801" t="n">
-        <v>9.83691501617432</v>
+        <v>9.83691310882568</v>
       </c>
       <c r="H801" t="n">
         <v>3764489</v>
@@ -23685,7 +23685,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G804" t="n">
-        <v>9.99131965637207</v>
+        <v>9.99132061004639</v>
       </c>
       <c r="H804" t="n">
         <v>5132683</v>
@@ -23714,7 +23714,7 @@
         <v>15.6949996948242</v>
       </c>
       <c r="G805" t="n">
-        <v>10.0974731445312</v>
+        <v>10.0974740982056</v>
       </c>
       <c r="H805" t="n">
         <v>5945945</v>
@@ -23772,7 +23772,7 @@
         <v>15.8850002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2197122573853</v>
+        <v>10.2197103500366</v>
       </c>
       <c r="H807" t="n">
         <v>6214672</v>
@@ -23830,7 +23830,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G809" t="n">
-        <v>10.2840461730957</v>
+        <v>10.28404712677</v>
       </c>
       <c r="H809" t="n">
         <v>4752978</v>
@@ -23859,7 +23859,7 @@
         <v>15.7950000762939</v>
       </c>
       <c r="G810" t="n">
-        <v>10.161808013916</v>
+        <v>10.1618089675903</v>
       </c>
       <c r="H810" t="n">
         <v>7293852</v>
@@ -23946,7 +23946,7 @@
         <v>15.7650003433228</v>
       </c>
       <c r="G813" t="n">
-        <v>10.1425094604492</v>
+        <v>10.1425085067749</v>
       </c>
       <c r="H813" t="n">
         <v>3300941</v>
@@ -24004,7 +24004,7 @@
         <v>16.0049991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>10.2969131469727</v>
+        <v>10.296911239624</v>
       </c>
       <c r="H815" t="n">
         <v>7739191</v>
@@ -24091,7 +24091,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G818" t="n">
-        <v>10.5896396636963</v>
+        <v>10.5896406173706</v>
       </c>
       <c r="H818" t="n">
         <v>4416257</v>
@@ -24120,7 +24120,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G819" t="n">
-        <v>10.563907623291</v>
+        <v>10.5639066696167</v>
       </c>
       <c r="H819" t="n">
         <v>5562238</v>
@@ -24178,7 +24178,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>10.5188722610474</v>
+        <v>10.518871307373</v>
       </c>
       <c r="H821" t="n">
         <v>5067259</v>
@@ -24236,7 +24236,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G823" t="n">
-        <v>10.5060043334961</v>
+        <v>10.5060052871704</v>
       </c>
       <c r="H823" t="n">
         <v>4007846</v>
@@ -24265,7 +24265,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G824" t="n">
-        <v>10.563907623291</v>
+        <v>10.5639066696167</v>
       </c>
       <c r="H824" t="n">
         <v>5992641</v>
@@ -24323,7 +24323,7 @@
         <v>16.5</v>
       </c>
       <c r="G826" t="n">
-        <v>10.6153755187988</v>
+        <v>10.6153764724731</v>
       </c>
       <c r="H826" t="n">
         <v>4444851</v>
@@ -24352,7 +24352,7 @@
         <v>16.6749992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7279615402222</v>
+        <v>10.7279605865479</v>
       </c>
       <c r="H827" t="n">
         <v>6192800</v>
@@ -24381,7 +24381,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G828" t="n">
-        <v>10.7022294998169</v>
+        <v>10.7022285461426</v>
       </c>
       <c r="H828" t="n">
         <v>5428271</v>
@@ -24410,7 +24410,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G829" t="n">
-        <v>10.7536954879761</v>
+        <v>10.7536973953247</v>
       </c>
       <c r="H829" t="n">
         <v>6674243</v>
@@ -24439,7 +24439,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7472629547119</v>
+        <v>10.7472639083862</v>
       </c>
       <c r="H830" t="n">
         <v>4446789</v>
@@ -24468,7 +24468,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G831" t="n">
-        <v>10.699010848999</v>
+        <v>10.6990118026733</v>
       </c>
       <c r="H831" t="n">
         <v>4781193</v>
@@ -24526,7 +24526,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G833" t="n">
-        <v>10.7022294998169</v>
+        <v>10.7022285461426</v>
       </c>
       <c r="H833" t="n">
         <v>4164996</v>
@@ -24555,7 +24555,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G834" t="n">
-        <v>10.7247457504272</v>
+        <v>10.7247467041016</v>
       </c>
       <c r="H834" t="n">
         <v>3369925</v>
@@ -24584,7 +24584,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G835" t="n">
-        <v>10.7504796981812</v>
+        <v>10.7504777908325</v>
       </c>
       <c r="H835" t="n">
         <v>5048841</v>
@@ -24613,7 +24613,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G836" t="n">
-        <v>10.8180322647095</v>
+        <v>10.8180332183838</v>
       </c>
       <c r="H836" t="n">
         <v>3884407</v>
@@ -24671,7 +24671,7 @@
         <v>17</v>
       </c>
       <c r="G838" t="n">
-        <v>10.9370527267456</v>
+        <v>10.9370536804199</v>
       </c>
       <c r="H838" t="n">
         <v>4478368</v>
@@ -24700,7 +24700,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>11.0657262802124</v>
+        <v>11.0657243728638</v>
       </c>
       <c r="H839" t="n">
         <v>7844547</v>
@@ -24787,7 +24787,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G842" t="n">
-        <v>10.9434862136841</v>
+        <v>10.9434852600098</v>
       </c>
       <c r="H842" t="n">
         <v>4191742</v>
@@ -24816,7 +24816,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>10.9756536483765</v>
+        <v>10.9756546020508</v>
       </c>
       <c r="H843" t="n">
         <v>3734993</v>
@@ -24845,7 +24845,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G844" t="n">
-        <v>11.091459274292</v>
+        <v>11.0914573669434</v>
       </c>
       <c r="H844" t="n">
         <v>5493569</v>
@@ -24874,7 +24874,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G845" t="n">
-        <v>11.0625066757202</v>
+        <v>11.0625076293945</v>
       </c>
       <c r="H845" t="n">
         <v>4475044</v>
@@ -24903,7 +24903,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G846" t="n">
-        <v>11.1300601959229</v>
+        <v>11.1300592422485</v>
       </c>
       <c r="H846" t="n">
         <v>4387043</v>
@@ -24961,7 +24961,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G848" t="n">
-        <v>11.1364936828613</v>
+        <v>11.136492729187</v>
       </c>
       <c r="H848" t="n">
         <v>4240886</v>
@@ -24990,7 +24990,7 @@
         <v>17.1550006866455</v>
       </c>
       <c r="G849" t="n">
-        <v>11.0367736816406</v>
+        <v>11.0367727279663</v>
       </c>
       <c r="H849" t="n">
         <v>5715128</v>
@@ -25077,7 +25077,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G852" t="n">
-        <v>10.8437662124634</v>
+        <v>10.8437671661377</v>
       </c>
       <c r="H852" t="n">
         <v>6694199</v>
@@ -25106,7 +25106,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G853" t="n">
-        <v>10.8823680877686</v>
+        <v>10.8823690414429</v>
       </c>
       <c r="H853" t="n">
         <v>4449894</v>
@@ -25135,7 +25135,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G854" t="n">
-        <v>10.8180322647095</v>
+        <v>10.8180332183838</v>
       </c>
       <c r="H854" t="n">
         <v>5182170</v>
@@ -25164,7 +25164,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G855" t="n">
-        <v>10.9756536483765</v>
+        <v>10.9756546020508</v>
       </c>
       <c r="H855" t="n">
         <v>7218056</v>
@@ -25193,7 +25193,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G856" t="n">
-        <v>10.9306201934814</v>
+        <v>10.9306211471558</v>
       </c>
       <c r="H856" t="n">
         <v>7020709</v>
@@ -25222,7 +25222,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G857" t="n">
-        <v>11.0206890106201</v>
+        <v>11.0206899642944</v>
       </c>
       <c r="H857" t="n">
         <v>11497461</v>
@@ -25309,7 +25309,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G860" t="n">
-        <v>11.093113899231</v>
+        <v>11.0931148529053</v>
       </c>
       <c r="H860" t="n">
         <v>5564986</v>
@@ -25338,7 +25338,7 @@
         <v>16.2950000762939</v>
       </c>
       <c r="G861" t="n">
-        <v>11.0693378448486</v>
+        <v>11.0693387985229</v>
       </c>
       <c r="H861" t="n">
         <v>4916433</v>
@@ -25367,7 +25367,7 @@
         <v>15.9549999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>10.8383722305298</v>
+        <v>10.8383741378784</v>
       </c>
       <c r="H862" t="n">
         <v>6673601</v>
@@ -25396,7 +25396,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G863" t="n">
-        <v>11.0557527542114</v>
+        <v>11.0557518005371</v>
       </c>
       <c r="H863" t="n">
         <v>6522584</v>
@@ -25425,7 +25425,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G864" t="n">
-        <v>10.9300813674927</v>
+        <v>10.9300804138184</v>
       </c>
       <c r="H864" t="n">
         <v>3723041</v>
@@ -25454,7 +25454,7 @@
         <v>15.9750003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>10.8519601821899</v>
+        <v>10.8519592285156</v>
       </c>
       <c r="H865" t="n">
         <v>13063051</v>
@@ -25483,7 +25483,7 @@
         <v>15.8050003051758</v>
       </c>
       <c r="G866" t="n">
-        <v>10.7364778518677</v>
+        <v>10.7364768981934</v>
       </c>
       <c r="H866" t="n">
         <v>7527854</v>
@@ -25541,7 +25541,7 @@
         <v>15.7150001525879</v>
       </c>
       <c r="G868" t="n">
-        <v>10.6753406524658</v>
+        <v>10.6753396987915</v>
       </c>
       <c r="H868" t="n">
         <v>5377229</v>
@@ -25599,7 +25599,7 @@
         <v>15.8900003433228</v>
       </c>
       <c r="G870" t="n">
-        <v>10.7942190170288</v>
+        <v>10.7942180633545</v>
       </c>
       <c r="H870" t="n">
         <v>5980767</v>
@@ -25628,7 +25628,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G871" t="n">
-        <v>10.705906867981</v>
+        <v>10.7059087753296</v>
       </c>
       <c r="H871" t="n">
         <v>5081405</v>
@@ -25657,7 +25657,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G872" t="n">
-        <v>10.7432689666748</v>
+        <v>10.7432699203491</v>
       </c>
       <c r="H872" t="n">
         <v>3961660</v>
@@ -25686,7 +25686,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G873" t="n">
-        <v>10.7704429626465</v>
+        <v>10.7704410552979</v>
       </c>
       <c r="H873" t="n">
         <v>3670515</v>
@@ -25744,7 +25744,7 @@
         <v>16.1450004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>10.9674415588379</v>
+        <v>10.9674434661865</v>
       </c>
       <c r="H875" t="n">
         <v>5411436</v>
@@ -25831,7 +25831,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G878" t="n">
-        <v>10.9606485366821</v>
+        <v>10.9606494903564</v>
       </c>
       <c r="H878" t="n">
         <v>3221022</v>
@@ -25860,7 +25860,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G879" t="n">
-        <v>11.0285806655884</v>
+        <v>11.0285816192627</v>
       </c>
       <c r="H879" t="n">
         <v>4436010</v>
@@ -25889,7 +25889,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G880" t="n">
-        <v>11.2459592819214</v>
+        <v>11.2459583282471</v>
       </c>
       <c r="H880" t="n">
         <v>7655669</v>
@@ -25918,7 +25918,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>11.310492515564</v>
+        <v>11.3104934692383</v>
       </c>
       <c r="H881" t="n">
         <v>4115535</v>
@@ -25947,7 +25947,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G882" t="n">
-        <v>11.2459592819214</v>
+        <v>11.2459583282471</v>
       </c>
       <c r="H882" t="n">
         <v>6413430</v>
@@ -26034,7 +26034,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G885" t="n">
-        <v>11.2867183685303</v>
+        <v>11.2867164611816</v>
       </c>
       <c r="H885" t="n">
         <v>4522112</v>
@@ -26063,7 +26063,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G886" t="n">
-        <v>11.2493553161621</v>
+        <v>11.2493562698364</v>
       </c>
       <c r="H886" t="n">
         <v>3310005</v>
@@ -26092,7 +26092,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G887" t="n">
-        <v>11.2153902053833</v>
+        <v>11.2153911590576</v>
       </c>
       <c r="H887" t="n">
         <v>3454666</v>
@@ -26121,7 +26121,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G888" t="n">
-        <v>11.2493553161621</v>
+        <v>11.2493562698364</v>
       </c>
       <c r="H888" t="n">
         <v>3064973</v>
@@ -26179,7 +26179,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G890" t="n">
-        <v>11.3886137008667</v>
+        <v>11.388614654541</v>
       </c>
       <c r="H890" t="n">
         <v>3977815</v>
@@ -26208,7 +26208,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G891" t="n">
-        <v>11.5924081802368</v>
+        <v>11.5924072265625</v>
       </c>
       <c r="H891" t="n">
         <v>6806510</v>
@@ -26237,7 +26237,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>11.6161813735962</v>
+        <v>11.6161823272705</v>
       </c>
       <c r="H892" t="n">
         <v>4154194</v>
@@ -26295,7 +26295,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G894" t="n">
-        <v>11.6263723373413</v>
+        <v>11.6263704299927</v>
       </c>
       <c r="H894" t="n">
         <v>3571789</v>
@@ -26353,7 +26353,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G896" t="n">
-        <v>11.6909046173096</v>
+        <v>11.6909065246582</v>
       </c>
       <c r="H896" t="n">
         <v>4822629</v>
@@ -26440,7 +26440,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G899" t="n">
-        <v>11.6637334823608</v>
+        <v>11.6637353897095</v>
       </c>
       <c r="H899" t="n">
         <v>2281702</v>
@@ -26498,7 +26498,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G901" t="n">
-        <v>11.5924081802368</v>
+        <v>11.5924072265625</v>
       </c>
       <c r="H901" t="n">
         <v>3894252</v>
@@ -26527,7 +26527,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G902" t="n">
-        <v>11.6025943756104</v>
+        <v>11.6025953292847</v>
       </c>
       <c r="H902" t="n">
         <v>5144636</v>
@@ -26556,7 +26556,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>11.480320930481</v>
+        <v>11.4803190231323</v>
       </c>
       <c r="H903" t="n">
         <v>5977321</v>
@@ -26585,7 +26585,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>11.5142879486084</v>
+        <v>11.5142869949341</v>
       </c>
       <c r="H904" t="n">
         <v>2305715</v>
@@ -26643,7 +26643,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G906" t="n">
-        <v>11.5448541641235</v>
+        <v>11.5448560714722</v>
       </c>
       <c r="H906" t="n">
         <v>2763422</v>
@@ -26730,7 +26730,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>11.5142879486084</v>
+        <v>11.5142869949341</v>
       </c>
       <c r="H909" t="n">
         <v>2559783</v>
@@ -26759,7 +26759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G910" t="n">
-        <v>11.3512516021729</v>
+        <v>11.3512496948242</v>
       </c>
       <c r="H910" t="n">
         <v>4261569</v>
@@ -26788,7 +26788,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G911" t="n">
-        <v>11.4395627975464</v>
+        <v>11.4395618438721</v>
       </c>
       <c r="H911" t="n">
         <v>3336326</v>
@@ -26817,7 +26817,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G912" t="n">
-        <v>11.4497518539429</v>
+        <v>11.4497528076172</v>
       </c>
       <c r="H912" t="n">
         <v>3548781</v>
@@ -26846,7 +26846,7 @@
         <v>16.6149997711182</v>
       </c>
       <c r="G913" t="n">
-        <v>11.2867183685303</v>
+        <v>11.2867164611816</v>
       </c>
       <c r="H913" t="n">
         <v>6750717</v>
@@ -26875,7 +26875,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G914" t="n">
-        <v>11.1678380966187</v>
+        <v>11.167839050293</v>
       </c>
       <c r="H914" t="n">
         <v>5521656</v>
@@ -26933,7 +26933,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G916" t="n">
-        <v>11.0795278549194</v>
+        <v>11.0795288085938</v>
       </c>
       <c r="H916" t="n">
         <v>4809948</v>
@@ -26991,7 +26991,7 @@
         <v>15.9899997711182</v>
       </c>
       <c r="G918" t="n">
-        <v>10.8621482849121</v>
+        <v>10.8621492385864</v>
       </c>
       <c r="H918" t="n">
         <v>7884078</v>
@@ -27049,7 +27049,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G920" t="n">
-        <v>10.9572505950928</v>
+        <v>10.9572534561157</v>
       </c>
       <c r="H920" t="n">
         <v>5133573</v>
@@ -27078,7 +27078,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G921" t="n">
-        <v>10.8145980834961</v>
+        <v>10.8145971298218</v>
       </c>
       <c r="H921" t="n">
         <v>5242099</v>
@@ -27136,7 +27136,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>10.9878215789795</v>
+        <v>10.9878196716309</v>
       </c>
       <c r="H923" t="n">
         <v>4102021</v>
@@ -27223,7 +27223,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G926" t="n">
-        <v>11.0863199234009</v>
+        <v>11.0863208770752</v>
       </c>
       <c r="H926" t="n">
         <v>3539056</v>
@@ -27252,7 +27252,7 @@
         <v>16.1650009155273</v>
       </c>
       <c r="G927" t="n">
-        <v>10.9810285568237</v>
+        <v>10.981029510498</v>
       </c>
       <c r="H927" t="n">
         <v>3699524</v>
@@ -27281,7 +27281,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G928" t="n">
-        <v>10.9946155548096</v>
+        <v>10.9946136474609</v>
       </c>
       <c r="H928" t="n">
         <v>2458143</v>
@@ -27310,7 +27310,7 @@
         <v>16.4300003051758</v>
       </c>
       <c r="G929" t="n">
-        <v>11.1610469818115</v>
+        <v>11.1610460281372</v>
       </c>
       <c r="H929" t="n">
         <v>5109052</v>
@@ -27368,7 +27368,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G931" t="n">
-        <v>11.1542530059814</v>
+        <v>11.1542520523071</v>
       </c>
       <c r="H931" t="n">
         <v>5445382</v>
@@ -27455,7 +27455,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G934" t="n">
-        <v>11.2391653060913</v>
+        <v>11.2391662597656</v>
       </c>
       <c r="H934" t="n">
         <v>3039642</v>
@@ -27542,7 +27542,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G937" t="n">
-        <v>11.6195802688599</v>
+        <v>11.6195783615112</v>
       </c>
       <c r="H937" t="n">
         <v>3814962</v>
@@ -27571,7 +27571,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>11.6841144561768</v>
+        <v>11.6841125488281</v>
       </c>
       <c r="H938" t="n">
         <v>3641753</v>
@@ -27600,7 +27600,7 @@
         <v>17.1749992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>11.6671304702759</v>
+        <v>11.6671295166016</v>
       </c>
       <c r="H939" t="n">
         <v>4568118</v>
@@ -27629,7 +27629,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>11.7792167663574</v>
+        <v>11.7792158126831</v>
       </c>
       <c r="H940" t="n">
         <v>4894449</v>
@@ -27658,7 +27658,7 @@
         <v>17.5</v>
       </c>
       <c r="G941" t="n">
-        <v>11.8879051208496</v>
+        <v>11.8879041671753</v>
       </c>
       <c r="H941" t="n">
         <v>6663877</v>
@@ -27687,7 +27687,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>11.8709230422974</v>
+        <v>11.8709239959717</v>
       </c>
       <c r="H942" t="n">
         <v>4537332</v>
@@ -27716,7 +27716,7 @@
         <v>17.375</v>
       </c>
       <c r="G943" t="n">
-        <v>11.8029909133911</v>
+        <v>11.8029928207397</v>
       </c>
       <c r="H943" t="n">
         <v>4120923</v>
@@ -27745,7 +27745,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>11.7690277099609</v>
+        <v>11.7690267562866</v>
       </c>
       <c r="H944" t="n">
         <v>4467012</v>
@@ -27774,7 +27774,7 @@
         <v>17.5</v>
       </c>
       <c r="G945" t="n">
-        <v>11.8879051208496</v>
+        <v>11.8879041671753</v>
       </c>
       <c r="H945" t="n">
         <v>5084522</v>
@@ -27832,7 +27832,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G947" t="n">
-        <v>12.1222677230835</v>
+        <v>12.1222686767578</v>
       </c>
       <c r="H947" t="n">
         <v>8929122</v>
@@ -27919,7 +27919,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G950" t="n">
-        <v>12.2003879547119</v>
+        <v>12.2003870010376</v>
       </c>
       <c r="H950" t="n">
         <v>3608491</v>
@@ -27977,7 +27977,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G952" t="n">
-        <v>12.1324586868286</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="H952" t="n">
         <v>4910819</v>
@@ -28006,7 +28006,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G953" t="n">
-        <v>12.0781126022339</v>
+        <v>12.0781135559082</v>
       </c>
       <c r="H953" t="n">
         <v>4061112</v>
@@ -28035,7 +28035,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G954" t="n">
-        <v>12.0509395599365</v>
+        <v>12.0509386062622</v>
       </c>
       <c r="H954" t="n">
         <v>4557669</v>
@@ -28064,7 +28064,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>11.8505420684814</v>
+        <v>11.8505430221558</v>
       </c>
       <c r="H955" t="n">
         <v>5138420</v>
@@ -28093,7 +28093,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G956" t="n">
-        <v>11.915078163147</v>
+        <v>11.9150800704956</v>
       </c>
       <c r="H956" t="n">
         <v>4343823</v>
@@ -28122,7 +28122,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>11.989803314209</v>
+        <v>11.9898023605347</v>
       </c>
       <c r="H957" t="n">
         <v>4248844</v>
@@ -28151,7 +28151,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G958" t="n">
-        <v>12.0713186264038</v>
+        <v>12.0713195800781</v>
       </c>
       <c r="H958" t="n">
         <v>3463562</v>
@@ -28180,7 +28180,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G959" t="n">
-        <v>12.0543365478516</v>
+        <v>12.0543384552002</v>
       </c>
       <c r="H959" t="n">
         <v>3167788</v>
@@ -28209,7 +28209,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G960" t="n">
-        <v>12.112078666687</v>
+        <v>12.1120777130127</v>
       </c>
       <c r="H960" t="n">
         <v>4099425</v>
@@ -28354,7 +28354,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G965" t="n">
-        <v>12.3022861480713</v>
+        <v>12.3022832870483</v>
       </c>
       <c r="H965" t="n">
         <v>3326854</v>
@@ -28383,7 +28383,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G966" t="n">
-        <v>12.2954912185669</v>
+        <v>12.2954921722412</v>
       </c>
       <c r="H966" t="n">
         <v>3766475</v>
@@ -28412,7 +28412,7 @@
         <v>18.1949996948242</v>
       </c>
       <c r="G967" t="n">
-        <v>12.3600254058838</v>
+        <v>12.3600244522095</v>
       </c>
       <c r="H967" t="n">
         <v>4285136</v>
@@ -28441,7 +28441,7 @@
         <v>18.375</v>
       </c>
       <c r="G968" t="n">
-        <v>12.4823017120361</v>
+        <v>12.4823007583618</v>
       </c>
       <c r="H968" t="n">
         <v>3753476</v>
@@ -28470,7 +28470,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G969" t="n">
-        <v>12.4687128067017</v>
+        <v>12.4687156677246</v>
       </c>
       <c r="H969" t="n">
         <v>3364987</v>
@@ -28557,7 +28557,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G972" t="n">
-        <v>12.4687128067017</v>
+        <v>12.4687156677246</v>
       </c>
       <c r="H972" t="n">
         <v>2775647</v>
@@ -28586,7 +28586,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G973" t="n">
-        <v>12.4958877563477</v>
+        <v>12.495888710022</v>
       </c>
       <c r="H973" t="n">
         <v>3161319</v>
@@ -28615,7 +28615,7 @@
         <v>18.3649997711182</v>
       </c>
       <c r="G974" t="n">
-        <v>12.4755086898804</v>
+        <v>12.4755096435547</v>
       </c>
       <c r="H974" t="n">
         <v>2897928</v>
@@ -28644,7 +28644,7 @@
         <v>18.2350006103516</v>
       </c>
       <c r="G975" t="n">
-        <v>12.3871984481812</v>
+        <v>12.3871974945068</v>
       </c>
       <c r="H975" t="n">
         <v>3479460</v>
@@ -28702,7 +28702,7 @@
         <v>18.375</v>
       </c>
       <c r="G977" t="n">
-        <v>12.4823017120361</v>
+        <v>12.4823007583618</v>
       </c>
       <c r="H977" t="n">
         <v>3216034</v>
@@ -28731,7 +28731,7 @@
         <v>18.5</v>
       </c>
       <c r="G978" t="n">
-        <v>12.567214012146</v>
+        <v>12.5672149658203</v>
       </c>
       <c r="H978" t="n">
         <v>4920828</v>
@@ -28760,7 +28760,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G979" t="n">
-        <v>12.6283531188965</v>
+        <v>12.6283540725708</v>
       </c>
       <c r="H979" t="n">
         <v>4067725</v>
@@ -28789,7 +28789,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G980" t="n">
-        <v>12.6317462921143</v>
+        <v>12.6317491531372</v>
       </c>
       <c r="H980" t="n">
         <v>4011817</v>
@@ -28818,7 +28818,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>13.0631103515625</v>
+        <v>13.0631093978882</v>
       </c>
       <c r="H981" t="n">
         <v>14625686</v>
@@ -28847,7 +28847,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G982" t="n">
-        <v>13.0291452407837</v>
+        <v>13.029146194458</v>
       </c>
       <c r="H982" t="n">
         <v>5717242</v>
@@ -28876,7 +28876,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G983" t="n">
-        <v>13.0359392166138</v>
+        <v>13.0359382629395</v>
       </c>
       <c r="H983" t="n">
         <v>2947823</v>
@@ -28905,7 +28905,7 @@
         <v>19.5</v>
       </c>
       <c r="G984" t="n">
-        <v>13.2465238571167</v>
+        <v>13.2465229034424</v>
       </c>
       <c r="H984" t="n">
         <v>6103117</v>
@@ -28934,7 +28934,7 @@
         <v>19.3349990844727</v>
       </c>
       <c r="G985" t="n">
-        <v>13.1344375610352</v>
+        <v>13.1344366073608</v>
       </c>
       <c r="H985" t="n">
         <v>4575222</v>
@@ -28963,7 +28963,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G986" t="n">
-        <v>13.0291452407837</v>
+        <v>13.029146194458</v>
       </c>
       <c r="H986" t="n">
         <v>4971188</v>
@@ -29050,7 +29050,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G989" t="n">
-        <v>12.7030763626099</v>
+        <v>12.7030773162842</v>
       </c>
       <c r="H989" t="n">
         <v>6541280</v>
@@ -29195,7 +29195,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G994" t="n">
-        <v>12.6962862014771</v>
+        <v>12.6962842941284</v>
       </c>
       <c r="H994" t="n">
         <v>5406710</v>
@@ -29224,7 +29224,7 @@
         <v>18.6949996948242</v>
       </c>
       <c r="G995" t="n">
-        <v>12.6996803283691</v>
+        <v>12.6996812820435</v>
       </c>
       <c r="H995" t="n">
         <v>2501863</v>
@@ -29253,7 +29253,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G996" t="n">
-        <v>12.6317462921143</v>
+        <v>12.6317491531372</v>
       </c>
       <c r="H996" t="n">
         <v>2966026</v>
@@ -29282,7 +29282,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>12.5875940322876</v>
+        <v>12.5875949859619</v>
       </c>
       <c r="H997" t="n">
         <v>2526653</v>
@@ -29311,7 +29311,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G998" t="n">
-        <v>12.4245586395264</v>
+        <v>12.4245624542236</v>
       </c>
       <c r="H998" t="n">
         <v>5049401</v>
@@ -29340,7 +29340,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>12.4109754562378</v>
+        <v>12.4109735488892</v>
       </c>
       <c r="H999" t="n">
         <v>3426403</v>
@@ -29398,7 +29398,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1001" t="n">
-        <v>12.3905954360962</v>
+        <v>12.3905935287476</v>
       </c>
       <c r="H1001" t="n">
         <v>3141875</v>
@@ -29456,7 +29456,7 @@
         <v>18.1949996948242</v>
       </c>
       <c r="G1003" t="n">
-        <v>12.3600254058838</v>
+        <v>12.3600244522095</v>
       </c>
       <c r="H1003" t="n">
         <v>3396373</v>
@@ -29514,7 +29514,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1005" t="n">
-        <v>12.4041805267334</v>
+        <v>12.4041814804077</v>
       </c>
       <c r="H1005" t="n">
         <v>2621413</v>
@@ -29572,7 +29572,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1007" t="n">
-        <v>12.4585256576538</v>
+        <v>12.4585247039795</v>
       </c>
       <c r="H1007" t="n">
         <v>3866999</v>
@@ -29601,7 +29601,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1008" t="n">
-        <v>12.5570240020752</v>
+        <v>12.5570249557495</v>
       </c>
       <c r="H1008" t="n">
         <v>2755179</v>
@@ -29659,7 +29659,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.6181650161743</v>
+        <v>12.6181640625</v>
       </c>
       <c r="H1010" t="n">
         <v>2705487</v>
@@ -29717,7 +29717,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G1012" t="n">
-        <v>12.8898859024048</v>
+        <v>12.8898878097534</v>
       </c>
       <c r="H1012" t="n">
         <v>10641521</v>
@@ -29775,7 +29775,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1014" t="n">
-        <v>12.6351451873779</v>
+        <v>12.6351461410522</v>
       </c>
       <c r="H1014" t="n">
         <v>2911339</v>
@@ -29804,7 +29804,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.4958877563477</v>
+        <v>12.495888710022</v>
       </c>
       <c r="H1015" t="n">
         <v>2474080</v>
@@ -29862,7 +29862,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5094738006592</v>
+        <v>12.5094728469849</v>
       </c>
       <c r="H1017" t="n">
         <v>2895677</v>
@@ -29891,7 +29891,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1018" t="n">
-        <v>12.4177684783936</v>
+        <v>12.4177665710449</v>
       </c>
       <c r="H1018" t="n">
         <v>2762173</v>
@@ -29920,7 +29920,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.5094738006592</v>
+        <v>12.5094728469849</v>
       </c>
       <c r="H1019" t="n">
         <v>2771286</v>
@@ -29949,7 +29949,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.4958877563477</v>
+        <v>12.495888710022</v>
       </c>
       <c r="H1020" t="n">
         <v>3185325</v>
@@ -29978,7 +29978,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.5468339920044</v>
+        <v>12.546835899353</v>
       </c>
       <c r="H1021" t="n">
         <v>2647411</v>
@@ -30065,7 +30065,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.5196628570557</v>
+        <v>12.51966381073</v>
       </c>
       <c r="H1024" t="n">
         <v>2816491</v>
@@ -30123,7 +30123,7 @@
         <v>18.2950000762939</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.42795753479</v>
+        <v>12.4279565811157</v>
       </c>
       <c r="H1026" t="n">
         <v>2875277</v>
@@ -30152,7 +30152,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4585256576538</v>
+        <v>12.4585247039795</v>
       </c>
       <c r="H1027" t="n">
         <v>3079304</v>
@@ -30181,7 +30181,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1028" t="n">
-        <v>12.4347496032715</v>
+        <v>12.4347486495972</v>
       </c>
       <c r="H1028" t="n">
         <v>1714146</v>
@@ -30210,7 +30210,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.4007844924927</v>
+        <v>12.4007835388184</v>
       </c>
       <c r="H1029" t="n">
         <v>2868108</v>
@@ -30239,7 +30239,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.3192672729492</v>
+        <v>12.3192663192749</v>
       </c>
       <c r="H1030" t="n">
         <v>2795535</v>
@@ -30268,7 +30268,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.183403968811</v>
+        <v>12.1834058761597</v>
       </c>
       <c r="H1031" t="n">
         <v>3733964</v>
@@ -30384,7 +30384,7 @@
         <v>18.2450008392334</v>
       </c>
       <c r="G1035" t="n">
-        <v>12.3939905166626</v>
+        <v>12.3939924240112</v>
       </c>
       <c r="H1035" t="n">
         <v>2767150</v>
@@ -30413,7 +30413,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.1528367996216</v>
+        <v>12.1528358459473</v>
       </c>
       <c r="H1036" t="n">
         <v>4704600</v>
@@ -30442,7 +30442,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1037" t="n">
-        <v>11.9524402618408</v>
+        <v>11.9524393081665</v>
       </c>
       <c r="H1037" t="n">
         <v>5966169</v>
@@ -30471,7 +30471,7 @@
         <v>17.6849994659424</v>
       </c>
       <c r="G1038" t="n">
-        <v>12.0135765075684</v>
+        <v>12.013578414917</v>
       </c>
       <c r="H1038" t="n">
         <v>3309059</v>
@@ -30500,7 +30500,7 @@
         <v>17.9449996948242</v>
       </c>
       <c r="G1039" t="n">
-        <v>12.1901969909668</v>
+        <v>12.1901998519897</v>
       </c>
       <c r="H1039" t="n">
         <v>3573424</v>
@@ -30529,7 +30529,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G1040" t="n">
-        <v>12.3192672729492</v>
+        <v>12.3192663192749</v>
       </c>
       <c r="H1040" t="n">
         <v>4226044</v>
@@ -30587,7 +30587,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.4687128067017</v>
+        <v>12.4687156677246</v>
       </c>
       <c r="H1042" t="n">
         <v>3674368</v>
@@ -30616,7 +30616,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1043" t="n">
-        <v>12.5264549255371</v>
+        <v>12.5264568328857</v>
       </c>
       <c r="H1043" t="n">
         <v>2617825</v>
@@ -30674,7 +30674,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.6181650161743</v>
+        <v>12.6181640625</v>
       </c>
       <c r="H1045" t="n">
         <v>3193337</v>
@@ -30703,7 +30703,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1046" t="n">
-        <v>12.6351451873779</v>
+        <v>12.6351461410522</v>
       </c>
       <c r="H1046" t="n">
         <v>2808861</v>
@@ -30732,7 +30732,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1047" t="n">
-        <v>12.7166614532471</v>
+        <v>12.7166604995728</v>
       </c>
       <c r="H1047" t="n">
         <v>3769186</v>
@@ -30761,7 +30761,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>12.7540245056152</v>
+        <v>12.7540235519409</v>
       </c>
       <c r="H1048" t="n">
         <v>2427382</v>
@@ -30790,7 +30790,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1049" t="n">
-        <v>12.757420539856</v>
+        <v>12.7574224472046</v>
       </c>
       <c r="H1049" t="n">
         <v>3008786</v>
@@ -30819,7 +30819,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1050" t="n">
-        <v>12.8253507614136</v>
+        <v>12.8253526687622</v>
       </c>
       <c r="H1050" t="n">
         <v>3853007</v>
@@ -30848,7 +30848,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G1051" t="n">
-        <v>12.6317462921143</v>
+        <v>12.6317491531372</v>
       </c>
       <c r="H1051" t="n">
         <v>5082450</v>
@@ -30877,7 +30877,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>12.5196628570557</v>
+        <v>12.51966381073</v>
       </c>
       <c r="H1052" t="n">
         <v>5000350</v>
@@ -30935,7 +30935,7 @@
         <v>17.3349990844727</v>
       </c>
       <c r="G1054" t="n">
-        <v>11.7758188247681</v>
+        <v>11.7758197784424</v>
       </c>
       <c r="H1054" t="n">
         <v>7915552</v>
@@ -30964,7 +30964,7 @@
         <v>17.2649993896484</v>
       </c>
       <c r="G1055" t="n">
-        <v>11.7282686233521</v>
+        <v>11.7282676696777</v>
       </c>
       <c r="H1055" t="n">
         <v>7087742</v>
@@ -30993,7 +30993,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>11.480320930481</v>
+        <v>11.4803190231323</v>
       </c>
       <c r="H1056" t="n">
         <v>7908586</v>
@@ -31109,7 +31109,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.9164934158325</v>
+        <v>10.9164943695068</v>
       </c>
       <c r="H1060" t="n">
         <v>5399861</v>
@@ -31167,7 +31167,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G1062" t="n">
-        <v>10.3526659011841</v>
+        <v>10.3526668548584</v>
       </c>
       <c r="H1062" t="n">
         <v>8479713</v>
@@ -31196,7 +31196,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.34729194641113</v>
+        <v>9.3472900390625</v>
       </c>
       <c r="H1063" t="n">
         <v>17007395</v>
@@ -31312,7 +31312,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.19925880432129</v>
+        <v>8.19925785064697</v>
       </c>
       <c r="H1067" t="n">
         <v>20830151</v>
@@ -31370,7 +31370,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1069" t="n">
-        <v>7.37050199508667</v>
+        <v>7.3705005645752</v>
       </c>
       <c r="H1069" t="n">
         <v>19657993</v>
@@ -31399,7 +31399,7 @@
         <v>10.3850002288818</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.05462217330933</v>
+        <v>7.05462265014648</v>
       </c>
       <c r="H1070" t="n">
         <v>11613218</v>
@@ -31428,7 +31428,7 @@
         <v>10.7349996566772</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.29238033294678</v>
+        <v>7.29238128662109</v>
       </c>
       <c r="H1071" t="n">
         <v>13513589</v>
@@ -31457,7 +31457,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.39767408370972</v>
+        <v>7.39767503738403</v>
       </c>
       <c r="H1072" t="n">
         <v>20334856</v>
@@ -31515,7 +31515,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.21963787078857</v>
+        <v>8.21963691711426</v>
       </c>
       <c r="H1074" t="n">
         <v>12760007</v>
@@ -31544,7 +31544,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>8.45739459991455</v>
+        <v>8.45739555358887</v>
       </c>
       <c r="H1075" t="n">
         <v>11973116</v>
@@ -31573,7 +31573,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.6000509262085</v>
+        <v>8.60005187988281</v>
       </c>
       <c r="H1076" t="n">
         <v>8371105</v>
@@ -31660,7 +31660,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.4302225112915</v>
+        <v>8.43022346496582</v>
       </c>
       <c r="H1079" t="n">
         <v>9416863</v>
@@ -31689,7 +31689,7 @@
         <v>12.0950002670288</v>
       </c>
       <c r="G1080" t="n">
-        <v>8.21624088287354</v>
+        <v>8.21624183654785</v>
       </c>
       <c r="H1080" t="n">
         <v>5472851</v>
@@ -31776,7 +31776,7 @@
         <v>12.5450000762939</v>
       </c>
       <c r="G1083" t="n">
-        <v>8.52192974090576</v>
+        <v>8.52192878723145</v>
       </c>
       <c r="H1083" t="n">
         <v>5245194</v>
@@ -31863,7 +31863,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G1086" t="n">
-        <v>8.74270629882812</v>
+        <v>8.74270534515381</v>
       </c>
       <c r="H1086" t="n">
         <v>6013229</v>
@@ -31892,7 +31892,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.92272186279297</v>
+        <v>8.92272281646729</v>
       </c>
       <c r="H1087" t="n">
         <v>7939984</v>
@@ -31950,7 +31950,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.41663646697998</v>
+        <v>8.41663837432861</v>
       </c>
       <c r="H1089" t="n">
         <v>6935117</v>
@@ -32124,7 +32124,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1095" t="n">
-        <v>8.40305137634277</v>
+        <v>8.40305042266846</v>
       </c>
       <c r="H1095" t="n">
         <v>4552998</v>
@@ -32211,7 +32211,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1098" t="n">
-        <v>9.03480815887451</v>
+        <v>9.03480911254883</v>
       </c>
       <c r="H1098" t="n">
         <v>7110520</v>
@@ -32240,7 +32240,7 @@
         <v>13.0150003433228</v>
       </c>
       <c r="G1099" t="n">
-        <v>8.84120559692383</v>
+        <v>8.84120655059814</v>
       </c>
       <c r="H1099" t="n">
         <v>8406539</v>
@@ -32327,7 +32327,7 @@
         <v>12.7349996566772</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.65099906921387</v>
+        <v>8.65099811553955</v>
       </c>
       <c r="H1102" t="n">
         <v>4911989</v>
@@ -32356,7 +32356,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.708740234375</v>
+        <v>8.70873928070068</v>
       </c>
       <c r="H1103" t="n">
         <v>4713189</v>
@@ -32385,7 +32385,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.8140344619751</v>
+        <v>8.81403255462646</v>
       </c>
       <c r="H1104" t="n">
         <v>3673701</v>
@@ -32443,7 +32443,7 @@
         <v>12.8050003051758</v>
       </c>
       <c r="G1106" t="n">
-        <v>8.6985502243042</v>
+        <v>8.69855117797852</v>
       </c>
       <c r="H1106" t="n">
         <v>3781225</v>
@@ -32617,7 +32617,7 @@
         <v>12.2600002288818</v>
       </c>
       <c r="G1112" t="n">
-        <v>8.67361450195312</v>
+        <v>8.67361545562744</v>
       </c>
       <c r="H1112" t="n">
         <v>6462514</v>
@@ -32646,7 +32646,7 @@
         <v>11.8950004577637</v>
       </c>
       <c r="G1113" t="n">
-        <v>8.4153881072998</v>
+        <v>8.41538619995117</v>
       </c>
       <c r="H1113" t="n">
         <v>8677564</v>
@@ -32791,7 +32791,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.03796195983887</v>
+        <v>9.03796291351318</v>
       </c>
       <c r="H1118" t="n">
         <v>5781139</v>
@@ -32849,7 +32849,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G1120" t="n">
-        <v>9.11932373046875</v>
+        <v>9.11932277679443</v>
       </c>
       <c r="H1120" t="n">
         <v>8301716</v>
@@ -32936,7 +32936,7 @@
         <v>14.0050001144409</v>
       </c>
       <c r="G1123" t="n">
-        <v>9.90815258026123</v>
+        <v>9.90815353393555</v>
       </c>
       <c r="H1123" t="n">
         <v>10542014</v>
@@ -32965,7 +32965,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1124" t="n">
-        <v>10.1769933700562</v>
+        <v>10.1769952774048</v>
       </c>
       <c r="H1124" t="n">
         <v>9168993</v>
@@ -32994,7 +32994,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1125" t="n">
-        <v>10.2017555236816</v>
+        <v>10.201756477356</v>
       </c>
       <c r="H1125" t="n">
         <v>8030461</v>
@@ -33023,7 +33023,7 @@
         <v>14.2650003433228</v>
       </c>
       <c r="G1126" t="n">
-        <v>10.0920972824097</v>
+        <v>10.092098236084</v>
       </c>
       <c r="H1126" t="n">
         <v>10146009</v>
@@ -33052,7 +33052,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G1127" t="n">
-        <v>9.88339424133301</v>
+        <v>9.88339328765869</v>
       </c>
       <c r="H1127" t="n">
         <v>5631448</v>
@@ -33081,7 +33081,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.50135803222656</v>
+        <v>9.50135707855225</v>
       </c>
       <c r="H1128" t="n">
         <v>7685800</v>
@@ -33197,7 +33197,7 @@
         <v>13.6049995422363</v>
       </c>
       <c r="G1132" t="n">
-        <v>9.62516403198242</v>
+        <v>9.62516498565674</v>
       </c>
       <c r="H1132" t="n">
         <v>4807176</v>
@@ -33226,7 +33226,7 @@
         <v>13.4350004196167</v>
       </c>
       <c r="G1133" t="n">
-        <v>9.50489521026611</v>
+        <v>9.5048942565918</v>
       </c>
       <c r="H1133" t="n">
         <v>4981298</v>
@@ -33255,7 +33255,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.63224029541016</v>
+        <v>9.63223934173584</v>
       </c>
       <c r="H1134" t="n">
         <v>12780721</v>
@@ -33284,7 +33284,7 @@
         <v>13.4300003051758</v>
       </c>
       <c r="G1135" t="n">
-        <v>9.50135803222656</v>
+        <v>9.50135707855225</v>
       </c>
       <c r="H1135" t="n">
         <v>3924211</v>
@@ -33313,7 +33313,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.64285087585449</v>
+        <v>9.64285182952881</v>
       </c>
       <c r="H1136" t="n">
         <v>4327719</v>
@@ -33342,7 +33342,7 @@
         <v>13.2650003433228</v>
       </c>
       <c r="G1137" t="n">
-        <v>9.38462448120117</v>
+        <v>9.38462352752686</v>
       </c>
       <c r="H1137" t="n">
         <v>5827239</v>
@@ -33371,7 +33371,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1138" t="n">
-        <v>9.40938568115234</v>
+        <v>9.40938472747803</v>
       </c>
       <c r="H1138" t="n">
         <v>5488017</v>
@@ -33429,7 +33429,7 @@
         <v>13.4200000762939</v>
       </c>
       <c r="G1140" t="n">
-        <v>9.49428272247314</v>
+        <v>9.49428176879883</v>
       </c>
       <c r="H1140" t="n">
         <v>4405401</v>
@@ -33458,7 +33458,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1141" t="n">
-        <v>9.52965641021729</v>
+        <v>9.52965545654297</v>
       </c>
       <c r="H1141" t="n">
         <v>4445370</v>
@@ -33487,7 +33487,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.52611827850342</v>
+        <v>9.52611923217773</v>
       </c>
       <c r="H1142" t="n">
         <v>4148541</v>
@@ -33516,7 +33516,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1143" t="n">
-        <v>9.78788280487061</v>
+        <v>9.78788471221924</v>
       </c>
       <c r="H1143" t="n">
         <v>5891432</v>
@@ -33574,7 +33574,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G1145" t="n">
-        <v>9.82325744628906</v>
+        <v>9.82325649261475</v>
       </c>
       <c r="H1145" t="n">
         <v>4130648</v>
@@ -33603,7 +33603,7 @@
         <v>13.7550001144409</v>
       </c>
       <c r="G1146" t="n">
-        <v>9.73128604888916</v>
+        <v>9.73128700256348</v>
       </c>
       <c r="H1146" t="n">
         <v>3252907</v>
@@ -33632,7 +33632,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1147" t="n">
-        <v>9.63224029541016</v>
+        <v>9.63223934173584</v>
       </c>
       <c r="H1147" t="n">
         <v>2531116</v>
@@ -33690,7 +33690,7 @@
         <v>13.4949998855591</v>
       </c>
       <c r="G1149" t="n">
-        <v>9.54734325408936</v>
+        <v>9.54734420776367</v>
       </c>
       <c r="H1149" t="n">
         <v>3095808</v>
@@ -33777,7 +33777,7 @@
         <v>13.8149995803833</v>
       </c>
       <c r="G1152" t="n">
-        <v>9.77373504638672</v>
+        <v>9.7737340927124</v>
       </c>
       <c r="H1152" t="n">
         <v>3660005</v>
@@ -33835,7 +33835,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.68529891967773</v>
+        <v>9.68529987335205</v>
       </c>
       <c r="H1154" t="n">
         <v>2886210</v>
@@ -33922,7 +33922,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G1157" t="n">
-        <v>9.84094524383545</v>
+        <v>9.84094429016113</v>
       </c>
       <c r="H1157" t="n">
         <v>2561135</v>
@@ -34009,7 +34009,7 @@
         <v>13.5150003433228</v>
       </c>
       <c r="G1160" t="n">
-        <v>9.56149291992188</v>
+        <v>9.56149387359619</v>
       </c>
       <c r="H1160" t="n">
         <v>2330922</v>
@@ -34067,7 +34067,7 @@
         <v>13.5</v>
       </c>
       <c r="G1162" t="n">
-        <v>9.55088138580322</v>
+        <v>9.55088043212891</v>
       </c>
       <c r="H1162" t="n">
         <v>2681591</v>
@@ -34154,7 +34154,7 @@
         <v>12.7349996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>9.00966358184814</v>
+        <v>9.00966453552246</v>
       </c>
       <c r="H1165" t="n">
         <v>4617459</v>
@@ -34212,7 +34212,7 @@
         <v>13.0349998474121</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.22190475463867</v>
+        <v>9.22190570831299</v>
       </c>
       <c r="H1167" t="n">
         <v>2583018</v>
@@ -34241,7 +34241,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>9.03796195983887</v>
+        <v>9.03796291351318</v>
       </c>
       <c r="H1168" t="n">
         <v>4001048</v>
@@ -34270,7 +34270,7 @@
         <v>12.7049999237061</v>
       </c>
       <c r="G1169" t="n">
-        <v>8.98843955993652</v>
+        <v>8.98844051361084</v>
       </c>
       <c r="H1169" t="n">
         <v>2963955</v>
@@ -34299,7 +34299,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>9.03796195983887</v>
+        <v>9.03796291351318</v>
       </c>
       <c r="H1170" t="n">
         <v>4186365</v>
@@ -34328,7 +34328,7 @@
         <v>13.2449998855591</v>
       </c>
       <c r="G1171" t="n">
-        <v>9.37047576904297</v>
+        <v>9.37047481536865</v>
       </c>
       <c r="H1171" t="n">
         <v>6891442</v>
@@ -34357,7 +34357,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1172" t="n">
-        <v>9.40938568115234</v>
+        <v>9.40938472747803</v>
       </c>
       <c r="H1172" t="n">
         <v>2996349</v>
@@ -34386,7 +34386,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G1173" t="n">
-        <v>9.31741428375244</v>
+        <v>9.31741523742676</v>
       </c>
       <c r="H1173" t="n">
         <v>2511229</v>
@@ -34502,7 +34502,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1177" t="n">
-        <v>9.29619026184082</v>
+        <v>9.29619121551514</v>
       </c>
       <c r="H1177" t="n">
         <v>4110380</v>
@@ -34531,7 +34531,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1178" t="n">
-        <v>9.21836853027344</v>
+        <v>9.21836948394775</v>
       </c>
       <c r="H1178" t="n">
         <v>2302067</v>
@@ -34560,7 +34560,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1179" t="n">
-        <v>9.15469455718994</v>
+        <v>9.15469646453857</v>
       </c>
       <c r="H1179" t="n">
         <v>2337724</v>
@@ -34676,7 +34676,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>9.40938568115234</v>
+        <v>9.40938472747803</v>
       </c>
       <c r="H1183" t="n">
         <v>3671195</v>
@@ -34705,7 +34705,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>9.36693668365479</v>
+        <v>9.36693859100342</v>
       </c>
       <c r="H1184" t="n">
         <v>2503471</v>
@@ -34821,7 +34821,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1188" t="n">
-        <v>9.16884613037109</v>
+        <v>9.16884517669678</v>
       </c>
       <c r="H1188" t="n">
         <v>3410133</v>
@@ -34850,7 +34850,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1189" t="n">
-        <v>9.06980037689209</v>
+        <v>9.06979846954346</v>
       </c>
       <c r="H1189" t="n">
         <v>4621571</v>
@@ -34937,7 +34937,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>9.16177082061768</v>
+        <v>9.16176986694336</v>
       </c>
       <c r="H1192" t="n">
         <v>3494986</v>
@@ -34966,7 +34966,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G1193" t="n">
-        <v>9.16884613037109</v>
+        <v>9.16884517669678</v>
       </c>
       <c r="H1193" t="n">
         <v>3159504</v>
@@ -34995,7 +34995,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1194" t="n">
-        <v>9.08394908905029</v>
+        <v>9.08394813537598</v>
       </c>
       <c r="H1194" t="n">
         <v>3247223</v>
@@ -35053,7 +35053,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1196" t="n">
-        <v>9.03796195983887</v>
+        <v>9.03796291351318</v>
       </c>
       <c r="H1196" t="n">
         <v>3564176</v>
@@ -35082,7 +35082,7 @@
         <v>12.8050003051758</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.0591869354248</v>
+        <v>9.05918598175049</v>
       </c>
       <c r="H1197" t="n">
         <v>3043126</v>
@@ -35111,7 +35111,7 @@
         <v>12.6750001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>8.96721649169922</v>
+        <v>8.9672155380249</v>
       </c>
       <c r="H1198" t="n">
         <v>4251910</v>
@@ -35169,7 +35169,7 @@
         <v>11.8450002670288</v>
       </c>
       <c r="G1200" t="n">
-        <v>8.38001251220703</v>
+        <v>8.38001346588135</v>
       </c>
       <c r="H1200" t="n">
         <v>8608529</v>
@@ -35256,7 +35256,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.2314453125</v>
+        <v>8.23144435882568</v>
       </c>
       <c r="H1203" t="n">
         <v>5031410</v>
@@ -35314,7 +35314,7 @@
         <v>12.0050001144409</v>
       </c>
       <c r="G1205" t="n">
-        <v>8.49320888519287</v>
+        <v>8.49320983886719</v>
       </c>
       <c r="H1205" t="n">
         <v>5482511</v>
@@ -35372,7 +35372,7 @@
         <v>12.0249996185303</v>
       </c>
       <c r="G1207" t="n">
-        <v>8.50735855102539</v>
+        <v>8.50735759735107</v>
       </c>
       <c r="H1207" t="n">
         <v>4257487</v>
@@ -35488,7 +35488,7 @@
         <v>12.375</v>
       </c>
       <c r="G1211" t="n">
-        <v>8.75497341156006</v>
+        <v>8.75497245788574</v>
       </c>
       <c r="H1211" t="n">
         <v>5567214</v>
@@ -35517,7 +35517,7 @@
         <v>12.335000038147</v>
       </c>
       <c r="G1212" t="n">
-        <v>8.72667503356934</v>
+        <v>8.72667407989502</v>
       </c>
       <c r="H1212" t="n">
         <v>3291594</v>
@@ -35546,7 +35546,7 @@
         <v>12.585000038147</v>
       </c>
       <c r="G1213" t="n">
-        <v>8.90354347229004</v>
+        <v>8.90354442596436</v>
       </c>
       <c r="H1213" t="n">
         <v>6433033</v>
@@ -35633,7 +35633,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1216" t="n">
-        <v>8.7372875213623</v>
+        <v>8.73728847503662</v>
       </c>
       <c r="H1216" t="n">
         <v>3050702</v>
@@ -35662,7 +35662,7 @@
         <v>12.3450002670288</v>
       </c>
       <c r="G1217" t="n">
-        <v>8.73375034332275</v>
+        <v>8.73374938964844</v>
       </c>
       <c r="H1217" t="n">
         <v>2826948</v>
@@ -35720,7 +35720,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1219" t="n">
-        <v>8.58871746063232</v>
+        <v>8.58871841430664</v>
       </c>
       <c r="H1219" t="n">
         <v>4439249</v>
@@ -35749,7 +35749,7 @@
         <v>12.2049999237061</v>
       </c>
       <c r="G1220" t="n">
-        <v>8.63470363616943</v>
+        <v>8.63470268249512</v>
       </c>
       <c r="H1220" t="n">
         <v>2494873</v>
@@ -35778,7 +35778,7 @@
         <v>12.2349996566772</v>
       </c>
       <c r="G1221" t="n">
-        <v>8.65592765808105</v>
+        <v>8.65592670440674</v>
       </c>
       <c r="H1221" t="n">
         <v>2214317</v>
@@ -35894,7 +35894,7 @@
         <v>11.875</v>
       </c>
       <c r="G1225" t="n">
-        <v>8.40123748779297</v>
+        <v>8.40123653411865</v>
       </c>
       <c r="H1225" t="n">
         <v>3098003</v>
@@ -35923,7 +35923,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>8.2314453125</v>
+        <v>8.23144435882568</v>
       </c>
       <c r="H1226" t="n">
         <v>4665464</v>
@@ -35952,7 +35952,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1227" t="n">
-        <v>8.03688812255859</v>
+        <v>8.03689002990723</v>
       </c>
       <c r="H1227" t="n">
         <v>6417383</v>
@@ -35981,7 +35981,7 @@
         <v>11.3950004577637</v>
       </c>
       <c r="G1228" t="n">
-        <v>8.06165218353271</v>
+        <v>8.06165027618408</v>
       </c>
       <c r="H1228" t="n">
         <v>4692614</v>
@@ -36010,7 +36010,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G1229" t="n">
-        <v>8.14300918579102</v>
+        <v>8.14301109313965</v>
       </c>
       <c r="H1229" t="n">
         <v>4762326</v>
@@ -36068,7 +36068,7 @@
         <v>12.0349998474121</v>
       </c>
       <c r="G1231" t="n">
-        <v>8.51443290710449</v>
+        <v>8.51443195343018</v>
       </c>
       <c r="H1231" t="n">
         <v>5228206</v>
@@ -36097,7 +36097,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1232" t="n">
-        <v>8.63116550445557</v>
+        <v>8.63116645812988</v>
       </c>
       <c r="H1232" t="n">
         <v>5173585</v>
@@ -36126,7 +36126,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1233" t="n">
-        <v>8.75851249694824</v>
+        <v>8.75851154327393</v>
       </c>
       <c r="H1233" t="n">
         <v>4920508</v>
@@ -36155,7 +36155,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1234" t="n">
-        <v>8.7372875213623</v>
+        <v>8.73728847503662</v>
       </c>
       <c r="H1234" t="n">
         <v>4421796</v>
@@ -36213,7 +36213,7 @@
         <v>13.4700002670288</v>
       </c>
       <c r="G1236" t="n">
-        <v>9.52965641021729</v>
+        <v>9.52965545654297</v>
       </c>
       <c r="H1236" t="n">
         <v>9114648</v>
@@ -36387,7 +36387,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.0673351287842</v>
+        <v>10.0673341751099</v>
       </c>
       <c r="H1242" t="n">
         <v>5139958</v>
@@ -36416,7 +36416,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1243" t="n">
-        <v>9.95413970947266</v>
+        <v>9.95414066314697</v>
       </c>
       <c r="H1243" t="n">
         <v>4861190</v>
@@ -36445,7 +36445,7 @@
         <v>14.2049999237061</v>
       </c>
       <c r="G1244" t="n">
-        <v>10.0496492385864</v>
+        <v>10.0496482849121</v>
       </c>
       <c r="H1244" t="n">
         <v>4629288</v>
@@ -36532,7 +36532,7 @@
         <v>14.4949998855591</v>
       </c>
       <c r="G1247" t="n">
-        <v>10.2548160552979</v>
+        <v>10.2548151016235</v>
       </c>
       <c r="H1247" t="n">
         <v>5738121</v>
@@ -36561,7 +36561,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1248" t="n">
-        <v>10.2371292114258</v>
+        <v>10.2371301651001</v>
       </c>
       <c r="H1248" t="n">
         <v>3619782</v>
@@ -36590,7 +36590,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1249" t="n">
-        <v>10.2371292114258</v>
+        <v>10.2371301651001</v>
       </c>
       <c r="H1249" t="n">
         <v>3944553</v>
@@ -36619,7 +36619,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G1250" t="n">
-        <v>10.1310081481934</v>
+        <v>10.131007194519</v>
       </c>
       <c r="H1250" t="n">
         <v>14333094</v>
@@ -36648,7 +36648,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1251" t="n">
-        <v>10.2371292114258</v>
+        <v>10.2371301651001</v>
       </c>
       <c r="H1251" t="n">
         <v>3994792</v>
@@ -36706,7 +36706,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1253" t="n">
-        <v>10.2371292114258</v>
+        <v>10.2371301651001</v>
       </c>
       <c r="H1253" t="n">
         <v>3535156</v>
@@ -36822,7 +36822,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.1345453262329</v>
+        <v>10.1345462799072</v>
       </c>
       <c r="H1257" t="n">
         <v>4131506</v>
@@ -36909,7 +36909,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1260" t="n">
-        <v>10.0885601043701</v>
+        <v>10.0885591506958</v>
       </c>
       <c r="H1260" t="n">
         <v>5601461</v>
@@ -36938,7 +36938,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1261" t="n">
-        <v>10.1027097702026</v>
+        <v>10.1027088165283</v>
       </c>
       <c r="H1261" t="n">
         <v>3064370</v>
@@ -36967,7 +36967,7 @@
         <v>14.2950000762939</v>
       </c>
       <c r="G1262" t="n">
-        <v>10.113320350647</v>
+        <v>10.1133222579956</v>
       </c>
       <c r="H1262" t="n">
         <v>4166620</v>
@@ -36996,7 +36996,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.1345453262329</v>
+        <v>10.1345462799072</v>
       </c>
       <c r="H1263" t="n">
         <v>3899524</v>
@@ -37054,7 +37054,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1265" t="n">
-        <v>9.82679557800293</v>
+        <v>9.82679462432861</v>
       </c>
       <c r="H1265" t="n">
         <v>7711365</v>
@@ -37083,7 +37083,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>9.97536468505859</v>
+        <v>9.97536373138428</v>
       </c>
       <c r="H1266" t="n">
         <v>3195968</v>
@@ -37112,7 +37112,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1267" t="n">
-        <v>10.1027097702026</v>
+        <v>10.1027088165283</v>
       </c>
       <c r="H1267" t="n">
         <v>3541181</v>
@@ -37141,7 +37141,7 @@
         <v>14.3649997711182</v>
       </c>
       <c r="G1268" t="n">
-        <v>10.1628437042236</v>
+        <v>10.1628446578979</v>
       </c>
       <c r="H1268" t="n">
         <v>2391937</v>
@@ -37170,7 +37170,7 @@
         <v>14.3149995803833</v>
       </c>
       <c r="G1269" t="n">
-        <v>10.1274700164795</v>
+        <v>10.1274719238281</v>
       </c>
       <c r="H1269" t="n">
         <v>2127173</v>
@@ -37199,7 +37199,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1270" t="n">
-        <v>10.0885601043701</v>
+        <v>10.0885591506958</v>
       </c>
       <c r="H1270" t="n">
         <v>2691933</v>
@@ -37228,7 +37228,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1271" t="n">
-        <v>9.95413970947266</v>
+        <v>9.95414066314697</v>
       </c>
       <c r="H1271" t="n">
         <v>3932920</v>
@@ -37257,7 +37257,7 @@
         <v>13.914999961853</v>
       </c>
       <c r="G1272" t="n">
-        <v>9.844482421875</v>
+        <v>9.84448051452637</v>
       </c>
       <c r="H1272" t="n">
         <v>4359534</v>
@@ -37315,7 +37315,7 @@
         <v>14.4700002670288</v>
       </c>
       <c r="G1274" t="n">
-        <v>10.2371292114258</v>
+        <v>10.2371301651001</v>
       </c>
       <c r="H1274" t="n">
         <v>3830765</v>
@@ -37373,7 +37373,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1276" t="n">
-        <v>10.2017555236816</v>
+        <v>10.201756477356</v>
       </c>
       <c r="H1276" t="n">
         <v>3271148</v>
@@ -37431,7 +37431,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G1278" t="n">
-        <v>10.290189743042</v>
+        <v>10.2901887893677</v>
       </c>
       <c r="H1278" t="n">
         <v>5563072</v>
@@ -37489,7 +37489,7 @@
         <v>14.3649997711182</v>
       </c>
       <c r="G1280" t="n">
-        <v>10.1628437042236</v>
+        <v>10.1628446578979</v>
       </c>
       <c r="H1280" t="n">
         <v>4649434</v>
@@ -37518,7 +37518,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1281" t="n">
-        <v>10.2300539016724</v>
+        <v>10.2300548553467</v>
       </c>
       <c r="H1281" t="n">
         <v>3111178</v>
@@ -37547,7 +37547,7 @@
         <v>14.5050001144409</v>
       </c>
       <c r="G1282" t="n">
-        <v>10.2618913650513</v>
+        <v>10.261890411377</v>
       </c>
       <c r="H1282" t="n">
         <v>4368479</v>
@@ -37605,7 +37605,7 @@
         <v>14.6549997329712</v>
       </c>
       <c r="G1284" t="n">
-        <v>10.3680114746094</v>
+        <v>10.3680105209351</v>
       </c>
       <c r="H1284" t="n">
         <v>6481249</v>
@@ -37663,7 +37663,7 @@
         <v>14.4049997329712</v>
       </c>
       <c r="G1286" t="n">
-        <v>10.1911430358887</v>
+        <v>10.191143989563</v>
       </c>
       <c r="H1286" t="n">
         <v>4577608</v>
@@ -37692,7 +37692,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G1287" t="n">
-        <v>10.290189743042</v>
+        <v>10.2901887893677</v>
       </c>
       <c r="H1287" t="n">
         <v>3677279</v>
@@ -37750,7 +37750,7 @@
         <v>14.4200000762939</v>
       </c>
       <c r="G1289" t="n">
-        <v>10.2017555236816</v>
+        <v>10.201756477356</v>
       </c>
       <c r="H1289" t="n">
         <v>6666288</v>
@@ -37779,7 +37779,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G1290" t="n">
-        <v>9.96828937530518</v>
+        <v>9.96829032897949</v>
       </c>
       <c r="H1290" t="n">
         <v>7886788</v>
@@ -37837,7 +37837,7 @@
         <v>14.4750003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.2406663894653</v>
+        <v>10.2406673431396</v>
       </c>
       <c r="H1292" t="n">
         <v>4187940</v>
@@ -37895,7 +37895,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1294" t="n">
-        <v>10.9092273712158</v>
+        <v>10.9092283248901</v>
       </c>
       <c r="H1294" t="n">
         <v>7979755</v>
@@ -37982,7 +37982,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1297" t="n">
-        <v>11.1922159194946</v>
+        <v>11.1922178268433</v>
       </c>
       <c r="H1297" t="n">
         <v>5318755</v>
@@ -38069,7 +38069,7 @@
         <v>15.664999961853</v>
       </c>
       <c r="G1300" t="n">
-        <v>11.0825595855713</v>
+        <v>11.082558631897</v>
       </c>
       <c r="H1300" t="n">
         <v>3055947</v>
@@ -38098,7 +38098,7 @@
         <v>15.8249998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.1957540512085</v>
+        <v>11.1957550048828</v>
       </c>
       <c r="H1301" t="n">
         <v>3873144</v>
@@ -38214,7 +38214,7 @@
         <v>15.5799999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>11.0224227905273</v>
+        <v>11.0224237442017</v>
       </c>
       <c r="H1305" t="n">
         <v>4059184</v>
@@ -38243,7 +38243,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1306" t="n">
-        <v>10.9941234588623</v>
+        <v>10.9941244125366</v>
       </c>
       <c r="H1306" t="n">
         <v>2973230</v>
@@ -38272,7 +38272,7 @@
         <v>15.5050001144409</v>
       </c>
       <c r="G1307" t="n">
-        <v>10.9693632125854</v>
+        <v>10.9693622589111</v>
       </c>
       <c r="H1307" t="n">
         <v>3328306</v>
@@ -38330,7 +38330,7 @@
         <v>15.835000038147</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.2028293609619</v>
+        <v>11.2028284072876</v>
       </c>
       <c r="H1309" t="n">
         <v>4923573</v>
@@ -38359,7 +38359,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>11.00119972229</v>
+        <v>11.0012006759644</v>
       </c>
       <c r="H1310" t="n">
         <v>4825120</v>
@@ -38388,7 +38388,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.199291229248</v>
+        <v>11.1992921829224</v>
       </c>
       <c r="H1311" t="n">
         <v>4003255</v>
@@ -38417,7 +38417,7 @@
         <v>15.875</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2311277389526</v>
+        <v>11.231128692627</v>
       </c>
       <c r="H1312" t="n">
         <v>4074042</v>
@@ -38446,7 +38446,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G1313" t="n">
-        <v>11.3407859802246</v>
+        <v>11.3407878875732</v>
       </c>
       <c r="H1313" t="n">
         <v>4605616</v>
@@ -38475,7 +38475,7 @@
         <v>16.0750007629395</v>
       </c>
       <c r="G1314" t="n">
-        <v>11.3726243972778</v>
+        <v>11.3726234436035</v>
       </c>
       <c r="H1314" t="n">
         <v>4076211</v>
@@ -38533,7 +38533,7 @@
         <v>16.5</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.6732978820801</v>
+        <v>11.6732988357544</v>
       </c>
       <c r="H1316" t="n">
         <v>7830908</v>
@@ -38562,7 +38562,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.6945238113403</v>
+        <v>11.694522857666</v>
       </c>
       <c r="H1317" t="n">
         <v>4486168</v>
@@ -38620,7 +38620,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.8607807159424</v>
+        <v>11.8607778549194</v>
       </c>
       <c r="H1319" t="n">
         <v>9043685</v>
@@ -38649,7 +38649,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G1320" t="n">
-        <v>11.9598274230957</v>
+        <v>11.9598255157471</v>
       </c>
       <c r="H1320" t="n">
         <v>4820812</v>
@@ -38678,7 +38678,7 @@
         <v>16.8349990844727</v>
       </c>
       <c r="G1321" t="n">
-        <v>11.9103002548218</v>
+        <v>11.9103012084961</v>
       </c>
       <c r="H1321" t="n">
         <v>5616744</v>
@@ -38707,7 +38707,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.9492111206055</v>
+        <v>11.9492120742798</v>
       </c>
       <c r="H1322" t="n">
         <v>5062686</v>
@@ -38881,7 +38881,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.9492111206055</v>
+        <v>11.9492120742798</v>
       </c>
       <c r="H1328" t="n">
         <v>3448568</v>
@@ -38910,7 +38910,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1329" t="n">
-        <v>11.9032278060913</v>
+        <v>11.903226852417</v>
       </c>
       <c r="H1329" t="n">
         <v>4378727</v>
@@ -38939,7 +38939,7 @@
         <v>16.9249992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>11.973973274231</v>
+        <v>11.9739742279053</v>
       </c>
       <c r="H1330" t="n">
         <v>3928160</v>
@@ -39084,7 +39084,7 @@
         <v>17.1350002288818</v>
       </c>
       <c r="G1335" t="n">
-        <v>12.1225452423096</v>
+        <v>12.1225433349609</v>
       </c>
       <c r="H1335" t="n">
         <v>5147652</v>
@@ -39113,7 +39113,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.1473045349121</v>
+        <v>12.1473054885864</v>
       </c>
       <c r="H1336" t="n">
         <v>3432252</v>
@@ -39142,7 +39142,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G1337" t="n">
-        <v>12.1013193130493</v>
+        <v>12.1013202667236</v>
       </c>
       <c r="H1337" t="n">
         <v>5538002</v>
@@ -39171,7 +39171,7 @@
         <v>16.9650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>12.0022745132446</v>
+        <v>12.0022735595703</v>
       </c>
       <c r="H1338" t="n">
         <v>4421859</v>
@@ -39200,7 +39200,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1339" t="n">
-        <v>12.0765571594238</v>
+        <v>12.0765581130981</v>
       </c>
       <c r="H1339" t="n">
         <v>3495771</v>
@@ -39287,7 +39287,7 @@
         <v>17.0249996185303</v>
       </c>
       <c r="G1342" t="n">
-        <v>12.0447206497192</v>
+        <v>12.0447225570679</v>
       </c>
       <c r="H1342" t="n">
         <v>3141375</v>
@@ -39403,7 +39403,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1346" t="n">
-        <v>11.9173755645752</v>
+        <v>11.9173765182495</v>
       </c>
       <c r="H1346" t="n">
         <v>4339084</v>
@@ -39432,7 +39432,7 @@
         <v>16.8349990844727</v>
       </c>
       <c r="G1347" t="n">
-        <v>11.9103002548218</v>
+        <v>11.9103012084961</v>
       </c>
       <c r="H1347" t="n">
         <v>3186304</v>
@@ -39461,7 +39461,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>11.9032278060913</v>
+        <v>11.903226852417</v>
       </c>
       <c r="H1348" t="n">
         <v>3372601</v>
@@ -39519,7 +39519,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G1350" t="n">
-        <v>11.9032278060913</v>
+        <v>11.903226852417</v>
       </c>
       <c r="H1350" t="n">
         <v>4182574</v>
@@ -39548,7 +39548,7 @@
         <v>16.9249992370605</v>
       </c>
       <c r="G1351" t="n">
-        <v>11.973973274231</v>
+        <v>11.9739742279053</v>
       </c>
       <c r="H1351" t="n">
         <v>3121400</v>
@@ -39577,7 +39577,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1352" t="n">
-        <v>11.8713903427124</v>
+        <v>11.8713912963867</v>
       </c>
       <c r="H1352" t="n">
         <v>7077482</v>
@@ -39606,7 +39606,7 @@
         <v>16.6849994659424</v>
       </c>
       <c r="G1353" t="n">
-        <v>11.804181098938</v>
+        <v>11.8041791915894</v>
       </c>
       <c r="H1353" t="n">
         <v>5395222</v>
@@ -39664,7 +39664,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1355" t="n">
-        <v>11.9138402938843</v>
+        <v>11.9138383865356</v>
       </c>
       <c r="H1355" t="n">
         <v>4860207</v>
@@ -39693,7 +39693,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>12.0624074935913</v>
+        <v>12.062406539917</v>
       </c>
       <c r="H1356" t="n">
         <v>3799970</v>
@@ -39722,7 +39722,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1357" t="n">
-        <v>12.1826791763306</v>
+        <v>12.1826782226562</v>
       </c>
       <c r="H1357" t="n">
         <v>8210086</v>
@@ -39751,7 +39751,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G1358" t="n">
-        <v>12.288800239563</v>
+        <v>12.2888011932373</v>
       </c>
       <c r="H1358" t="n">
         <v>5410437</v>
@@ -39867,7 +39867,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1362" t="n">
-        <v>12.4090700149536</v>
+        <v>12.4090719223022</v>
       </c>
       <c r="H1362" t="n">
         <v>6246702</v>
@@ -39896,7 +39896,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1363" t="n">
-        <v>12.4798164367676</v>
+        <v>12.4798154830933</v>
       </c>
       <c r="H1363" t="n">
         <v>9000170</v>
@@ -39983,7 +39983,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G1366" t="n">
-        <v>12.3347854614258</v>
+        <v>12.3347864151001</v>
       </c>
       <c r="H1366" t="n">
         <v>8295458</v>
@@ -40070,7 +40070,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>12.6815633773804</v>
+        <v>12.6815624237061</v>
       </c>
       <c r="H1369" t="n">
         <v>9401155</v>
@@ -40099,7 +40099,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1370" t="n">
-        <v>12.5615015029907</v>
+        <v>12.5615005493164</v>
       </c>
       <c r="H1370" t="n">
         <v>5020867</v>
@@ -40215,7 +40215,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1374" t="n">
-        <v>12.6177816390991</v>
+        <v>12.6177797317505</v>
       </c>
       <c r="H1374" t="n">
         <v>3195260</v>
@@ -40418,7 +40418,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1381" t="n">
-        <v>12.8916721343994</v>
+        <v>12.8916730880737</v>
       </c>
       <c r="H1381" t="n">
         <v>4629257</v>
@@ -40447,7 +40447,7 @@
         <v>17.125</v>
       </c>
       <c r="G1382" t="n">
-        <v>12.8504009246826</v>
+        <v>12.8503999710083</v>
       </c>
       <c r="H1382" t="n">
         <v>3620976</v>
@@ -40476,7 +40476,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>12.8616552352905</v>
+        <v>12.8616561889648</v>
       </c>
       <c r="H1383" t="n">
         <v>3054956</v>
@@ -40505,7 +40505,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>12.8691596984863</v>
+        <v>12.8691606521606</v>
       </c>
       <c r="H1384" t="n">
         <v>3293082</v>
@@ -40534,7 +40534,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.8916721343994</v>
+        <v>12.8916730880737</v>
       </c>
       <c r="H1385" t="n">
         <v>2584909</v>
@@ -40563,7 +40563,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G1386" t="n">
-        <v>12.8804178237915</v>
+        <v>12.8804168701172</v>
       </c>
       <c r="H1386" t="n">
         <v>3746068</v>
@@ -40621,7 +40621,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>12.6740579605103</v>
+        <v>12.6740589141846</v>
       </c>
       <c r="H1388" t="n">
         <v>9118160</v>
@@ -40679,7 +40679,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1390" t="n">
-        <v>12.6703071594238</v>
+        <v>12.6703090667725</v>
       </c>
       <c r="H1390" t="n">
         <v>2517399</v>
@@ -40708,7 +40708,7 @@
         <v>16.6550006866455</v>
       </c>
       <c r="G1391" t="n">
-        <v>12.4977178573608</v>
+        <v>12.4977188110352</v>
       </c>
       <c r="H1391" t="n">
         <v>3975295</v>
@@ -40795,7 +40795,7 @@
         <v>16.75</v>
       </c>
       <c r="G1394" t="n">
-        <v>12.5690059661865</v>
+        <v>12.5690050125122</v>
       </c>
       <c r="H1394" t="n">
         <v>3033079</v>
@@ -40853,7 +40853,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G1396" t="n">
-        <v>12.6853170394897</v>
+        <v>12.6853151321411</v>
       </c>
       <c r="H1396" t="n">
         <v>5392566</v>
@@ -40911,7 +40911,7 @@
         <v>17</v>
       </c>
       <c r="G1398" t="n">
-        <v>12.7566022872925</v>
+        <v>12.7566013336182</v>
       </c>
       <c r="H1398" t="n">
         <v>2567542</v>
@@ -40940,7 +40940,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G1399" t="n">
-        <v>12.8654088973999</v>
+        <v>12.8654098510742</v>
       </c>
       <c r="H1399" t="n">
         <v>2993797</v>
@@ -40969,7 +40969,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1400" t="n">
-        <v>12.6365413665771</v>
+        <v>12.6365404129028</v>
       </c>
       <c r="H1400" t="n">
         <v>4559372</v>
@@ -41056,7 +41056,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1403" t="n">
-        <v>12.6703071594238</v>
+        <v>12.6703090667725</v>
       </c>
       <c r="H1403" t="n">
         <v>4656013</v>
@@ -41085,7 +41085,7 @@
         <v>17.0049991607666</v>
       </c>
       <c r="G1404" t="n">
-        <v>12.7603530883789</v>
+        <v>12.7603540420532</v>
       </c>
       <c r="H1404" t="n">
         <v>3010578</v>
@@ -41143,7 +41143,7 @@
         <v>16.9249992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>12.7003211975098</v>
+        <v>12.7003231048584</v>
       </c>
       <c r="H1406" t="n">
         <v>2632538</v>
@@ -41201,7 +41201,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G1408" t="n">
-        <v>12.5577516555786</v>
+        <v>12.5577507019043</v>
       </c>
       <c r="H1408" t="n">
         <v>2921647</v>
@@ -41317,7 +41317,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1412" t="n">
-        <v>12.5990228652954</v>
+        <v>12.5990219116211</v>
       </c>
       <c r="H1412" t="n">
         <v>3007617</v>
@@ -41346,7 +41346,7 @@
         <v>16.7350006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>12.5577516555786</v>
+        <v>12.5577507019043</v>
       </c>
       <c r="H1413" t="n">
         <v>3394595</v>
@@ -41404,7 +41404,7 @@
         <v>16.7549991607666</v>
       </c>
       <c r="G1415" t="n">
-        <v>12.5727567672729</v>
+        <v>12.5727558135986</v>
       </c>
       <c r="H1415" t="n">
         <v>4014245</v>
@@ -41433,7 +41433,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1416" t="n">
-        <v>12.5990228652954</v>
+        <v>12.5990219116211</v>
       </c>
       <c r="H1416" t="n">
         <v>2784209</v>
@@ -41462,7 +41462,7 @@
         <v>16.8150005340576</v>
       </c>
       <c r="G1417" t="n">
-        <v>12.6177816390991</v>
+        <v>12.6177797317505</v>
       </c>
       <c r="H1417" t="n">
         <v>3135723</v>
@@ -41491,7 +41491,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>12.6440448760986</v>
+        <v>12.6440439224243</v>
       </c>
       <c r="H1418" t="n">
         <v>3080314</v>
@@ -41520,7 +41520,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1419" t="n">
-        <v>12.6440448760986</v>
+        <v>12.6440439224243</v>
       </c>
       <c r="H1419" t="n">
         <v>3054926</v>
@@ -41549,7 +41549,7 @@
         <v>16.6749992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>12.5127258300781</v>
+        <v>12.5127248764038</v>
       </c>
       <c r="H1420" t="n">
         <v>5689490</v>
@@ -41578,7 +41578,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.437686920166</v>
+        <v>12.4376878738403</v>
       </c>
       <c r="H1421" t="n">
         <v>4349147</v>
@@ -41607,7 +41607,7 @@
         <v>16.625</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.4752073287964</v>
+        <v>12.4752063751221</v>
       </c>
       <c r="H1422" t="n">
         <v>3233201</v>
@@ -41636,7 +41636,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.6665563583374</v>
+        <v>12.6665554046631</v>
       </c>
       <c r="H1423" t="n">
         <v>4490693</v>
@@ -41665,7 +41665,7 @@
         <v>16.9650001525879</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.7303400039673</v>
+        <v>12.730339050293</v>
       </c>
       <c r="H1424" t="n">
         <v>2223045</v>
@@ -41723,7 +41723,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G1426" t="n">
-        <v>12.9029273986816</v>
+        <v>12.902928352356</v>
       </c>
       <c r="H1426" t="n">
         <v>4030683</v>
@@ -41752,7 +41752,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G1427" t="n">
-        <v>12.9929752349854</v>
+        <v>12.9929733276367</v>
       </c>
       <c r="H1427" t="n">
         <v>3581818</v>
@@ -41781,7 +41781,7 @@
         <v>17.375</v>
       </c>
       <c r="G1428" t="n">
-        <v>13.0379981994629</v>
+        <v>13.0379972457886</v>
       </c>
       <c r="H1428" t="n">
         <v>2797230</v>
@@ -41810,7 +41810,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1429" t="n">
-        <v>12.9629602432251</v>
+        <v>12.9629573822021</v>
       </c>
       <c r="H1429" t="n">
         <v>2703430</v>
@@ -41839,7 +41839,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.8916721343994</v>
+        <v>12.8916730880737</v>
       </c>
       <c r="H1430" t="n">
         <v>2930261</v>
@@ -41868,7 +41868,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1431" t="n">
-        <v>12.9667110443115</v>
+        <v>12.9667119979858</v>
       </c>
       <c r="H1431" t="n">
         <v>3029659</v>
@@ -41897,7 +41897,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.8091297149658</v>
+        <v>12.8091287612915</v>
       </c>
       <c r="H1432" t="n">
         <v>4628841</v>
@@ -41984,7 +41984,7 @@
         <v>17.125</v>
       </c>
       <c r="G1435" t="n">
-        <v>12.8504009246826</v>
+        <v>12.8503999710083</v>
       </c>
       <c r="H1435" t="n">
         <v>1814141</v>
@@ -42042,7 +42042,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.8166341781616</v>
+        <v>12.816632270813</v>
       </c>
       <c r="H1437" t="n">
         <v>2585238</v>
@@ -42071,7 +42071,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>12.8691596984863</v>
+        <v>12.8691606521606</v>
       </c>
       <c r="H1438" t="n">
         <v>1967382</v>
@@ -42129,7 +42129,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G1440" t="n">
-        <v>12.95920753479</v>
+        <v>12.9592065811157</v>
       </c>
       <c r="H1440" t="n">
         <v>6246758</v>
@@ -42187,7 +42187,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G1442" t="n">
-        <v>13.0342454910278</v>
+        <v>13.0342473983765</v>
       </c>
       <c r="H1442" t="n">
         <v>3151345</v>
@@ -42216,7 +42216,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1443" t="n">
-        <v>12.9967260360718</v>
+        <v>12.9967269897461</v>
       </c>
       <c r="H1443" t="n">
         <v>4368045</v>
@@ -42332,7 +42332,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G1447" t="n">
-        <v>13.3156414031982</v>
+        <v>13.3156433105469</v>
       </c>
       <c r="H1447" t="n">
         <v>5118386</v>
@@ -42361,7 +42361,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1448" t="n">
-        <v>13.079270362854</v>
+        <v>13.0792713165283</v>
       </c>
       <c r="H1448" t="n">
         <v>4314816</v>
@@ -42390,7 +42390,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>13.2443542480469</v>
+        <v>13.2443552017212</v>
       </c>
       <c r="H1449" t="n">
         <v>4837767</v>
@@ -42477,7 +42477,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1452" t="n">
-        <v>13.4094409942627</v>
+        <v>13.4094400405884</v>
       </c>
       <c r="H1452" t="n">
         <v>4740108</v>
@@ -42506,7 +42506,7 @@
         <v>17.6849994659424</v>
       </c>
       <c r="G1453" t="n">
-        <v>13.2706165313721</v>
+        <v>13.2706184387207</v>
       </c>
       <c r="H1453" t="n">
         <v>8146643</v>
@@ -42535,7 +42535,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>13.0942783355713</v>
+        <v>13.094277381897</v>
       </c>
       <c r="H1454" t="n">
         <v>7102386</v>
@@ -42593,7 +42593,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>13.4919815063477</v>
+        <v>13.491982460022</v>
       </c>
       <c r="H1456" t="n">
         <v>7118240</v>
@@ -42622,7 +42622,7 @@
         <v>18.125</v>
       </c>
       <c r="G1457" t="n">
-        <v>13.6007900238037</v>
+        <v>13.6007881164551</v>
       </c>
       <c r="H1457" t="n">
         <v>6311515</v>
@@ -42651,7 +42651,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G1458" t="n">
-        <v>13.7546186447144</v>
+        <v>13.7546195983887</v>
       </c>
       <c r="H1458" t="n">
         <v>6410552</v>
@@ -42680,7 +42680,7 @@
         <v>18.625</v>
       </c>
       <c r="G1459" t="n">
-        <v>13.9759826660156</v>
+        <v>13.9759845733643</v>
       </c>
       <c r="H1459" t="n">
         <v>8266720</v>
@@ -42709,7 +42709,7 @@
         <v>18.25</v>
       </c>
       <c r="G1460" t="n">
-        <v>13.6945886611938</v>
+        <v>13.6945896148682</v>
       </c>
       <c r="H1460" t="n">
         <v>8874072</v>
@@ -42738,7 +42738,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1461" t="n">
-        <v>13.822154045105</v>
+        <v>13.8221521377563</v>
       </c>
       <c r="H1461" t="n">
         <v>7247760</v>
@@ -42767,7 +42767,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1462" t="n">
-        <v>13.7996406555176</v>
+        <v>13.7996425628662</v>
       </c>
       <c r="H1462" t="n">
         <v>6722809</v>
@@ -42796,7 +42796,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G1463" t="n">
-        <v>13.8146505355835</v>
+        <v>13.8146495819092</v>
       </c>
       <c r="H1463" t="n">
         <v>4729941</v>
@@ -42825,7 +42825,7 @@
         <v>18.375</v>
       </c>
       <c r="G1464" t="n">
-        <v>13.7883863449097</v>
+        <v>13.7883853912354</v>
       </c>
       <c r="H1464" t="n">
         <v>5950696</v>
@@ -42912,7 +42912,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1467" t="n">
-        <v>14.0772867202759</v>
+        <v>14.0772857666016</v>
       </c>
       <c r="H1467" t="n">
         <v>7007802</v>
@@ -42970,7 +42970,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1469" t="n">
-        <v>14.1785879135132</v>
+        <v>14.1785869598389</v>
       </c>
       <c r="H1469" t="n">
         <v>5899777</v>
@@ -43057,7 +43057,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>14.0510225296021</v>
+        <v>14.0510234832764</v>
       </c>
       <c r="H1472" t="n">
         <v>6136444</v>
@@ -43086,7 +43086,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1473" t="n">
-        <v>14.099796295166</v>
+        <v>14.0997972488403</v>
       </c>
       <c r="H1473" t="n">
         <v>5314614</v>
@@ -43144,7 +43144,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1475" t="n">
-        <v>14.2190275192261</v>
+        <v>14.2190265655518</v>
       </c>
       <c r="H1475" t="n">
         <v>4074796</v>
@@ -43173,7 +43173,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1476" t="n">
-        <v>14.3382549285889</v>
+        <v>14.3382539749146</v>
       </c>
       <c r="H1476" t="n">
         <v>4067206</v>
@@ -43202,7 +43202,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1477" t="n">
-        <v>14.2882566452026</v>
+        <v>14.2882585525513</v>
       </c>
       <c r="H1477" t="n">
         <v>4669894</v>
@@ -43318,7 +43318,7 @@
         <v>18.7549991607666</v>
       </c>
       <c r="G1481" t="n">
-        <v>14.4267168045044</v>
+        <v>14.4267139434814</v>
       </c>
       <c r="H1481" t="n">
         <v>3715245</v>
@@ -43347,7 +43347,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1482" t="n">
-        <v>14.4921016693115</v>
+        <v>14.4921007156372</v>
       </c>
       <c r="H1482" t="n">
         <v>2739837</v>
@@ -43405,7 +43405,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1484" t="n">
-        <v>14.5844068527222</v>
+        <v>14.5844049453735</v>
       </c>
       <c r="H1484" t="n">
         <v>4381558</v>
@@ -43492,7 +43492,7 @@
         <v>18.9950008392334</v>
       </c>
       <c r="G1487" t="n">
-        <v>14.6113300323486</v>
+        <v>14.6113290786743</v>
       </c>
       <c r="H1487" t="n">
         <v>4103204</v>
@@ -43521,7 +43521,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G1488" t="n">
-        <v>14.6959428787231</v>
+        <v>14.6959447860718</v>
       </c>
       <c r="H1488" t="n">
         <v>3423152</v>
@@ -43550,7 +43550,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G1489" t="n">
-        <v>14.5959453582764</v>
+        <v>14.5959444046021</v>
       </c>
       <c r="H1489" t="n">
         <v>4313251</v>
@@ -43579,7 +43579,7 @@
         <v>18.9850006103516</v>
       </c>
       <c r="G1490" t="n">
-        <v>14.6036367416382</v>
+        <v>14.6036376953125</v>
       </c>
       <c r="H1490" t="n">
         <v>2437110</v>
@@ -43637,7 +43637,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>14.7305564880371</v>
+        <v>14.7305583953857</v>
       </c>
       <c r="H1492" t="n">
         <v>4338793</v>
@@ -43666,7 +43666,7 @@
         <v>19.1350002288818</v>
       </c>
       <c r="G1493" t="n">
-        <v>14.7190208435059</v>
+        <v>14.7190189361572</v>
       </c>
       <c r="H1493" t="n">
         <v>6075096</v>
@@ -43695,7 +43695,7 @@
         <v>19.2399997711182</v>
       </c>
       <c r="G1494" t="n">
-        <v>14.7997884750366</v>
+        <v>14.799786567688</v>
       </c>
       <c r="H1494" t="n">
         <v>3832106</v>
@@ -43724,7 +43724,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1495" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344091415405</v>
       </c>
       <c r="H1495" t="n">
         <v>9433010</v>
@@ -43753,7 +43753,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1496" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344091415405</v>
       </c>
       <c r="H1496" t="n">
         <v>5548195</v>
@@ -43782,7 +43782,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1497" t="n">
-        <v>14.3074865341187</v>
+        <v>14.307487487793</v>
       </c>
       <c r="H1497" t="n">
         <v>4468618</v>
@@ -43811,7 +43811,7 @@
         <v>18.2849998474121</v>
       </c>
       <c r="G1498" t="n">
-        <v>14.0651817321777</v>
+        <v>14.0651826858521</v>
       </c>
       <c r="H1498" t="n">
         <v>5559416</v>
@@ -43840,7 +43840,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.1536407470703</v>
+        <v>14.1536426544189</v>
       </c>
       <c r="H1499" t="n">
         <v>3238825</v>
@@ -43869,7 +43869,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.1305656433105</v>
+        <v>14.1305675506592</v>
       </c>
       <c r="H1500" t="n">
         <v>6389063</v>
@@ -43898,7 +43898,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.1536407470703</v>
+        <v>14.1536426544189</v>
       </c>
       <c r="H1501" t="n">
         <v>3885101</v>
@@ -44014,7 +44014,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G1505" t="n">
-        <v>13.6382665634155</v>
+        <v>13.6382656097412</v>
       </c>
       <c r="H1505" t="n">
         <v>7236451</v>
@@ -44043,7 +44043,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G1506" t="n">
-        <v>13.9459524154663</v>
+        <v>13.9459543228149</v>
       </c>
       <c r="H1506" t="n">
         <v>4754985</v>
@@ -44101,7 +44101,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G1508" t="n">
-        <v>13.9921064376831</v>
+        <v>13.9921073913574</v>
       </c>
       <c r="H1508" t="n">
         <v>4923683</v>
@@ -44130,7 +44130,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.3151798248291</v>
+        <v>14.3151788711548</v>
       </c>
       <c r="H1509" t="n">
         <v>6505718</v>
@@ -44159,7 +44159,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1510" t="n">
-        <v>14.3844089508057</v>
+        <v>14.38440990448</v>
       </c>
       <c r="H1510" t="n">
         <v>5504173</v>
@@ -44188,7 +44188,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.2267179489136</v>
+        <v>14.2267198562622</v>
       </c>
       <c r="H1511" t="n">
         <v>4290654</v>
@@ -44246,7 +44246,7 @@
         <v>18.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.230565071106</v>
+        <v>14.2305660247803</v>
       </c>
       <c r="H1513" t="n">
         <v>11545814</v>
@@ -44275,7 +44275,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1514" t="n">
-        <v>14.2190275192261</v>
+        <v>14.2190265655518</v>
       </c>
       <c r="H1514" t="n">
         <v>3534166</v>
@@ -44304,7 +44304,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.1921052932739</v>
+        <v>14.1921033859253</v>
       </c>
       <c r="H1515" t="n">
         <v>6203016</v>
@@ -44333,7 +44333,7 @@
         <v>18.5</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.230565071106</v>
+        <v>14.2305660247803</v>
       </c>
       <c r="H1516" t="n">
         <v>4204960</v>
@@ -44362,7 +44362,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.3382549285889</v>
+        <v>14.3382539749146</v>
       </c>
       <c r="H1517" t="n">
         <v>7473948</v>
@@ -44391,7 +44391,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.2267179489136</v>
+        <v>14.2267198562622</v>
       </c>
       <c r="H1518" t="n">
         <v>10030772</v>
@@ -44420,7 +44420,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.1305656433105</v>
+        <v>14.1305675506592</v>
       </c>
       <c r="H1519" t="n">
         <v>5659427</v>
@@ -44478,7 +44478,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1521" t="n">
-        <v>14.1459503173828</v>
+        <v>14.1459512710571</v>
       </c>
       <c r="H1521" t="n">
         <v>2825490</v>
@@ -44565,7 +44565,7 @@
         <v>18.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.422869682312</v>
+        <v>14.4228687286377</v>
       </c>
       <c r="H1524" t="n">
         <v>3147730</v>
@@ -44594,7 +44594,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1525" t="n">
-        <v>14.3690242767334</v>
+        <v>14.3690233230591</v>
       </c>
       <c r="H1525" t="n">
         <v>2381748</v>
@@ -44681,7 +44681,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1528" t="n">
-        <v>14.6190214157104</v>
+        <v>14.6190204620361</v>
       </c>
       <c r="H1528" t="n">
         <v>4396718</v>
@@ -44739,7 +44739,7 @@
         <v>18.4650001525879</v>
       </c>
       <c r="G1530" t="n">
-        <v>14.2036418914795</v>
+        <v>14.2036437988281</v>
       </c>
       <c r="H1530" t="n">
         <v>5909180</v>
@@ -44768,7 +44768,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.2844104766846</v>
+        <v>14.2844095230103</v>
       </c>
       <c r="H1531" t="n">
         <v>3772558</v>
@@ -44826,7 +44826,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1533" t="n">
-        <v>14.2997941970825</v>
+        <v>14.2997961044312</v>
       </c>
       <c r="H1533" t="n">
         <v>2928563</v>
@@ -44855,7 +44855,7 @@
         <v>18.7450008392334</v>
       </c>
       <c r="G1534" t="n">
-        <v>14.4190254211426</v>
+        <v>14.4190235137939</v>
       </c>
       <c r="H1534" t="n">
         <v>3613089</v>
@@ -45000,7 +45000,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.3997926712036</v>
+        <v>14.3997917175293</v>
       </c>
       <c r="H1539" t="n">
         <v>7807260</v>
@@ -45029,7 +45029,7 @@
         <v>18.875</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.519021987915</v>
+        <v>14.5190238952637</v>
       </c>
       <c r="H1540" t="n">
         <v>3329355</v>
@@ -45116,7 +45116,7 @@
         <v>17.8950004577637</v>
       </c>
       <c r="G1543" t="n">
-        <v>13.7651882171631</v>
+        <v>13.7651863098145</v>
       </c>
       <c r="H1543" t="n">
         <v>4768825</v>
@@ -45261,7 +45261,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1548" t="n">
-        <v>14.3690242767334</v>
+        <v>14.3690233230591</v>
       </c>
       <c r="H1548" t="n">
         <v>3634331</v>
@@ -45290,7 +45290,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1549" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344091415405</v>
       </c>
       <c r="H1549" t="n">
         <v>4947772</v>
@@ -45319,7 +45319,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G1550" t="n">
-        <v>14.3574867248535</v>
+        <v>14.3574876785278</v>
       </c>
       <c r="H1550" t="n">
         <v>4702601</v>
@@ -45377,7 +45377,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G1552" t="n">
-        <v>13.9921064376831</v>
+        <v>13.9921073913574</v>
       </c>
       <c r="H1552" t="n">
         <v>5089672</v>
@@ -45464,7 +45464,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>14.3459482192993</v>
+        <v>14.345947265625</v>
       </c>
       <c r="H1555" t="n">
         <v>4968596</v>
@@ -45522,7 +45522,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1557" t="n">
-        <v>14.1190271377563</v>
+        <v>14.1190280914307</v>
       </c>
       <c r="H1557" t="n">
         <v>8900583</v>
@@ -45580,7 +45580,7 @@
         <v>18.9549999237061</v>
       </c>
       <c r="G1559" t="n">
-        <v>14.5805606842041</v>
+        <v>14.5805597305298</v>
       </c>
       <c r="H1559" t="n">
         <v>5076033</v>
@@ -45609,7 +45609,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1560" t="n">
-        <v>14.3151798248291</v>
+        <v>14.3151788711548</v>
       </c>
       <c r="H1560" t="n">
         <v>5085745</v>
@@ -45638,7 +45638,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1561" t="n">
-        <v>14.2613344192505</v>
+        <v>14.2613353729248</v>
       </c>
       <c r="H1561" t="n">
         <v>3509650</v>
@@ -45667,7 +45667,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.1190271377563</v>
+        <v>14.1190280914307</v>
       </c>
       <c r="H1562" t="n">
         <v>4477407</v>
@@ -45783,7 +45783,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G1566" t="n">
-        <v>13.7613410949707</v>
+        <v>13.7613401412964</v>
       </c>
       <c r="H1566" t="n">
         <v>8063379</v>
@@ -45812,7 +45812,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G1567" t="n">
-        <v>13.6382665634155</v>
+        <v>13.6382656097412</v>
       </c>
       <c r="H1567" t="n">
         <v>7497126</v>
@@ -45841,7 +45841,7 @@
         <v>17.3349990844727</v>
       </c>
       <c r="G1568" t="n">
-        <v>13.3344230651855</v>
+        <v>13.3344240188599</v>
       </c>
       <c r="H1568" t="n">
         <v>6965863</v>
@@ -45870,7 +45870,7 @@
         <v>17.2250003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.249810218811</v>
+        <v>13.2498092651367</v>
       </c>
       <c r="H1569" t="n">
         <v>6456422</v>
@@ -45899,7 +45899,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1570" t="n">
-        <v>13.1921186447144</v>
+        <v>13.19211769104</v>
       </c>
       <c r="H1570" t="n">
         <v>3572910</v>
@@ -45928,7 +45928,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1571" t="n">
-        <v>12.4844369888306</v>
+        <v>12.4844350814819</v>
       </c>
       <c r="H1571" t="n">
         <v>10030323</v>
@@ -45986,7 +45986,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>12.4421281814575</v>
+        <v>12.4421272277832</v>
       </c>
       <c r="H1573" t="n">
         <v>10028130</v>
@@ -46044,7 +46044,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1575" t="n">
-        <v>12.922890663147</v>
+        <v>12.9228916168213</v>
       </c>
       <c r="H1575" t="n">
         <v>6318342</v>
@@ -46073,7 +46073,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1576" t="n">
-        <v>13.2075023651123</v>
+        <v>13.2075033187866</v>
       </c>
       <c r="H1576" t="n">
         <v>9023591</v>
@@ -46131,7 +46131,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G1578" t="n">
-        <v>13.776725769043</v>
+        <v>13.7767267227173</v>
       </c>
       <c r="H1578" t="n">
         <v>10096800</v>
@@ -46160,7 +46160,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1579" t="n">
-        <v>14.2882566452026</v>
+        <v>14.2882585525513</v>
       </c>
       <c r="H1579" t="n">
         <v>11303014</v>
@@ -46189,7 +46189,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.3151798248291</v>
+        <v>14.3151788711548</v>
       </c>
       <c r="H1580" t="n">
         <v>13399054</v>
@@ -46218,7 +46218,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.442099571228</v>
+        <v>14.4421005249023</v>
       </c>
       <c r="H1581" t="n">
         <v>17285196</v>
@@ -46305,7 +46305,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1584" t="n">
-        <v>14.5228691101074</v>
+        <v>14.5228681564331</v>
       </c>
       <c r="H1584" t="n">
         <v>5145780</v>
@@ -46363,7 +46363,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1586" t="n">
-        <v>14.9382467269897</v>
+        <v>14.9382476806641</v>
       </c>
       <c r="H1586" t="n">
         <v>10166818</v>
@@ -46392,7 +46392,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.4920845031738</v>
+        <v>15.4920864105225</v>
       </c>
       <c r="H1587" t="n">
         <v>14733341</v>
@@ -46421,7 +46421,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1588" t="n">
-        <v>15.1767044067383</v>
+        <v>15.1767053604126</v>
       </c>
       <c r="H1588" t="n">
         <v>15007472</v>
@@ -46450,7 +46450,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1589" t="n">
-        <v>15.4767026901245</v>
+        <v>15.4767017364502</v>
       </c>
       <c r="H1589" t="n">
         <v>10618253</v>
@@ -46479,7 +46479,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.976692199707</v>
+        <v>15.97669506073</v>
       </c>
       <c r="H1590" t="n">
         <v>11260196</v>
@@ -46537,7 +46537,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.6151609420776</v>
+        <v>15.6151580810547</v>
       </c>
       <c r="H1592" t="n">
         <v>9005729</v>
@@ -46653,7 +46653,7 @@
         <v>19.5849990844727</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.0651664733887</v>
+        <v>15.0651693344116</v>
       </c>
       <c r="H1596" t="n">
         <v>6981816</v>
@@ -46682,7 +46682,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.953631401062</v>
+        <v>14.9536323547363</v>
       </c>
       <c r="H1597" t="n">
         <v>4614740</v>
@@ -46711,7 +46711,7 @@
         <v>19.2749996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>14.8267107009888</v>
+        <v>14.8267097473145</v>
       </c>
       <c r="H1598" t="n">
         <v>9007026</v>
@@ -46740,7 +46740,7 @@
         <v>19.1849994659424</v>
       </c>
       <c r="G1599" t="n">
-        <v>14.7574796676636</v>
+        <v>14.7574806213379</v>
       </c>
       <c r="H1599" t="n">
         <v>4828608</v>
@@ -46798,7 +46798,7 @@
         <v>18.75</v>
       </c>
       <c r="G1601" t="n">
-        <v>14.422869682312</v>
+        <v>14.4228687286377</v>
       </c>
       <c r="H1601" t="n">
         <v>9599569</v>
@@ -46827,7 +46827,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344091415405</v>
       </c>
       <c r="H1602" t="n">
         <v>6239086</v>
@@ -46972,7 +46972,7 @@
         <v>18.1049995422363</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.926721572876</v>
+        <v>13.9267225265503</v>
       </c>
       <c r="H1607" t="n">
         <v>5555196</v>
@@ -47001,7 +47001,7 @@
         <v>18</v>
       </c>
       <c r="G1608" t="n">
-        <v>13.8459539413452</v>
+        <v>13.8459548950195</v>
       </c>
       <c r="H1608" t="n">
         <v>4568683</v>
@@ -47030,7 +47030,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.9228763580322</v>
+        <v>13.9228773117065</v>
       </c>
       <c r="H1609" t="n">
         <v>3485129</v>
@@ -47088,7 +47088,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>14.08056640625</v>
+        <v>14.0805673599243</v>
       </c>
       <c r="H1611" t="n">
         <v>4614763</v>
@@ -47117,7 +47117,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.9997997283936</v>
+        <v>13.9997987747192</v>
       </c>
       <c r="H1612" t="n">
         <v>2918096</v>
@@ -47146,7 +47146,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.8382625579834</v>
+        <v>13.8382635116577</v>
       </c>
       <c r="H1613" t="n">
         <v>4892173</v>
@@ -47175,7 +47175,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G1614" t="n">
-        <v>13.6421117782593</v>
+        <v>13.6421127319336</v>
       </c>
       <c r="H1614" t="n">
         <v>4662698</v>
@@ -47233,7 +47233,7 @@
         <v>17.7099990844727</v>
       </c>
       <c r="G1616" t="n">
-        <v>13.6228818893433</v>
+        <v>13.6228799819946</v>
       </c>
       <c r="H1616" t="n">
         <v>4650153</v>
@@ -47262,7 +47262,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1617" t="n">
-        <v>13.6613426208496</v>
+        <v>13.6613435745239</v>
       </c>
       <c r="H1617" t="n">
         <v>5183768</v>
@@ -47291,7 +47291,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.592113494873</v>
+        <v>13.5921125411987</v>
       </c>
       <c r="H1618" t="n">
         <v>4482591</v>
@@ -47320,7 +47320,7 @@
         <v>17.7350006103516</v>
       </c>
       <c r="G1619" t="n">
-        <v>13.6421117782593</v>
+        <v>13.6421127319336</v>
       </c>
       <c r="H1619" t="n">
         <v>3720029</v>
@@ -47349,7 +47349,7 @@
         <v>17.8150005340576</v>
       </c>
       <c r="G1620" t="n">
-        <v>13.7036504745483</v>
+        <v>13.703649520874</v>
       </c>
       <c r="H1620" t="n">
         <v>3406202</v>
@@ -47378,7 +47378,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1621" t="n">
-        <v>13.9228763580322</v>
+        <v>13.9228773117065</v>
       </c>
       <c r="H1621" t="n">
         <v>6086063</v>
@@ -47407,7 +47407,7 @@
         <v>18</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8459539413452</v>
+        <v>13.8459548950195</v>
       </c>
       <c r="H1622" t="n">
         <v>3968470</v>
@@ -47436,7 +47436,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1623" t="n">
-        <v>13.9228763580322</v>
+        <v>13.9228773117065</v>
       </c>
       <c r="H1623" t="n">
         <v>8843595</v>
@@ -47523,7 +47523,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>14.1283559799194</v>
+        <v>14.1283550262451</v>
       </c>
       <c r="H1626" t="n">
         <v>3879269</v>
@@ -47581,7 +47581,7 @@
         <v>17.4249992370605</v>
       </c>
       <c r="G1628" t="n">
-        <v>14.251033782959</v>
+        <v>14.2510328292847</v>
       </c>
       <c r="H1628" t="n">
         <v>2500658</v>
@@ -47639,7 +47639,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1630" t="n">
-        <v>13.9361610412598</v>
+        <v>13.9361619949341</v>
       </c>
       <c r="H1630" t="n">
         <v>5009278</v>
@@ -47697,7 +47697,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G1632" t="n">
-        <v>13.8298406600952</v>
+        <v>13.8298416137695</v>
       </c>
       <c r="H1632" t="n">
         <v>3678924</v>
@@ -47784,7 +47784,7 @@
         <v>16.9349994659424</v>
       </c>
       <c r="G1635" t="n">
-        <v>13.8502864837646</v>
+        <v>13.8502855300903</v>
       </c>
       <c r="H1635" t="n">
         <v>2967521</v>
@@ -47900,7 +47900,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1639" t="n">
-        <v>12.8238859176636</v>
+        <v>12.8238868713379</v>
       </c>
       <c r="H1639" t="n">
         <v>8134466</v>
@@ -48074,7 +48074,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.0038118362427</v>
+        <v>13.003812789917</v>
       </c>
       <c r="H1645" t="n">
         <v>2609822</v>
@@ -48219,7 +48219,7 @@
         <v>15.5349998474121</v>
       </c>
       <c r="G1650" t="n">
-        <v>12.7052984237671</v>
+        <v>12.7052974700928</v>
       </c>
       <c r="H1650" t="n">
         <v>5670469</v>
@@ -48625,7 +48625,7 @@
         <v>14.5649995803833</v>
       </c>
       <c r="G1664" t="n">
-        <v>11.9119825363159</v>
+        <v>11.9119834899902</v>
       </c>
       <c r="H1664" t="n">
         <v>3036400</v>
@@ -48741,7 +48741,7 @@
         <v>14.2399997711182</v>
       </c>
       <c r="G1668" t="n">
-        <v>11.6461820602417</v>
+        <v>11.6461811065674</v>
       </c>
       <c r="H1668" t="n">
         <v>6429481</v>
@@ -48770,7 +48770,7 @@
         <v>14.2950000762939</v>
       </c>
       <c r="G1669" t="n">
-        <v>11.6911640167236</v>
+        <v>11.6911630630493</v>
       </c>
       <c r="H1669" t="n">
         <v>2486689</v>
@@ -48799,7 +48799,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1670" t="n">
-        <v>11.899715423584</v>
+        <v>11.8997163772583</v>
       </c>
       <c r="H1670" t="n">
         <v>2404776</v>
@@ -48828,7 +48828,7 @@
         <v>14.2600002288818</v>
       </c>
       <c r="G1671" t="n">
-        <v>11.6625394821167</v>
+        <v>11.6625385284424</v>
       </c>
       <c r="H1671" t="n">
         <v>11243026</v>
@@ -48886,7 +48886,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1673" t="n">
-        <v>11.8097505569458</v>
+        <v>11.8097515106201</v>
       </c>
       <c r="H1673" t="n">
         <v>2979994</v>
@@ -48915,7 +48915,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G1674" t="n">
-        <v>11.9283399581909</v>
+        <v>11.9283409118652</v>
       </c>
       <c r="H1674" t="n">
         <v>3548875</v>
@@ -48973,7 +48973,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>11.9406080245972</v>
+        <v>11.9406070709229</v>
       </c>
       <c r="H1676" t="n">
         <v>3998821</v>
@@ -49002,7 +49002,7 @@
         <v>14.6750001907349</v>
       </c>
       <c r="G1677" t="n">
-        <v>12.0019474029541</v>
+        <v>12.0019464492798</v>
       </c>
       <c r="H1677" t="n">
         <v>3735126</v>
@@ -49437,7 +49437,7 @@
         <v>15.0749998092651</v>
       </c>
       <c r="G1692" t="n">
-        <v>12.3290853500366</v>
+        <v>12.3290863037109</v>
       </c>
       <c r="H1692" t="n">
         <v>2773293</v>
@@ -49524,7 +49524,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.1205348968506</v>
+        <v>12.1205339431763</v>
       </c>
       <c r="H1695" t="n">
         <v>3981288</v>
@@ -49582,7 +49582,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1697" t="n">
-        <v>11.8670015335083</v>
+        <v>11.8670024871826</v>
       </c>
       <c r="H1697" t="n">
         <v>3274827</v>
@@ -49669,7 +49669,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1700" t="n">
-        <v>11.9406080245972</v>
+        <v>11.9406070709229</v>
       </c>
       <c r="H1700" t="n">
         <v>2477481</v>
@@ -49756,7 +49756,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1703" t="n">
-        <v>12.2268552780151</v>
+        <v>12.2268543243408</v>
       </c>
       <c r="H1703" t="n">
         <v>3319291</v>
@@ -49814,7 +49814,7 @@
         <v>15.1850004196167</v>
       </c>
       <c r="G1705" t="n">
-        <v>12.4190502166748</v>
+        <v>12.4190511703491</v>
       </c>
       <c r="H1705" t="n">
         <v>3948735</v>
@@ -49959,7 +49959,7 @@
         <v>14.875</v>
       </c>
       <c r="G1710" t="n">
-        <v>12.1655168533325</v>
+        <v>12.1655158996582</v>
       </c>
       <c r="H1710" t="n">
         <v>4020982</v>
@@ -49988,7 +49988,7 @@
         <v>14.914999961853</v>
       </c>
       <c r="G1711" t="n">
-        <v>12.1982307434082</v>
+        <v>12.1982297897339</v>
       </c>
       <c r="H1711" t="n">
         <v>3276314</v>
@@ -50307,7 +50307,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G1722" t="n">
-        <v>11.3517551422119</v>
+        <v>11.3517560958862</v>
       </c>
       <c r="H1722" t="n">
         <v>3812376</v>
@@ -50510,7 +50510,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1729" t="n">
-        <v>11.7770366668701</v>
+        <v>11.7770376205444</v>
       </c>
       <c r="H1729" t="n">
         <v>2290424</v>
@@ -50539,7 +50539,7 @@
         <v>14.4750003814697</v>
       </c>
       <c r="G1730" t="n">
-        <v>11.8383760452271</v>
+        <v>11.8383769989014</v>
       </c>
       <c r="H1730" t="n">
         <v>3124336</v>
@@ -50568,7 +50568,7 @@
         <v>14.6549997329712</v>
       </c>
       <c r="G1731" t="n">
-        <v>11.9855899810791</v>
+        <v>11.9855890274048</v>
       </c>
       <c r="H1731" t="n">
         <v>2813046</v>
@@ -50655,7 +50655,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1734" t="n">
-        <v>12.1368932723999</v>
+        <v>12.1368923187256</v>
       </c>
       <c r="H1734" t="n">
         <v>3612265</v>
@@ -50742,7 +50742,7 @@
         <v>15.0749998092651</v>
       </c>
       <c r="G1737" t="n">
-        <v>12.3290853500366</v>
+        <v>12.3290863037109</v>
       </c>
       <c r="H1737" t="n">
         <v>2680668</v>
@@ -51119,7 +51119,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G1750" t="n">
-        <v>13.9893207550049</v>
+        <v>13.9893217086792</v>
       </c>
       <c r="H1750" t="n">
         <v>3768252</v>
@@ -51177,7 +51177,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G1752" t="n">
-        <v>13.8993577957153</v>
+        <v>13.8993587493896</v>
       </c>
       <c r="H1752" t="n">
         <v>2969110</v>
@@ -51264,7 +51264,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1755" t="n">
-        <v>13.8870906829834</v>
+        <v>13.8870887756348</v>
       </c>
       <c r="H1755" t="n">
         <v>2805548</v>
@@ -51293,7 +51293,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G1756" t="n">
-        <v>13.8298406600952</v>
+        <v>13.8298416137695</v>
       </c>
       <c r="H1756" t="n">
         <v>4889106</v>
@@ -51409,7 +51409,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1760" t="n">
-        <v>13.854377746582</v>
+        <v>13.8543767929077</v>
       </c>
       <c r="H1760" t="n">
         <v>3496495</v>
@@ -51438,7 +51438,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1761" t="n">
-        <v>13.854377746582</v>
+        <v>13.8543767929077</v>
       </c>
       <c r="H1761" t="n">
         <v>5883393</v>
@@ -51467,7 +51467,7 @@
         <v>17.125</v>
       </c>
       <c r="G1762" t="n">
-        <v>14.0056781768799</v>
+        <v>14.0056772232056</v>
       </c>
       <c r="H1762" t="n">
         <v>3717737</v>
@@ -51525,7 +51525,7 @@
         <v>17.2150001525879</v>
       </c>
       <c r="G1764" t="n">
-        <v>14.0792856216431</v>
+        <v>14.0792865753174</v>
       </c>
       <c r="H1764" t="n">
         <v>1748815</v>
@@ -51554,7 +51554,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G1765" t="n">
-        <v>14.0751943588257</v>
+        <v>14.0751953125</v>
       </c>
       <c r="H1765" t="n">
         <v>3654628</v>
@@ -51641,7 +51641,7 @@
         <v>17.3150005340576</v>
       </c>
       <c r="G1768" t="n">
-        <v>14.1610708236694</v>
+        <v>14.1610698699951</v>
       </c>
       <c r="H1768" t="n">
         <v>5244536</v>
@@ -51844,7 +51844,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1775" t="n">
-        <v>13.6826276779175</v>
+        <v>13.6826267242432</v>
       </c>
       <c r="H1775" t="n">
         <v>2245072</v>
@@ -51873,7 +51873,7 @@
         <v>16.9799995422363</v>
       </c>
       <c r="G1776" t="n">
-        <v>13.8870906829834</v>
+        <v>13.8870887756348</v>
       </c>
       <c r="H1776" t="n">
         <v>3453831</v>
@@ -52105,7 +52105,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1784" t="n">
-        <v>13.7807712554932</v>
+        <v>13.7807703018188</v>
       </c>
       <c r="H1784" t="n">
         <v>2678337</v>
@@ -52163,7 +52163,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1786" t="n">
-        <v>14.1283559799194</v>
+        <v>14.1283550262451</v>
       </c>
       <c r="H1786" t="n">
         <v>2149995</v>
@@ -52279,7 +52279,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1790" t="n">
-        <v>14.2305870056152</v>
+        <v>14.2305879592896</v>
       </c>
       <c r="H1790" t="n">
         <v>2566221</v>
@@ -52366,7 +52366,7 @@
         <v>17.4249992370605</v>
       </c>
       <c r="G1793" t="n">
-        <v>14.251033782959</v>
+        <v>14.2510328292847</v>
       </c>
       <c r="H1793" t="n">
         <v>2517504</v>
@@ -52395,7 +52395,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1794" t="n">
-        <v>14.3205509185791</v>
+        <v>14.3205518722534</v>
       </c>
       <c r="H1794" t="n">
         <v>2839496</v>
@@ -52424,7 +52424,7 @@
         <v>17.5249996185303</v>
       </c>
       <c r="G1795" t="n">
-        <v>14.3328189849854</v>
+        <v>14.332818031311</v>
       </c>
       <c r="H1795" t="n">
         <v>3496597</v>
@@ -52540,7 +52540,7 @@
         <v>17.9150009155273</v>
       </c>
       <c r="G1799" t="n">
-        <v>14.6517820358276</v>
+        <v>14.6517810821533</v>
       </c>
       <c r="H1799" t="n">
         <v>2893595</v>
@@ -52569,7 +52569,7 @@
         <v>17.8649997711182</v>
       </c>
       <c r="G1800" t="n">
-        <v>14.6108875274658</v>
+        <v>14.6108865737915</v>
       </c>
       <c r="H1800" t="n">
         <v>3403422</v>
@@ -52685,7 +52685,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>14.6395130157471</v>
+        <v>14.6395111083984</v>
       </c>
       <c r="H1804" t="n">
         <v>4074363</v>
@@ -52801,7 +52801,7 @@
         <v>18.1100006103516</v>
       </c>
       <c r="G1808" t="n">
-        <v>14.8112602233887</v>
+        <v>14.8112621307373</v>
       </c>
       <c r="H1808" t="n">
         <v>3629439</v>
@@ -52859,7 +52859,7 @@
         <v>18.1550006866455</v>
       </c>
       <c r="G1810" t="n">
-        <v>14.8480634689331</v>
+        <v>14.8480653762817</v>
       </c>
       <c r="H1810" t="n">
         <v>2933139</v>
@@ -52888,7 +52888,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1811" t="n">
-        <v>14.9012231826782</v>
+        <v>14.9012241363525</v>
       </c>
       <c r="H1811" t="n">
         <v>3157170</v>
@@ -52917,7 +52917,7 @@
         <v>18.2450008392334</v>
       </c>
       <c r="G1812" t="n">
-        <v>14.9216709136963</v>
+        <v>14.9216718673706</v>
       </c>
       <c r="H1812" t="n">
         <v>3182588</v>
@@ -52975,7 +52975,7 @@
         <v>18.25</v>
       </c>
       <c r="G1814" t="n">
-        <v>14.9257583618164</v>
+        <v>14.925760269165</v>
       </c>
       <c r="H1814" t="n">
         <v>2393037</v>
@@ -53033,7 +53033,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1816" t="n">
-        <v>14.9707403182983</v>
+        <v>14.970742225647</v>
       </c>
       <c r="H1816" t="n">
         <v>3254847</v>
@@ -53149,7 +53149,7 @@
         <v>18.1299991607666</v>
       </c>
       <c r="G1820" t="n">
-        <v>14.8276166915894</v>
+        <v>14.827618598938</v>
       </c>
       <c r="H1820" t="n">
         <v>3441917</v>
@@ -53642,7 +53642,7 @@
         <v>17.2150001525879</v>
       </c>
       <c r="G1837" t="n">
-        <v>14.0792856216431</v>
+        <v>14.0792865753174</v>
       </c>
       <c r="H1837" t="n">
         <v>14292623</v>
@@ -53845,7 +53845,7 @@
         <v>17.8549995422363</v>
       </c>
       <c r="G1844" t="n">
-        <v>14.6027097702026</v>
+        <v>14.6027088165283</v>
       </c>
       <c r="H1844" t="n">
         <v>1750950</v>
@@ -53990,7 +53990,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G1849" t="n">
-        <v>14.9584732055664</v>
+        <v>14.958475112915</v>
       </c>
       <c r="H1849" t="n">
         <v>1984767</v>
@@ -54048,7 +54048,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1851" t="n">
-        <v>15.1711130142212</v>
+        <v>15.1711149215698</v>
       </c>
       <c r="H1851" t="n">
         <v>2839912</v>
@@ -54222,7 +54222,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1857" t="n">
-        <v>15.453272819519</v>
+        <v>15.4532718658447</v>
       </c>
       <c r="H1857" t="n">
         <v>4239236</v>
@@ -54280,7 +54280,7 @@
         <v>19.0900001525879</v>
       </c>
       <c r="G1859" t="n">
-        <v>15.6127548217773</v>
+        <v>15.6127529144287</v>
       </c>
       <c r="H1859" t="n">
         <v>2861089</v>
@@ -54309,7 +54309,7 @@
         <v>19.0949993133545</v>
       </c>
       <c r="G1860" t="n">
-        <v>15.6168432235718</v>
+        <v>15.6168441772461</v>
       </c>
       <c r="H1860" t="n">
         <v>2569651</v>
@@ -54425,7 +54425,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1864" t="n">
-        <v>15.5432367324829</v>
+        <v>15.5432348251343</v>
       </c>
       <c r="H1864" t="n">
         <v>1865369</v>
@@ -54541,7 +54541,7 @@
         <v>18.5049991607666</v>
       </c>
       <c r="G1868" t="n">
-        <v>15.1343107223511</v>
+        <v>15.1343116760254</v>
       </c>
       <c r="H1868" t="n">
         <v>4102251</v>
@@ -54628,7 +54628,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G1871" t="n">
-        <v>15.5187015533447</v>
+        <v>15.5186996459961</v>
       </c>
       <c r="H1871" t="n">
         <v>2383309</v>
@@ -54686,7 +54686,7 @@
         <v>18.6049995422363</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.2160968780518</v>
+        <v>15.2160949707031</v>
       </c>
       <c r="H1873" t="n">
         <v>4279197</v>
@@ -54715,7 +54715,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1874" t="n">
-        <v>15.3101482391357</v>
+        <v>15.3101472854614</v>
       </c>
       <c r="H1874" t="n">
         <v>3598031</v>
@@ -54744,7 +54744,7 @@
         <v>18.8649997711182</v>
       </c>
       <c r="G1875" t="n">
-        <v>15.4287376403809</v>
+        <v>15.4287357330322</v>
       </c>
       <c r="H1875" t="n">
         <v>3192778</v>
@@ -54860,7 +54860,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1879" t="n">
-        <v>15.5432367324829</v>
+        <v>15.5432348251343</v>
       </c>
       <c r="H1879" t="n">
         <v>8274071</v>
@@ -79951,6 +79951,64 @@
         <v>1221416</v>
       </c>
       <c r="I2744" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>42.7000007629395</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>42.7000007629395</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>41.6100006103516</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>41.9599990844727</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>41.9599990844727</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>1840744</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>41.9000015258789</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>42.3899993896484</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>41.8199996948242</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>42.3300018310547</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>42.3300018310547</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>1579745</v>
+      </c>
+      <c r="I2746" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/G.MI.xlsx
+++ b/data/G.MI.xlsx
@@ -427,7 +427,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G2" t="n">
-        <v>8.82273292541504</v>
+        <v>8.82273483276367</v>
       </c>
       <c r="H2" t="n">
         <v>8813463</v>
@@ -456,7 +456,7 @@
         <v>16.3700008392334</v>
       </c>
       <c r="G3" t="n">
-        <v>8.91531848907471</v>
+        <v>8.91531658172607</v>
       </c>
       <c r="H3" t="n">
         <v>6212233</v>
@@ -514,7 +514,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G5" t="n">
-        <v>8.73014831542969</v>
+        <v>8.730149269104</v>
       </c>
       <c r="H5" t="n">
         <v>9816902</v>
@@ -572,7 +572,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>8.39248752593994</v>
+        <v>8.39248847961426</v>
       </c>
       <c r="H7" t="n">
         <v>10432648</v>
@@ -630,7 +630,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G9" t="n">
-        <v>8.68113327026367</v>
+        <v>8.68113422393799</v>
       </c>
       <c r="H9" t="n">
         <v>6266552</v>
@@ -717,7 +717,7 @@
         <v>15.0699996948242</v>
       </c>
       <c r="G12" t="n">
-        <v>8.20732021331787</v>
+        <v>8.20731925964355</v>
       </c>
       <c r="H12" t="n">
         <v>7444744</v>
@@ -746,7 +746,7 @@
         <v>15.1800003051758</v>
       </c>
       <c r="G13" t="n">
-        <v>8.26722621917725</v>
+        <v>8.26722717285156</v>
       </c>
       <c r="H13" t="n">
         <v>5220065</v>
@@ -775,7 +775,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G14" t="n">
-        <v>7.94045829772949</v>
+        <v>7.94046020507812</v>
       </c>
       <c r="H14" t="n">
         <v>9513157</v>
@@ -833,7 +833,7 @@
         <v>14.9200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>8.1256275177002</v>
+        <v>8.12562656402588</v>
       </c>
       <c r="H16" t="n">
         <v>8398594</v>
@@ -891,7 +891,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>7.70627355575562</v>
+        <v>7.70627546310425</v>
       </c>
       <c r="H18" t="n">
         <v>17105392</v>
@@ -920,7 +920,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G19" t="n">
-        <v>7.60280084609985</v>
+        <v>7.60279989242554</v>
       </c>
       <c r="H19" t="n">
         <v>15563747</v>
@@ -949,7 +949,7 @@
         <v>13.3900003433228</v>
       </c>
       <c r="G20" t="n">
-        <v>7.2923698425293</v>
+        <v>7.29236888885498</v>
       </c>
       <c r="H20" t="n">
         <v>12172727</v>
@@ -978,7 +978,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G21" t="n">
-        <v>7.51021575927734</v>
+        <v>7.51021480560303</v>
       </c>
       <c r="H21" t="n">
         <v>9216215</v>
@@ -1036,7 +1036,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G23" t="n">
-        <v>7.10175609588623</v>
+        <v>7.10175514221191</v>
       </c>
       <c r="H23" t="n">
         <v>9708451</v>
@@ -1065,7 +1065,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G24" t="n">
-        <v>6.92747831344604</v>
+        <v>6.92747974395752</v>
       </c>
       <c r="H24" t="n">
         <v>12420806</v>
@@ -1094,7 +1094,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G25" t="n">
-        <v>6.85123443603516</v>
+        <v>6.851233959198</v>
       </c>
       <c r="H25" t="n">
         <v>15546483</v>
@@ -1123,7 +1123,7 @@
         <v>12.2399997711182</v>
       </c>
       <c r="G26" t="n">
-        <v>6.66606426239014</v>
+        <v>6.66606569290161</v>
       </c>
       <c r="H26" t="n">
         <v>12839676</v>
@@ -1152,7 +1152,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G27" t="n">
-        <v>6.45911169052124</v>
+        <v>6.4591121673584</v>
       </c>
       <c r="H27" t="n">
         <v>12818374</v>
@@ -1181,7 +1181,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G28" t="n">
-        <v>6.19769668579102</v>
+        <v>6.19769811630249</v>
       </c>
       <c r="H28" t="n">
         <v>14776781</v>
@@ -1239,7 +1239,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G30" t="n">
-        <v>5.96896028518677</v>
+        <v>5.96896076202393</v>
       </c>
       <c r="H30" t="n">
         <v>15791674</v>
@@ -1268,7 +1268,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G31" t="n">
-        <v>6.07243585586548</v>
+        <v>6.07243680953979</v>
       </c>
       <c r="H31" t="n">
         <v>12586956</v>
@@ -1384,7 +1384,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="G35" t="n">
-        <v>6.44277477264404</v>
+        <v>6.44277334213257</v>
       </c>
       <c r="H35" t="n">
         <v>9100095</v>
@@ -1413,7 +1413,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G36" t="n">
-        <v>6.37741994857788</v>
+        <v>6.37741947174072</v>
       </c>
       <c r="H36" t="n">
         <v>9185136</v>
@@ -1442,7 +1442,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G37" t="n">
-        <v>6.6061577796936</v>
+        <v>6.60615634918213</v>
       </c>
       <c r="H37" t="n">
         <v>7480049</v>
@@ -1471,7 +1471,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G38" t="n">
-        <v>6.60071134567261</v>
+        <v>6.60071086883545</v>
       </c>
       <c r="H38" t="n">
         <v>8394663</v>
@@ -1587,7 +1587,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G42" t="n">
-        <v>6.97649383544922</v>
+        <v>6.97649335861206</v>
       </c>
       <c r="H42" t="n">
         <v>9637114</v>
@@ -1616,7 +1616,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G43" t="n">
-        <v>7.03095483779907</v>
+        <v>7.03095531463623</v>
       </c>
       <c r="H43" t="n">
         <v>9057402</v>
@@ -1645,7 +1645,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G44" t="n">
-        <v>7.1398777961731</v>
+        <v>7.13987684249878</v>
       </c>
       <c r="H44" t="n">
         <v>9000959</v>
@@ -1674,7 +1674,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>7.13443231582642</v>
+        <v>7.13443279266357</v>
       </c>
       <c r="H45" t="n">
         <v>6775484</v>
@@ -1703,7 +1703,7 @@
         <v>12.9700002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>7.06363248825073</v>
+        <v>7.06363201141357</v>
       </c>
       <c r="H46" t="n">
         <v>7064034</v>
@@ -1761,7 +1761,7 @@
         <v>12.8699998855591</v>
       </c>
       <c r="G48" t="n">
-        <v>7.00917053222656</v>
+        <v>7.00917100906372</v>
       </c>
       <c r="H48" t="n">
         <v>7199577</v>
@@ -1790,7 +1790,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G49" t="n">
-        <v>7.06907749176025</v>
+        <v>7.06907796859741</v>
       </c>
       <c r="H49" t="n">
         <v>5929215</v>
@@ -1819,7 +1819,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G50" t="n">
-        <v>7.05818653106689</v>
+        <v>7.05818557739258</v>
       </c>
       <c r="H50" t="n">
         <v>13767476</v>
@@ -1906,7 +1906,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G53" t="n">
-        <v>7.46119976043701</v>
+        <v>7.4611988067627</v>
       </c>
       <c r="H53" t="n">
         <v>6342213</v>
@@ -1935,7 +1935,7 @@
         <v>13.8500003814697</v>
       </c>
       <c r="G54" t="n">
-        <v>7.54289150238037</v>
+        <v>7.54289245605469</v>
       </c>
       <c r="H54" t="n">
         <v>5967449</v>
@@ -1964,7 +1964,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G55" t="n">
-        <v>7.55923175811768</v>
+        <v>7.55923128128052</v>
       </c>
       <c r="H55" t="n">
         <v>8641086</v>
@@ -1993,7 +1993,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G56" t="n">
-        <v>7.43396854400635</v>
+        <v>7.43396711349487</v>
       </c>
       <c r="H56" t="n">
         <v>15946828</v>
@@ -2051,7 +2051,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G58" t="n">
-        <v>7.2542462348938</v>
+        <v>7.25424575805664</v>
       </c>
       <c r="H58" t="n">
         <v>10450774</v>
@@ -2080,7 +2080,7 @@
         <v>13.2399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>7.21067762374878</v>
+        <v>7.21067714691162</v>
       </c>
       <c r="H59" t="n">
         <v>7927596</v>
@@ -2109,7 +2109,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G60" t="n">
-        <v>7.05274057388306</v>
+        <v>7.05273866653442</v>
       </c>
       <c r="H60" t="n">
         <v>9447130</v>
@@ -2138,7 +2138,7 @@
         <v>13.0600004196167</v>
       </c>
       <c r="G61" t="n">
-        <v>7.11264705657959</v>
+        <v>7.11264753341675</v>
       </c>
       <c r="H61" t="n">
         <v>8194105</v>
@@ -2167,7 +2167,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G62" t="n">
-        <v>7.16710901260376</v>
+        <v>7.1671085357666</v>
       </c>
       <c r="H62" t="n">
         <v>5977968</v>
@@ -2196,7 +2196,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G63" t="n">
-        <v>7.09630870819092</v>
+        <v>7.09631013870239</v>
       </c>
       <c r="H63" t="n">
         <v>8427502</v>
@@ -2225,7 +2225,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G64" t="n">
-        <v>6.99283218383789</v>
+        <v>6.99283266067505</v>
       </c>
       <c r="H64" t="n">
         <v>7948810</v>
@@ -2399,7 +2399,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G70" t="n">
-        <v>6.83489513397217</v>
+        <v>6.83489370346069</v>
       </c>
       <c r="H70" t="n">
         <v>7972522</v>
@@ -2428,7 +2428,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G71" t="n">
-        <v>6.85667943954468</v>
+        <v>6.85668039321899</v>
       </c>
       <c r="H71" t="n">
         <v>9344188</v>
@@ -2486,7 +2486,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G73" t="n">
-        <v>7.2542462348938</v>
+        <v>7.25424575805664</v>
       </c>
       <c r="H73" t="n">
         <v>9306936</v>
@@ -2515,7 +2515,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G74" t="n">
-        <v>7.17800045013428</v>
+        <v>7.17800092697144</v>
       </c>
       <c r="H74" t="n">
         <v>6180792</v>
@@ -2544,7 +2544,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G75" t="n">
-        <v>7.16166305541992</v>
+        <v>7.16166257858276</v>
       </c>
       <c r="H75" t="n">
         <v>6869865</v>
@@ -2602,7 +2602,7 @@
         <v>13.3599996566772</v>
       </c>
       <c r="G77" t="n">
-        <v>7.27603101730347</v>
+        <v>7.27603197097778</v>
       </c>
       <c r="H77" t="n">
         <v>6262916</v>
@@ -2747,7 +2747,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G82" t="n">
-        <v>7.47209215164185</v>
+        <v>7.47209119796753</v>
       </c>
       <c r="H82" t="n">
         <v>6354299</v>
@@ -2805,7 +2805,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G84" t="n">
-        <v>7.2542462348938</v>
+        <v>7.25424575805664</v>
       </c>
       <c r="H84" t="n">
         <v>9311590</v>
@@ -2834,7 +2834,7 @@
         <v>13.3100004196167</v>
       </c>
       <c r="G85" t="n">
-        <v>7.24880123138428</v>
+        <v>7.24880170822144</v>
       </c>
       <c r="H85" t="n">
         <v>4741059</v>
@@ -2863,7 +2863,7 @@
         <v>13.039999961853</v>
       </c>
       <c r="G86" t="n">
-        <v>7.10175609588623</v>
+        <v>7.10175514221191</v>
       </c>
       <c r="H86" t="n">
         <v>6965987</v>
@@ -2892,7 +2892,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G87" t="n">
-        <v>7.09630870819092</v>
+        <v>7.09631013870239</v>
       </c>
       <c r="H87" t="n">
         <v>6042673</v>
@@ -2950,7 +2950,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G89" t="n">
-        <v>7.04184818267822</v>
+        <v>7.04184865951538</v>
       </c>
       <c r="H89" t="n">
         <v>7651592</v>
@@ -2979,7 +2979,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G90" t="n">
-        <v>7.04184818267822</v>
+        <v>7.04184865951538</v>
       </c>
       <c r="H90" t="n">
         <v>5919376</v>
@@ -3008,7 +3008,7 @@
         <v>13.25</v>
       </c>
       <c r="G91" t="n">
-        <v>7.21612548828125</v>
+        <v>7.21612405776978</v>
       </c>
       <c r="H91" t="n">
         <v>8908822</v>
@@ -3037,7 +3037,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G92" t="n">
-        <v>7.1398777961731</v>
+        <v>7.13987684249878</v>
       </c>
       <c r="H92" t="n">
         <v>8029065</v>
@@ -3066,7 +3066,7 @@
         <v>12.5900001525879</v>
       </c>
       <c r="G93" t="n">
-        <v>6.85667943954468</v>
+        <v>6.85668039321899</v>
       </c>
       <c r="H93" t="n">
         <v>19974264</v>
@@ -3095,7 +3095,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G94" t="n">
-        <v>6.78043413162231</v>
+        <v>6.78043460845947</v>
       </c>
       <c r="H94" t="n">
         <v>10320486</v>
@@ -3153,7 +3153,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G96" t="n">
-        <v>6.75864839553833</v>
+        <v>6.75864791870117</v>
       </c>
       <c r="H96" t="n">
         <v>9350204</v>
@@ -3211,7 +3211,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G98" t="n">
-        <v>6.81311082839966</v>
+        <v>6.81310987472534</v>
       </c>
       <c r="H98" t="n">
         <v>8273143</v>
@@ -3269,7 +3269,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G100" t="n">
-        <v>7.00730991363525</v>
+        <v>7.00731039047241</v>
       </c>
       <c r="H100" t="n">
         <v>7591339</v>
@@ -3298,7 +3298,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>7.4113564491272</v>
+        <v>7.41135740280151</v>
       </c>
       <c r="H101" t="n">
         <v>9433124</v>
@@ -3327,7 +3327,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G102" t="n">
-        <v>7.51525449752808</v>
+        <v>7.51525259017944</v>
       </c>
       <c r="H102" t="n">
         <v>9385715</v>
@@ -3356,7 +3356,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G103" t="n">
-        <v>7.51525449752808</v>
+        <v>7.51525259017944</v>
       </c>
       <c r="H103" t="n">
         <v>7099537</v>
@@ -3385,7 +3385,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G104" t="n">
-        <v>7.57297468185425</v>
+        <v>7.57297372817993</v>
       </c>
       <c r="H104" t="n">
         <v>4580345</v>
@@ -3414,7 +3414,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G105" t="n">
-        <v>7.60760688781738</v>
+        <v>7.6076078414917</v>
       </c>
       <c r="H105" t="n">
         <v>4459577</v>
@@ -3443,7 +3443,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G106" t="n">
-        <v>7.52102518081665</v>
+        <v>7.52102613449097</v>
       </c>
       <c r="H106" t="n">
         <v>8234351</v>
@@ -3501,7 +3501,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G108" t="n">
-        <v>7.43444585800171</v>
+        <v>7.43444442749023</v>
       </c>
       <c r="H108" t="n">
         <v>4536490</v>
@@ -3530,7 +3530,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G109" t="n">
-        <v>7.22664976119995</v>
+        <v>7.22664928436279</v>
       </c>
       <c r="H109" t="n">
         <v>8338944</v>
@@ -3559,7 +3559,7 @@
         <v>12.5</v>
       </c>
       <c r="G110" t="n">
-        <v>7.21510553359985</v>
+        <v>7.21510601043701</v>
       </c>
       <c r="H110" t="n">
         <v>3883393</v>
@@ -3675,7 +3675,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G114" t="n">
-        <v>7.10543632507324</v>
+        <v>7.10543489456177</v>
       </c>
       <c r="H114" t="n">
         <v>10633674</v>
@@ -3704,7 +3704,7 @@
         <v>11.9099998474121</v>
       </c>
       <c r="G115" t="n">
-        <v>6.87455177307129</v>
+        <v>6.87455224990845</v>
       </c>
       <c r="H115" t="n">
         <v>9110142</v>
@@ -3733,7 +3733,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G116" t="n">
-        <v>6.6783013343811</v>
+        <v>6.67830085754395</v>
       </c>
       <c r="H116" t="n">
         <v>9051962</v>
@@ -3762,7 +3762,7 @@
         <v>11.6099996566772</v>
       </c>
       <c r="G117" t="n">
-        <v>6.70138835906982</v>
+        <v>6.70139074325562</v>
       </c>
       <c r="H117" t="n">
         <v>6912548</v>
@@ -3791,7 +3791,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G118" t="n">
-        <v>6.62635278701782</v>
+        <v>6.62635231018066</v>
       </c>
       <c r="H118" t="n">
         <v>12346070</v>
@@ -3820,7 +3820,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G119" t="n">
-        <v>6.88609600067139</v>
+        <v>6.8860969543457</v>
       </c>
       <c r="H119" t="n">
         <v>11874246</v>
@@ -3849,7 +3849,7 @@
         <v>12.289999961853</v>
       </c>
       <c r="G120" t="n">
-        <v>7.0938925743103</v>
+        <v>7.09389162063599</v>
       </c>
       <c r="H120" t="n">
         <v>8839028</v>
@@ -3878,7 +3878,7 @@
         <v>12.5100002288818</v>
       </c>
       <c r="G121" t="n">
-        <v>7.22087717056274</v>
+        <v>7.22087812423706</v>
       </c>
       <c r="H121" t="n">
         <v>6552869</v>
@@ -3907,7 +3907,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G122" t="n">
-        <v>7.26128244400024</v>
+        <v>7.26128196716309</v>
       </c>
       <c r="H122" t="n">
         <v>6049193</v>
@@ -3936,7 +3936,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G123" t="n">
-        <v>7.57297468185425</v>
+        <v>7.57297372817993</v>
       </c>
       <c r="H123" t="n">
         <v>9854901</v>
@@ -3965,7 +3965,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G124" t="n">
-        <v>6.30311584472656</v>
+        <v>6.3031153678894</v>
       </c>
       <c r="H124" t="n">
         <v>34410764</v>
@@ -3994,7 +3994,7 @@
         <v>9.99499988555908</v>
       </c>
       <c r="G125" t="n">
-        <v>5.76919841766357</v>
+        <v>5.76919889450073</v>
       </c>
       <c r="H125" t="n">
         <v>24134297</v>
@@ -4023,7 +4023,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G126" t="n">
-        <v>5.85866451263428</v>
+        <v>5.85866498947144</v>
       </c>
       <c r="H126" t="n">
         <v>18052411</v>
@@ -4052,7 +4052,7 @@
         <v>10.3900003433228</v>
       </c>
       <c r="G127" t="n">
-        <v>5.99719524383545</v>
+        <v>5.99719476699829</v>
       </c>
       <c r="H127" t="n">
         <v>13590828</v>
@@ -4081,7 +4081,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.08954763412476</v>
+        <v>6.08954906463623</v>
       </c>
       <c r="H128" t="n">
         <v>13839943</v>
@@ -4197,7 +4197,7 @@
         <v>9.8149995803833</v>
       </c>
       <c r="G132" t="n">
-        <v>5.66529941558838</v>
+        <v>5.6653003692627</v>
       </c>
       <c r="H132" t="n">
         <v>19065078</v>
@@ -4255,7 +4255,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G134" t="n">
-        <v>6.11840867996216</v>
+        <v>6.11840915679932</v>
       </c>
       <c r="H134" t="n">
         <v>17273291</v>
@@ -4342,7 +4342,7 @@
         <v>11.1099996566772</v>
       </c>
       <c r="G137" t="n">
-        <v>6.41278600692749</v>
+        <v>6.41278648376465</v>
       </c>
       <c r="H137" t="n">
         <v>8413080</v>
@@ -4371,7 +4371,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G138" t="n">
-        <v>6.58017587661743</v>
+        <v>6.58017492294312</v>
       </c>
       <c r="H138" t="n">
         <v>9565721</v>
@@ -4400,7 +4400,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G139" t="n">
-        <v>6.51668310165405</v>
+        <v>6.51668167114258</v>
       </c>
       <c r="H139" t="n">
         <v>9994193</v>
@@ -4429,7 +4429,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G140" t="n">
-        <v>6.5513162612915</v>
+        <v>6.55131530761719</v>
       </c>
       <c r="H140" t="n">
         <v>6444579</v>
@@ -4487,7 +4487,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G142" t="n">
-        <v>6.55708646774292</v>
+        <v>6.55708694458008</v>
       </c>
       <c r="H142" t="n">
         <v>7559840</v>
@@ -4516,7 +4516,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G143" t="n">
-        <v>6.51668310165405</v>
+        <v>6.51668167114258</v>
       </c>
       <c r="H143" t="n">
         <v>8332885</v>
@@ -4545,7 +4545,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G144" t="n">
-        <v>6.48782205581665</v>
+        <v>6.48782300949097</v>
       </c>
       <c r="H144" t="n">
         <v>6107951</v>
@@ -4603,7 +4603,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G146" t="n">
-        <v>6.40124130249023</v>
+        <v>6.40124177932739</v>
       </c>
       <c r="H146" t="n">
         <v>7777276</v>
@@ -4632,7 +4632,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G147" t="n">
-        <v>6.52245473861694</v>
+        <v>6.52245569229126</v>
       </c>
       <c r="H147" t="n">
         <v>7218806</v>
@@ -4661,7 +4661,7 @@
         <v>10.9899997711182</v>
       </c>
       <c r="G148" t="n">
-        <v>6.34352016448975</v>
+        <v>6.34351968765259</v>
       </c>
       <c r="H148" t="n">
         <v>8257620</v>
@@ -4719,7 +4719,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G150" t="n">
-        <v>6.77065515518188</v>
+        <v>6.77065420150757</v>
       </c>
       <c r="H150" t="n">
         <v>9195105</v>
@@ -4748,7 +4748,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G151" t="n">
-        <v>6.50513982772827</v>
+        <v>6.50513935089111</v>
       </c>
       <c r="H151" t="n">
         <v>12278968</v>
@@ -4777,7 +4777,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G152" t="n">
-        <v>6.48782205581665</v>
+        <v>6.48782300949097</v>
       </c>
       <c r="H152" t="n">
         <v>8766213</v>
@@ -4806,7 +4806,7 @@
         <v>11.2700004577637</v>
       </c>
       <c r="G153" t="n">
-        <v>6.50513982772827</v>
+        <v>6.50513935089111</v>
       </c>
       <c r="H153" t="n">
         <v>5917393</v>
@@ -4864,7 +4864,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G155" t="n">
-        <v>6.90341377258301</v>
+        <v>6.90341186523438</v>
       </c>
       <c r="H155" t="n">
         <v>7882791</v>
@@ -4893,7 +4893,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>6.98422145843506</v>
+        <v>6.98422193527222</v>
       </c>
       <c r="H156" t="n">
         <v>7997306</v>
@@ -4922,7 +4922,7 @@
         <v>12.1099996566772</v>
       </c>
       <c r="G157" t="n">
-        <v>6.98999404907227</v>
+        <v>6.98999357223511</v>
       </c>
       <c r="H157" t="n">
         <v>7790957</v>
@@ -4951,7 +4951,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G158" t="n">
-        <v>7.03039789199829</v>
+        <v>7.03039741516113</v>
       </c>
       <c r="H158" t="n">
         <v>5503107</v>
@@ -4980,7 +4980,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G159" t="n">
-        <v>6.98422145843506</v>
+        <v>6.98422193527222</v>
       </c>
       <c r="H159" t="n">
         <v>6328424</v>
@@ -5009,7 +5009,7 @@
         <v>11.75</v>
       </c>
       <c r="G160" t="n">
-        <v>6.78219938278198</v>
+        <v>6.78219842910767</v>
       </c>
       <c r="H160" t="n">
         <v>8826122</v>
@@ -5038,7 +5038,7 @@
         <v>11.4300003051758</v>
       </c>
       <c r="G161" t="n">
-        <v>6.59749126434326</v>
+        <v>6.59749317169189</v>
       </c>
       <c r="H161" t="n">
         <v>11733873</v>
@@ -5096,7 +5096,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G163" t="n">
-        <v>6.40124130249023</v>
+        <v>6.40124177932739</v>
       </c>
       <c r="H163" t="n">
         <v>10743233</v>
@@ -5125,7 +5125,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G164" t="n">
-        <v>6.45319080352783</v>
+        <v>6.45319032669067</v>
       </c>
       <c r="H164" t="n">
         <v>6886585</v>
@@ -5212,7 +5212,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G167" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822828292847</v>
       </c>
       <c r="H167" t="n">
         <v>10954401</v>
@@ -5241,7 +5241,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G168" t="n">
-        <v>6.45896244049072</v>
+        <v>6.45896053314209</v>
       </c>
       <c r="H168" t="n">
         <v>9516470</v>
@@ -5270,7 +5270,7 @@
         <v>10.9700002670288</v>
       </c>
       <c r="G169" t="n">
-        <v>6.33197641372681</v>
+        <v>6.33197689056396</v>
       </c>
       <c r="H169" t="n">
         <v>8449827</v>
@@ -5328,7 +5328,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>6.58017587661743</v>
+        <v>6.58017492294312</v>
       </c>
       <c r="H171" t="n">
         <v>14284519</v>
@@ -5357,7 +5357,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G172" t="n">
-        <v>6.64944124221802</v>
+        <v>6.64944219589233</v>
       </c>
       <c r="H172" t="n">
         <v>14457087</v>
@@ -5386,7 +5386,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>6.69561815261841</v>
+        <v>6.69561767578125</v>
       </c>
       <c r="H173" t="n">
         <v>10129486</v>
@@ -5415,7 +5415,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G174" t="n">
-        <v>6.64366865158081</v>
+        <v>6.64366960525513</v>
       </c>
       <c r="H174" t="n">
         <v>7255728</v>
@@ -5444,7 +5444,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G175" t="n">
-        <v>6.59172105789185</v>
+        <v>6.59172058105469</v>
       </c>
       <c r="H175" t="n">
         <v>7201471</v>
@@ -5473,7 +5473,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G176" t="n">
-        <v>6.68407344818115</v>
+        <v>6.68407440185547</v>
       </c>
       <c r="H176" t="n">
         <v>9393017</v>
@@ -5502,7 +5502,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G177" t="n">
-        <v>6.85146379470825</v>
+        <v>6.85146427154541</v>
       </c>
       <c r="H177" t="n">
         <v>13932586</v>
@@ -5589,7 +5589,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G180" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822828292847</v>
       </c>
       <c r="H180" t="n">
         <v>12394032</v>
@@ -5618,7 +5618,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G181" t="n">
-        <v>6.41855812072754</v>
+        <v>6.41855716705322</v>
       </c>
       <c r="H181" t="n">
         <v>13961223</v>
@@ -5647,7 +5647,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G182" t="n">
-        <v>6.52245473861694</v>
+        <v>6.52245569229126</v>
       </c>
       <c r="H182" t="n">
         <v>17635178</v>
@@ -5705,7 +5705,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G184" t="n">
-        <v>6.45896244049072</v>
+        <v>6.45896053314209</v>
       </c>
       <c r="H184" t="n">
         <v>9845181</v>
@@ -5734,7 +5734,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G185" t="n">
-        <v>6.44164609909058</v>
+        <v>6.44164705276489</v>
       </c>
       <c r="H185" t="n">
         <v>7916766</v>
@@ -5792,7 +5792,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G187" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822828292847</v>
       </c>
       <c r="H187" t="n">
         <v>8857866</v>
@@ -5821,7 +5821,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G188" t="n">
-        <v>6.46473360061646</v>
+        <v>6.46473455429077</v>
       </c>
       <c r="H188" t="n">
         <v>5747565</v>
@@ -5879,7 +5879,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G190" t="n">
-        <v>6.28579998016357</v>
+        <v>6.28580045700073</v>
       </c>
       <c r="H190" t="n">
         <v>8152832</v>
@@ -5908,7 +5908,7 @@
         <v>10.9099998474121</v>
       </c>
       <c r="G191" t="n">
-        <v>6.29734325408936</v>
+        <v>6.2973427772522</v>
       </c>
       <c r="H191" t="n">
         <v>8512534</v>
@@ -5937,7 +5937,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G192" t="n">
-        <v>6.32620477676392</v>
+        <v>6.32620525360107</v>
       </c>
       <c r="H192" t="n">
         <v>6317897</v>
@@ -5995,7 +5995,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G194" t="n">
-        <v>6.23962306976318</v>
+        <v>6.23962354660034</v>
       </c>
       <c r="H194" t="n">
         <v>6357213</v>
@@ -6024,7 +6024,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G195" t="n">
-        <v>6.22230577468872</v>
+        <v>6.2223072052002</v>
       </c>
       <c r="H195" t="n">
         <v>7615999</v>
@@ -6053,7 +6053,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G196" t="n">
-        <v>6.48205041885376</v>
+        <v>6.4820499420166</v>
       </c>
       <c r="H196" t="n">
         <v>14421992</v>
@@ -6082,7 +6082,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G197" t="n">
-        <v>6.56863164901733</v>
+        <v>6.56863117218018</v>
       </c>
       <c r="H197" t="n">
         <v>11639969</v>
@@ -6111,7 +6111,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G198" t="n">
-        <v>6.52822685241699</v>
+        <v>6.52822828292847</v>
       </c>
       <c r="H198" t="n">
         <v>9955363</v>
@@ -6140,7 +6140,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G199" t="n">
-        <v>6.56286001205444</v>
+        <v>6.5628604888916</v>
       </c>
       <c r="H199" t="n">
         <v>6209487</v>
@@ -6169,7 +6169,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G200" t="n">
-        <v>6.55708646774292</v>
+        <v>6.55708694458008</v>
       </c>
       <c r="H200" t="n">
         <v>5693282</v>
@@ -6198,7 +6198,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G201" t="n">
-        <v>6.64944124221802</v>
+        <v>6.64944219589233</v>
       </c>
       <c r="H201" t="n">
         <v>6865636</v>
@@ -6227,7 +6227,7 @@
         <v>11.1899995803833</v>
       </c>
       <c r="G202" t="n">
-        <v>6.45896244049072</v>
+        <v>6.45896053314209</v>
       </c>
       <c r="H202" t="n">
         <v>8949862</v>
@@ -6256,7 +6256,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G203" t="n">
-        <v>6.56286001205444</v>
+        <v>6.5628604888916</v>
       </c>
       <c r="H203" t="n">
         <v>7401056</v>
@@ -6314,7 +6314,7 @@
         <v>11.8699998855591</v>
       </c>
       <c r="G205" t="n">
-        <v>6.85146379470825</v>
+        <v>6.85146427154541</v>
       </c>
       <c r="H205" t="n">
         <v>8014119</v>
@@ -6343,7 +6343,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G206" t="n">
-        <v>6.8803243637085</v>
+        <v>6.88032388687134</v>
       </c>
       <c r="H206" t="n">
         <v>6058132</v>
@@ -6372,7 +6372,7 @@
         <v>11.8900003433228</v>
       </c>
       <c r="G207" t="n">
-        <v>6.86300802230835</v>
+        <v>6.86300849914551</v>
       </c>
       <c r="H207" t="n">
         <v>7506451</v>
@@ -6401,7 +6401,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G208" t="n">
-        <v>6.89186763763428</v>
+        <v>6.89186859130859</v>
       </c>
       <c r="H208" t="n">
         <v>5934021</v>
@@ -6459,7 +6459,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G210" t="n">
-        <v>6.96113443374634</v>
+        <v>6.96113300323486</v>
       </c>
       <c r="H210" t="n">
         <v>6276601</v>
@@ -6488,7 +6488,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G211" t="n">
-        <v>7.01885461807251</v>
+        <v>7.01885414123535</v>
       </c>
       <c r="H211" t="n">
         <v>6705835</v>
@@ -6517,7 +6517,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G212" t="n">
-        <v>7.00153636932373</v>
+        <v>7.00153875350952</v>
       </c>
       <c r="H212" t="n">
         <v>7368438</v>
@@ -6546,7 +6546,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G213" t="n">
-        <v>6.83992004394531</v>
+        <v>6.839919090271</v>
       </c>
       <c r="H213" t="n">
         <v>9730239</v>
@@ -6575,7 +6575,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G214" t="n">
-        <v>6.79374361038208</v>
+        <v>6.79374313354492</v>
       </c>
       <c r="H214" t="n">
         <v>7043555</v>
@@ -6633,7 +6633,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G216" t="n">
-        <v>6.52245473861694</v>
+        <v>6.52245569229126</v>
       </c>
       <c r="H216" t="n">
         <v>9179340</v>
@@ -6691,7 +6691,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G218" t="n">
-        <v>6.38969707489014</v>
+        <v>6.38969755172729</v>
       </c>
       <c r="H218" t="n">
         <v>7904227</v>
@@ -6720,7 +6720,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G219" t="n">
-        <v>6.5455436706543</v>
+        <v>6.54554319381714</v>
       </c>
       <c r="H219" t="n">
         <v>6994491</v>
@@ -6749,7 +6749,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G220" t="n">
-        <v>6.64366865158081</v>
+        <v>6.64366960525513</v>
       </c>
       <c r="H220" t="n">
         <v>4846995</v>
@@ -6778,7 +6778,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G221" t="n">
-        <v>6.78797149658203</v>
+        <v>6.78797054290771</v>
       </c>
       <c r="H221" t="n">
         <v>15436963</v>
@@ -6807,7 +6807,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G222" t="n">
-        <v>6.79374361038208</v>
+        <v>6.79374313354492</v>
       </c>
       <c r="H222" t="n">
         <v>18839988</v>
@@ -6836,7 +6836,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G223" t="n">
-        <v>6.78797149658203</v>
+        <v>6.78797054290771</v>
       </c>
       <c r="H223" t="n">
         <v>8397323</v>
@@ -6865,7 +6865,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.83992004394531</v>
+        <v>6.839919090271</v>
       </c>
       <c r="H224" t="n">
         <v>10160700</v>
@@ -6894,7 +6894,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G225" t="n">
-        <v>6.77642679214478</v>
+        <v>6.77642631530762</v>
       </c>
       <c r="H225" t="n">
         <v>8656075</v>
@@ -6923,7 +6923,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G226" t="n">
-        <v>6.69561815261841</v>
+        <v>6.69561767578125</v>
       </c>
       <c r="H226" t="n">
         <v>8032846</v>
@@ -6952,7 +6952,7 @@
         <v>11.4099998474121</v>
       </c>
       <c r="G227" t="n">
-        <v>6.58594799041748</v>
+        <v>6.5859489440918</v>
       </c>
       <c r="H227" t="n">
         <v>11510186</v>
@@ -7010,7 +7010,7 @@
         <v>11.2299995422363</v>
       </c>
       <c r="G229" t="n">
-        <v>6.48205041885376</v>
+        <v>6.4820499420166</v>
       </c>
       <c r="H229" t="n">
         <v>7631683</v>
@@ -7068,7 +7068,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G231" t="n">
-        <v>6.52245473861694</v>
+        <v>6.52245569229126</v>
       </c>
       <c r="H231" t="n">
         <v>17290146</v>
@@ -7126,7 +7126,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69561815261841</v>
+        <v>6.69561767578125</v>
       </c>
       <c r="H233" t="n">
         <v>13130118</v>
@@ -7213,7 +7213,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G236" t="n">
-        <v>6.8803243637085</v>
+        <v>6.88032388687134</v>
       </c>
       <c r="H236" t="n">
         <v>15814753</v>
@@ -7271,7 +7271,7 @@
         <v>12.3100004196167</v>
       </c>
       <c r="G238" t="n">
-        <v>7.10543632507324</v>
+        <v>7.10543489456177</v>
       </c>
       <c r="H238" t="n">
         <v>12074647</v>
@@ -7300,7 +7300,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G239" t="n">
-        <v>7.04194211959839</v>
+        <v>7.04194307327271</v>
       </c>
       <c r="H239" t="n">
         <v>17922065</v>
@@ -7358,7 +7358,7 @@
         <v>13.7700004577637</v>
       </c>
       <c r="G241" t="n">
-        <v>7.94816017150879</v>
+        <v>7.94816112518311</v>
       </c>
       <c r="H241" t="n">
         <v>27435629</v>
@@ -7416,7 +7416,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G243" t="n">
-        <v>8.09246063232422</v>
+        <v>8.09246253967285</v>
       </c>
       <c r="H243" t="n">
         <v>17725328</v>
@@ -7445,7 +7445,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G244" t="n">
-        <v>8.11555004119873</v>
+        <v>8.11555099487305</v>
       </c>
       <c r="H244" t="n">
         <v>13689455</v>
@@ -7474,7 +7474,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G245" t="n">
-        <v>8.05782890319824</v>
+        <v>8.05782985687256</v>
       </c>
       <c r="H245" t="n">
         <v>13653874</v>
@@ -7503,7 +7503,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G246" t="n">
-        <v>7.97702026367188</v>
+        <v>7.97701835632324</v>
       </c>
       <c r="H246" t="n">
         <v>9895069</v>
@@ -7532,7 +7532,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G247" t="n">
-        <v>8.17904281616211</v>
+        <v>8.17904376983643</v>
       </c>
       <c r="H247" t="n">
         <v>13264285</v>
@@ -7735,7 +7735,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G254" t="n">
-        <v>8.30025863647461</v>
+        <v>8.30025768280029</v>
       </c>
       <c r="H254" t="n">
         <v>3930033</v>
@@ -7764,7 +7764,7 @@
         <v>14.1899995803833</v>
       </c>
       <c r="G255" t="n">
-        <v>8.19058799743652</v>
+        <v>8.19058609008789</v>
       </c>
       <c r="H255" t="n">
         <v>4984411</v>
@@ -7822,7 +7822,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G257" t="n">
-        <v>8.15018272399902</v>
+        <v>8.15018177032471</v>
       </c>
       <c r="H257" t="n">
         <v>3586162</v>
@@ -7909,7 +7909,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G260" t="n">
-        <v>8.38106536865234</v>
+        <v>8.38106632232666</v>
       </c>
       <c r="H260" t="n">
         <v>6953513</v>
@@ -7967,7 +7967,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G262" t="n">
-        <v>8.34643459320068</v>
+        <v>8.34643363952637</v>
       </c>
       <c r="H262" t="n">
         <v>4300811</v>
@@ -8025,7 +8025,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G264" t="n">
-        <v>8.17904281616211</v>
+        <v>8.17904376983643</v>
       </c>
       <c r="H264" t="n">
         <v>7985375</v>
@@ -8054,7 +8054,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G265" t="n">
-        <v>8.12709522247314</v>
+        <v>8.12709426879883</v>
       </c>
       <c r="H265" t="n">
         <v>8877713</v>
@@ -8083,7 +8083,7 @@
         <v>13.9099998474121</v>
       </c>
       <c r="G266" t="n">
-        <v>8.02896881103516</v>
+        <v>8.02896785736084</v>
       </c>
       <c r="H266" t="n">
         <v>5797945</v>
@@ -8112,7 +8112,7 @@
         <v>14.0200004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>8.09246063232422</v>
+        <v>8.09246253967285</v>
       </c>
       <c r="H267" t="n">
         <v>6018850</v>
@@ -8141,7 +8141,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G268" t="n">
-        <v>7.90775394439697</v>
+        <v>7.90775489807129</v>
       </c>
       <c r="H268" t="n">
         <v>9686115</v>
@@ -8199,7 +8199,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G270" t="n">
-        <v>7.82117462158203</v>
+        <v>7.82117557525635</v>
       </c>
       <c r="H270" t="n">
         <v>11031719</v>
@@ -8257,7 +8257,7 @@
         <v>13.710000038147</v>
       </c>
       <c r="G272" t="n">
-        <v>7.9135274887085</v>
+        <v>7.91352653503418</v>
       </c>
       <c r="H272" t="n">
         <v>10132450</v>
@@ -8402,7 +8402,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G277" t="n">
-        <v>8.88900852203369</v>
+        <v>8.88901042938232</v>
       </c>
       <c r="H277" t="n">
         <v>13161667</v>
@@ -8518,7 +8518,7 @@
         <v>14.9399995803833</v>
       </c>
       <c r="G281" t="n">
-        <v>8.62349319458008</v>
+        <v>8.62349414825439</v>
       </c>
       <c r="H281" t="n">
         <v>15703226</v>
@@ -8721,7 +8721,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G288" t="n">
-        <v>8.52536869049072</v>
+        <v>8.52536773681641</v>
       </c>
       <c r="H288" t="n">
         <v>8911764</v>
@@ -8750,7 +8750,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G289" t="n">
-        <v>8.66389846801758</v>
+        <v>8.66389751434326</v>
       </c>
       <c r="H289" t="n">
         <v>10197528</v>
@@ -8779,7 +8779,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G290" t="n">
-        <v>8.50228023529053</v>
+        <v>8.50228118896484</v>
       </c>
       <c r="H290" t="n">
         <v>10605907</v>
@@ -8808,7 +8808,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G291" t="n">
-        <v>8.53114032745361</v>
+        <v>8.53114128112793</v>
       </c>
       <c r="H291" t="n">
         <v>6504167</v>
@@ -8837,7 +8837,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G292" t="n">
-        <v>8.57731628417969</v>
+        <v>8.577317237854</v>
       </c>
       <c r="H292" t="n">
         <v>8507711</v>
@@ -8895,7 +8895,7 @@
         <v>14.6199998855591</v>
       </c>
       <c r="G294" t="n">
-        <v>8.43878650665283</v>
+        <v>8.43878555297852</v>
       </c>
       <c r="H294" t="n">
         <v>9612922</v>
@@ -8924,7 +8924,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>8.37529373168945</v>
+        <v>8.37529277801514</v>
       </c>
       <c r="H295" t="n">
         <v>7464036</v>
@@ -9011,7 +9011,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G298" t="n">
-        <v>7.90775394439697</v>
+        <v>7.90775489807129</v>
       </c>
       <c r="H298" t="n">
         <v>16724105</v>
@@ -9127,7 +9127,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G302" t="n">
-        <v>8.05782890319824</v>
+        <v>8.05782985687256</v>
       </c>
       <c r="H302" t="n">
         <v>7607569</v>
@@ -9214,7 +9214,7 @@
         <v>13.960000038147</v>
       </c>
       <c r="G305" t="n">
-        <v>8.05782890319824</v>
+        <v>8.05782985687256</v>
       </c>
       <c r="H305" t="n">
         <v>8192329</v>
@@ -9243,7 +9243,7 @@
         <v>14.1199998855591</v>
       </c>
       <c r="G306" t="n">
-        <v>8.15018272399902</v>
+        <v>8.15018177032471</v>
       </c>
       <c r="H306" t="n">
         <v>7721589</v>
@@ -9272,7 +9272,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G307" t="n">
-        <v>8.18481540679932</v>
+        <v>8.18481636047363</v>
       </c>
       <c r="H307" t="n">
         <v>7553571</v>
@@ -9301,7 +9301,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G308" t="n">
-        <v>8.17904281616211</v>
+        <v>8.17904376983643</v>
       </c>
       <c r="H308" t="n">
         <v>4597907</v>
@@ -9330,7 +9330,7 @@
         <v>14.039999961853</v>
       </c>
       <c r="G309" t="n">
-        <v>8.10400676727295</v>
+        <v>8.10400581359863</v>
       </c>
       <c r="H309" t="n">
         <v>9584039</v>
@@ -9359,7 +9359,7 @@
         <v>14.210000038147</v>
       </c>
       <c r="G310" t="n">
-        <v>8.2021312713623</v>
+        <v>8.20213031768799</v>
       </c>
       <c r="H310" t="n">
         <v>7402497</v>
@@ -9562,7 +9562,7 @@
         <v>14.5900001525879</v>
       </c>
       <c r="G317" t="n">
-        <v>8.42146968841553</v>
+        <v>8.42147064208984</v>
       </c>
       <c r="H317" t="n">
         <v>9353520</v>
@@ -9591,7 +9591,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G318" t="n">
-        <v>8.40992641448975</v>
+        <v>8.40992736816406</v>
       </c>
       <c r="H318" t="n">
         <v>7984197</v>
@@ -9649,7 +9649,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G320" t="n">
-        <v>8.52536869049072</v>
+        <v>8.52536773681641</v>
       </c>
       <c r="H320" t="n">
         <v>8129357</v>
@@ -9678,7 +9678,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G321" t="n">
-        <v>8.49073600769043</v>
+        <v>8.49073505401611</v>
       </c>
       <c r="H321" t="n">
         <v>5351013</v>
@@ -9736,7 +9736,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G323" t="n">
-        <v>8.52536869049072</v>
+        <v>8.52536773681641</v>
       </c>
       <c r="H323" t="n">
         <v>7727246</v>
@@ -9765,7 +9765,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G324" t="n">
-        <v>8.43301486968994</v>
+        <v>8.43301391601562</v>
       </c>
       <c r="H324" t="n">
         <v>9250700</v>
@@ -9852,7 +9852,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G327" t="n">
-        <v>8.26562213897705</v>
+        <v>8.26562404632568</v>
       </c>
       <c r="H327" t="n">
         <v>5065491</v>
@@ -9881,7 +9881,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G328" t="n">
-        <v>8.24253559112549</v>
+        <v>8.2425365447998</v>
       </c>
       <c r="H328" t="n">
         <v>4284730</v>
@@ -9939,7 +9939,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G330" t="n">
-        <v>8.18481540679932</v>
+        <v>8.18481636047363</v>
       </c>
       <c r="H330" t="n">
         <v>6275754</v>
@@ -10113,7 +10113,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G336" t="n">
-        <v>8.53114032745361</v>
+        <v>8.53114128112793</v>
       </c>
       <c r="H336" t="n">
         <v>14369101</v>
@@ -10142,7 +10142,7 @@
         <v>14.8199996948242</v>
       </c>
       <c r="G337" t="n">
-        <v>8.55422782897949</v>
+        <v>8.55422878265381</v>
       </c>
       <c r="H337" t="n">
         <v>5536735</v>
@@ -10229,7 +10229,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G340" t="n">
-        <v>8.38683795928955</v>
+        <v>8.38683891296387</v>
       </c>
       <c r="H340" t="n">
         <v>4732198</v>
@@ -10374,7 +10374,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G345" t="n">
-        <v>8.81974411010742</v>
+        <v>8.81974506378174</v>
       </c>
       <c r="H345" t="n">
         <v>8451119</v>
@@ -10403,7 +10403,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G346" t="n">
-        <v>8.84860420227051</v>
+        <v>8.84860515594482</v>
       </c>
       <c r="H346" t="n">
         <v>6043272</v>
@@ -10606,7 +10606,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G353" t="n">
-        <v>8.68698596954346</v>
+        <v>8.68698692321777</v>
       </c>
       <c r="H353" t="n">
         <v>17111637</v>
@@ -10635,7 +10635,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G354" t="n">
-        <v>8.73316287994385</v>
+        <v>8.73316478729248</v>
       </c>
       <c r="H354" t="n">
         <v>10390572</v>
@@ -10693,7 +10693,7 @@
         <v>14.6700000762939</v>
       </c>
       <c r="G356" t="n">
-        <v>8.94036960601807</v>
+        <v>8.94037055969238</v>
       </c>
       <c r="H356" t="n">
         <v>7459778</v>
@@ -10722,7 +10722,7 @@
         <v>14.4300003051758</v>
       </c>
       <c r="G357" t="n">
-        <v>8.79410743713379</v>
+        <v>8.79410648345947</v>
       </c>
       <c r="H357" t="n">
         <v>6528540</v>
@@ -10751,7 +10751,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G358" t="n">
-        <v>8.76972961425781</v>
+        <v>8.7697286605835</v>
       </c>
       <c r="H358" t="n">
         <v>5634717</v>
@@ -10780,7 +10780,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G359" t="n">
-        <v>8.74535083770752</v>
+        <v>8.74535179138184</v>
       </c>
       <c r="H359" t="n">
         <v>5592941</v>
@@ -10809,7 +10809,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G360" t="n">
-        <v>8.56861591339111</v>
+        <v>8.56861686706543</v>
       </c>
       <c r="H360" t="n">
         <v>6590299</v>
@@ -11041,7 +11041,7 @@
         <v>13.9700002670288</v>
       </c>
       <c r="G368" t="n">
-        <v>8.51376914978027</v>
+        <v>8.51376819610596</v>
       </c>
       <c r="H368" t="n">
         <v>8969613</v>
@@ -11099,7 +11099,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G370" t="n">
-        <v>8.66612529754639</v>
+        <v>8.6661262512207</v>
       </c>
       <c r="H370" t="n">
         <v>8294383</v>
@@ -11186,7 +11186,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G373" t="n">
-        <v>8.78191947937012</v>
+        <v>8.7819185256958</v>
       </c>
       <c r="H373" t="n">
         <v>14000240</v>
@@ -11244,7 +11244,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G375" t="n">
-        <v>8.90380573272705</v>
+        <v>8.9038028717041</v>
       </c>
       <c r="H375" t="n">
         <v>6373118</v>
@@ -11273,7 +11273,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G376" t="n">
-        <v>8.80020141601562</v>
+        <v>8.80020046234131</v>
       </c>
       <c r="H376" t="n">
         <v>4880519</v>
@@ -11302,7 +11302,7 @@
         <v>14.6899995803833</v>
       </c>
       <c r="G377" t="n">
-        <v>8.95255851745605</v>
+        <v>8.95255947113037</v>
       </c>
       <c r="H377" t="n">
         <v>8282691</v>
@@ -11331,7 +11331,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G378" t="n">
-        <v>8.86114406585693</v>
+        <v>8.86114311218262</v>
       </c>
       <c r="H378" t="n">
         <v>4126827</v>
@@ -11360,7 +11360,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G379" t="n">
-        <v>8.83067321777344</v>
+        <v>8.8306713104248</v>
       </c>
       <c r="H379" t="n">
         <v>4281758</v>
@@ -11418,7 +11418,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G381" t="n">
-        <v>8.73316287994385</v>
+        <v>8.73316478729248</v>
       </c>
       <c r="H381" t="n">
         <v>5677869</v>
@@ -11447,7 +11447,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G382" t="n">
-        <v>8.8550500869751</v>
+        <v>8.85504913330078</v>
       </c>
       <c r="H382" t="n">
         <v>7129296</v>
@@ -11505,7 +11505,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G384" t="n">
-        <v>8.78191947937012</v>
+        <v>8.7819185256958</v>
       </c>
       <c r="H384" t="n">
         <v>5634414</v>
@@ -11534,7 +11534,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G385" t="n">
-        <v>8.8977108001709</v>
+        <v>8.89770984649658</v>
       </c>
       <c r="H385" t="n">
         <v>4993574</v>
@@ -11563,7 +11563,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G386" t="n">
-        <v>8.93427658081055</v>
+        <v>8.93427753448486</v>
       </c>
       <c r="H386" t="n">
         <v>5051498</v>
@@ -11621,7 +11621,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G388" t="n">
-        <v>9.17195606231689</v>
+        <v>9.17195510864258</v>
       </c>
       <c r="H388" t="n">
         <v>10232128</v>
@@ -11679,7 +11679,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G390" t="n">
-        <v>9.17195606231689</v>
+        <v>9.17195510864258</v>
       </c>
       <c r="H390" t="n">
         <v>4811579</v>
@@ -11708,7 +11708,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G391" t="n">
-        <v>9.13538837432861</v>
+        <v>9.13538932800293</v>
       </c>
       <c r="H391" t="n">
         <v>4976109</v>
@@ -11853,7 +11853,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G396" t="n">
-        <v>9.30603122711182</v>
+        <v>9.3060302734375</v>
       </c>
       <c r="H396" t="n">
         <v>5090753</v>
@@ -12085,7 +12085,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G404" t="n">
-        <v>9.30603122711182</v>
+        <v>9.3060302734375</v>
       </c>
       <c r="H404" t="n">
         <v>3965992</v>
@@ -12230,7 +12230,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G409" t="n">
-        <v>9.70825481414795</v>
+        <v>9.70825576782227</v>
       </c>
       <c r="H409" t="n">
         <v>4919197</v>
@@ -12259,7 +12259,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G410" t="n">
-        <v>9.79966926574707</v>
+        <v>9.7996711730957</v>
       </c>
       <c r="H410" t="n">
         <v>5528680</v>
@@ -12288,7 +12288,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G411" t="n">
-        <v>9.76310539245605</v>
+        <v>9.76310443878174</v>
       </c>
       <c r="H411" t="n">
         <v>4406257</v>
@@ -12346,7 +12346,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G413" t="n">
-        <v>9.58027362823486</v>
+        <v>9.58027458190918</v>
       </c>
       <c r="H413" t="n">
         <v>4896013</v>
@@ -12375,7 +12375,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G414" t="n">
-        <v>9.40963172912598</v>
+        <v>9.40963268280029</v>
       </c>
       <c r="H414" t="n">
         <v>5885179</v>
@@ -12578,7 +12578,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G421" t="n">
-        <v>9.28774738311768</v>
+        <v>9.28774642944336</v>
       </c>
       <c r="H421" t="n">
         <v>4876525</v>
@@ -12694,7 +12694,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G425" t="n">
-        <v>9.12929439544678</v>
+        <v>9.12929534912109</v>
       </c>
       <c r="H425" t="n">
         <v>6430468</v>
@@ -12897,7 +12897,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G432" t="n">
-        <v>9.12929439544678</v>
+        <v>9.12929534912109</v>
       </c>
       <c r="H432" t="n">
         <v>4782153</v>
@@ -12984,7 +12984,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G435" t="n">
-        <v>9.4705753326416</v>
+        <v>9.47057628631592</v>
       </c>
       <c r="H435" t="n">
         <v>6196669</v>
@@ -13071,7 +13071,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G438" t="n">
-        <v>9.336501121521</v>
+        <v>9.33650207519531</v>
       </c>
       <c r="H438" t="n">
         <v>6766626</v>
@@ -13129,7 +13129,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>9.47667121887207</v>
+        <v>9.47667026519775</v>
       </c>
       <c r="H440" t="n">
         <v>3195954</v>
@@ -13158,7 +13158,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G441" t="n">
-        <v>9.47667121887207</v>
+        <v>9.47667026519775</v>
       </c>
       <c r="H441" t="n">
         <v>5385574</v>
@@ -13274,7 +13274,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G445" t="n">
-        <v>9.30603122711182</v>
+        <v>9.3060302734375</v>
       </c>
       <c r="H445" t="n">
         <v>5577703</v>
@@ -13332,7 +13332,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G447" t="n">
-        <v>9.45838928222656</v>
+        <v>9.45838737487793</v>
       </c>
       <c r="H447" t="n">
         <v>4551096</v>
@@ -13419,7 +13419,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G450" t="n">
-        <v>9.70216178894043</v>
+        <v>9.7021598815918</v>
       </c>
       <c r="H450" t="n">
         <v>5777557</v>
@@ -13506,7 +13506,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G453" t="n">
-        <v>9.51323509216309</v>
+        <v>9.5132360458374</v>
       </c>
       <c r="H453" t="n">
         <v>4928012</v>
@@ -13535,7 +13535,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G454" t="n">
-        <v>9.51323509216309</v>
+        <v>9.5132360458374</v>
       </c>
       <c r="H454" t="n">
         <v>3315712</v>
@@ -13564,7 +13564,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G455" t="n">
-        <v>9.42791843414307</v>
+        <v>9.42791748046875</v>
       </c>
       <c r="H455" t="n">
         <v>5112544</v>
@@ -13593,7 +13593,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G456" t="n">
-        <v>9.4705753326416</v>
+        <v>9.47057628631592</v>
       </c>
       <c r="H456" t="n">
         <v>5113218</v>
@@ -13651,7 +13651,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G458" t="n">
-        <v>9.43401050567627</v>
+        <v>9.43400955200195</v>
       </c>
       <c r="H458" t="n">
         <v>4394253</v>
@@ -13680,7 +13680,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G459" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H459" t="n">
         <v>4853077</v>
@@ -13709,7 +13709,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G460" t="n">
-        <v>9.31212425231934</v>
+        <v>9.31212520599365</v>
       </c>
       <c r="H460" t="n">
         <v>6408839</v>
@@ -13738,7 +13738,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G461" t="n">
-        <v>9.336501121521</v>
+        <v>9.33650207519531</v>
       </c>
       <c r="H461" t="n">
         <v>5113182</v>
@@ -13767,7 +13767,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>9.336501121521</v>
+        <v>9.33650207519531</v>
       </c>
       <c r="H462" t="n">
         <v>5103039</v>
@@ -13825,7 +13825,7 @@
         <v>15.6099996566772</v>
       </c>
       <c r="G464" t="n">
-        <v>9.51323509216309</v>
+        <v>9.5132360458374</v>
       </c>
       <c r="H464" t="n">
         <v>4665406</v>
@@ -13883,7 +13883,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G466" t="n">
-        <v>9.5376148223877</v>
+        <v>9.53761291503906</v>
       </c>
       <c r="H466" t="n">
         <v>5602376</v>
@@ -13941,7 +13941,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G468" t="n">
-        <v>9.5376148223877</v>
+        <v>9.53761291503906</v>
       </c>
       <c r="H468" t="n">
         <v>5622102</v>
@@ -14057,7 +14057,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G472" t="n">
-        <v>9.70825481414795</v>
+        <v>9.70825576782227</v>
       </c>
       <c r="H472" t="n">
         <v>4601910</v>
@@ -14115,7 +14115,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>9.5376148223877</v>
+        <v>9.53761291503906</v>
       </c>
       <c r="H474" t="n">
         <v>4310682</v>
@@ -14202,7 +14202,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G477" t="n">
-        <v>9.46448230743408</v>
+        <v>9.4644832611084</v>
       </c>
       <c r="H477" t="n">
         <v>4793218</v>
@@ -14231,7 +14231,7 @@
         <v>15.7700004577637</v>
       </c>
       <c r="G478" t="n">
-        <v>9.61074638366699</v>
+        <v>9.61074733734131</v>
       </c>
       <c r="H478" t="n">
         <v>8017354</v>
@@ -14260,7 +14260,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G479" t="n">
-        <v>9.47667121887207</v>
+        <v>9.47667026519775</v>
       </c>
       <c r="H479" t="n">
         <v>5134316</v>
@@ -14289,7 +14289,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G480" t="n">
-        <v>9.37306690216064</v>
+        <v>9.37306785583496</v>
       </c>
       <c r="H480" t="n">
         <v>6454695</v>
@@ -14318,7 +14318,7 @@
         <v>15.2700004577637</v>
       </c>
       <c r="G481" t="n">
-        <v>9.30603122711182</v>
+        <v>9.3060302734375</v>
       </c>
       <c r="H481" t="n">
         <v>5486171</v>
@@ -14405,7 +14405,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G484" t="n">
-        <v>9.28774738311768</v>
+        <v>9.28774642944336</v>
       </c>
       <c r="H484" t="n">
         <v>3345978</v>
@@ -14579,7 +14579,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G490" t="n">
-        <v>9.22680282592773</v>
+        <v>9.22680473327637</v>
       </c>
       <c r="H490" t="n">
         <v>5490228</v>
@@ -14637,7 +14637,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G492" t="n">
-        <v>9.37306690216064</v>
+        <v>9.37306785583496</v>
       </c>
       <c r="H492" t="n">
         <v>5305139</v>
@@ -14753,7 +14753,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G496" t="n">
-        <v>9.20242595672607</v>
+        <v>9.20242691040039</v>
       </c>
       <c r="H496" t="n">
         <v>4499730</v>
@@ -14782,7 +14782,7 @@
         <v>15.1899995803833</v>
       </c>
       <c r="G497" t="n">
-        <v>9.25727462768555</v>
+        <v>9.25727558135986</v>
       </c>
       <c r="H497" t="n">
         <v>4333453</v>
@@ -14811,7 +14811,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G498" t="n">
-        <v>9.31212425231934</v>
+        <v>9.31212520599365</v>
       </c>
       <c r="H498" t="n">
         <v>4469888</v>
@@ -14840,7 +14840,7 @@
         <v>15.3100004196167</v>
       </c>
       <c r="G499" t="n">
-        <v>9.33040618896484</v>
+        <v>9.33040714263916</v>
       </c>
       <c r="H499" t="n">
         <v>3019971</v>
@@ -14927,7 +14927,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H502" t="n">
         <v>7025531</v>
@@ -14956,7 +14956,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G503" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H503" t="n">
         <v>7473414</v>
@@ -14985,7 +14985,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G504" t="n">
-        <v>9.45838928222656</v>
+        <v>9.45838737487793</v>
       </c>
       <c r="H504" t="n">
         <v>4775495</v>
@@ -15014,7 +15014,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G505" t="n">
-        <v>9.39134883880615</v>
+        <v>9.39134979248047</v>
       </c>
       <c r="H505" t="n">
         <v>4087366</v>
@@ -15072,7 +15072,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G507" t="n">
-        <v>9.28774738311768</v>
+        <v>9.28774642944336</v>
       </c>
       <c r="H507" t="n">
         <v>6928129</v>
@@ -15101,7 +15101,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G508" t="n">
-        <v>9.31212425231934</v>
+        <v>9.31212520599365</v>
       </c>
       <c r="H508" t="n">
         <v>3624996</v>
@@ -15130,7 +15130,7 @@
         <v>15.25</v>
       </c>
       <c r="G509" t="n">
-        <v>9.29384231567383</v>
+        <v>9.29384136199951</v>
       </c>
       <c r="H509" t="n">
         <v>3234122</v>
@@ -15217,7 +15217,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G512" t="n">
-        <v>9.15367221832275</v>
+        <v>9.15367126464844</v>
       </c>
       <c r="H512" t="n">
         <v>5300727</v>
@@ -15246,7 +15246,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G513" t="n">
-        <v>9.07444477081299</v>
+        <v>9.0744457244873</v>
       </c>
       <c r="H513" t="n">
         <v>8118315</v>
@@ -15420,7 +15420,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G519" t="n">
-        <v>9.58027362823486</v>
+        <v>9.58027458190918</v>
       </c>
       <c r="H519" t="n">
         <v>5891548</v>
@@ -15478,7 +15478,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G521" t="n">
-        <v>9.55589580535889</v>
+        <v>9.55589771270752</v>
       </c>
       <c r="H521" t="n">
         <v>3333390</v>
@@ -15594,7 +15594,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G525" t="n">
-        <v>9.85451793670654</v>
+        <v>9.85451889038086</v>
       </c>
       <c r="H525" t="n">
         <v>14229701</v>
@@ -15623,7 +15623,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G526" t="n">
-        <v>9.86670875549316</v>
+        <v>9.86670780181885</v>
       </c>
       <c r="H526" t="n">
         <v>4997658</v>
@@ -15652,7 +15652,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G527" t="n">
-        <v>9.76919937133789</v>
+        <v>9.76919841766357</v>
       </c>
       <c r="H527" t="n">
         <v>4887951</v>
@@ -15681,7 +15681,7 @@
         <v>16.1900005340576</v>
       </c>
       <c r="G528" t="n">
-        <v>9.86670875549316</v>
+        <v>9.86670780181885</v>
       </c>
       <c r="H528" t="n">
         <v>8329698</v>
@@ -15710,7 +15710,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G529" t="n">
-        <v>9.87280082702637</v>
+        <v>9.872802734375</v>
       </c>
       <c r="H529" t="n">
         <v>6365879</v>
@@ -15768,7 +15768,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>9.87280082702637</v>
+        <v>9.872802734375</v>
       </c>
       <c r="H531" t="n">
         <v>4458701</v>
@@ -15797,7 +15797,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G532" t="n">
-        <v>9.741774559021</v>
+        <v>9.74177360534668</v>
       </c>
       <c r="H532" t="n">
         <v>6561651</v>
@@ -15826,7 +15826,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G533" t="n">
-        <v>9.73263168334961</v>
+        <v>9.73263263702393</v>
       </c>
       <c r="H533" t="n">
         <v>5375837</v>
@@ -15855,7 +15855,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G534" t="n">
-        <v>9.76919937133789</v>
+        <v>9.76919841766357</v>
       </c>
       <c r="H534" t="n">
         <v>7719426</v>
@@ -15884,7 +15884,7 @@
         <v>15.9449996948242</v>
       </c>
       <c r="G535" t="n">
-        <v>9.71739673614502</v>
+        <v>9.7173957824707</v>
       </c>
       <c r="H535" t="n">
         <v>7404108</v>
@@ -15913,7 +15913,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G536" t="n">
-        <v>9.58027362823486</v>
+        <v>9.58027458190918</v>
       </c>
       <c r="H536" t="n">
         <v>8482680</v>
@@ -15942,7 +15942,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G537" t="n">
-        <v>9.31212425231934</v>
+        <v>9.31212520599365</v>
       </c>
       <c r="H537" t="n">
         <v>14347815</v>
@@ -15971,7 +15971,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G538" t="n">
-        <v>9.56808662414551</v>
+        <v>9.56808471679688</v>
       </c>
       <c r="H538" t="n">
         <v>9984938</v>
@@ -16058,7 +16058,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G541" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H541" t="n">
         <v>4635218</v>
@@ -16232,7 +16232,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G547" t="n">
-        <v>9.40049076080322</v>
+        <v>9.40049171447754</v>
       </c>
       <c r="H547" t="n">
         <v>5648307</v>
@@ -16261,7 +16261,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G548" t="n">
-        <v>9.42791843414307</v>
+        <v>9.42791748046875</v>
       </c>
       <c r="H548" t="n">
         <v>3399052</v>
@@ -16290,7 +16290,7 @@
         <v>15.3199996948242</v>
       </c>
       <c r="G549" t="n">
-        <v>9.336501121521</v>
+        <v>9.33650207519531</v>
       </c>
       <c r="H549" t="n">
         <v>6237027</v>
@@ -16319,7 +16319,7 @@
         <v>15.3649997711182</v>
       </c>
       <c r="G550" t="n">
-        <v>9.36392593383789</v>
+        <v>9.36392688751221</v>
       </c>
       <c r="H550" t="n">
         <v>3899987</v>
@@ -16348,7 +16348,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G551" t="n">
-        <v>9.39134883880615</v>
+        <v>9.39134979248047</v>
       </c>
       <c r="H551" t="n">
         <v>2970106</v>
@@ -16377,7 +16377,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G552" t="n">
-        <v>9.39744567871094</v>
+        <v>9.39744472503662</v>
       </c>
       <c r="H552" t="n">
         <v>4082100</v>
@@ -16406,7 +16406,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G553" t="n">
-        <v>9.40963172912598</v>
+        <v>9.40963268280029</v>
       </c>
       <c r="H553" t="n">
         <v>4248533</v>
@@ -16464,7 +16464,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G555" t="n">
-        <v>9.17195606231689</v>
+        <v>9.17195510864258</v>
       </c>
       <c r="H555" t="n">
         <v>8922762</v>
@@ -16609,7 +16609,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G560" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H560" t="n">
         <v>3237762</v>
@@ -16638,7 +16638,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>9.41572761535645</v>
+        <v>9.41572666168213</v>
       </c>
       <c r="H561" t="n">
         <v>4167119</v>
@@ -16667,7 +16667,7 @@
         <v>15.4849996566772</v>
       </c>
       <c r="G562" t="n">
-        <v>9.43705749511719</v>
+        <v>9.43705654144287</v>
       </c>
       <c r="H562" t="n">
         <v>4422978</v>
@@ -16725,7 +16725,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>9.56808662414551</v>
+        <v>9.56808471679688</v>
       </c>
       <c r="H564" t="n">
         <v>12431022</v>
@@ -16754,7 +16754,7 @@
         <v>15.7250003814697</v>
       </c>
       <c r="G565" t="n">
-        <v>9.58332061767578</v>
+        <v>9.5833215713501</v>
       </c>
       <c r="H565" t="n">
         <v>13794698</v>
@@ -16783,7 +16783,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="G566" t="n">
-        <v>9.56199264526367</v>
+        <v>9.56199169158936</v>
       </c>
       <c r="H566" t="n">
         <v>6329836</v>
@@ -16870,7 +16870,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>9.5071439743042</v>
+        <v>9.50714302062988</v>
       </c>
       <c r="H569" t="n">
         <v>6786377</v>
@@ -16899,7 +16899,7 @@
         <v>15.4250001907349</v>
       </c>
       <c r="G570" t="n">
-        <v>9.40049076080322</v>
+        <v>9.40049171447754</v>
       </c>
       <c r="H570" t="n">
         <v>7378374</v>
@@ -16957,7 +16957,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G572" t="n">
-        <v>9.43401050567627</v>
+        <v>9.43400955200195</v>
       </c>
       <c r="H572" t="n">
         <v>4596941</v>
@@ -17015,7 +17015,7 @@
         <v>15.625</v>
       </c>
       <c r="G574" t="n">
-        <v>9.52237701416016</v>
+        <v>9.52237796783447</v>
       </c>
       <c r="H574" t="n">
         <v>5849706</v>
@@ -17160,7 +17160,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G579" t="n">
-        <v>9.73263168334961</v>
+        <v>9.73263263702393</v>
       </c>
       <c r="H579" t="n">
         <v>5675417</v>
@@ -17189,7 +17189,7 @@
         <v>16.0300006866455</v>
       </c>
       <c r="G580" t="n">
-        <v>9.76919937133789</v>
+        <v>9.76919841766357</v>
       </c>
       <c r="H580" t="n">
         <v>4678830</v>
@@ -17218,7 +17218,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G581" t="n">
-        <v>9.72958469390869</v>
+        <v>9.72958564758301</v>
       </c>
       <c r="H581" t="n">
         <v>3572026</v>
@@ -17247,7 +17247,7 @@
         <v>16.2049999237061</v>
       </c>
       <c r="G582" t="n">
-        <v>9.87585067749023</v>
+        <v>9.87584781646729</v>
       </c>
       <c r="H582" t="n">
         <v>4938134</v>
@@ -17276,7 +17276,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G583" t="n">
-        <v>9.85756683349609</v>
+        <v>9.85756587982178</v>
       </c>
       <c r="H583" t="n">
         <v>5193807</v>
@@ -17305,7 +17305,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G584" t="n">
-        <v>9.85451793670654</v>
+        <v>9.85451889038086</v>
       </c>
       <c r="H584" t="n">
         <v>2547585</v>
@@ -17334,7 +17334,7 @@
         <v>16.2549991607666</v>
       </c>
       <c r="G585" t="n">
-        <v>9.9063196182251</v>
+        <v>9.90632057189941</v>
       </c>
       <c r="H585" t="n">
         <v>6197281</v>
@@ -17363,7 +17363,7 @@
         <v>16.3950004577637</v>
       </c>
       <c r="G586" t="n">
-        <v>9.99164199829102</v>
+        <v>9.9916410446167</v>
       </c>
       <c r="H586" t="n">
         <v>5709039</v>
@@ -17421,7 +17421,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G588" t="n">
-        <v>10.1866588592529</v>
+        <v>10.1866598129272</v>
       </c>
       <c r="H588" t="n">
         <v>6937160</v>
@@ -17450,7 +17450,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G589" t="n">
-        <v>10.3085470199585</v>
+        <v>10.3085460662842</v>
       </c>
       <c r="H589" t="n">
         <v>5412434</v>
@@ -17479,7 +17479,7 @@
         <v>17.0550003051758</v>
       </c>
       <c r="G590" t="n">
-        <v>10.3938655853271</v>
+        <v>10.3938665390015</v>
       </c>
       <c r="H590" t="n">
         <v>5932050</v>
@@ -17537,7 +17537,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G592" t="n">
-        <v>10.2628383636475</v>
+        <v>10.2628393173218</v>
       </c>
       <c r="H592" t="n">
         <v>7553796</v>
@@ -17595,7 +17595,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G594" t="n">
-        <v>10.2018947601318</v>
+        <v>10.2018957138062</v>
       </c>
       <c r="H594" t="n">
         <v>5948888</v>
@@ -17624,7 +17624,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G595" t="n">
-        <v>10.2536964416504</v>
+        <v>10.2536973953247</v>
       </c>
       <c r="H595" t="n">
         <v>4486053</v>
@@ -17653,7 +17653,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G596" t="n">
-        <v>10.2506494522095</v>
+        <v>10.2506484985352</v>
       </c>
       <c r="H596" t="n">
         <v>3996552</v>
@@ -17769,7 +17769,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G600" t="n">
-        <v>10.0921974182129</v>
+        <v>10.0921964645386</v>
       </c>
       <c r="H600" t="n">
         <v>5548187</v>
@@ -17827,7 +17827,7 @@
         <v>16.5</v>
       </c>
       <c r="G602" t="n">
-        <v>10.0556316375732</v>
+        <v>10.0556306838989</v>
       </c>
       <c r="H602" t="n">
         <v>3301578</v>
@@ -17856,7 +17856,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G603" t="n">
-        <v>10.0921974182129</v>
+        <v>10.0921964645386</v>
       </c>
       <c r="H603" t="n">
         <v>4190167</v>
@@ -17914,7 +17914,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G605" t="n">
-        <v>9.86061191558838</v>
+        <v>9.8606128692627</v>
       </c>
       <c r="H605" t="n">
         <v>12595812</v>
@@ -17943,7 +17943,7 @@
         <v>16.2350006103516</v>
       </c>
       <c r="G606" t="n">
-        <v>9.89413166046143</v>
+        <v>9.89413261413574</v>
       </c>
       <c r="H606" t="n">
         <v>7807615</v>
@@ -18146,7 +18146,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G613" t="n">
-        <v>9.42194938659668</v>
+        <v>9.421950340271</v>
       </c>
       <c r="H613" t="n">
         <v>9941412</v>
@@ -18175,7 +18175,7 @@
         <v>14.1350002288818</v>
       </c>
       <c r="G614" t="n">
-        <v>9.09383678436279</v>
+        <v>9.09383773803711</v>
       </c>
       <c r="H614" t="n">
         <v>14805815</v>
@@ -18204,7 +18204,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G615" t="n">
-        <v>9.14852237701416</v>
+        <v>9.14852333068848</v>
       </c>
       <c r="H615" t="n">
         <v>11805952</v>
@@ -18320,7 +18320,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G619" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H619" t="n">
         <v>7182041</v>
@@ -18349,7 +18349,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G620" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H620" t="n">
         <v>7830245</v>
@@ -18378,7 +18378,7 @@
         <v>14.4049997329712</v>
       </c>
       <c r="G621" t="n">
-        <v>9.26754379272461</v>
+        <v>9.26754474639893</v>
       </c>
       <c r="H621" t="n">
         <v>4722584</v>
@@ -18407,7 +18407,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G622" t="n">
-        <v>9.11635589599609</v>
+        <v>9.11635780334473</v>
       </c>
       <c r="H622" t="n">
         <v>6098385</v>
@@ -18436,7 +18436,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G623" t="n">
-        <v>9.3833475112915</v>
+        <v>9.38334846496582</v>
       </c>
       <c r="H623" t="n">
         <v>8132960</v>
@@ -18523,7 +18523,7 @@
         <v>14.7349996566772</v>
       </c>
       <c r="G626" t="n">
-        <v>9.47985076904297</v>
+        <v>9.47985172271729</v>
       </c>
       <c r="H626" t="n">
         <v>9337415</v>
@@ -18552,7 +18552,7 @@
         <v>14.5950002670288</v>
       </c>
       <c r="G627" t="n">
-        <v>9.3897819519043</v>
+        <v>9.38978290557861</v>
       </c>
       <c r="H627" t="n">
         <v>7853948</v>
@@ -18581,7 +18581,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G628" t="n">
-        <v>9.3479642868042</v>
+        <v>9.34796333312988</v>
       </c>
       <c r="H628" t="n">
         <v>3956775</v>
@@ -18610,7 +18610,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G629" t="n">
-        <v>9.3833475112915</v>
+        <v>9.38334846496582</v>
       </c>
       <c r="H629" t="n">
         <v>4492025</v>
@@ -18668,7 +18668,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G631" t="n">
-        <v>9.28684520721436</v>
+        <v>9.28684616088867</v>
       </c>
       <c r="H631" t="n">
         <v>4660571</v>
@@ -18697,7 +18697,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G632" t="n">
-        <v>9.35439682006836</v>
+        <v>9.35439777374268</v>
       </c>
       <c r="H632" t="n">
         <v>3243473</v>
@@ -18726,7 +18726,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G633" t="n">
-        <v>9.1935567855835</v>
+        <v>9.19355869293213</v>
       </c>
       <c r="H633" t="n">
         <v>3783491</v>
@@ -18784,7 +18784,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G635" t="n">
-        <v>9.1935567855835</v>
+        <v>9.19355869293213</v>
       </c>
       <c r="H635" t="n">
         <v>5340654</v>
@@ -18813,7 +18813,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G636" t="n">
-        <v>9.11957263946533</v>
+        <v>9.11957168579102</v>
       </c>
       <c r="H636" t="n">
         <v>4991788</v>
@@ -18842,7 +18842,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G637" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H637" t="n">
         <v>4871372</v>
@@ -18987,7 +18987,7 @@
         <v>14.539999961853</v>
       </c>
       <c r="G642" t="n">
-        <v>9.35439682006836</v>
+        <v>9.35439777374268</v>
       </c>
       <c r="H642" t="n">
         <v>3149780</v>
@@ -19016,7 +19016,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G643" t="n">
-        <v>9.35761260986328</v>
+        <v>9.35761451721191</v>
       </c>
       <c r="H643" t="n">
         <v>2266231</v>
@@ -19045,7 +19045,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G644" t="n">
-        <v>9.3157958984375</v>
+        <v>9.31579685211182</v>
       </c>
       <c r="H644" t="n">
         <v>3014064</v>
@@ -19190,7 +19190,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G649" t="n">
-        <v>9.43159961700439</v>
+        <v>9.43160057067871</v>
       </c>
       <c r="H649" t="n">
         <v>3725702</v>
@@ -19248,7 +19248,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G651" t="n">
-        <v>9.39943408966064</v>
+        <v>9.39943218231201</v>
       </c>
       <c r="H651" t="n">
         <v>3481748</v>
@@ -19277,7 +19277,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>9.33509635925293</v>
+        <v>9.33509731292725</v>
       </c>
       <c r="H652" t="n">
         <v>5165820</v>
@@ -19306,7 +19306,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G653" t="n">
-        <v>9.35761260986328</v>
+        <v>9.35761451721191</v>
       </c>
       <c r="H653" t="n">
         <v>2920898</v>
@@ -19335,7 +19335,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G654" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020053863525</v>
       </c>
       <c r="H654" t="n">
         <v>3763142</v>
@@ -19364,7 +19364,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G655" t="n">
-        <v>9.48306941986084</v>
+        <v>9.48306846618652</v>
       </c>
       <c r="H655" t="n">
         <v>3921466</v>
@@ -19393,7 +19393,7 @@
         <v>14.7700004577637</v>
       </c>
       <c r="G656" t="n">
-        <v>9.50236892700195</v>
+        <v>9.50236988067627</v>
       </c>
       <c r="H656" t="n">
         <v>2675893</v>
@@ -19422,7 +19422,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G657" t="n">
-        <v>9.54740428924561</v>
+        <v>9.54740333557129</v>
       </c>
       <c r="H657" t="n">
         <v>3604056</v>
@@ -19596,7 +19596,7 @@
         <v>14.8850002288818</v>
       </c>
       <c r="G663" t="n">
-        <v>9.57635593414307</v>
+        <v>9.57635688781738</v>
       </c>
       <c r="H663" t="n">
         <v>2447881</v>
@@ -19683,7 +19683,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G666" t="n">
-        <v>9.64712333679199</v>
+        <v>9.64712524414062</v>
       </c>
       <c r="H666" t="n">
         <v>3078990</v>
@@ -19712,7 +19712,7 @@
         <v>14.6850004196167</v>
       </c>
       <c r="G667" t="n">
-        <v>9.44768333435059</v>
+        <v>9.4476842880249</v>
       </c>
       <c r="H667" t="n">
         <v>5999121</v>
@@ -19741,7 +19741,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G668" t="n">
-        <v>9.39943408966064</v>
+        <v>9.39943218231201</v>
       </c>
       <c r="H668" t="n">
         <v>3214408</v>
@@ -19828,7 +19828,7 @@
         <v>14.4549999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>9.29971218109131</v>
+        <v>9.29971122741699</v>
       </c>
       <c r="H671" t="n">
         <v>4659567</v>
@@ -19886,7 +19886,7 @@
         <v>14.664999961853</v>
       </c>
       <c r="G673" t="n">
-        <v>9.43481731414795</v>
+        <v>9.43481636047363</v>
       </c>
       <c r="H673" t="n">
         <v>3967619</v>
@@ -19944,7 +19944,7 @@
         <v>14.7399997711182</v>
       </c>
       <c r="G675" t="n">
-        <v>9.48306941986084</v>
+        <v>9.48306846618652</v>
       </c>
       <c r="H675" t="n">
         <v>2884965</v>
@@ -20002,7 +20002,7 @@
         <v>14.8549995422363</v>
       </c>
       <c r="G677" t="n">
-        <v>9.55705451965332</v>
+        <v>9.557053565979</v>
       </c>
       <c r="H677" t="n">
         <v>3150734</v>
@@ -20031,7 +20031,7 @@
         <v>14.7650003433228</v>
       </c>
       <c r="G678" t="n">
-        <v>9.49915218353271</v>
+        <v>9.4991512298584</v>
       </c>
       <c r="H678" t="n">
         <v>3851946</v>
@@ -20060,7 +20060,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G679" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020053863525</v>
       </c>
       <c r="H679" t="n">
         <v>3126453</v>
@@ -20147,7 +20147,7 @@
         <v>14.585000038147</v>
       </c>
       <c r="G682" t="n">
-        <v>9.3833475112915</v>
+        <v>9.38334846496582</v>
       </c>
       <c r="H682" t="n">
         <v>4079776</v>
@@ -20234,7 +20234,7 @@
         <v>14.8249998092651</v>
       </c>
       <c r="G685" t="n">
-        <v>9.53775405883789</v>
+        <v>9.53775310516357</v>
       </c>
       <c r="H685" t="n">
         <v>3235761</v>
@@ -20263,7 +20263,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G686" t="n">
-        <v>9.52166938781738</v>
+        <v>9.5216703414917</v>
       </c>
       <c r="H686" t="n">
         <v>3974247</v>
@@ -20292,7 +20292,7 @@
         <v>15.125</v>
       </c>
       <c r="G687" t="n">
-        <v>9.73076152801514</v>
+        <v>9.73076057434082</v>
       </c>
       <c r="H687" t="n">
         <v>8818496</v>
@@ -20321,7 +20321,7 @@
         <v>15.0349998474121</v>
       </c>
       <c r="G688" t="n">
-        <v>9.67285919189453</v>
+        <v>9.67285823822021</v>
       </c>
       <c r="H688" t="n">
         <v>4917992</v>
@@ -20350,7 +20350,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G689" t="n">
-        <v>9.65999126434326</v>
+        <v>9.65999221801758</v>
       </c>
       <c r="H689" t="n">
         <v>3804454</v>
@@ -20408,7 +20408,7 @@
         <v>15.0349998474121</v>
       </c>
       <c r="G691" t="n">
-        <v>9.67285919189453</v>
+        <v>9.67285823822021</v>
       </c>
       <c r="H691" t="n">
         <v>2748470</v>
@@ -20437,7 +20437,7 @@
         <v>15.125</v>
       </c>
       <c r="G692" t="n">
-        <v>9.73076152801514</v>
+        <v>9.73076057434082</v>
       </c>
       <c r="H692" t="n">
         <v>4706478</v>
@@ -20524,7 +20524,7 @@
         <v>15.1549997329712</v>
       </c>
       <c r="G695" t="n">
-        <v>9.75006103515625</v>
+        <v>9.75006294250488</v>
       </c>
       <c r="H695" t="n">
         <v>5294798</v>
@@ -20698,7 +20698,7 @@
         <v>14.8800001144409</v>
       </c>
       <c r="G701" t="n">
-        <v>9.57313823699951</v>
+        <v>9.57313919067383</v>
       </c>
       <c r="H701" t="n">
         <v>15394005</v>
@@ -20756,7 +20756,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G703" t="n">
-        <v>9.42194938659668</v>
+        <v>9.421950340271</v>
       </c>
       <c r="H703" t="n">
         <v>6979794</v>
@@ -20872,7 +20872,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G707" t="n">
-        <v>9.29649639129639</v>
+        <v>9.29649543762207</v>
       </c>
       <c r="H707" t="n">
         <v>8920458</v>
@@ -20959,7 +20959,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G710" t="n">
-        <v>9.18712520599365</v>
+        <v>9.18712425231934</v>
       </c>
       <c r="H710" t="n">
         <v>8447984</v>
@@ -20988,7 +20988,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G711" t="n">
-        <v>9.11635589599609</v>
+        <v>9.11635780334473</v>
       </c>
       <c r="H711" t="n">
         <v>7135294</v>
@@ -21017,7 +21017,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G712" t="n">
-        <v>9.09705448150635</v>
+        <v>9.09705543518066</v>
       </c>
       <c r="H712" t="n">
         <v>6246372</v>
@@ -21046,7 +21046,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G713" t="n">
-        <v>9.2064266204834</v>
+        <v>9.20642471313477</v>
       </c>
       <c r="H713" t="n">
         <v>7407382</v>
@@ -21133,7 +21133,7 @@
         <v>14.0500001907349</v>
       </c>
       <c r="G716" t="n">
-        <v>9.03915405273438</v>
+        <v>9.03915309906006</v>
       </c>
       <c r="H716" t="n">
         <v>7883378</v>
@@ -21191,7 +21191,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G718" t="n">
-        <v>8.8943977355957</v>
+        <v>8.89439678192139</v>
       </c>
       <c r="H718" t="n">
         <v>7797104</v>
@@ -21220,7 +21220,7 @@
         <v>13.75</v>
       </c>
       <c r="G719" t="n">
-        <v>8.84614562988281</v>
+        <v>8.8461446762085</v>
       </c>
       <c r="H719" t="n">
         <v>4634443</v>
@@ -21249,7 +21249,7 @@
         <v>14.0450000762939</v>
       </c>
       <c r="G720" t="n">
-        <v>9.0359354019165</v>
+        <v>9.03593444824219</v>
       </c>
       <c r="H720" t="n">
         <v>7100699</v>
@@ -21365,7 +21365,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G724" t="n">
-        <v>9.18712520599365</v>
+        <v>9.18712425231934</v>
       </c>
       <c r="H724" t="n">
         <v>5408171</v>
@@ -21423,7 +21423,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G726" t="n">
-        <v>9.25467777252197</v>
+        <v>9.25467586517334</v>
       </c>
       <c r="H726" t="n">
         <v>3691753</v>
@@ -21481,7 +21481,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G728" t="n">
-        <v>9.18712520599365</v>
+        <v>9.18712425231934</v>
       </c>
       <c r="H728" t="n">
         <v>2598306</v>
@@ -21510,7 +21510,7 @@
         <v>14.375</v>
       </c>
       <c r="G729" t="n">
-        <v>9.24824237823486</v>
+        <v>9.2482442855835</v>
       </c>
       <c r="H729" t="n">
         <v>4373616</v>
@@ -21539,7 +21539,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G730" t="n">
-        <v>9.25467777252197</v>
+        <v>9.25467586517334</v>
       </c>
       <c r="H730" t="n">
         <v>3623659</v>
@@ -21568,7 +21568,7 @@
         <v>14.4350004196167</v>
       </c>
       <c r="G731" t="n">
-        <v>9.28684520721436</v>
+        <v>9.28684616088867</v>
       </c>
       <c r="H731" t="n">
         <v>3128092</v>
@@ -21597,7 +21597,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G732" t="n">
-        <v>9.1935567855835</v>
+        <v>9.19355869293213</v>
       </c>
       <c r="H732" t="n">
         <v>2832097</v>
@@ -21626,7 +21626,7 @@
         <v>14.3900003433228</v>
       </c>
       <c r="G733" t="n">
-        <v>9.25789356231689</v>
+        <v>9.25789451599121</v>
       </c>
       <c r="H733" t="n">
         <v>3847030</v>
@@ -21655,7 +21655,7 @@
         <v>14.3400001525879</v>
       </c>
       <c r="G734" t="n">
-        <v>9.22572612762451</v>
+        <v>9.2257251739502</v>
       </c>
       <c r="H734" t="n">
         <v>3801474</v>
@@ -21742,7 +21742,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G737" t="n">
-        <v>9.30292892456055</v>
+        <v>9.30292987823486</v>
       </c>
       <c r="H737" t="n">
         <v>4897438</v>
@@ -21771,7 +21771,7 @@
         <v>14.1599998474121</v>
       </c>
       <c r="G738" t="n">
-        <v>9.10992240905762</v>
+        <v>9.1099214553833</v>
       </c>
       <c r="H738" t="n">
         <v>6954782</v>
@@ -21800,7 +21800,7 @@
         <v>14.2849998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>9.19034099578857</v>
+        <v>9.19034194946289</v>
       </c>
       <c r="H739" t="n">
         <v>7573101</v>
@@ -21829,7 +21829,7 @@
         <v>14.2250003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>9.15174102783203</v>
+        <v>9.15174007415771</v>
       </c>
       <c r="H740" t="n">
         <v>4519581</v>
@@ -21858,7 +21858,7 @@
         <v>14.2550001144409</v>
       </c>
       <c r="G741" t="n">
-        <v>9.17104148864746</v>
+        <v>9.17104244232178</v>
       </c>
       <c r="H741" t="n">
         <v>3629350</v>
@@ -21916,7 +21916,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G743" t="n">
-        <v>9.45733451843262</v>
+        <v>9.45733547210693</v>
       </c>
       <c r="H743" t="n">
         <v>5744901</v>
@@ -21945,7 +21945,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G744" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020053863525</v>
       </c>
       <c r="H744" t="n">
         <v>3824756</v>
@@ -22003,7 +22003,7 @@
         <v>14.8900003433228</v>
       </c>
       <c r="G746" t="n">
-        <v>9.5795726776123</v>
+        <v>9.57957172393799</v>
       </c>
       <c r="H746" t="n">
         <v>5194375</v>
@@ -22032,7 +22032,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G747" t="n">
-        <v>9.65677452087402</v>
+        <v>9.65677356719971</v>
       </c>
       <c r="H747" t="n">
         <v>7459546</v>
@@ -22061,7 +22061,7 @@
         <v>14.8450002670288</v>
       </c>
       <c r="G748" t="n">
-        <v>9.55062007904053</v>
+        <v>9.55062103271484</v>
       </c>
       <c r="H748" t="n">
         <v>4397725</v>
@@ -22090,7 +22090,7 @@
         <v>14.7200002670288</v>
       </c>
       <c r="G749" t="n">
-        <v>9.47020149230957</v>
+        <v>9.47020053863525</v>
       </c>
       <c r="H749" t="n">
         <v>5686754</v>
@@ -22119,7 +22119,7 @@
         <v>14.2849998474121</v>
       </c>
       <c r="G750" t="n">
-        <v>9.19034099578857</v>
+        <v>9.19034194946289</v>
       </c>
       <c r="H750" t="n">
         <v>10197579</v>
@@ -22177,7 +22177,7 @@
         <v>14.1750001907349</v>
       </c>
       <c r="G752" t="n">
-        <v>9.11957263946533</v>
+        <v>9.11957168579102</v>
       </c>
       <c r="H752" t="n">
         <v>4693850</v>
@@ -22235,7 +22235,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G754" t="n">
-        <v>9.23537731170654</v>
+        <v>9.23537635803223</v>
       </c>
       <c r="H754" t="n">
         <v>6843267</v>
@@ -22293,7 +22293,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G756" t="n">
-        <v>9.25467777252197</v>
+        <v>9.25467586517334</v>
       </c>
       <c r="H756" t="n">
         <v>5037982</v>
@@ -22380,7 +22380,7 @@
         <v>14.6450004577637</v>
       </c>
       <c r="G759" t="n">
-        <v>9.42194938659668</v>
+        <v>9.421950340271</v>
       </c>
       <c r="H759" t="n">
         <v>8335712</v>
@@ -22438,7 +22438,7 @@
         <v>14.5299997329712</v>
       </c>
       <c r="G761" t="n">
-        <v>9.3479642868042</v>
+        <v>9.34796333312988</v>
       </c>
       <c r="H761" t="n">
         <v>9460245</v>
@@ -22467,7 +22467,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G762" t="n">
-        <v>9.24502658843994</v>
+        <v>9.24502754211426</v>
       </c>
       <c r="H762" t="n">
         <v>6405329</v>
@@ -22525,7 +22525,7 @@
         <v>14.5050001144409</v>
       </c>
       <c r="G764" t="n">
-        <v>9.33187961578369</v>
+        <v>9.33188056945801</v>
       </c>
       <c r="H764" t="n">
         <v>4847874</v>
@@ -22554,7 +22554,7 @@
         <v>14.5450000762939</v>
       </c>
       <c r="G765" t="n">
-        <v>9.35761260986328</v>
+        <v>9.35761451721191</v>
       </c>
       <c r="H765" t="n">
         <v>5061299</v>
@@ -22612,7 +22612,7 @@
         <v>14.6850004196167</v>
       </c>
       <c r="G767" t="n">
-        <v>9.44768333435059</v>
+        <v>9.4476842880249</v>
       </c>
       <c r="H767" t="n">
         <v>4428502</v>
@@ -22670,7 +22670,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G769" t="n">
-        <v>9.52810478210449</v>
+        <v>9.52810287475586</v>
       </c>
       <c r="H769" t="n">
         <v>6671972</v>
@@ -22757,7 +22757,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G772" t="n">
-        <v>9.61817359924316</v>
+        <v>9.61817264556885</v>
       </c>
       <c r="H772" t="n">
         <v>3832986</v>
@@ -22873,7 +22873,7 @@
         <v>15.3699998855591</v>
       </c>
       <c r="G776" t="n">
-        <v>9.88838386535645</v>
+        <v>9.88838291168213</v>
       </c>
       <c r="H776" t="n">
         <v>6681631</v>
@@ -22931,7 +22931,7 @@
         <v>15.3149995803833</v>
       </c>
       <c r="G778" t="n">
-        <v>9.85299682617188</v>
+        <v>9.85299777984619</v>
       </c>
       <c r="H778" t="n">
         <v>5736013</v>
@@ -23018,7 +23018,7 @@
         <v>15.4549999237061</v>
       </c>
       <c r="G781" t="n">
-        <v>9.94306755065918</v>
+        <v>9.9430685043335</v>
       </c>
       <c r="H781" t="n">
         <v>5210337</v>
@@ -23076,7 +23076,7 @@
         <v>15.4449996948242</v>
       </c>
       <c r="G783" t="n">
-        <v>9.9366340637207</v>
+        <v>9.93663597106934</v>
       </c>
       <c r="H783" t="n">
         <v>4741959</v>
@@ -23105,7 +23105,7 @@
         <v>15.4549999237061</v>
       </c>
       <c r="G784" t="n">
-        <v>9.94306755065918</v>
+        <v>9.9430685043335</v>
       </c>
       <c r="H784" t="n">
         <v>5863857</v>
@@ -23192,7 +23192,7 @@
         <v>15.25</v>
       </c>
       <c r="G787" t="n">
-        <v>9.81117916107178</v>
+        <v>9.81118011474609</v>
       </c>
       <c r="H787" t="n">
         <v>5078796</v>
@@ -23337,7 +23337,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G792" t="n">
-        <v>9.64390754699707</v>
+        <v>9.64390850067139</v>
       </c>
       <c r="H792" t="n">
         <v>4561008</v>
@@ -23424,7 +23424,7 @@
         <v>15.0150003433228</v>
       </c>
       <c r="G795" t="n">
-        <v>9.65999126434326</v>
+        <v>9.65999221801758</v>
       </c>
       <c r="H795" t="n">
         <v>5571066</v>
@@ -23511,7 +23511,7 @@
         <v>15.164999961853</v>
       </c>
       <c r="G798" t="n">
-        <v>9.75649547576904</v>
+        <v>9.75649452209473</v>
       </c>
       <c r="H798" t="n">
         <v>4227766</v>
@@ -23540,7 +23540,7 @@
         <v>15.2250003814697</v>
       </c>
       <c r="G799" t="n">
-        <v>9.7950963973999</v>
+        <v>9.79509735107422</v>
       </c>
       <c r="H799" t="n">
         <v>3880189</v>
@@ -23598,7 +23598,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G801" t="n">
-        <v>9.83691501617432</v>
+        <v>9.83691310882568</v>
       </c>
       <c r="H801" t="n">
         <v>3764489</v>
@@ -23656,7 +23656,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G803" t="n">
-        <v>9.98488712310791</v>
+        <v>9.98488616943359</v>
       </c>
       <c r="H803" t="n">
         <v>4909207</v>
@@ -23772,7 +23772,7 @@
         <v>15.8850002288818</v>
       </c>
       <c r="G807" t="n">
-        <v>10.2197122573853</v>
+        <v>10.2197113037109</v>
       </c>
       <c r="H807" t="n">
         <v>6214672</v>
@@ -23830,7 +23830,7 @@
         <v>15.9849996566772</v>
       </c>
       <c r="G809" t="n">
-        <v>10.28404712677</v>
+        <v>10.2840461730957</v>
       </c>
       <c r="H809" t="n">
         <v>4752978</v>
@@ -23917,7 +23917,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>10.1650266647339</v>
+        <v>10.1650276184082</v>
       </c>
       <c r="H812" t="n">
         <v>2656063</v>
@@ -23975,7 +23975,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G814" t="n">
-        <v>10.1714601516724</v>
+        <v>10.171459197998</v>
       </c>
       <c r="H814" t="n">
         <v>3558829</v>
@@ -24004,7 +24004,7 @@
         <v>16.0049991607666</v>
       </c>
       <c r="G815" t="n">
-        <v>10.2969131469727</v>
+        <v>10.296914100647</v>
       </c>
       <c r="H815" t="n">
         <v>7739191</v>
@@ -24062,7 +24062,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G817" t="n">
-        <v>10.6025075912476</v>
+        <v>10.6025085449219</v>
       </c>
       <c r="H817" t="n">
         <v>6260687</v>
@@ -24178,7 +24178,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G821" t="n">
-        <v>10.5188722610474</v>
+        <v>10.518871307373</v>
       </c>
       <c r="H821" t="n">
         <v>5067259</v>
@@ -24236,7 +24236,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G823" t="n">
-        <v>10.5060052871704</v>
+        <v>10.5060043334961</v>
       </c>
       <c r="H823" t="n">
         <v>4007846</v>
@@ -24323,7 +24323,7 @@
         <v>16.5</v>
       </c>
       <c r="G826" t="n">
-        <v>10.6153764724731</v>
+        <v>10.6153755187988</v>
       </c>
       <c r="H826" t="n">
         <v>4444851</v>
@@ -24352,7 +24352,7 @@
         <v>16.6749992370605</v>
       </c>
       <c r="G827" t="n">
-        <v>10.7279634475708</v>
+        <v>10.7279624938965</v>
       </c>
       <c r="H827" t="n">
         <v>6192800</v>
@@ -24381,7 +24381,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G828" t="n">
-        <v>10.7022275924683</v>
+        <v>10.7022285461426</v>
       </c>
       <c r="H828" t="n">
         <v>5428271</v>
@@ -24410,7 +24410,7 @@
         <v>16.7150001525879</v>
       </c>
       <c r="G829" t="n">
-        <v>10.7536954879761</v>
+        <v>10.7536964416504</v>
       </c>
       <c r="H829" t="n">
         <v>6674243</v>
@@ -24439,7 +24439,7 @@
         <v>16.7049999237061</v>
       </c>
       <c r="G830" t="n">
-        <v>10.7472648620605</v>
+        <v>10.7472629547119</v>
       </c>
       <c r="H830" t="n">
         <v>4446789</v>
@@ -24497,7 +24497,7 @@
         <v>16.6949996948242</v>
       </c>
       <c r="G832" t="n">
-        <v>10.7408294677734</v>
+        <v>10.7408304214478</v>
       </c>
       <c r="H832" t="n">
         <v>3821650</v>
@@ -24526,7 +24526,7 @@
         <v>16.6350002288818</v>
       </c>
       <c r="G833" t="n">
-        <v>10.7022275924683</v>
+        <v>10.7022285461426</v>
       </c>
       <c r="H833" t="n">
         <v>4164996</v>
@@ -24584,7 +24584,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G835" t="n">
-        <v>10.7504806518555</v>
+        <v>10.7504796981812</v>
       </c>
       <c r="H835" t="n">
         <v>5048841</v>
@@ -24700,7 +24700,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G839" t="n">
-        <v>11.0657234191895</v>
+        <v>11.0657253265381</v>
       </c>
       <c r="H839" t="n">
         <v>7844547</v>
@@ -24787,7 +24787,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G842" t="n">
-        <v>10.9434881210327</v>
+        <v>10.9434862136841</v>
       </c>
       <c r="H842" t="n">
         <v>4191742</v>
@@ -24816,7 +24816,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G843" t="n">
-        <v>10.9756555557251</v>
+        <v>10.9756546020508</v>
       </c>
       <c r="H843" t="n">
         <v>3734993</v>
@@ -24874,7 +24874,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G845" t="n">
-        <v>11.0625057220459</v>
+        <v>11.0625066757202</v>
       </c>
       <c r="H845" t="n">
         <v>4475044</v>
@@ -24932,7 +24932,7 @@
         <v>17.2950000762939</v>
       </c>
       <c r="G847" t="n">
-        <v>11.1268434524536</v>
+        <v>11.1268424987793</v>
       </c>
       <c r="H847" t="n">
         <v>3826715</v>
@@ -24961,7 +24961,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G848" t="n">
-        <v>11.1364936828613</v>
+        <v>11.1364946365356</v>
       </c>
       <c r="H848" t="n">
         <v>4240886</v>
@@ -24990,7 +24990,7 @@
         <v>17.1550006866455</v>
       </c>
       <c r="G849" t="n">
-        <v>11.0367736816406</v>
+        <v>11.0367727279663</v>
       </c>
       <c r="H849" t="n">
         <v>5715128</v>
@@ -25019,7 +25019,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G850" t="n">
-        <v>10.9949550628662</v>
+        <v>10.9949560165405</v>
       </c>
       <c r="H850" t="n">
         <v>5995152</v>
@@ -25077,7 +25077,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G852" t="n">
-        <v>10.8437662124634</v>
+        <v>10.8437671661377</v>
       </c>
       <c r="H852" t="n">
         <v>6694199</v>
@@ -25106,7 +25106,7 @@
         <v>16.9150009155273</v>
       </c>
       <c r="G853" t="n">
-        <v>10.8823680877686</v>
+        <v>10.8823671340942</v>
       </c>
       <c r="H853" t="n">
         <v>4449894</v>
@@ -25164,7 +25164,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G855" t="n">
-        <v>10.9756555557251</v>
+        <v>10.9756546020508</v>
       </c>
       <c r="H855" t="n">
         <v>7218056</v>
@@ -25309,7 +25309,7 @@
         <v>16.3299999237061</v>
       </c>
       <c r="G860" t="n">
-        <v>11.093113899231</v>
+        <v>11.0931148529053</v>
       </c>
       <c r="H860" t="n">
         <v>5564986</v>
@@ -25338,7 +25338,7 @@
         <v>16.2950000762939</v>
       </c>
       <c r="G861" t="n">
-        <v>11.0693387985229</v>
+        <v>11.0693378448486</v>
       </c>
       <c r="H861" t="n">
         <v>4916433</v>
@@ -25367,7 +25367,7 @@
         <v>15.9549999237061</v>
       </c>
       <c r="G862" t="n">
-        <v>10.8383731842041</v>
+        <v>10.8383722305298</v>
       </c>
       <c r="H862" t="n">
         <v>6673601</v>
@@ -25425,7 +25425,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G864" t="n">
-        <v>10.9300804138184</v>
+        <v>10.930079460144</v>
       </c>
       <c r="H864" t="n">
         <v>3723041</v>
@@ -25454,7 +25454,7 @@
         <v>15.9750003814697</v>
       </c>
       <c r="G865" t="n">
-        <v>10.8519611358643</v>
+        <v>10.8519620895386</v>
       </c>
       <c r="H865" t="n">
         <v>13063051</v>
@@ -25570,7 +25570,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G869" t="n">
-        <v>10.6515636444092</v>
+        <v>10.6515645980835</v>
       </c>
       <c r="H869" t="n">
         <v>5171957</v>
@@ -25657,7 +25657,7 @@
         <v>15.8149995803833</v>
       </c>
       <c r="G872" t="n">
-        <v>10.7432708740234</v>
+        <v>10.7432699203491</v>
       </c>
       <c r="H872" t="n">
         <v>3961660</v>
@@ -25686,7 +25686,7 @@
         <v>15.8549995422363</v>
       </c>
       <c r="G873" t="n">
-        <v>10.7704439163208</v>
+        <v>10.7704429626465</v>
       </c>
       <c r="H873" t="n">
         <v>3670515</v>
@@ -25744,7 +25744,7 @@
         <v>16.1450004577637</v>
       </c>
       <c r="G875" t="n">
-        <v>10.9674425125122</v>
+        <v>10.9674415588379</v>
       </c>
       <c r="H875" t="n">
         <v>5411436</v>
@@ -25773,7 +25773,7 @@
         <v>16.1100006103516</v>
       </c>
       <c r="G876" t="n">
-        <v>10.9436664581299</v>
+        <v>10.9436674118042</v>
       </c>
       <c r="H876" t="n">
         <v>3876917</v>
@@ -25831,7 +25831,7 @@
         <v>16.1350002288818</v>
       </c>
       <c r="G878" t="n">
-        <v>10.9606504440308</v>
+        <v>10.9606494903564</v>
       </c>
       <c r="H878" t="n">
         <v>3221022</v>
@@ -25918,7 +25918,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G881" t="n">
-        <v>11.3104944229126</v>
+        <v>11.310492515564</v>
       </c>
       <c r="H881" t="n">
         <v>4115535</v>
@@ -25976,7 +25976,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G883" t="n">
-        <v>11.3308734893799</v>
+        <v>11.3308725357056</v>
       </c>
       <c r="H883" t="n">
         <v>8963521</v>
@@ -26092,7 +26092,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G887" t="n">
-        <v>11.2153921127319</v>
+        <v>11.2153911590576</v>
       </c>
       <c r="H887" t="n">
         <v>3454666</v>
@@ -26150,7 +26150,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G889" t="n">
-        <v>11.2969064712524</v>
+        <v>11.2969074249268</v>
       </c>
       <c r="H889" t="n">
         <v>3119492</v>
@@ -26179,7 +26179,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G890" t="n">
-        <v>11.3886137008667</v>
+        <v>11.3886127471924</v>
       </c>
       <c r="H890" t="n">
         <v>3977815</v>
@@ -26208,7 +26208,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G891" t="n">
-        <v>11.5924062728882</v>
+        <v>11.5924072265625</v>
       </c>
       <c r="H891" t="n">
         <v>6806510</v>
@@ -26295,7 +26295,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G894" t="n">
-        <v>11.626371383667</v>
+        <v>11.6263704299927</v>
       </c>
       <c r="H894" t="n">
         <v>3571789</v>
@@ -26324,7 +26324,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G895" t="n">
-        <v>11.6603393554688</v>
+        <v>11.6603374481201</v>
       </c>
       <c r="H895" t="n">
         <v>5295642</v>
@@ -26353,7 +26353,7 @@
         <v>17.2099990844727</v>
       </c>
       <c r="G896" t="n">
-        <v>11.6909046173096</v>
+        <v>11.6909036636353</v>
       </c>
       <c r="H896" t="n">
         <v>4822629</v>
@@ -26382,7 +26382,7 @@
         <v>17.2049999237061</v>
       </c>
       <c r="G897" t="n">
-        <v>11.6875085830688</v>
+        <v>11.6875104904175</v>
       </c>
       <c r="H897" t="n">
         <v>3663309</v>
@@ -26411,7 +26411,7 @@
         <v>17.1350002288818</v>
       </c>
       <c r="G898" t="n">
-        <v>11.6399583816528</v>
+        <v>11.6399593353271</v>
       </c>
       <c r="H898" t="n">
         <v>3020880</v>
@@ -26469,7 +26469,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G900" t="n">
-        <v>11.6603393554688</v>
+        <v>11.6603374481201</v>
       </c>
       <c r="H900" t="n">
         <v>3247492</v>
@@ -26498,7 +26498,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G901" t="n">
-        <v>11.5924062728882</v>
+        <v>11.5924072265625</v>
       </c>
       <c r="H901" t="n">
         <v>3894252</v>
@@ -26527,7 +26527,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G902" t="n">
-        <v>11.602596282959</v>
+        <v>11.6025953292847</v>
       </c>
       <c r="H902" t="n">
         <v>5144636</v>
@@ -26556,7 +26556,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>11.480320930481</v>
+        <v>11.4803190231323</v>
       </c>
       <c r="H903" t="n">
         <v>5977321</v>
@@ -26585,7 +26585,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>11.5142860412598</v>
+        <v>11.5142879486084</v>
       </c>
       <c r="H904" t="n">
         <v>2305715</v>
@@ -26614,7 +26614,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G905" t="n">
-        <v>11.5007009506226</v>
+        <v>11.5006999969482</v>
       </c>
       <c r="H905" t="n">
         <v>2861437</v>
@@ -26643,7 +26643,7 @@
         <v>16.9950008392334</v>
       </c>
       <c r="G906" t="n">
-        <v>11.5448551177979</v>
+        <v>11.5448541641235</v>
       </c>
       <c r="H906" t="n">
         <v>2763422</v>
@@ -26672,7 +26672,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G907" t="n">
-        <v>11.4667348861694</v>
+        <v>11.4667339324951</v>
       </c>
       <c r="H907" t="n">
         <v>5068467</v>
@@ -26730,7 +26730,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G909" t="n">
-        <v>11.5142860412598</v>
+        <v>11.5142879486084</v>
       </c>
       <c r="H909" t="n">
         <v>2559783</v>
@@ -26759,7 +26759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G910" t="n">
-        <v>11.3512525558472</v>
+        <v>11.3512506484985</v>
       </c>
       <c r="H910" t="n">
         <v>4261569</v>
@@ -26817,7 +26817,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G912" t="n">
-        <v>11.4497509002686</v>
+        <v>11.4497518539429</v>
       </c>
       <c r="H912" t="n">
         <v>3548781</v>
@@ -26904,7 +26904,7 @@
         <v>16.3349990844727</v>
       </c>
       <c r="G915" t="n">
-        <v>11.096510887146</v>
+        <v>11.0965099334717</v>
       </c>
       <c r="H915" t="n">
         <v>3860177</v>
@@ -26933,7 +26933,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G916" t="n">
-        <v>11.0795269012451</v>
+        <v>11.0795288085938</v>
       </c>
       <c r="H916" t="n">
         <v>4809948</v>
@@ -26962,7 +26962,7 @@
         <v>16.4349994659424</v>
       </c>
       <c r="G917" t="n">
-        <v>11.1644401550293</v>
+        <v>11.1644411087036</v>
       </c>
       <c r="H917" t="n">
         <v>4317641</v>
@@ -27020,7 +27020,7 @@
         <v>16.0400009155273</v>
       </c>
       <c r="G919" t="n">
-        <v>10.8961153030396</v>
+        <v>10.8961143493652</v>
       </c>
       <c r="H919" t="n">
         <v>3363564</v>
@@ -27049,7 +27049,7 @@
         <v>16.1299991607666</v>
       </c>
       <c r="G920" t="n">
-        <v>10.9572525024414</v>
+        <v>10.9572515487671</v>
       </c>
       <c r="H920" t="n">
         <v>5133573</v>
@@ -27136,7 +27136,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G923" t="n">
-        <v>10.9878215789795</v>
+        <v>10.9878206253052</v>
       </c>
       <c r="H923" t="n">
         <v>4102021</v>
@@ -27165,7 +27165,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G924" t="n">
-        <v>11.0183906555176</v>
+        <v>11.0183897018433</v>
       </c>
       <c r="H924" t="n">
         <v>3380884</v>
@@ -27223,7 +27223,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G926" t="n">
-        <v>11.0863218307495</v>
+        <v>11.0863208770752</v>
       </c>
       <c r="H926" t="n">
         <v>3539056</v>
@@ -27281,7 +27281,7 @@
         <v>16.1849994659424</v>
       </c>
       <c r="G928" t="n">
-        <v>10.9946155548096</v>
+        <v>10.9946146011353</v>
       </c>
       <c r="H928" t="n">
         <v>2458143</v>
@@ -27368,7 +27368,7 @@
         <v>16.4200000762939</v>
       </c>
       <c r="G931" t="n">
-        <v>11.1542530059814</v>
+        <v>11.1542520523071</v>
       </c>
       <c r="H931" t="n">
         <v>5445382</v>
@@ -27455,7 +27455,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G934" t="n">
-        <v>11.2391653060913</v>
+        <v>11.2391662597656</v>
       </c>
       <c r="H934" t="n">
         <v>3039642</v>
@@ -27484,7 +27484,7 @@
         <v>16.8349990844727</v>
       </c>
       <c r="G935" t="n">
-        <v>11.436164855957</v>
+        <v>11.4361658096313</v>
       </c>
       <c r="H935" t="n">
         <v>4795238</v>
@@ -27513,7 +27513,7 @@
         <v>17.0450000762939</v>
       </c>
       <c r="G936" t="n">
-        <v>11.578821182251</v>
+        <v>11.5788202285767</v>
       </c>
       <c r="H936" t="n">
         <v>6939288</v>
@@ -27571,7 +27571,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G938" t="n">
-        <v>11.6841125488281</v>
+        <v>11.6841135025024</v>
       </c>
       <c r="H938" t="n">
         <v>3641753</v>
@@ -27600,7 +27600,7 @@
         <v>17.1749992370605</v>
       </c>
       <c r="G939" t="n">
-        <v>11.6671295166016</v>
+        <v>11.6671304702759</v>
       </c>
       <c r="H939" t="n">
         <v>4568118</v>
@@ -27629,7 +27629,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G940" t="n">
-        <v>11.7792148590088</v>
+        <v>11.7792167663574</v>
       </c>
       <c r="H940" t="n">
         <v>4894449</v>
@@ -27658,7 +27658,7 @@
         <v>17.5</v>
       </c>
       <c r="G941" t="n">
-        <v>11.8879060745239</v>
+        <v>11.8879041671753</v>
       </c>
       <c r="H941" t="n">
         <v>6663877</v>
@@ -27687,7 +27687,7 @@
         <v>17.4750003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>11.8709239959717</v>
+        <v>11.870922088623</v>
       </c>
       <c r="H942" t="n">
         <v>4537332</v>
@@ -27716,7 +27716,7 @@
         <v>17.375</v>
       </c>
       <c r="G943" t="n">
-        <v>11.8029937744141</v>
+        <v>11.8029928207397</v>
       </c>
       <c r="H943" t="n">
         <v>4120923</v>
@@ -27745,7 +27745,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G944" t="n">
-        <v>11.7690267562866</v>
+        <v>11.7690277099609</v>
       </c>
       <c r="H944" t="n">
         <v>4467012</v>
@@ -27774,7 +27774,7 @@
         <v>17.5</v>
       </c>
       <c r="G945" t="n">
-        <v>11.8879060745239</v>
+        <v>11.8879041671753</v>
       </c>
       <c r="H945" t="n">
         <v>5084522</v>
@@ -27803,7 +27803,7 @@
         <v>17.8850002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>12.1494398117065</v>
+        <v>12.1494407653809</v>
       </c>
       <c r="H946" t="n">
         <v>9346284</v>
@@ -27861,7 +27861,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G948" t="n">
-        <v>12.1664228439331</v>
+        <v>12.1664218902588</v>
       </c>
       <c r="H948" t="n">
         <v>4520651</v>
@@ -27919,7 +27919,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G950" t="n">
-        <v>12.2003879547119</v>
+        <v>12.2003889083862</v>
       </c>
       <c r="H950" t="n">
         <v>3608491</v>
@@ -27977,7 +27977,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G952" t="n">
-        <v>12.13245677948</v>
+        <v>12.1324577331543</v>
       </c>
       <c r="H952" t="n">
         <v>4910819</v>
@@ -28006,7 +28006,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G953" t="n">
-        <v>12.0781135559082</v>
+        <v>12.0781126022339</v>
       </c>
       <c r="H953" t="n">
         <v>4061112</v>
@@ -28064,7 +28064,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G955" t="n">
-        <v>11.8505439758301</v>
+        <v>11.8505420684814</v>
       </c>
       <c r="H955" t="n">
         <v>5138420</v>
@@ -28093,7 +28093,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G956" t="n">
-        <v>11.915078163147</v>
+        <v>11.9150791168213</v>
       </c>
       <c r="H956" t="n">
         <v>4343823</v>
@@ -28122,7 +28122,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>11.989800453186</v>
+        <v>11.9898014068604</v>
       </c>
       <c r="H957" t="n">
         <v>4248844</v>
@@ -28151,7 +28151,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G958" t="n">
-        <v>12.0713195800781</v>
+        <v>12.0713186264038</v>
       </c>
       <c r="H958" t="n">
         <v>3463562</v>
@@ -28180,7 +28180,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G959" t="n">
-        <v>12.0543365478516</v>
+        <v>12.0543375015259</v>
       </c>
       <c r="H959" t="n">
         <v>3167788</v>
@@ -28238,7 +28238,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G961" t="n">
-        <v>12.1392507553101</v>
+        <v>12.1392498016357</v>
       </c>
       <c r="H961" t="n">
         <v>3926165</v>
@@ -28296,7 +28296,7 @@
         <v>17.9650001525879</v>
       </c>
       <c r="G963" t="n">
-        <v>12.203784942627</v>
+        <v>12.2037830352783</v>
       </c>
       <c r="H963" t="n">
         <v>2806790</v>
@@ -28325,7 +28325,7 @@
         <v>18.1049995422363</v>
       </c>
       <c r="G964" t="n">
-        <v>12.2988872528076</v>
+        <v>12.2988882064819</v>
       </c>
       <c r="H964" t="n">
         <v>4232438</v>
@@ -28412,7 +28412,7 @@
         <v>18.1949996948242</v>
       </c>
       <c r="G967" t="n">
-        <v>12.3600263595581</v>
+        <v>12.3600254058838</v>
       </c>
       <c r="H967" t="n">
         <v>4285136</v>
@@ -28441,7 +28441,7 @@
         <v>18.375</v>
       </c>
       <c r="G968" t="n">
-        <v>12.4822998046875</v>
+        <v>12.4823007583618</v>
       </c>
       <c r="H968" t="n">
         <v>3753476</v>
@@ -28470,7 +28470,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G969" t="n">
-        <v>12.4687156677246</v>
+        <v>12.468713760376</v>
       </c>
       <c r="H969" t="n">
         <v>3364987</v>
@@ -28499,7 +28499,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G970" t="n">
-        <v>12.492488861084</v>
+        <v>12.4924917221069</v>
       </c>
       <c r="H970" t="n">
         <v>2695686</v>
@@ -28557,7 +28557,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G972" t="n">
-        <v>12.4687156677246</v>
+        <v>12.468713760376</v>
       </c>
       <c r="H972" t="n">
         <v>2775647</v>
@@ -28586,7 +28586,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G973" t="n">
-        <v>12.4958868026733</v>
+        <v>12.4958877563477</v>
       </c>
       <c r="H973" t="n">
         <v>3161319</v>
@@ -28644,7 +28644,7 @@
         <v>18.2350006103516</v>
       </c>
       <c r="G975" t="n">
-        <v>12.3871984481812</v>
+        <v>12.3871974945068</v>
       </c>
       <c r="H975" t="n">
         <v>3479460</v>
@@ -28673,7 +28673,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>12.3464393615723</v>
+        <v>12.3464384078979</v>
       </c>
       <c r="H976" t="n">
         <v>4407355</v>
@@ -28702,7 +28702,7 @@
         <v>18.375</v>
       </c>
       <c r="G977" t="n">
-        <v>12.4822998046875</v>
+        <v>12.4823007583618</v>
       </c>
       <c r="H977" t="n">
         <v>3216034</v>
@@ -28789,7 +28789,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G980" t="n">
-        <v>12.6317481994629</v>
+        <v>12.6317491531372</v>
       </c>
       <c r="H980" t="n">
         <v>4011817</v>
@@ -28818,7 +28818,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G981" t="n">
-        <v>13.0631113052368</v>
+        <v>13.0631093978882</v>
       </c>
       <c r="H981" t="n">
         <v>14625686</v>
@@ -28876,7 +28876,7 @@
         <v>19.1900005340576</v>
       </c>
       <c r="G983" t="n">
-        <v>13.0359373092651</v>
+        <v>13.0359392166138</v>
       </c>
       <c r="H983" t="n">
         <v>2947823</v>
@@ -28905,7 +28905,7 @@
         <v>19.5</v>
       </c>
       <c r="G984" t="n">
-        <v>13.2465219497681</v>
+        <v>13.2465238571167</v>
       </c>
       <c r="H984" t="n">
         <v>6103117</v>
@@ -28934,7 +28934,7 @@
         <v>19.3349990844727</v>
       </c>
       <c r="G985" t="n">
-        <v>13.1344366073608</v>
+        <v>13.1344385147095</v>
       </c>
       <c r="H985" t="n">
         <v>4575222</v>
@@ -28992,7 +28992,7 @@
         <v>19.1700000762939</v>
       </c>
       <c r="G987" t="n">
-        <v>13.0223522186279</v>
+        <v>13.0223503112793</v>
       </c>
       <c r="H987" t="n">
         <v>4418484</v>
@@ -29050,7 +29050,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G989" t="n">
-        <v>12.7030773162842</v>
+        <v>12.7030763626099</v>
       </c>
       <c r="H989" t="n">
         <v>6541280</v>
@@ -29079,7 +29079,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G990" t="n">
-        <v>12.662317276001</v>
+        <v>12.6623182296753</v>
       </c>
       <c r="H990" t="n">
         <v>5290220</v>
@@ -29166,7 +29166,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G993" t="n">
-        <v>12.5943880081177</v>
+        <v>12.594386100769</v>
       </c>
       <c r="H993" t="n">
         <v>2812432</v>
@@ -29195,7 +29195,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G994" t="n">
-        <v>12.6962833404541</v>
+        <v>12.6962823867798</v>
       </c>
       <c r="H994" t="n">
         <v>5406710</v>
@@ -29224,7 +29224,7 @@
         <v>18.6949996948242</v>
       </c>
       <c r="G995" t="n">
-        <v>12.6996812820435</v>
+        <v>12.6996793746948</v>
       </c>
       <c r="H995" t="n">
         <v>2501863</v>
@@ -29253,7 +29253,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G996" t="n">
-        <v>12.6317481994629</v>
+        <v>12.6317491531372</v>
       </c>
       <c r="H996" t="n">
         <v>2966026</v>
@@ -29282,7 +29282,7 @@
         <v>18.5300006866455</v>
       </c>
       <c r="G997" t="n">
-        <v>12.5875949859619</v>
+        <v>12.5875940322876</v>
       </c>
       <c r="H997" t="n">
         <v>2526653</v>
@@ -29340,7 +29340,7 @@
         <v>18.2700004577637</v>
       </c>
       <c r="G999" t="n">
-        <v>12.4109745025635</v>
+        <v>12.4109754562378</v>
       </c>
       <c r="H999" t="n">
         <v>3426403</v>
@@ -29369,7 +29369,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1000" t="n">
-        <v>12.492488861084</v>
+        <v>12.4924917221069</v>
       </c>
       <c r="H1000" t="n">
         <v>3054969</v>
@@ -29398,7 +29398,7 @@
         <v>18.2399997711182</v>
       </c>
       <c r="G1001" t="n">
-        <v>12.3905944824219</v>
+        <v>12.3905954360962</v>
       </c>
       <c r="H1001" t="n">
         <v>3141875</v>
@@ -29427,7 +29427,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G1002" t="n">
-        <v>12.3702144622803</v>
+        <v>12.370213508606</v>
       </c>
       <c r="H1002" t="n">
         <v>2719728</v>
@@ -29456,7 +29456,7 @@
         <v>18.1949996948242</v>
       </c>
       <c r="G1003" t="n">
-        <v>12.3600263595581</v>
+        <v>12.3600254058838</v>
       </c>
       <c r="H1003" t="n">
         <v>3396373</v>
@@ -29485,7 +29485,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>12.377007484436</v>
+        <v>12.3770065307617</v>
       </c>
       <c r="H1004" t="n">
         <v>3626855</v>
@@ -29543,7 +29543,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1006" t="n">
-        <v>12.4721126556396</v>
+        <v>12.4721117019653</v>
       </c>
       <c r="H1006" t="n">
         <v>3575754</v>
@@ -29572,7 +29572,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1007" t="n">
-        <v>12.4585247039795</v>
+        <v>12.4585266113281</v>
       </c>
       <c r="H1007" t="n">
         <v>3866999</v>
@@ -29601,7 +29601,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1008" t="n">
-        <v>12.5570259094238</v>
+        <v>12.5570240020752</v>
       </c>
       <c r="H1008" t="n">
         <v>2755179</v>
@@ -29630,7 +29630,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G1009" t="n">
-        <v>12.5740079879761</v>
+        <v>12.5740070343018</v>
       </c>
       <c r="H1009" t="n">
         <v>2998254</v>
@@ -29659,7 +29659,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1010" t="n">
-        <v>12.6181640625</v>
+        <v>12.6181631088257</v>
       </c>
       <c r="H1010" t="n">
         <v>2705487</v>
@@ -29746,7 +29746,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1013" t="n">
-        <v>12.6894903182983</v>
+        <v>12.6894912719727</v>
       </c>
       <c r="H1013" t="n">
         <v>4236919</v>
@@ -29804,7 +29804,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G1015" t="n">
-        <v>12.4958868026733</v>
+        <v>12.4958877563477</v>
       </c>
       <c r="H1015" t="n">
         <v>2474080</v>
@@ -29833,7 +29833,7 @@
         <v>18.5100002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>12.5740079879761</v>
+        <v>12.5740070343018</v>
       </c>
       <c r="H1016" t="n">
         <v>2027654</v>
@@ -29862,7 +29862,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1017" t="n">
-        <v>12.5094757080078</v>
+        <v>12.5094738006592</v>
       </c>
       <c r="H1017" t="n">
         <v>2895677</v>
@@ -29920,7 +29920,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1019" t="n">
-        <v>12.5094757080078</v>
+        <v>12.5094738006592</v>
       </c>
       <c r="H1019" t="n">
         <v>2771286</v>
@@ -29949,7 +29949,7 @@
         <v>18.3950004577637</v>
       </c>
       <c r="G1020" t="n">
-        <v>12.4958868026733</v>
+        <v>12.4958877563477</v>
       </c>
       <c r="H1020" t="n">
         <v>3185325</v>
@@ -29978,7 +29978,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1021" t="n">
-        <v>12.546835899353</v>
+        <v>12.5468330383301</v>
       </c>
       <c r="H1021" t="n">
         <v>2647411</v>
@@ -30007,7 +30007,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1022" t="n">
-        <v>12.5943880081177</v>
+        <v>12.594386100769</v>
       </c>
       <c r="H1022" t="n">
         <v>2656448</v>
@@ -30065,7 +30065,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G1024" t="n">
-        <v>12.5196619033813</v>
+        <v>12.5196628570557</v>
       </c>
       <c r="H1024" t="n">
         <v>2816491</v>
@@ -30094,7 +30094,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1025" t="n">
-        <v>12.3634223937988</v>
+        <v>12.3634243011475</v>
       </c>
       <c r="H1025" t="n">
         <v>4588413</v>
@@ -30123,7 +30123,7 @@
         <v>18.2950000762939</v>
       </c>
       <c r="G1026" t="n">
-        <v>12.42795753479</v>
+        <v>12.4279584884644</v>
       </c>
       <c r="H1026" t="n">
         <v>2875277</v>
@@ -30152,7 +30152,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1027" t="n">
-        <v>12.4585247039795</v>
+        <v>12.4585266113281</v>
       </c>
       <c r="H1027" t="n">
         <v>3079304</v>
@@ -30210,7 +30210,7 @@
         <v>18.2549991607666</v>
       </c>
       <c r="G1029" t="n">
-        <v>12.4007835388184</v>
+        <v>12.400785446167</v>
       </c>
       <c r="H1029" t="n">
         <v>2868108</v>
@@ -30239,7 +30239,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G1030" t="n">
-        <v>12.3192672729492</v>
+        <v>12.3192663192749</v>
       </c>
       <c r="H1030" t="n">
         <v>2795535</v>
@@ -30268,7 +30268,7 @@
         <v>17.9349994659424</v>
       </c>
       <c r="G1031" t="n">
-        <v>12.183403968811</v>
+        <v>12.1834030151367</v>
       </c>
       <c r="H1031" t="n">
         <v>3733964</v>
@@ -30297,7 +30297,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1032" t="n">
-        <v>12.3226642608643</v>
+        <v>12.3226633071899</v>
       </c>
       <c r="H1032" t="n">
         <v>3042815</v>
@@ -30355,7 +30355,7 @@
         <v>18.1749992370605</v>
       </c>
       <c r="G1034" t="n">
-        <v>12.3464393615723</v>
+        <v>12.3464384078979</v>
       </c>
       <c r="H1034" t="n">
         <v>5455090</v>
@@ -30384,7 +30384,7 @@
         <v>18.2450008392334</v>
       </c>
       <c r="G1035" t="n">
-        <v>12.3939924240112</v>
+        <v>12.3939905166626</v>
       </c>
       <c r="H1035" t="n">
         <v>2767150</v>
@@ -30413,7 +30413,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G1036" t="n">
-        <v>12.1528358459473</v>
+        <v>12.1528348922729</v>
       </c>
       <c r="H1036" t="n">
         <v>4704600</v>
@@ -30442,7 +30442,7 @@
         <v>17.5949993133545</v>
       </c>
       <c r="G1037" t="n">
-        <v>11.9524383544922</v>
+        <v>11.9524393081665</v>
       </c>
       <c r="H1037" t="n">
         <v>5966169</v>
@@ -30529,7 +30529,7 @@
         <v>18.1350002288818</v>
       </c>
       <c r="G1040" t="n">
-        <v>12.3192672729492</v>
+        <v>12.3192663192749</v>
       </c>
       <c r="H1040" t="n">
         <v>4226044</v>
@@ -30587,7 +30587,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1042" t="n">
-        <v>12.4687156677246</v>
+        <v>12.468713760376</v>
       </c>
       <c r="H1042" t="n">
         <v>3674368</v>
@@ -30674,7 +30674,7 @@
         <v>18.5750007629395</v>
       </c>
       <c r="G1045" t="n">
-        <v>12.6181640625</v>
+        <v>12.6181631088257</v>
       </c>
       <c r="H1045" t="n">
         <v>3193337</v>
@@ -30761,7 +30761,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>12.7540254592896</v>
+        <v>12.7540264129639</v>
       </c>
       <c r="H1048" t="n">
         <v>2427382</v>
@@ -30790,7 +30790,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1049" t="n">
-        <v>12.757420539856</v>
+        <v>12.7574214935303</v>
       </c>
       <c r="H1049" t="n">
         <v>3008786</v>
@@ -30819,7 +30819,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1050" t="n">
-        <v>12.8253517150879</v>
+        <v>12.8253498077393</v>
       </c>
       <c r="H1050" t="n">
         <v>3853007</v>
@@ -30848,7 +30848,7 @@
         <v>18.5949993133545</v>
       </c>
       <c r="G1051" t="n">
-        <v>12.6317481994629</v>
+        <v>12.6317491531372</v>
       </c>
       <c r="H1051" t="n">
         <v>5082450</v>
@@ -30877,7 +30877,7 @@
         <v>18.4300003051758</v>
       </c>
       <c r="G1052" t="n">
-        <v>12.5196619033813</v>
+        <v>12.5196628570557</v>
       </c>
       <c r="H1052" t="n">
         <v>5000350</v>
@@ -30906,7 +30906,7 @@
         <v>17.4349994659424</v>
       </c>
       <c r="G1053" t="n">
-        <v>11.8437509536743</v>
+        <v>11.84375</v>
       </c>
       <c r="H1053" t="n">
         <v>13283162</v>
@@ -30993,7 +30993,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1056" t="n">
-        <v>11.480320930481</v>
+        <v>11.4803190231323</v>
       </c>
       <c r="H1056" t="n">
         <v>7908586</v>
@@ -31109,7 +31109,7 @@
         <v>16.0699996948242</v>
       </c>
       <c r="G1060" t="n">
-        <v>10.9164924621582</v>
+        <v>10.9164934158325</v>
       </c>
       <c r="H1060" t="n">
         <v>5399861</v>
@@ -31138,7 +31138,7 @@
         <v>15.7349996566772</v>
       </c>
       <c r="G1061" t="n">
-        <v>10.6889247894287</v>
+        <v>10.6889266967773</v>
       </c>
       <c r="H1061" t="n">
         <v>7362280</v>
@@ -31196,7 +31196,7 @@
         <v>13.7600002288818</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.34728908538818</v>
+        <v>9.3472900390625</v>
       </c>
       <c r="H1063" t="n">
         <v>17007395</v>
@@ -31225,7 +31225,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.20463562011719</v>
+        <v>9.20463752746582</v>
       </c>
       <c r="H1064" t="n">
         <v>12651017</v>
@@ -31254,7 +31254,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.20463562011719</v>
+        <v>9.20463752746582</v>
       </c>
       <c r="H1065" t="n">
         <v>9978347</v>
@@ -31283,7 +31283,7 @@
         <v>11.7950000762939</v>
       </c>
       <c r="G1066" t="n">
-        <v>8.01244926452637</v>
+        <v>8.01244831085205</v>
       </c>
       <c r="H1066" t="n">
         <v>23447815</v>
@@ -31428,7 +31428,7 @@
         <v>10.7349996566772</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.29238033294678</v>
+        <v>7.29238128662109</v>
       </c>
       <c r="H1071" t="n">
         <v>13513589</v>
@@ -31457,7 +31457,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.3976731300354</v>
+        <v>7.39767408370972</v>
       </c>
       <c r="H1072" t="n">
         <v>20334856</v>
@@ -31515,7 +31515,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.21963691711426</v>
+        <v>8.21963882446289</v>
       </c>
       <c r="H1074" t="n">
         <v>12760007</v>
@@ -31544,7 +31544,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1075" t="n">
-        <v>8.45739459991455</v>
+        <v>8.45739555358887</v>
       </c>
       <c r="H1075" t="n">
         <v>11973116</v>
@@ -31573,7 +31573,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1076" t="n">
-        <v>8.6000509262085</v>
+        <v>8.60005187988281</v>
       </c>
       <c r="H1076" t="n">
         <v>8371105</v>
@@ -31660,7 +31660,7 @@
         <v>12.4099998474121</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.43022346496582</v>
+        <v>8.4302225112915</v>
       </c>
       <c r="H1079" t="n">
         <v>9416863</v>
@@ -31747,7 +31747,7 @@
         <v>12.1850004196167</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.27737998962402</v>
+        <v>8.27737903594971</v>
       </c>
       <c r="H1082" t="n">
         <v>5128477</v>
@@ -31805,7 +31805,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496417999268</v>
       </c>
       <c r="H1084" t="n">
         <v>8798015</v>
@@ -31834,7 +31834,7 @@
         <v>12.7849998474121</v>
       </c>
       <c r="G1085" t="n">
-        <v>8.68496513366699</v>
+        <v>8.68496417999268</v>
       </c>
       <c r="H1085" t="n">
         <v>4900900</v>
@@ -31892,7 +31892,7 @@
         <v>13.1350002288818</v>
       </c>
       <c r="G1087" t="n">
-        <v>8.92272281646729</v>
+        <v>8.9227237701416</v>
       </c>
       <c r="H1087" t="n">
         <v>7939984</v>
@@ -31921,7 +31921,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.55929279327393</v>
+        <v>8.55929183959961</v>
       </c>
       <c r="H1088" t="n">
         <v>7869448</v>
@@ -31950,7 +31950,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.4166374206543</v>
+        <v>8.41663837432861</v>
       </c>
       <c r="H1089" t="n">
         <v>6935117</v>
@@ -31979,7 +31979,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.51174068450928</v>
+        <v>8.51173973083496</v>
       </c>
       <c r="H1090" t="n">
         <v>9531585</v>
@@ -32008,7 +32008,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G1091" t="n">
-        <v>8.51174068450928</v>
+        <v>8.51173973083496</v>
       </c>
       <c r="H1091" t="n">
         <v>4115313</v>
@@ -32037,7 +32037,7 @@
         <v>12.164999961853</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.2637939453125</v>
+        <v>8.26379299163818</v>
       </c>
       <c r="H1092" t="n">
         <v>5335813</v>
@@ -32095,7 +32095,7 @@
         <v>12.4650001525879</v>
       </c>
       <c r="G1094" t="n">
-        <v>8.46758556365967</v>
+        <v>8.46758460998535</v>
       </c>
       <c r="H1094" t="n">
         <v>3857279</v>
@@ -32124,7 +32124,7 @@
         <v>12.3699998855591</v>
       </c>
       <c r="G1095" t="n">
-        <v>8.40305137634277</v>
+        <v>8.40305042266846</v>
       </c>
       <c r="H1095" t="n">
         <v>4552998</v>
@@ -32153,7 +32153,7 @@
         <v>12.7449998855591</v>
       </c>
       <c r="G1096" t="n">
-        <v>8.65779209136963</v>
+        <v>8.65779113769531</v>
       </c>
       <c r="H1096" t="n">
         <v>5642728</v>
@@ -32269,7 +32269,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1100" t="n">
-        <v>8.62722396850586</v>
+        <v>8.62722301483154</v>
       </c>
       <c r="H1100" t="n">
         <v>6500932</v>
@@ -32298,7 +32298,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.78686046600342</v>
+        <v>8.78686141967773</v>
       </c>
       <c r="H1101" t="n">
         <v>4946486</v>
@@ -32327,7 +32327,7 @@
         <v>12.7349996566772</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.65099811553955</v>
+        <v>8.65100002288818</v>
       </c>
       <c r="H1102" t="n">
         <v>4911989</v>
@@ -32385,7 +32385,7 @@
         <v>12.9750003814697</v>
       </c>
       <c r="G1104" t="n">
-        <v>8.81403255462646</v>
+        <v>8.81403350830078</v>
       </c>
       <c r="H1104" t="n">
         <v>3673701</v>
@@ -32472,7 +32472,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.53211975097656</v>
+        <v>8.53211879730225</v>
       </c>
       <c r="H1107" t="n">
         <v>5402087</v>
@@ -32530,7 +32530,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.53211975097656</v>
+        <v>8.53211879730225</v>
       </c>
       <c r="H1109" t="n">
         <v>6258175</v>
@@ -32559,7 +32559,7 @@
         <v>12.414999961853</v>
       </c>
       <c r="G1110" t="n">
-        <v>8.78327369689941</v>
+        <v>8.7832727432251</v>
       </c>
       <c r="H1110" t="n">
         <v>6876957</v>
@@ -32646,7 +32646,7 @@
         <v>11.8950004577637</v>
       </c>
       <c r="G1113" t="n">
-        <v>8.41538715362549</v>
+        <v>8.41538619995117</v>
       </c>
       <c r="H1113" t="n">
         <v>8677564</v>
@@ -32704,7 +32704,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1115" t="n">
-        <v>8.58164310455322</v>
+        <v>8.58164405822754</v>
       </c>
       <c r="H1115" t="n">
         <v>4913960</v>
@@ -32762,7 +32762,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1117" t="n">
-        <v>8.99905300140381</v>
+        <v>8.99905109405518</v>
       </c>
       <c r="H1117" t="n">
         <v>8977372</v>
@@ -32791,7 +32791,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.03796291351318</v>
+        <v>9.03796195983887</v>
       </c>
       <c r="H1118" t="n">
         <v>5781139</v>
@@ -32965,7 +32965,7 @@
         <v>14.3850002288818</v>
       </c>
       <c r="G1124" t="n">
-        <v>10.1769943237305</v>
+        <v>10.1769933700562</v>
       </c>
       <c r="H1124" t="n">
         <v>9168993</v>
@@ -33023,7 +33023,7 @@
         <v>14.2650003433228</v>
       </c>
       <c r="G1126" t="n">
-        <v>10.0920963287354</v>
+        <v>10.0920972824097</v>
       </c>
       <c r="H1126" t="n">
         <v>10146009</v>
@@ -33139,7 +33139,7 @@
         <v>13.4049997329712</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.48367023468018</v>
+        <v>9.48367118835449</v>
       </c>
       <c r="H1130" t="n">
         <v>5598219</v>
@@ -33168,7 +33168,7 @@
         <v>13.7049999237061</v>
       </c>
       <c r="G1131" t="n">
-        <v>9.6959114074707</v>
+        <v>9.69591236114502</v>
       </c>
       <c r="H1131" t="n">
         <v>7205054</v>
@@ -33255,7 +33255,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1134" t="n">
-        <v>9.63223934173584</v>
+        <v>9.63224029541016</v>
       </c>
       <c r="H1134" t="n">
         <v>12780721</v>
@@ -33313,7 +33313,7 @@
         <v>13.6300001144409</v>
       </c>
       <c r="G1136" t="n">
-        <v>9.64285087585449</v>
+        <v>9.64285182952881</v>
       </c>
       <c r="H1136" t="n">
         <v>4327719</v>
@@ -33487,7 +33487,7 @@
         <v>13.4650001525879</v>
       </c>
       <c r="G1142" t="n">
-        <v>9.52612018585205</v>
+        <v>9.52611923217773</v>
       </c>
       <c r="H1142" t="n">
         <v>4148541</v>
@@ -33516,7 +33516,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1143" t="n">
-        <v>9.78788280487061</v>
+        <v>9.78788375854492</v>
       </c>
       <c r="H1143" t="n">
         <v>5891432</v>
@@ -33545,7 +33545,7 @@
         <v>13.7449998855591</v>
       </c>
       <c r="G1144" t="n">
-        <v>9.72421073913574</v>
+        <v>9.72421169281006</v>
       </c>
       <c r="H1144" t="n">
         <v>2060773</v>
@@ -33574,7 +33574,7 @@
         <v>13.8850002288818</v>
       </c>
       <c r="G1145" t="n">
-        <v>9.82325839996338</v>
+        <v>9.82325744628906</v>
       </c>
       <c r="H1145" t="n">
         <v>4130648</v>
@@ -33603,7 +33603,7 @@
         <v>13.7550001144409</v>
       </c>
       <c r="G1146" t="n">
-        <v>9.73128604888916</v>
+        <v>9.73128509521484</v>
       </c>
       <c r="H1146" t="n">
         <v>3252907</v>
@@ -33632,7 +33632,7 @@
         <v>13.6149997711182</v>
       </c>
       <c r="G1147" t="n">
-        <v>9.63223934173584</v>
+        <v>9.63224029541016</v>
       </c>
       <c r="H1147" t="n">
         <v>2531116</v>
@@ -33806,7 +33806,7 @@
         <v>13.8199996948242</v>
       </c>
       <c r="G1153" t="n">
-        <v>9.77727031707764</v>
+        <v>9.77727127075195</v>
       </c>
       <c r="H1153" t="n">
         <v>2449297</v>
@@ -33835,7 +33835,7 @@
         <v>13.6899995803833</v>
       </c>
       <c r="G1154" t="n">
-        <v>9.68529891967773</v>
+        <v>9.68529987335205</v>
       </c>
       <c r="H1154" t="n">
         <v>2886210</v>
@@ -33864,7 +33864,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1155" t="n">
-        <v>9.74897289276123</v>
+        <v>9.74897193908691</v>
       </c>
       <c r="H1155" t="n">
         <v>4328531</v>
@@ -33951,7 +33951,7 @@
         <v>13.7799997329712</v>
       </c>
       <c r="G1158" t="n">
-        <v>9.74897289276123</v>
+        <v>9.74897193908691</v>
       </c>
       <c r="H1158" t="n">
         <v>3002723</v>
@@ -33980,7 +33980,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1159" t="n">
-        <v>9.61455154418945</v>
+        <v>9.61455249786377</v>
       </c>
       <c r="H1159" t="n">
         <v>3422739</v>
@@ -34038,7 +34038,7 @@
         <v>13.5900001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>9.61455154418945</v>
+        <v>9.61455249786377</v>
       </c>
       <c r="H1161" t="n">
         <v>2582629</v>
@@ -34096,7 +34096,7 @@
         <v>12.8100004196167</v>
       </c>
       <c r="G1163" t="n">
-        <v>9.06272411346436</v>
+        <v>9.06272506713867</v>
       </c>
       <c r="H1163" t="n">
         <v>10784598</v>
@@ -34154,7 +34154,7 @@
         <v>12.7349996566772</v>
       </c>
       <c r="G1165" t="n">
-        <v>9.00966262817383</v>
+        <v>9.00966453552246</v>
       </c>
       <c r="H1165" t="n">
         <v>4617459</v>
@@ -34183,7 +34183,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1166" t="n">
-        <v>9.15115833282471</v>
+        <v>9.15115928649902</v>
       </c>
       <c r="H1166" t="n">
         <v>4492625</v>
@@ -34241,7 +34241,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>9.03796291351318</v>
+        <v>9.03796195983887</v>
       </c>
       <c r="H1168" t="n">
         <v>4001048</v>
@@ -34299,7 +34299,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1170" t="n">
-        <v>9.03796291351318</v>
+        <v>9.03796195983887</v>
       </c>
       <c r="H1170" t="n">
         <v>4186365</v>
@@ -34328,7 +34328,7 @@
         <v>13.2449998855591</v>
       </c>
       <c r="G1171" t="n">
-        <v>9.37047481536865</v>
+        <v>9.37047386169434</v>
       </c>
       <c r="H1171" t="n">
         <v>6891442</v>
@@ -34386,7 +34386,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G1173" t="n">
-        <v>9.31741428375244</v>
+        <v>9.31741523742676</v>
       </c>
       <c r="H1173" t="n">
         <v>2511229</v>
@@ -34444,7 +34444,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G1175" t="n">
-        <v>9.13347053527832</v>
+        <v>9.13347244262695</v>
       </c>
       <c r="H1175" t="n">
         <v>2725556</v>
@@ -34473,7 +34473,7 @@
         <v>12.9350004196167</v>
       </c>
       <c r="G1176" t="n">
-        <v>9.15115833282471</v>
+        <v>9.15115928649902</v>
       </c>
       <c r="H1176" t="n">
         <v>3358883</v>
@@ -34502,7 +34502,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1177" t="n">
-        <v>9.29619026184082</v>
+        <v>9.29619121551514</v>
       </c>
       <c r="H1177" t="n">
         <v>4110380</v>
@@ -34531,7 +34531,7 @@
         <v>13.0299997329712</v>
       </c>
       <c r="G1178" t="n">
-        <v>9.21836853027344</v>
+        <v>9.21836757659912</v>
       </c>
       <c r="H1178" t="n">
         <v>2302067</v>
@@ -34560,7 +34560,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G1179" t="n">
-        <v>9.15469455718994</v>
+        <v>9.15469551086426</v>
       </c>
       <c r="H1179" t="n">
         <v>2337724</v>
@@ -34734,7 +34734,7 @@
         <v>13.0050001144409</v>
       </c>
       <c r="G1185" t="n">
-        <v>9.20068264007568</v>
+        <v>9.20068168640137</v>
       </c>
       <c r="H1185" t="n">
         <v>3802213</v>
@@ -34763,7 +34763,7 @@
         <v>13.0249996185303</v>
       </c>
       <c r="G1186" t="n">
-        <v>9.21482944488525</v>
+        <v>9.21483039855957</v>
       </c>
       <c r="H1186" t="n">
         <v>2998346</v>
@@ -34850,7 +34850,7 @@
         <v>12.8199996948242</v>
       </c>
       <c r="G1189" t="n">
-        <v>9.06979942321777</v>
+        <v>9.06979846954346</v>
       </c>
       <c r="H1189" t="n">
         <v>4621571</v>
@@ -34879,7 +34879,7 @@
         <v>12.9099998474121</v>
       </c>
       <c r="G1190" t="n">
-        <v>9.13347053527832</v>
+        <v>9.13347244262695</v>
       </c>
       <c r="H1190" t="n">
         <v>2080889</v>
@@ -34908,7 +34908,7 @@
         <v>12.6850004196167</v>
       </c>
       <c r="G1191" t="n">
-        <v>8.97429084777832</v>
+        <v>8.974289894104</v>
       </c>
       <c r="H1191" t="n">
         <v>3974922</v>
@@ -34937,7 +34937,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1192" t="n">
-        <v>9.16177082061768</v>
+        <v>9.16176986694336</v>
       </c>
       <c r="H1192" t="n">
         <v>3494986</v>
@@ -35024,7 +35024,7 @@
         <v>12.8249998092651</v>
       </c>
       <c r="G1195" t="n">
-        <v>9.07333469390869</v>
+        <v>9.07333660125732</v>
       </c>
       <c r="H1195" t="n">
         <v>2273671</v>
@@ -35053,7 +35053,7 @@
         <v>12.7749996185303</v>
       </c>
       <c r="G1196" t="n">
-        <v>9.03796291351318</v>
+        <v>9.03796195983887</v>
       </c>
       <c r="H1196" t="n">
         <v>3564176</v>
@@ -35082,7 +35082,7 @@
         <v>12.8050003051758</v>
       </c>
       <c r="G1197" t="n">
-        <v>9.05918788909912</v>
+        <v>9.0591869354248</v>
       </c>
       <c r="H1197" t="n">
         <v>3043126</v>
@@ -35111,7 +35111,7 @@
         <v>12.6750001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>8.96721649169922</v>
+        <v>8.9672155380249</v>
       </c>
       <c r="H1198" t="n">
         <v>4251910</v>
@@ -35198,7 +35198,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G1201" t="n">
-        <v>8.33402729034424</v>
+        <v>8.33402633666992</v>
       </c>
       <c r="H1201" t="n">
         <v>4138263</v>
@@ -35227,7 +35227,7 @@
         <v>11.7299995422363</v>
       </c>
       <c r="G1202" t="n">
-        <v>8.2986536026001</v>
+        <v>8.29865455627441</v>
       </c>
       <c r="H1202" t="n">
         <v>3824661</v>
@@ -35256,7 +35256,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1203" t="n">
-        <v>8.2314453125</v>
+        <v>8.23144435882568</v>
       </c>
       <c r="H1203" t="n">
         <v>5031410</v>
@@ -35401,7 +35401,7 @@
         <v>11.8649997711182</v>
       </c>
       <c r="G1208" t="n">
-        <v>8.39416408538818</v>
+        <v>8.39416313171387</v>
       </c>
       <c r="H1208" t="n">
         <v>4485785</v>
@@ -35459,7 +35459,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1210" t="n">
-        <v>8.53919506072998</v>
+        <v>8.53919410705566</v>
       </c>
       <c r="H1210" t="n">
         <v>2546618</v>
@@ -35488,7 +35488,7 @@
         <v>12.375</v>
       </c>
       <c r="G1211" t="n">
-        <v>8.75497436523438</v>
+        <v>8.75497341156006</v>
       </c>
       <c r="H1211" t="n">
         <v>5567214</v>
@@ -35517,7 +35517,7 @@
         <v>12.335000038147</v>
       </c>
       <c r="G1212" t="n">
-        <v>8.72667503356934</v>
+        <v>8.72667598724365</v>
       </c>
       <c r="H1212" t="n">
         <v>3291594</v>
@@ -35546,7 +35546,7 @@
         <v>12.585000038147</v>
       </c>
       <c r="G1213" t="n">
-        <v>8.90354442596436</v>
+        <v>8.90354251861572</v>
       </c>
       <c r="H1213" t="n">
         <v>6433033</v>
@@ -35604,7 +35604,7 @@
         <v>12.4799995422363</v>
       </c>
       <c r="G1215" t="n">
-        <v>8.82925796508789</v>
+        <v>8.82925891876221</v>
       </c>
       <c r="H1215" t="n">
         <v>3093281</v>
@@ -35691,7 +35691,7 @@
         <v>11.914999961853</v>
       </c>
       <c r="G1218" t="n">
-        <v>8.42953586578369</v>
+        <v>8.42953491210938</v>
       </c>
       <c r="H1218" t="n">
         <v>6076985</v>
@@ -35720,7 +35720,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G1219" t="n">
-        <v>8.58871650695801</v>
+        <v>8.58871746063232</v>
       </c>
       <c r="H1219" t="n">
         <v>4439249</v>
@@ -35778,7 +35778,7 @@
         <v>12.2349996566772</v>
       </c>
       <c r="G1221" t="n">
-        <v>8.65592670440674</v>
+        <v>8.65592765808105</v>
       </c>
       <c r="H1221" t="n">
         <v>2214317</v>
@@ -35807,7 +35807,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1222" t="n">
-        <v>8.44014835357666</v>
+        <v>8.44014930725098</v>
       </c>
       <c r="H1222" t="n">
         <v>4059323</v>
@@ -35865,7 +35865,7 @@
         <v>12.0600004196167</v>
       </c>
       <c r="G1224" t="n">
-        <v>8.53211975097656</v>
+        <v>8.53211879730225</v>
       </c>
       <c r="H1224" t="n">
         <v>2545617</v>
@@ -35894,7 +35894,7 @@
         <v>11.875</v>
       </c>
       <c r="G1225" t="n">
-        <v>8.40123653411865</v>
+        <v>8.40123844146729</v>
       </c>
       <c r="H1225" t="n">
         <v>3098003</v>
@@ -35923,7 +35923,7 @@
         <v>11.6350002288818</v>
       </c>
       <c r="G1226" t="n">
-        <v>8.2314453125</v>
+        <v>8.23144435882568</v>
       </c>
       <c r="H1226" t="n">
         <v>4665464</v>
@@ -35952,7 +35952,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G1227" t="n">
-        <v>8.03688812255859</v>
+        <v>8.03688907623291</v>
       </c>
       <c r="H1227" t="n">
         <v>6417383</v>
@@ -36039,7 +36039,7 @@
         <v>11.8050003051758</v>
       </c>
       <c r="G1230" t="n">
-        <v>8.35171508789062</v>
+        <v>8.35171413421631</v>
       </c>
       <c r="H1230" t="n">
         <v>4722851</v>
@@ -36068,7 +36068,7 @@
         <v>12.0349998474121</v>
       </c>
       <c r="G1231" t="n">
-        <v>8.51443386077881</v>
+        <v>8.51443195343018</v>
       </c>
       <c r="H1231" t="n">
         <v>5228206</v>
@@ -36097,7 +36097,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1232" t="n">
-        <v>8.63116550445557</v>
+        <v>8.63116645812988</v>
       </c>
       <c r="H1232" t="n">
         <v>5173585</v>
@@ -36184,7 +36184,7 @@
         <v>13.1599998474121</v>
       </c>
       <c r="G1235" t="n">
-        <v>9.31033992767334</v>
+        <v>9.31033897399902</v>
       </c>
       <c r="H1235" t="n">
         <v>14538622</v>
@@ -36271,7 +36271,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1238" t="n">
-        <v>9.52258110046387</v>
+        <v>9.52258205413818</v>
       </c>
       <c r="H1238" t="n">
         <v>6182317</v>
@@ -36300,7 +36300,7 @@
         <v>13.6350002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>9.64638996124268</v>
+        <v>9.64638900756836</v>
       </c>
       <c r="H1239" t="n">
         <v>5553838</v>
@@ -36358,7 +36358,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1241" t="n">
-        <v>9.99658679962158</v>
+        <v>9.9965877532959</v>
       </c>
       <c r="H1241" t="n">
         <v>5483119</v>
@@ -36387,7 +36387,7 @@
         <v>14.2299995422363</v>
       </c>
       <c r="G1242" t="n">
-        <v>10.0673360824585</v>
+        <v>10.0673370361328</v>
       </c>
       <c r="H1242" t="n">
         <v>5139958</v>
@@ -36474,7 +36474,7 @@
         <v>14.2200002670288</v>
       </c>
       <c r="G1245" t="n">
-        <v>10.0602607727051</v>
+        <v>10.0602626800537</v>
       </c>
       <c r="H1245" t="n">
         <v>5571562</v>
@@ -36503,7 +36503,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1246" t="n">
-        <v>10.1734561920166</v>
+        <v>10.1734552383423</v>
       </c>
       <c r="H1246" t="n">
         <v>5544202</v>
@@ -36677,7 +36677,7 @@
         <v>14.4250001907349</v>
       </c>
       <c r="G1252" t="n">
-        <v>10.2052927017212</v>
+        <v>10.2052917480469</v>
       </c>
       <c r="H1252" t="n">
         <v>4363796</v>
@@ -36735,7 +36735,7 @@
         <v>14.5699996948242</v>
       </c>
       <c r="G1254" t="n">
-        <v>10.3078765869141</v>
+        <v>10.3078756332397</v>
       </c>
       <c r="H1254" t="n">
         <v>4416653</v>
@@ -36822,7 +36822,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1257" t="n">
-        <v>10.1345453262329</v>
+        <v>10.1345443725586</v>
       </c>
       <c r="H1257" t="n">
         <v>4131506</v>
@@ -36851,7 +36851,7 @@
         <v>14.3549995422363</v>
       </c>
       <c r="G1258" t="n">
-        <v>10.1557683944702</v>
+        <v>10.1557693481445</v>
       </c>
       <c r="H1258" t="n">
         <v>4846552</v>
@@ -36996,7 +36996,7 @@
         <v>14.3249998092651</v>
       </c>
       <c r="G1263" t="n">
-        <v>10.1345453262329</v>
+        <v>10.1345443725586</v>
       </c>
       <c r="H1263" t="n">
         <v>3899524</v>
@@ -37025,7 +37025,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1264" t="n">
-        <v>10.1734561920166</v>
+        <v>10.1734552383423</v>
       </c>
       <c r="H1264" t="n">
         <v>10357764</v>
@@ -37257,7 +37257,7 @@
         <v>13.914999961853</v>
       </c>
       <c r="G1272" t="n">
-        <v>9.844482421875</v>
+        <v>9.84448146820068</v>
       </c>
       <c r="H1272" t="n">
         <v>4359534</v>
@@ -37460,7 +37460,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1279" t="n">
-        <v>10.1876068115234</v>
+        <v>10.1876058578491</v>
       </c>
       <c r="H1279" t="n">
         <v>4673770</v>
@@ -37518,7 +37518,7 @@
         <v>14.460000038147</v>
       </c>
       <c r="G1281" t="n">
-        <v>10.2300548553467</v>
+        <v>10.2300539016724</v>
       </c>
       <c r="H1281" t="n">
         <v>3111178</v>
@@ -37634,7 +37634,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1285" t="n">
-        <v>10.2654275894165</v>
+        <v>10.2654285430908</v>
       </c>
       <c r="H1285" t="n">
         <v>5871169</v>
@@ -37721,7 +37721,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1288" t="n">
-        <v>10.1734561920166</v>
+        <v>10.1734552383423</v>
       </c>
       <c r="H1288" t="n">
         <v>4347578</v>
@@ -37779,7 +37779,7 @@
         <v>14.0900001525879</v>
       </c>
       <c r="G1290" t="n">
-        <v>9.96828842163086</v>
+        <v>9.96828937530518</v>
       </c>
       <c r="H1290" t="n">
         <v>7886788</v>
@@ -37808,7 +37808,7 @@
         <v>14.2550001144409</v>
       </c>
       <c r="G1291" t="n">
-        <v>10.0850229263306</v>
+        <v>10.0850238800049</v>
       </c>
       <c r="H1291" t="n">
         <v>3540987</v>
@@ -37837,7 +37837,7 @@
         <v>14.4750003814697</v>
       </c>
       <c r="G1292" t="n">
-        <v>10.2406663894653</v>
+        <v>10.2406673431396</v>
       </c>
       <c r="H1292" t="n">
         <v>4187940</v>
@@ -37866,7 +37866,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G1293" t="n">
-        <v>10.5767154693604</v>
+        <v>10.576714515686</v>
       </c>
       <c r="H1293" t="n">
         <v>10944013</v>
@@ -37895,7 +37895,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1294" t="n">
-        <v>10.9092273712158</v>
+        <v>10.9092283248901</v>
       </c>
       <c r="H1294" t="n">
         <v>7979755</v>
@@ -37924,7 +37924,7 @@
         <v>15.5349998474121</v>
       </c>
       <c r="G1295" t="n">
-        <v>10.9905872344971</v>
+        <v>10.9905881881714</v>
       </c>
       <c r="H1295" t="n">
         <v>7231476</v>
@@ -37953,7 +37953,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1296" t="n">
-        <v>11.121470451355</v>
+        <v>11.1214694976807</v>
       </c>
       <c r="H1296" t="n">
         <v>7215414</v>
@@ -38011,7 +38011,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1298" t="n">
-        <v>11.14976978302</v>
+        <v>11.1497688293457</v>
       </c>
       <c r="H1298" t="n">
         <v>4843098</v>
@@ -38040,7 +38040,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1299" t="n">
-        <v>11.1073217391968</v>
+        <v>11.1073198318481</v>
       </c>
       <c r="H1299" t="n">
         <v>3010088</v>
@@ -38098,7 +38098,7 @@
         <v>15.8249998092651</v>
       </c>
       <c r="G1301" t="n">
-        <v>11.1957521438599</v>
+        <v>11.1957530975342</v>
       </c>
       <c r="H1301" t="n">
         <v>3873144</v>
@@ -38185,7 +38185,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G1304" t="n">
-        <v>10.9163026809692</v>
+        <v>10.9163036346436</v>
       </c>
       <c r="H1304" t="n">
         <v>4861836</v>
@@ -38243,7 +38243,7 @@
         <v>15.539999961853</v>
       </c>
       <c r="G1306" t="n">
-        <v>10.9941244125366</v>
+        <v>10.9941253662109</v>
       </c>
       <c r="H1306" t="n">
         <v>2973230</v>
@@ -38272,7 +38272,7 @@
         <v>15.5050001144409</v>
       </c>
       <c r="G1307" t="n">
-        <v>10.9693622589111</v>
+        <v>10.9693632125854</v>
       </c>
       <c r="H1307" t="n">
         <v>3328306</v>
@@ -38330,7 +38330,7 @@
         <v>15.835000038147</v>
       </c>
       <c r="G1309" t="n">
-        <v>11.2028303146362</v>
+        <v>11.2028293609619</v>
       </c>
       <c r="H1309" t="n">
         <v>4923573</v>
@@ -38388,7 +38388,7 @@
         <v>15.8299999237061</v>
       </c>
       <c r="G1311" t="n">
-        <v>11.199291229248</v>
+        <v>11.1992921829224</v>
       </c>
       <c r="H1311" t="n">
         <v>4003255</v>
@@ -38417,7 +38417,7 @@
         <v>15.875</v>
       </c>
       <c r="G1312" t="n">
-        <v>11.2311296463013</v>
+        <v>11.231128692627</v>
       </c>
       <c r="H1312" t="n">
         <v>4074042</v>
@@ -38533,7 +38533,7 @@
         <v>16.5</v>
       </c>
       <c r="G1316" t="n">
-        <v>11.6732978820801</v>
+        <v>11.6732988357544</v>
       </c>
       <c r="H1316" t="n">
         <v>7830908</v>
@@ -38562,7 +38562,7 @@
         <v>16.5300006866455</v>
       </c>
       <c r="G1317" t="n">
-        <v>11.694522857666</v>
+        <v>11.6945219039917</v>
       </c>
       <c r="H1317" t="n">
         <v>4486168</v>
@@ -38620,7 +38620,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G1319" t="n">
-        <v>11.8607797622681</v>
+        <v>11.8607788085938</v>
       </c>
       <c r="H1319" t="n">
         <v>9043685</v>
@@ -38649,7 +38649,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G1320" t="n">
-        <v>11.9598255157471</v>
+        <v>11.9598245620728</v>
       </c>
       <c r="H1320" t="n">
         <v>4820812</v>
@@ -38707,7 +38707,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1322" t="n">
-        <v>11.9492111206055</v>
+        <v>11.9492130279541</v>
       </c>
       <c r="H1322" t="n">
         <v>5062686</v>
@@ -38794,7 +38794,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1325" t="n">
-        <v>11.8360157012939</v>
+        <v>11.8360166549683</v>
       </c>
       <c r="H1325" t="n">
         <v>14777969</v>
@@ -38823,7 +38823,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1326" t="n">
-        <v>11.8890771865845</v>
+        <v>11.8890781402588</v>
       </c>
       <c r="H1326" t="n">
         <v>4136645</v>
@@ -38852,7 +38852,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1327" t="n">
-        <v>11.8855390548706</v>
+        <v>11.8855400085449</v>
       </c>
       <c r="H1327" t="n">
         <v>3269431</v>
@@ -38881,7 +38881,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1328" t="n">
-        <v>11.9492111206055</v>
+        <v>11.9492130279541</v>
       </c>
       <c r="H1328" t="n">
         <v>3448568</v>
@@ -38968,7 +38968,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1331" t="n">
-        <v>12.069483757019</v>
+        <v>12.0694828033447</v>
       </c>
       <c r="H1331" t="n">
         <v>5137316</v>
@@ -39026,7 +39026,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1333" t="n">
-        <v>12.069483757019</v>
+        <v>12.0694828033447</v>
       </c>
       <c r="H1333" t="n">
         <v>4823009</v>
@@ -39084,7 +39084,7 @@
         <v>17.1350002288818</v>
       </c>
       <c r="G1335" t="n">
-        <v>12.1225442886353</v>
+        <v>12.1225433349609</v>
       </c>
       <c r="H1335" t="n">
         <v>5147652</v>
@@ -39113,7 +39113,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G1336" t="n">
-        <v>12.1473045349121</v>
+        <v>12.1473054885864</v>
       </c>
       <c r="H1336" t="n">
         <v>3432252</v>
@@ -39142,7 +39142,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G1337" t="n">
-        <v>12.1013193130493</v>
+        <v>12.1013174057007</v>
       </c>
       <c r="H1337" t="n">
         <v>5538002</v>
@@ -39171,7 +39171,7 @@
         <v>16.9650001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>12.0022745132446</v>
+        <v>12.0022735595703</v>
       </c>
       <c r="H1338" t="n">
         <v>4421859</v>
@@ -39229,7 +39229,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1340" t="n">
-        <v>12.0871696472168</v>
+        <v>12.0871686935425</v>
       </c>
       <c r="H1340" t="n">
         <v>3688042</v>
@@ -39258,7 +39258,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1341" t="n">
-        <v>12.0871696472168</v>
+        <v>12.0871686935425</v>
       </c>
       <c r="H1341" t="n">
         <v>3154811</v>
@@ -39345,7 +39345,7 @@
         <v>17.2250003814697</v>
       </c>
       <c r="G1344" t="n">
-        <v>12.1862144470215</v>
+        <v>12.1862163543701</v>
       </c>
       <c r="H1344" t="n">
         <v>4653578</v>
@@ -39403,7 +39403,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1346" t="n">
-        <v>11.9173765182495</v>
+        <v>11.9173755645752</v>
       </c>
       <c r="H1346" t="n">
         <v>4339084</v>
@@ -39577,7 +39577,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1352" t="n">
-        <v>11.8713912963867</v>
+        <v>11.871392250061</v>
       </c>
       <c r="H1352" t="n">
         <v>7077482</v>
@@ -39693,7 +39693,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1356" t="n">
-        <v>12.0624074935913</v>
+        <v>12.062406539917</v>
       </c>
       <c r="H1356" t="n">
         <v>3799970</v>
@@ -39722,7 +39722,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1357" t="n">
-        <v>12.1826791763306</v>
+        <v>12.1826772689819</v>
       </c>
       <c r="H1357" t="n">
         <v>8210086</v>
@@ -39751,7 +39751,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G1358" t="n">
-        <v>12.288800239563</v>
+        <v>12.2888011932373</v>
       </c>
       <c r="H1358" t="n">
         <v>5410437</v>
@@ -39780,7 +39780,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1359" t="n">
-        <v>12.4232196807861</v>
+        <v>12.4232187271118</v>
       </c>
       <c r="H1359" t="n">
         <v>5085810</v>
@@ -39809,7 +39809,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1360" t="n">
-        <v>12.3170976638794</v>
+        <v>12.3170986175537</v>
       </c>
       <c r="H1360" t="n">
         <v>7031757</v>
@@ -39838,7 +39838,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1361" t="n">
-        <v>12.3666200637817</v>
+        <v>12.3666210174561</v>
       </c>
       <c r="H1361" t="n">
         <v>7372310</v>
@@ -39867,7 +39867,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1362" t="n">
-        <v>12.4090700149536</v>
+        <v>12.4090709686279</v>
       </c>
       <c r="H1362" t="n">
         <v>6246702</v>
@@ -39896,7 +39896,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1363" t="n">
-        <v>12.4798164367676</v>
+        <v>12.4798173904419</v>
       </c>
       <c r="H1363" t="n">
         <v>9000170</v>
@@ -39925,7 +39925,7 @@
         <v>17.6450004577637</v>
       </c>
       <c r="G1364" t="n">
-        <v>12.4833555221558</v>
+        <v>12.4833545684814</v>
       </c>
       <c r="H1364" t="n">
         <v>5048117</v>
@@ -39954,7 +39954,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1365" t="n">
-        <v>12.5081167221069</v>
+        <v>12.5081176757812</v>
       </c>
       <c r="H1365" t="n">
         <v>8807830</v>
@@ -40012,7 +40012,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G1367" t="n">
-        <v>12.3418607711792</v>
+        <v>12.3418598175049</v>
       </c>
       <c r="H1367" t="n">
         <v>7820921</v>
@@ -40070,7 +40070,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1369" t="n">
-        <v>12.6815633773804</v>
+        <v>12.6815643310547</v>
       </c>
       <c r="H1369" t="n">
         <v>9401155</v>
@@ -40099,7 +40099,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1370" t="n">
-        <v>12.5615005493164</v>
+        <v>12.5615015029907</v>
       </c>
       <c r="H1370" t="n">
         <v>5020867</v>
@@ -40186,7 +40186,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1373" t="n">
-        <v>12.6402921676636</v>
+        <v>12.6402912139893</v>
       </c>
       <c r="H1373" t="n">
         <v>3775566</v>
@@ -40273,7 +40273,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1376" t="n">
-        <v>12.7190837860107</v>
+        <v>12.7190847396851</v>
       </c>
       <c r="H1376" t="n">
         <v>2631804</v>
@@ -40360,7 +40360,7 @@
         <v>17.25</v>
       </c>
       <c r="G1379" t="n">
-        <v>12.9442005157471</v>
+        <v>12.9441995620728</v>
       </c>
       <c r="H1379" t="n">
         <v>4279209</v>
@@ -40389,7 +40389,7 @@
         <v>17.2250003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>12.9254398345947</v>
+        <v>12.925440788269</v>
       </c>
       <c r="H1380" t="n">
         <v>4160641</v>
@@ -40418,7 +40418,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1381" t="n">
-        <v>12.8916711807251</v>
+        <v>12.8916721343994</v>
       </c>
       <c r="H1381" t="n">
         <v>4629257</v>
@@ -40534,7 +40534,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1385" t="n">
-        <v>12.8916711807251</v>
+        <v>12.8916721343994</v>
       </c>
       <c r="H1385" t="n">
         <v>2584909</v>
@@ -40621,7 +40621,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1388" t="n">
-        <v>12.6740579605103</v>
+        <v>12.6740589141846</v>
       </c>
       <c r="H1388" t="n">
         <v>9118160</v>
@@ -40650,7 +40650,7 @@
         <v>16.9349994659424</v>
       </c>
       <c r="G1389" t="n">
-        <v>12.7078275680542</v>
+        <v>12.7078266143799</v>
       </c>
       <c r="H1389" t="n">
         <v>3244573</v>
@@ -40679,7 +40679,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1390" t="n">
-        <v>12.6703071594238</v>
+        <v>12.6703090667725</v>
       </c>
       <c r="H1390" t="n">
         <v>2517399</v>
@@ -40708,7 +40708,7 @@
         <v>16.6550006866455</v>
       </c>
       <c r="G1391" t="n">
-        <v>12.4977178573608</v>
+        <v>12.4977188110352</v>
       </c>
       <c r="H1391" t="n">
         <v>3975295</v>
@@ -40766,7 +40766,7 @@
         <v>17.0149993896484</v>
       </c>
       <c r="G1393" t="n">
-        <v>12.7678575515747</v>
+        <v>12.767858505249</v>
       </c>
       <c r="H1393" t="n">
         <v>2462978</v>
@@ -40795,7 +40795,7 @@
         <v>16.75</v>
       </c>
       <c r="G1394" t="n">
-        <v>12.5690040588379</v>
+        <v>12.5690050125122</v>
       </c>
       <c r="H1394" t="n">
         <v>3033079</v>
@@ -40853,7 +40853,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G1396" t="n">
-        <v>12.6853170394897</v>
+        <v>12.6853160858154</v>
       </c>
       <c r="H1396" t="n">
         <v>5392566</v>
@@ -40882,7 +40882,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G1397" t="n">
-        <v>12.8053770065308</v>
+        <v>12.8053779602051</v>
       </c>
       <c r="H1397" t="n">
         <v>3656356</v>
@@ -40969,7 +40969,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1400" t="n">
-        <v>12.6365394592285</v>
+        <v>12.6365404129028</v>
       </c>
       <c r="H1400" t="n">
         <v>4559372</v>
@@ -40998,7 +40998,7 @@
         <v>16.9349994659424</v>
       </c>
       <c r="G1401" t="n">
-        <v>12.7078275680542</v>
+        <v>12.7078266143799</v>
       </c>
       <c r="H1401" t="n">
         <v>2783058</v>
@@ -41056,7 +41056,7 @@
         <v>16.8850002288818</v>
       </c>
       <c r="G1403" t="n">
-        <v>12.6703071594238</v>
+        <v>12.6703090667725</v>
       </c>
       <c r="H1403" t="n">
         <v>4656013</v>
@@ -41085,7 +41085,7 @@
         <v>17.0049991607666</v>
       </c>
       <c r="G1404" t="n">
-        <v>12.7603530883789</v>
+        <v>12.7603549957275</v>
       </c>
       <c r="H1404" t="n">
         <v>3010578</v>
@@ -41230,7 +41230,7 @@
         <v>16.2250003814697</v>
       </c>
       <c r="G1409" t="n">
-        <v>12.1750516891479</v>
+        <v>12.1750526428223</v>
       </c>
       <c r="H1409" t="n">
         <v>5756359</v>
@@ -41259,7 +41259,7 @@
         <v>16.3899993896484</v>
       </c>
       <c r="G1410" t="n">
-        <v>12.2988653182983</v>
+        <v>12.2988634109497</v>
       </c>
       <c r="H1410" t="n">
         <v>3376099</v>
@@ -41288,7 +41288,7 @@
         <v>16.7450008392334</v>
       </c>
       <c r="G1411" t="n">
-        <v>12.5652532577515</v>
+        <v>12.5652542114258</v>
       </c>
       <c r="H1411" t="n">
         <v>5143629</v>
@@ -41317,7 +41317,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1412" t="n">
-        <v>12.5990219116211</v>
+        <v>12.5990209579468</v>
       </c>
       <c r="H1412" t="n">
         <v>3007617</v>
@@ -41375,7 +41375,7 @@
         <v>16.8449993133545</v>
       </c>
       <c r="G1414" t="n">
-        <v>12.6402921676636</v>
+        <v>12.6402912139893</v>
       </c>
       <c r="H1414" t="n">
         <v>3198006</v>
@@ -41433,7 +41433,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1416" t="n">
-        <v>12.5990219116211</v>
+        <v>12.5990209579468</v>
       </c>
       <c r="H1416" t="n">
         <v>2784209</v>
@@ -41549,7 +41549,7 @@
         <v>16.6749992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>12.5127258300781</v>
+        <v>12.5127267837524</v>
       </c>
       <c r="H1420" t="n">
         <v>5689490</v>
@@ -41578,7 +41578,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>12.4376859664917</v>
+        <v>12.437686920166</v>
       </c>
       <c r="H1421" t="n">
         <v>4349147</v>
@@ -41607,7 +41607,7 @@
         <v>16.625</v>
       </c>
       <c r="G1422" t="n">
-        <v>12.4752073287964</v>
+        <v>12.4752063751221</v>
       </c>
       <c r="H1422" t="n">
         <v>3233201</v>
@@ -41636,7 +41636,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1423" t="n">
-        <v>12.6665563583374</v>
+        <v>12.6665554046631</v>
       </c>
       <c r="H1423" t="n">
         <v>4490693</v>
@@ -41665,7 +41665,7 @@
         <v>16.9650001525879</v>
       </c>
       <c r="G1424" t="n">
-        <v>12.7303400039673</v>
+        <v>12.730339050293</v>
       </c>
       <c r="H1424" t="n">
         <v>2223045</v>
@@ -41723,7 +41723,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G1426" t="n">
-        <v>12.9029264450073</v>
+        <v>12.9029273986816</v>
       </c>
       <c r="H1426" t="n">
         <v>4030683</v>
@@ -41839,7 +41839,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1430" t="n">
-        <v>12.8916711807251</v>
+        <v>12.8916721343994</v>
       </c>
       <c r="H1430" t="n">
         <v>2930261</v>
@@ -41868,7 +41868,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1431" t="n">
-        <v>12.9667110443115</v>
+        <v>12.9667119979858</v>
       </c>
       <c r="H1431" t="n">
         <v>3029659</v>
@@ -41897,7 +41897,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1432" t="n">
-        <v>12.8091297149658</v>
+        <v>12.8091287612915</v>
       </c>
       <c r="H1432" t="n">
         <v>4628841</v>
@@ -41926,7 +41926,7 @@
         <v>17.0650005340576</v>
       </c>
       <c r="G1433" t="n">
-        <v>12.8053770065308</v>
+        <v>12.8053779602051</v>
       </c>
       <c r="H1433" t="n">
         <v>2362468</v>
@@ -41955,7 +41955,7 @@
         <v>17.1550006866455</v>
       </c>
       <c r="G1434" t="n">
-        <v>12.8729124069214</v>
+        <v>12.8729133605957</v>
       </c>
       <c r="H1434" t="n">
         <v>2258140</v>
@@ -42042,7 +42042,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1437" t="n">
-        <v>12.8166341781616</v>
+        <v>12.8166332244873</v>
       </c>
       <c r="H1437" t="n">
         <v>2585238</v>
@@ -42100,7 +42100,7 @@
         <v>17.1149997711182</v>
       </c>
       <c r="G1439" t="n">
-        <v>12.8428964614868</v>
+        <v>12.8428955078125</v>
       </c>
       <c r="H1439" t="n">
         <v>1534763</v>
@@ -42187,7 +42187,7 @@
         <v>17.3700008392334</v>
       </c>
       <c r="G1442" t="n">
-        <v>13.0342454910278</v>
+        <v>13.0342473983765</v>
       </c>
       <c r="H1442" t="n">
         <v>3151345</v>
@@ -42303,7 +42303,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1446" t="n">
-        <v>13.2518587112427</v>
+        <v>13.251859664917</v>
       </c>
       <c r="H1446" t="n">
         <v>6638451</v>
@@ -42332,7 +42332,7 @@
         <v>17.7450008392334</v>
       </c>
       <c r="G1447" t="n">
-        <v>13.3156414031982</v>
+        <v>13.3156423568726</v>
       </c>
       <c r="H1447" t="n">
         <v>5118386</v>
@@ -42361,7 +42361,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G1448" t="n">
-        <v>13.0792684555054</v>
+        <v>13.0792694091797</v>
       </c>
       <c r="H1448" t="n">
         <v>4314816</v>
@@ -42390,7 +42390,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1449" t="n">
-        <v>13.2443542480469</v>
+        <v>13.2443552017212</v>
       </c>
       <c r="H1449" t="n">
         <v>4837767</v>
@@ -42419,7 +42419,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1450" t="n">
-        <v>13.2068347930908</v>
+        <v>13.2068357467651</v>
       </c>
       <c r="H1450" t="n">
         <v>4703034</v>
@@ -42448,7 +42448,7 @@
         <v>17.7150001525879</v>
       </c>
       <c r="G1451" t="n">
-        <v>13.2931299209595</v>
+        <v>13.2931318283081</v>
       </c>
       <c r="H1451" t="n">
         <v>6037331</v>
@@ -42506,7 +42506,7 @@
         <v>17.6849994659424</v>
       </c>
       <c r="G1453" t="n">
-        <v>13.2706165313721</v>
+        <v>13.2706184387207</v>
       </c>
       <c r="H1453" t="n">
         <v>8146643</v>
@@ -42535,7 +42535,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>13.0942792892456</v>
+        <v>13.0942783355713</v>
       </c>
       <c r="H1454" t="n">
         <v>7102386</v>
@@ -42564,7 +42564,7 @@
         <v>17.7150001525879</v>
       </c>
       <c r="G1455" t="n">
-        <v>13.2931299209595</v>
+        <v>13.2931318283081</v>
       </c>
       <c r="H1455" t="n">
         <v>6145431</v>
@@ -42593,7 +42593,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>13.491982460022</v>
+        <v>13.4919834136963</v>
       </c>
       <c r="H1456" t="n">
         <v>7118240</v>
@@ -42651,7 +42651,7 @@
         <v>18.3299999237061</v>
       </c>
       <c r="G1458" t="n">
-        <v>13.7546195983887</v>
+        <v>13.75461769104</v>
       </c>
       <c r="H1458" t="n">
         <v>6410552</v>
@@ -42680,7 +42680,7 @@
         <v>18.625</v>
       </c>
       <c r="G1459" t="n">
-        <v>13.9759826660156</v>
+        <v>13.9759836196899</v>
       </c>
       <c r="H1459" t="n">
         <v>8266720</v>
@@ -42796,7 +42796,7 @@
         <v>18.4099998474121</v>
       </c>
       <c r="G1463" t="n">
-        <v>13.8146505355835</v>
+        <v>13.8146495819092</v>
       </c>
       <c r="H1463" t="n">
         <v>4729941</v>
@@ -42883,7 +42883,7 @@
         <v>18.5849990844727</v>
       </c>
       <c r="G1466" t="n">
-        <v>13.9459686279297</v>
+        <v>13.9459667205811</v>
       </c>
       <c r="H1466" t="n">
         <v>7521395</v>
@@ -42912,7 +42912,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1467" t="n">
-        <v>14.0772848129272</v>
+        <v>14.0772857666016</v>
       </c>
       <c r="H1467" t="n">
         <v>7007802</v>
@@ -42941,7 +42941,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1468" t="n">
-        <v>14.1035490036011</v>
+        <v>14.1035499572754</v>
       </c>
       <c r="H1468" t="n">
         <v>4700177</v>
@@ -42970,7 +42970,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1469" t="n">
-        <v>14.1785869598389</v>
+        <v>14.1785879135132</v>
       </c>
       <c r="H1469" t="n">
         <v>5899777</v>
@@ -42999,7 +42999,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G1470" t="n">
-        <v>14.2498750686646</v>
+        <v>14.2498741149902</v>
       </c>
       <c r="H1470" t="n">
         <v>5280649</v>
@@ -43028,7 +43028,7 @@
         <v>18.7099990844727</v>
       </c>
       <c r="G1471" t="n">
-        <v>14.0397653579712</v>
+        <v>14.0397644042969</v>
       </c>
       <c r="H1471" t="n">
         <v>5431751</v>
@@ -43057,7 +43057,7 @@
         <v>18.7250003814697</v>
       </c>
       <c r="G1472" t="n">
-        <v>14.0510225296021</v>
+        <v>14.0510215759277</v>
       </c>
       <c r="H1472" t="n">
         <v>6136444</v>
@@ -43086,7 +43086,7 @@
         <v>18.7900009155273</v>
       </c>
       <c r="G1473" t="n">
-        <v>14.0997972488403</v>
+        <v>14.0997982025146</v>
       </c>
       <c r="H1473" t="n">
         <v>5314614</v>
@@ -43144,7 +43144,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1475" t="n">
-        <v>14.2190275192261</v>
+        <v>14.2190256118774</v>
       </c>
       <c r="H1475" t="n">
         <v>4074796</v>
@@ -43173,7 +43173,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1476" t="n">
-        <v>14.3382558822632</v>
+        <v>14.3382549285889</v>
       </c>
       <c r="H1476" t="n">
         <v>4067206</v>
@@ -43260,7 +43260,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G1479" t="n">
-        <v>14.3767175674438</v>
+        <v>14.3767166137695</v>
       </c>
       <c r="H1479" t="n">
         <v>3137435</v>
@@ -43289,7 +43289,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1480" t="n">
-        <v>14.4767160415649</v>
+        <v>14.4767150878906</v>
       </c>
       <c r="H1480" t="n">
         <v>6331494</v>
@@ -43347,7 +43347,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1482" t="n">
-        <v>14.4921007156372</v>
+        <v>14.4920997619629</v>
       </c>
       <c r="H1482" t="n">
         <v>2739837</v>
@@ -43463,7 +43463,7 @@
         <v>19.0750007629395</v>
       </c>
       <c r="G1486" t="n">
-        <v>14.6728677749634</v>
+        <v>14.6728658676147</v>
       </c>
       <c r="H1486" t="n">
         <v>3252721</v>
@@ -43521,7 +43521,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G1488" t="n">
-        <v>14.6959438323975</v>
+        <v>14.6959419250488</v>
       </c>
       <c r="H1488" t="n">
         <v>3423152</v>
@@ -43550,7 +43550,7 @@
         <v>18.9750003814697</v>
       </c>
       <c r="G1489" t="n">
-        <v>14.5959434509277</v>
+        <v>14.5959453582764</v>
       </c>
       <c r="H1489" t="n">
         <v>4313251</v>
@@ -43637,7 +43637,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>14.7305583953857</v>
+        <v>14.7305564880371</v>
       </c>
       <c r="H1492" t="n">
         <v>4338793</v>
@@ -43666,7 +43666,7 @@
         <v>19.1350002288818</v>
       </c>
       <c r="G1493" t="n">
-        <v>14.7190217971802</v>
+        <v>14.7190198898315</v>
       </c>
       <c r="H1493" t="n">
         <v>6075096</v>
@@ -43724,7 +43724,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1495" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1495" t="n">
         <v>9433010</v>
@@ -43753,7 +43753,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1496" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1496" t="n">
         <v>5548195</v>
@@ -43840,7 +43840,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1499" t="n">
-        <v>14.1536436080933</v>
+        <v>14.1536426544189</v>
       </c>
       <c r="H1499" t="n">
         <v>3238825</v>
@@ -43869,7 +43869,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1500" t="n">
-        <v>14.1305675506592</v>
+        <v>14.1305665969849</v>
       </c>
       <c r="H1500" t="n">
         <v>6389063</v>
@@ -43898,7 +43898,7 @@
         <v>18.3999996185303</v>
       </c>
       <c r="G1501" t="n">
-        <v>14.1536436080933</v>
+        <v>14.1536426544189</v>
       </c>
       <c r="H1501" t="n">
         <v>3885101</v>
@@ -43927,7 +43927,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1502" t="n">
-        <v>14.0921049118042</v>
+        <v>14.0921039581299</v>
       </c>
       <c r="H1502" t="n">
         <v>3138374</v>
@@ -43985,7 +43985,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1504" t="n">
-        <v>13.6921110153198</v>
+        <v>13.6921100616455</v>
       </c>
       <c r="H1504" t="n">
         <v>4125151</v>
@@ -44072,7 +44072,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1507" t="n">
-        <v>13.8767242431641</v>
+        <v>13.8767232894897</v>
       </c>
       <c r="H1507" t="n">
         <v>6037184</v>
@@ -44101,7 +44101,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G1508" t="n">
-        <v>13.9921073913574</v>
+        <v>13.9921064376831</v>
       </c>
       <c r="H1508" t="n">
         <v>4923683</v>
@@ -44130,7 +44130,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1509" t="n">
-        <v>14.3151807785034</v>
+        <v>14.3151798248291</v>
       </c>
       <c r="H1509" t="n">
         <v>6505718</v>
@@ -44188,7 +44188,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1511" t="n">
-        <v>14.2267198562622</v>
+        <v>14.2267189025879</v>
       </c>
       <c r="H1511" t="n">
         <v>4290654</v>
@@ -44246,7 +44246,7 @@
         <v>18.5</v>
       </c>
       <c r="G1513" t="n">
-        <v>14.2305660247803</v>
+        <v>14.2305641174316</v>
       </c>
       <c r="H1513" t="n">
         <v>11545814</v>
@@ -44275,7 +44275,7 @@
         <v>18.4850006103516</v>
       </c>
       <c r="G1514" t="n">
-        <v>14.2190275192261</v>
+        <v>14.2190256118774</v>
       </c>
       <c r="H1514" t="n">
         <v>3534166</v>
@@ -44304,7 +44304,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1515" t="n">
-        <v>14.1921043395996</v>
+        <v>14.1921033859253</v>
       </c>
       <c r="H1515" t="n">
         <v>6203016</v>
@@ -44333,7 +44333,7 @@
         <v>18.5</v>
       </c>
       <c r="G1516" t="n">
-        <v>14.2305660247803</v>
+        <v>14.2305641174316</v>
       </c>
       <c r="H1516" t="n">
         <v>4204960</v>
@@ -44362,7 +44362,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1517" t="n">
-        <v>14.3382558822632</v>
+        <v>14.3382549285889</v>
       </c>
       <c r="H1517" t="n">
         <v>7473948</v>
@@ -44391,7 +44391,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1518" t="n">
-        <v>14.2267198562622</v>
+        <v>14.2267189025879</v>
       </c>
       <c r="H1518" t="n">
         <v>10030772</v>
@@ -44420,7 +44420,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1519" t="n">
-        <v>14.1305675506592</v>
+        <v>14.1305665969849</v>
       </c>
       <c r="H1519" t="n">
         <v>5659427</v>
@@ -44507,7 +44507,7 @@
         <v>18.6350002288818</v>
       </c>
       <c r="G1522" t="n">
-        <v>14.3344097137451</v>
+        <v>14.3344087600708</v>
       </c>
       <c r="H1522" t="n">
         <v>3341179</v>
@@ -44536,7 +44536,7 @@
         <v>18.5499992370605</v>
       </c>
       <c r="G1523" t="n">
-        <v>14.2690258026123</v>
+        <v>14.269024848938</v>
       </c>
       <c r="H1523" t="n">
         <v>2168806</v>
@@ -44565,7 +44565,7 @@
         <v>18.75</v>
       </c>
       <c r="G1524" t="n">
-        <v>14.4228706359863</v>
+        <v>14.422869682312</v>
       </c>
       <c r="H1524" t="n">
         <v>3147730</v>
@@ -44652,7 +44652,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1527" t="n">
-        <v>14.4767160415649</v>
+        <v>14.4767150878906</v>
       </c>
       <c r="H1527" t="n">
         <v>2801936</v>
@@ -44739,7 +44739,7 @@
         <v>18.4650001525879</v>
       </c>
       <c r="G1530" t="n">
-        <v>14.2036418914795</v>
+        <v>14.2036409378052</v>
       </c>
       <c r="H1530" t="n">
         <v>5909180</v>
@@ -44768,7 +44768,7 @@
         <v>18.5699996948242</v>
       </c>
       <c r="G1531" t="n">
-        <v>14.2844114303589</v>
+        <v>14.2844095230103</v>
       </c>
       <c r="H1531" t="n">
         <v>3772558</v>
@@ -44913,7 +44913,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1536" t="n">
-        <v>14.1844129562378</v>
+        <v>14.1844120025635</v>
       </c>
       <c r="H1536" t="n">
         <v>8633579</v>
@@ -44942,7 +44942,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1537" t="n">
-        <v>14.2921028137207</v>
+        <v>14.2921018600464</v>
       </c>
       <c r="H1537" t="n">
         <v>5020767</v>
@@ -44971,7 +44971,7 @@
         <v>18.8549995422363</v>
       </c>
       <c r="G1538" t="n">
-        <v>14.5036382675171</v>
+        <v>14.5036373138428</v>
       </c>
       <c r="H1538" t="n">
         <v>7901405</v>
@@ -45000,7 +45000,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1539" t="n">
-        <v>14.3997936248779</v>
+        <v>14.3997926712036</v>
       </c>
       <c r="H1539" t="n">
         <v>7807260</v>
@@ -45029,7 +45029,7 @@
         <v>18.875</v>
       </c>
       <c r="G1540" t="n">
-        <v>14.5190238952637</v>
+        <v>14.519021987915</v>
       </c>
       <c r="H1540" t="n">
         <v>3329355</v>
@@ -45087,7 +45087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>13.6921110153198</v>
+        <v>13.6921100616455</v>
       </c>
       <c r="H1542" t="n">
         <v>7280068</v>
@@ -45145,7 +45145,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1544" t="n">
-        <v>13.8844146728516</v>
+        <v>13.8844137191772</v>
       </c>
       <c r="H1544" t="n">
         <v>4602059</v>
@@ -45232,7 +45232,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1547" t="n">
-        <v>14.2921028137207</v>
+        <v>14.2921018600464</v>
       </c>
       <c r="H1547" t="n">
         <v>6669744</v>
@@ -45290,7 +45290,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1549" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1549" t="n">
         <v>4947772</v>
@@ -45319,7 +45319,7 @@
         <v>18.6650009155273</v>
       </c>
       <c r="G1550" t="n">
-        <v>14.3574876785278</v>
+        <v>14.3574867248535</v>
       </c>
       <c r="H1550" t="n">
         <v>4702601</v>
@@ -45377,7 +45377,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G1552" t="n">
-        <v>13.9921073913574</v>
+        <v>13.9921064376831</v>
       </c>
       <c r="H1552" t="n">
         <v>5089672</v>
@@ -45406,7 +45406,7 @@
         <v>18.3449993133545</v>
       </c>
       <c r="G1553" t="n">
-        <v>14.1113348007202</v>
+        <v>14.1113338470459</v>
       </c>
       <c r="H1553" t="n">
         <v>3546227</v>
@@ -45435,7 +45435,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1554" t="n">
-        <v>14.1844129562378</v>
+        <v>14.1844120025635</v>
       </c>
       <c r="H1554" t="n">
         <v>3922104</v>
@@ -45464,7 +45464,7 @@
         <v>18.6499996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>14.3459482192993</v>
+        <v>14.345947265625</v>
       </c>
       <c r="H1555" t="n">
         <v>4968596</v>
@@ -45493,7 +45493,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1556" t="n">
-        <v>14.3228721618652</v>
+        <v>14.3228712081909</v>
       </c>
       <c r="H1556" t="n">
         <v>3542442</v>
@@ -45522,7 +45522,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1557" t="n">
-        <v>14.1190271377563</v>
+        <v>14.119026184082</v>
       </c>
       <c r="H1557" t="n">
         <v>8900583</v>
@@ -45551,7 +45551,7 @@
         <v>18.6900005340576</v>
       </c>
       <c r="G1558" t="n">
-        <v>14.3767175674438</v>
+        <v>14.3767166137695</v>
       </c>
       <c r="H1558" t="n">
         <v>5607680</v>
@@ -45609,7 +45609,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1560" t="n">
-        <v>14.3151807785034</v>
+        <v>14.3151798248291</v>
       </c>
       <c r="H1560" t="n">
         <v>5085745</v>
@@ -45638,7 +45638,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1561" t="n">
-        <v>14.2613353729248</v>
+        <v>14.2613344192505</v>
       </c>
       <c r="H1561" t="n">
         <v>3509650</v>
@@ -45667,7 +45667,7 @@
         <v>18.3549995422363</v>
       </c>
       <c r="G1562" t="n">
-        <v>14.1190271377563</v>
+        <v>14.119026184082</v>
       </c>
       <c r="H1562" t="n">
         <v>4477407</v>
@@ -45696,7 +45696,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1563" t="n">
-        <v>13.9382619857788</v>
+        <v>13.9382610321045</v>
       </c>
       <c r="H1563" t="n">
         <v>6141277</v>
@@ -45870,7 +45870,7 @@
         <v>17.2250003814697</v>
       </c>
       <c r="G1569" t="n">
-        <v>13.2498092651367</v>
+        <v>13.249810218811</v>
       </c>
       <c r="H1569" t="n">
         <v>6456422</v>
@@ -45928,7 +45928,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G1571" t="n">
-        <v>12.4844360351562</v>
+        <v>12.4844369888306</v>
       </c>
       <c r="H1571" t="n">
         <v>10030323</v>
@@ -46044,7 +46044,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1575" t="n">
-        <v>12.922890663147</v>
+        <v>12.9228916168213</v>
       </c>
       <c r="H1575" t="n">
         <v>6318342</v>
@@ -46131,7 +46131,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G1578" t="n">
-        <v>13.7767267227173</v>
+        <v>13.776725769043</v>
       </c>
       <c r="H1578" t="n">
         <v>10096800</v>
@@ -46189,7 +46189,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1580" t="n">
-        <v>14.3151807785034</v>
+        <v>14.3151798248291</v>
       </c>
       <c r="H1580" t="n">
         <v>13399054</v>
@@ -46218,7 +46218,7 @@
         <v>18.7749996185303</v>
       </c>
       <c r="G1581" t="n">
-        <v>14.4421005249023</v>
+        <v>14.442099571228</v>
       </c>
       <c r="H1581" t="n">
         <v>17285196</v>
@@ -46247,7 +46247,7 @@
         <v>18.7350006103516</v>
       </c>
       <c r="G1582" t="n">
-        <v>14.4113321304321</v>
+        <v>14.4113311767578</v>
       </c>
       <c r="H1582" t="n">
         <v>5057436</v>
@@ -46276,7 +46276,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1583" t="n">
-        <v>14.4767160415649</v>
+        <v>14.4767150878906</v>
       </c>
       <c r="H1583" t="n">
         <v>4296578</v>
@@ -46392,7 +46392,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.4920864105225</v>
+        <v>15.4920845031738</v>
       </c>
       <c r="H1587" t="n">
         <v>14733341</v>
@@ -46479,7 +46479,7 @@
         <v>20.7700004577637</v>
       </c>
       <c r="G1590" t="n">
-        <v>15.9766912460327</v>
+        <v>15.9766931533813</v>
       </c>
       <c r="H1590" t="n">
         <v>11260196</v>
@@ -46566,7 +46566,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.5459308624268</v>
+        <v>15.5459289550781</v>
       </c>
       <c r="H1593" t="n">
         <v>6443625</v>
@@ -46595,7 +46595,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1594" t="n">
-        <v>15.3690099716187</v>
+        <v>15.3690090179443</v>
       </c>
       <c r="H1594" t="n">
         <v>7386796</v>
@@ -46624,7 +46624,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.8920946121216</v>
+        <v>14.8920927047729</v>
       </c>
       <c r="H1595" t="n">
         <v>9232540</v>
@@ -46653,7 +46653,7 @@
         <v>19.5849990844727</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.0651683807373</v>
+        <v>15.0651664733887</v>
       </c>
       <c r="H1596" t="n">
         <v>6981816</v>
@@ -46711,7 +46711,7 @@
         <v>19.2749996185303</v>
       </c>
       <c r="G1598" t="n">
-        <v>14.8267116546631</v>
+        <v>14.8267097473145</v>
       </c>
       <c r="H1598" t="n">
         <v>9007026</v>
@@ -46769,7 +46769,7 @@
         <v>19.2649993896484</v>
       </c>
       <c r="G1600" t="n">
-        <v>14.819019317627</v>
+        <v>14.8190183639526</v>
       </c>
       <c r="H1600" t="n">
         <v>4928945</v>
@@ -46798,7 +46798,7 @@
         <v>18.75</v>
       </c>
       <c r="G1601" t="n">
-        <v>14.4228706359863</v>
+        <v>14.422869682312</v>
       </c>
       <c r="H1601" t="n">
         <v>9599569</v>
@@ -46827,7 +46827,7 @@
         <v>18.7649993896484</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.4344081878662</v>
+        <v>14.4344072341919</v>
       </c>
       <c r="H1602" t="n">
         <v>6239086</v>
@@ -46885,7 +46885,7 @@
         <v>18.4150009155273</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.1651821136475</v>
+        <v>14.1651811599731</v>
       </c>
       <c r="H1604" t="n">
         <v>8154787</v>
@@ -46914,7 +46914,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G1605" t="n">
-        <v>13.9382619857788</v>
+        <v>13.9382610321045</v>
       </c>
       <c r="H1605" t="n">
         <v>5554763</v>
@@ -46972,7 +46972,7 @@
         <v>18.1049995422363</v>
       </c>
       <c r="G1607" t="n">
-        <v>13.9267225265503</v>
+        <v>13.926721572876</v>
       </c>
       <c r="H1607" t="n">
         <v>5555196</v>
@@ -47001,7 +47001,7 @@
         <v>18</v>
       </c>
       <c r="G1608" t="n">
-        <v>13.8459548950195</v>
+        <v>13.8459539413452</v>
       </c>
       <c r="H1608" t="n">
         <v>4568683</v>
@@ -47030,7 +47030,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1609" t="n">
-        <v>13.9228773117065</v>
+        <v>13.9228763580322</v>
       </c>
       <c r="H1609" t="n">
         <v>3485129</v>
@@ -47059,7 +47059,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.8074960708618</v>
+        <v>13.8074951171875</v>
       </c>
       <c r="H1610" t="n">
         <v>6827060</v>
@@ -47088,7 +47088,7 @@
         <v>18.3050003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>14.0805673599243</v>
+        <v>14.08056640625</v>
       </c>
       <c r="H1611" t="n">
         <v>4614763</v>
@@ -47146,7 +47146,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.8382635116577</v>
+        <v>13.8382625579834</v>
       </c>
       <c r="H1613" t="n">
         <v>4892173</v>
@@ -47262,7 +47262,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1617" t="n">
-        <v>13.6613426208496</v>
+        <v>13.6613435745239</v>
       </c>
       <c r="H1617" t="n">
         <v>5183768</v>
@@ -47291,7 +47291,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.5921125411987</v>
+        <v>13.592113494873</v>
       </c>
       <c r="H1618" t="n">
         <v>4482591</v>
@@ -47378,7 +47378,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1621" t="n">
-        <v>13.9228773117065</v>
+        <v>13.9228763580322</v>
       </c>
       <c r="H1621" t="n">
         <v>6086063</v>
@@ -47407,7 +47407,7 @@
         <v>18</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8459548950195</v>
+        <v>13.8459539413452</v>
       </c>
       <c r="H1622" t="n">
         <v>3968470</v>
@@ -47436,7 +47436,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1623" t="n">
-        <v>13.9228773117065</v>
+        <v>13.9228763580322</v>
       </c>
       <c r="H1623" t="n">
         <v>8843595</v>
@@ -47465,7 +47465,7 @@
         <v>17.9950008392334</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.8421096801758</v>
+        <v>13.8421087265015</v>
       </c>
       <c r="H1624" t="n">
         <v>8826584</v>
@@ -80038,6 +80038,35 @@
         <v>1388701</v>
       </c>
       <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>42.7200012207031</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>42.7799987792969</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>42.2599983215332</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>42.3199996948242</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>42.3199996948242</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>1592679</v>
+      </c>
+      <c r="I2748" t="s">
         <v>9</v>
       </c>
     </row>
